--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A4B959-F507-4513-924E-ECCE0D0D9EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9A96A9-7114-481F-938F-3902FBF5B208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31530" yWindow="2910" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31530" yWindow="2910" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="1493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="1503">
   <si>
     <t>ID</t>
   </si>
@@ -4516,6 +4516,36 @@
   <si>
     <t>..</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MT3_021</t>
+  </si>
+  <si>
+    <t>主塔 21层</t>
+  </si>
+  <si>
+    <t>MT3_022</t>
+  </si>
+  <si>
+    <t>主塔 22层</t>
+  </si>
+  <si>
+    <t>MT3_023</t>
+  </si>
+  <si>
+    <t>主塔 23层</t>
+  </si>
+  <si>
+    <t>MT3_024</t>
+  </si>
+  <si>
+    <t>主塔 24层</t>
+  </si>
+  <si>
+    <t>MT3_025</t>
+  </si>
+  <si>
+    <t>主塔 25层</t>
   </si>
 </sst>
 </file>
@@ -11059,7 +11089,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -11344,6 +11374,51 @@
         <v>64</v>
       </c>
     </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="9" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="9" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="9" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="9" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="9" t="s">
+        <v>1502</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengmingliu\LudorkProjects\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9A96A9-7114-481F-938F-3902FBF5B208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B2211-A68B-4CDC-B54E-4A24D57DBC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31530" yWindow="2910" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6990" yWindow="2430" windowWidth="28470" windowHeight="16050" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="1503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="1505">
   <si>
     <t>ID</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Mota</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>魔    塔</t>
-  </si>
-  <si>
     <t>MAP_01</t>
   </si>
   <si>
@@ -166,67 +160,34 @@
     <t>MT3_010</t>
   </si>
   <si>
-    <t>主塔 10层</t>
-  </si>
-  <si>
     <t>MT3_011</t>
   </si>
   <si>
-    <t>主塔 11层</t>
-  </si>
-  <si>
     <t>MT3_012</t>
   </si>
   <si>
-    <t>主塔 12层</t>
-  </si>
-  <si>
     <t>MT3_013</t>
   </si>
   <si>
-    <t>主塔 13层</t>
-  </si>
-  <si>
     <t>MT3_014</t>
   </si>
   <si>
-    <t>主塔 14层</t>
-  </si>
-  <si>
     <t>MT3_015</t>
   </si>
   <si>
-    <t>主塔 15层</t>
-  </si>
-  <si>
     <t>MT3_016</t>
   </si>
   <si>
-    <t>主塔 16层</t>
-  </si>
-  <si>
     <t>MT3_017</t>
   </si>
   <si>
-    <t>主塔 17层</t>
-  </si>
-  <si>
     <t>MT3_018</t>
   </si>
   <si>
-    <t>主塔 18层</t>
-  </si>
-  <si>
     <t>MT3_019</t>
   </si>
   <si>
-    <t>主塔 19层</t>
-  </si>
-  <si>
     <t>MT3_020</t>
-  </si>
-  <si>
-    <t>主塔 20层</t>
   </si>
   <si>
     <t>TITLE_START</t>
@@ -4521,31 +4482,83 @@
     <t>MT3_021</t>
   </si>
   <si>
-    <t>主塔 21层</t>
-  </si>
-  <si>
     <t>MT3_022</t>
   </si>
   <si>
-    <t>主塔 22层</t>
-  </si>
-  <si>
     <t>MT3_023</t>
   </si>
   <si>
-    <t>主塔 23层</t>
-  </si>
-  <si>
     <t>MT3_024</t>
   </si>
   <si>
-    <t>主塔 24层</t>
-  </si>
-  <si>
     <t>MT3_025</t>
   </si>
   <si>
-    <t>主塔 25层</t>
+    <t>Main Tower</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主    塔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主塔10层</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主塔11层</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主塔12层</t>
+  </si>
+  <si>
+    <t>主塔13层</t>
+  </si>
+  <si>
+    <t>主塔14层</t>
+  </si>
+  <si>
+    <t>主塔15层</t>
+  </si>
+  <si>
+    <t>主塔16层</t>
+  </si>
+  <si>
+    <t>主塔17层</t>
+  </si>
+  <si>
+    <t>主塔18层</t>
+  </si>
+  <si>
+    <t>主塔19层</t>
+  </si>
+  <si>
+    <t>主塔20层</t>
+  </si>
+  <si>
+    <t>主塔21层</t>
+  </si>
+  <si>
+    <t>主塔22层</t>
+  </si>
+  <si>
+    <t>主塔23层</t>
+  </si>
+  <si>
+    <t>主塔24层</t>
+  </si>
+  <si>
+    <t>魔塔25层</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mota2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔    塔</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4628,7 +4641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -4641,6 +4654,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -4875,651 +4889,651 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
         <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C37" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C47" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C49" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B50" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B51" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C53" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B54" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5550,694 +5564,694 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="B2" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="C2" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="B3" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="C3" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="B4" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="C4" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>886</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="B6" t="s">
-        <v>888</v>
+        <v>875</v>
       </c>
       <c r="C6" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="B8" t="s">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="C8" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>895</v>
+        <v>882</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>897</v>
+        <v>884</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="B10" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="C10" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="B11" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>903</v>
+        <v>890</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
       <c r="B12" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="C12" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>907</v>
+        <v>894</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>908</v>
+        <v>895</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>909</v>
+        <v>896</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="B14" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="B15" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>916</v>
+        <v>903</v>
       </c>
       <c r="B16" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="C16" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="B17" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="C17" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="B18" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="C18" t="s">
-        <v>924</v>
+        <v>911</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="B19" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C19" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="B20" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="C20" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="B21" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="C21" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>936</v>
+        <v>923</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="B24" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="C24" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="B25" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="C25" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="B26" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="C26" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="B27" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="C27" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="B28" t="s">
-        <v>953</v>
+        <v>940</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>955</v>
+        <v>942</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
       <c r="C30" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="C31" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="C32" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="C33" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="C34" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="C35" t="s">
-        <v>969</v>
+        <v>956</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>970</v>
+        <v>957</v>
       </c>
       <c r="C36" t="s">
-        <v>971</v>
+        <v>958</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>972</v>
+        <v>959</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>973</v>
+        <v>960</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>974</v>
+        <v>961</v>
       </c>
       <c r="C38" t="s">
-        <v>975</v>
+        <v>962</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>976</v>
+        <v>963</v>
       </c>
       <c r="C39" t="s">
-        <v>977</v>
+        <v>964</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>978</v>
+        <v>965</v>
       </c>
       <c r="C40" t="s">
-        <v>979</v>
+        <v>966</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="C41" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="C42" t="s">
-        <v>983</v>
+        <v>970</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>984</v>
+        <v>971</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>986</v>
+        <v>973</v>
       </c>
       <c r="C44" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
       <c r="C45" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="C46" t="s">
-        <v>991</v>
+        <v>978</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>992</v>
+        <v>979</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>993</v>
+        <v>980</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>994</v>
+        <v>981</v>
       </c>
       <c r="C48" t="s">
-        <v>995</v>
+        <v>982</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="C49" t="s">
-        <v>997</v>
+        <v>984</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>998</v>
+        <v>985</v>
       </c>
       <c r="C50" t="s">
-        <v>999</v>
+        <v>986</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1000</v>
+        <v>987</v>
       </c>
       <c r="C51" t="s">
-        <v>1001</v>
+        <v>988</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1002</v>
+        <v>989</v>
       </c>
       <c r="C52" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="C53" t="s">
-        <v>1005</v>
+        <v>992</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1006</v>
+        <v>993</v>
       </c>
       <c r="C54" t="s">
-        <v>1007</v>
+        <v>994</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="C55" t="s">
-        <v>1009</v>
+        <v>996</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1010</v>
+        <v>997</v>
       </c>
       <c r="C56" t="s">
-        <v>1011</v>
+        <v>998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="C57" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="C58" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C59" t="s">
-        <v>1017</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="C60" t="s">
-        <v>1019</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1020</v>
+        <v>1007</v>
       </c>
       <c r="C61" t="s">
-        <v>1021</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1022</v>
+        <v>1009</v>
       </c>
       <c r="C62" t="s">
-        <v>1023</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="C63" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="C64" t="s">
-        <v>1027</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1028</v>
+        <v>1015</v>
       </c>
       <c r="C65" t="s">
-        <v>1029</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1030</v>
+        <v>1017</v>
       </c>
       <c r="C66" t="s">
-        <v>1031</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1032</v>
+        <v>1019</v>
       </c>
       <c r="C67" t="s">
-        <v>1033</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="C68" t="s">
-        <v>1035</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1036</v>
+        <v>1023</v>
       </c>
       <c r="C69" t="s">
-        <v>1037</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1038</v>
+        <v>1025</v>
       </c>
       <c r="C70" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
       <c r="C71" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
       <c r="C72" t="s">
-        <v>1043</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1044</v>
+        <v>1031</v>
       </c>
       <c r="C73" t="s">
-        <v>1045</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1046</v>
+        <v>1033</v>
       </c>
       <c r="C74" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1048</v>
+        <v>1035</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>1049</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1050</v>
+        <v>1037</v>
       </c>
       <c r="C76" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
       <c r="C77" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
@@ -6268,24 +6282,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
       <c r="B2" t="s">
-        <v>1055</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="B3" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="C3" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
     </row>
   </sheetData>
@@ -6317,206 +6331,206 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>1060</v>
+        <v>1047</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1062</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1064</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>1066</v>
+        <v>1053</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1068</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>1070</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>1072</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>1079</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>1081</v>
+        <v>1068</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>1083</v>
+        <v>1070</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>1085</v>
+        <v>1072</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6" t="s">
-        <v>1086</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>1087</v>
+        <v>1074</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>1088</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>1089</v>
+        <v>1076</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>1090</v>
+        <v>1077</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>1091</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>1092</v>
+        <v>1079</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>1093</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>1094</v>
+        <v>1081</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>1095</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>1096</v>
+        <v>1083</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>1097</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>1099</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>1101</v>
+        <v>1088</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>1102</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>1103</v>
+        <v>1090</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>1104</v>
+        <v>1091</v>
       </c>
     </row>
   </sheetData>
@@ -6546,1808 +6560,1808 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>1105</v>
+        <v>1092</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1106</v>
+        <v>1093</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1107</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>1108</v>
+        <v>1095</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1109</v>
+        <v>1096</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1110</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1130</v>
+        <v>1117</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>1151</v>
+        <v>1138</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>1152</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>1153</v>
+        <v>1140</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>1154</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>1155</v>
+        <v>1142</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>1164</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>1166</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>1167</v>
+        <v>1154</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>1168</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>1169</v>
+        <v>1156</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>1170</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>1171</v>
+        <v>1158</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>1172</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>1173</v>
+        <v>1160</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>1174</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>1181</v>
+        <v>1168</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>1182</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>1183</v>
+        <v>1170</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>1184</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>1185</v>
+        <v>1172</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>1186</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>1187</v>
+        <v>1174</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>1188</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>1189</v>
+        <v>1176</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>1190</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>1191</v>
+        <v>1178</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>1192</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>1193</v>
+        <v>1180</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>1195</v>
+        <v>1182</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>1196</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>1197</v>
+        <v>1184</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>1200</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>1201</v>
+        <v>1188</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>1202</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>1203</v>
+        <v>1190</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>1206</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>1207</v>
+        <v>1194</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>1209</v>
+        <v>1196</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>1210</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>1212</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>1214</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>1219</v>
+        <v>1206</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>1221</v>
+        <v>1208</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>1223</v>
+        <v>1210</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>1224</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>1225</v>
+        <v>1212</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>1226</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>1227</v>
+        <v>1214</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>1228</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>1229</v>
+        <v>1216</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>1230</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>1231</v>
+        <v>1218</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>1232</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>1233</v>
+        <v>1220</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>1234</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>1235</v>
+        <v>1222</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>1236</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>1237</v>
+        <v>1224</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>1239</v>
+        <v>1226</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>1240</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>1241</v>
+        <v>1228</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>1242</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>1243</v>
+        <v>1230</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>1244</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>1245</v>
+        <v>1232</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>1246</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
-        <v>1248</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>1249</v>
+        <v>1236</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>1250</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>1251</v>
+        <v>1238</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>1252</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>1253</v>
+        <v>1240</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>1254</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>1255</v>
+        <v>1242</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>1256</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>1257</v>
+        <v>1244</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>1258</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>1259</v>
+        <v>1246</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>1260</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>1262</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
-        <v>1264</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>1265</v>
+        <v>1252</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
-        <v>1266</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>1267</v>
+        <v>1254</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6" t="s">
-        <v>1268</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>1269</v>
+        <v>1256</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>1271</v>
+        <v>1258</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>1273</v>
+        <v>1260</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6" t="s">
-        <v>1274</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>1275</v>
+        <v>1262</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6" t="s">
-        <v>1276</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6" t="s">
-        <v>1278</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>1279</v>
+        <v>1266</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6" t="s">
-        <v>1280</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>1281</v>
+        <v>1268</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6" t="s">
-        <v>1282</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>1283</v>
+        <v>1270</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6" t="s">
-        <v>1284</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>1285</v>
+        <v>1272</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6" t="s">
-        <v>1286</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>1287</v>
+        <v>1274</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>1288</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>1289</v>
+        <v>1276</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
-        <v>1290</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>1291</v>
+        <v>1278</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
-        <v>1292</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>1293</v>
+        <v>1280</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>1294</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>1295</v>
+        <v>1282</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
-        <v>1296</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>1298</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>1299</v>
+        <v>1286</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
-        <v>1300</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>1301</v>
+        <v>1288</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
-        <v>1302</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>1303</v>
+        <v>1290</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>1305</v>
+        <v>1292</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>1306</v>
+        <v>1293</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6" t="s">
-        <v>1309</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6" t="s">
-        <v>1311</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>1312</v>
+        <v>1299</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="6" t="s">
-        <v>1313</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6" t="s">
-        <v>1315</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6" t="s">
-        <v>1317</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>1318</v>
+        <v>1305</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>1323</v>
+        <v>1310</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6" t="s">
-        <v>1324</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6" t="s">
-        <v>1326</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>1327</v>
+        <v>1314</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6" t="s">
-        <v>1328</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>1329</v>
+        <v>1316</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6" t="s">
-        <v>1330</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>1331</v>
+        <v>1318</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6" t="s">
-        <v>1332</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>1333</v>
+        <v>1320</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6" t="s">
-        <v>1334</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>1335</v>
+        <v>1322</v>
       </c>
       <c r="B112" s="6"/>
       <c r="C112" s="6" t="s">
-        <v>1336</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>1337</v>
+        <v>1324</v>
       </c>
       <c r="B113" s="6"/>
       <c r="C113" s="6" t="s">
-        <v>1338</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>1339</v>
+        <v>1326</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6" t="s">
-        <v>1340</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>1341</v>
+        <v>1328</v>
       </c>
       <c r="B115" s="6"/>
       <c r="C115" s="6" t="s">
-        <v>1342</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>1343</v>
+        <v>1330</v>
       </c>
       <c r="B116" s="6"/>
       <c r="C116" s="6" t="s">
-        <v>1344</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>1345</v>
+        <v>1332</v>
       </c>
       <c r="B117" s="6"/>
       <c r="C117" s="6" t="s">
-        <v>1346</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>1347</v>
+        <v>1334</v>
       </c>
       <c r="B118" s="6"/>
       <c r="C118" s="6" t="s">
-        <v>1348</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>1349</v>
+        <v>1336</v>
       </c>
       <c r="B119" s="6"/>
       <c r="C119" s="6" t="s">
-        <v>1350</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>1351</v>
+        <v>1338</v>
       </c>
       <c r="B120" s="6"/>
       <c r="C120" s="6" t="s">
-        <v>1352</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>1353</v>
+        <v>1340</v>
       </c>
       <c r="B121" s="6"/>
       <c r="C121" s="6" t="s">
-        <v>1354</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
       <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>1357</v>
+        <v>1344</v>
       </c>
       <c r="B123" s="6"/>
       <c r="C123" s="6" t="s">
-        <v>1358</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
-        <v>1359</v>
+        <v>1346</v>
       </c>
       <c r="B124" s="6"/>
       <c r="C124" s="6" t="s">
-        <v>1360</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
-        <v>1361</v>
+        <v>1348</v>
       </c>
       <c r="B125" s="6"/>
       <c r="C125" s="6" t="s">
-        <v>1362</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
-        <v>1363</v>
+        <v>1350</v>
       </c>
       <c r="B126" s="6"/>
       <c r="C126" s="6" t="s">
-        <v>1364</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
-        <v>1365</v>
+        <v>1352</v>
       </c>
       <c r="B127" s="6"/>
       <c r="C127" s="6" t="s">
-        <v>1366</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
-        <v>1367</v>
+        <v>1354</v>
       </c>
       <c r="B128" s="6"/>
       <c r="C128" s="6" t="s">
-        <v>1368</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="B129" s="6"/>
       <c r="C129" s="6" t="s">
-        <v>1370</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
-        <v>1371</v>
+        <v>1358</v>
       </c>
       <c r="B130" s="6"/>
       <c r="C130" s="6" t="s">
-        <v>1372</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
-        <v>1373</v>
+        <v>1360</v>
       </c>
       <c r="B131" s="6"/>
       <c r="C131" s="6" t="s">
-        <v>1374</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
-        <v>1375</v>
+        <v>1362</v>
       </c>
       <c r="B132" s="6"/>
       <c r="C132" s="6" t="s">
-        <v>1376</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>1377</v>
+        <v>1364</v>
       </c>
       <c r="B133" s="6"/>
       <c r="C133" s="6" t="s">
-        <v>1378</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>1379</v>
+        <v>1366</v>
       </c>
       <c r="B134" s="6"/>
       <c r="C134" s="6" t="s">
-        <v>1380</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>1381</v>
+        <v>1368</v>
       </c>
       <c r="B135" s="6"/>
       <c r="C135" s="6" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>1383</v>
+        <v>1370</v>
       </c>
       <c r="B136" s="6"/>
       <c r="C136" s="6" t="s">
-        <v>1384</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>1385</v>
+        <v>1372</v>
       </c>
       <c r="B137" s="6"/>
       <c r="C137" s="6" t="s">
-        <v>1386</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>1387</v>
+        <v>1374</v>
       </c>
       <c r="B138" s="6"/>
       <c r="C138" s="6" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>1389</v>
+        <v>1376</v>
       </c>
       <c r="B139" s="6"/>
       <c r="C139" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="B140" s="6"/>
       <c r="C140" s="6" t="s">
-        <v>1391</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>1392</v>
+        <v>1379</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="6" t="s">
-        <v>1393</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>1394</v>
+        <v>1381</v>
       </c>
       <c r="B142" s="6"/>
       <c r="C142" s="6" t="s">
-        <v>1395</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>1396</v>
+        <v>1383</v>
       </c>
       <c r="B143" s="6"/>
       <c r="C143" s="6" t="s">
-        <v>1397</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>1398</v>
+        <v>1385</v>
       </c>
       <c r="B144" s="6"/>
       <c r="C144" s="6" t="s">
-        <v>1399</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
-        <v>1400</v>
+        <v>1387</v>
       </c>
       <c r="B145" s="6"/>
       <c r="C145" s="6" t="s">
-        <v>1401</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
-        <v>1402</v>
+        <v>1389</v>
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="6" t="s">
-        <v>1403</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
-        <v>1404</v>
+        <v>1391</v>
       </c>
       <c r="B147" s="6"/>
       <c r="C147" s="6" t="s">
-        <v>1405</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>1406</v>
+        <v>1393</v>
       </c>
       <c r="B148" s="6"/>
       <c r="C148" s="6" t="s">
-        <v>1407</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>1408</v>
+        <v>1395</v>
       </c>
       <c r="B149" s="6"/>
       <c r="C149" s="6" t="s">
-        <v>1409</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>1410</v>
+        <v>1397</v>
       </c>
       <c r="B150" s="6"/>
       <c r="C150" s="6" t="s">
-        <v>1411</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>1412</v>
+        <v>1399</v>
       </c>
       <c r="B151" s="6"/>
       <c r="C151" s="6" t="s">
-        <v>1413</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>1414</v>
+        <v>1401</v>
       </c>
       <c r="B152" s="6"/>
       <c r="C152" s="6" t="s">
-        <v>1415</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>1416</v>
+        <v>1403</v>
       </c>
       <c r="B153" s="6"/>
       <c r="C153" s="6" t="s">
-        <v>1417</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>1418</v>
+        <v>1405</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6" t="s">
-        <v>1419</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>1420</v>
+        <v>1407</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="6" t="s">
-        <v>1421</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>1422</v>
+        <v>1409</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6" t="s">
-        <v>1423</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>1424</v>
+        <v>1411</v>
       </c>
       <c r="B157" s="6"/>
       <c r="C157" s="6" t="s">
-        <v>1425</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>1426</v>
+        <v>1413</v>
       </c>
       <c r="B158" s="6"/>
       <c r="C158" s="6" t="s">
-        <v>1427</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>1428</v>
+        <v>1415</v>
       </c>
       <c r="B159" s="6"/>
       <c r="C159" s="6" t="s">
-        <v>1429</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>1430</v>
+        <v>1417</v>
       </c>
       <c r="B160" s="6"/>
       <c r="C160" s="6" t="s">
-        <v>1431</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>1432</v>
+        <v>1419</v>
       </c>
       <c r="B161" s="6"/>
       <c r="C161" s="6" t="s">
-        <v>1433</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>1434</v>
+        <v>1421</v>
       </c>
       <c r="B162" s="6"/>
       <c r="C162" s="6" t="s">
-        <v>1435</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>1436</v>
+        <v>1423</v>
       </c>
       <c r="B163" s="6"/>
       <c r="C163" s="6" t="s">
-        <v>1437</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>1438</v>
+        <v>1425</v>
       </c>
       <c r="B164" s="6"/>
       <c r="C164" s="6" t="s">
-        <v>1439</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>1440</v>
+        <v>1427</v>
       </c>
       <c r="B165" s="6"/>
       <c r="C165" s="6" t="s">
-        <v>1441</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>1442</v>
+        <v>1429</v>
       </c>
       <c r="B166" s="6"/>
       <c r="C166" s="6" t="s">
-        <v>1443</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="6" t="s">
-        <v>1444</v>
+        <v>1431</v>
       </c>
       <c r="B167" s="6"/>
       <c r="C167" s="6" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
-        <v>1445</v>
+        <v>1432</v>
       </c>
       <c r="B168" s="6"/>
       <c r="C168" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
-        <v>1446</v>
+        <v>1433</v>
       </c>
       <c r="B169" s="6"/>
       <c r="C169" s="6" t="s">
-        <v>1391</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="6" t="s">
-        <v>1447</v>
+        <v>1434</v>
       </c>
       <c r="B170" s="6"/>
       <c r="C170" s="6" t="s">
-        <v>1393</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="6" t="s">
-        <v>1448</v>
+        <v>1435</v>
       </c>
       <c r="B171" s="6"/>
       <c r="C171" s="6" t="s">
-        <v>1395</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
-        <v>1449</v>
+        <v>1436</v>
       </c>
       <c r="B172" s="6"/>
       <c r="C172" s="6" t="s">
-        <v>1397</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
-        <v>1450</v>
+        <v>1437</v>
       </c>
       <c r="B173" s="6"/>
       <c r="C173" s="6" t="s">
-        <v>1399</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
-        <v>1451</v>
+        <v>1438</v>
       </c>
       <c r="B174" s="6"/>
       <c r="C174" s="6" t="s">
-        <v>1401</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
-        <v>1452</v>
+        <v>1439</v>
       </c>
       <c r="B175" s="6"/>
       <c r="C175" s="6" t="s">
-        <v>1403</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
-        <v>1453</v>
+        <v>1440</v>
       </c>
       <c r="B176" s="6"/>
       <c r="C176" s="6" t="s">
-        <v>1405</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
-        <v>1454</v>
+        <v>1441</v>
       </c>
       <c r="B177" s="6"/>
       <c r="C177" s="6" t="s">
-        <v>1407</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="6" t="s">
-        <v>1455</v>
+        <v>1442</v>
       </c>
       <c r="B178" s="6"/>
       <c r="C178" s="6" t="s">
-        <v>1409</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="6" t="s">
-        <v>1456</v>
+        <v>1443</v>
       </c>
       <c r="B179" s="6"/>
       <c r="C179" s="6" t="s">
-        <v>1411</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
-        <v>1457</v>
+        <v>1444</v>
       </c>
       <c r="B180" s="6"/>
       <c r="C180" s="6" t="s">
-        <v>1413</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6" t="s">
-        <v>1458</v>
+        <v>1445</v>
       </c>
       <c r="B181" s="6"/>
       <c r="C181" s="6" t="s">
-        <v>1415</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="6" t="s">
-        <v>1459</v>
+        <v>1446</v>
       </c>
       <c r="B182" s="6"/>
       <c r="C182" s="6" t="s">
-        <v>1417</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
-        <v>1460</v>
+        <v>1447</v>
       </c>
       <c r="B183" s="6"/>
       <c r="C183" s="6" t="s">
-        <v>1419</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
-        <v>1461</v>
+        <v>1448</v>
       </c>
       <c r="B184" s="6"/>
       <c r="C184" s="6" t="s">
-        <v>1462</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
-        <v>1463</v>
+        <v>1450</v>
       </c>
       <c r="B185" s="6"/>
       <c r="C185" s="6" t="s">
-        <v>1423</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="6" t="s">
-        <v>1464</v>
+        <v>1451</v>
       </c>
       <c r="B186" s="6"/>
       <c r="C186" s="6" t="s">
-        <v>1465</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="6" t="s">
-        <v>1466</v>
+        <v>1453</v>
       </c>
       <c r="B187" s="6"/>
       <c r="C187" s="6" t="s">
-        <v>1467</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
-        <v>1468</v>
+        <v>1455</v>
       </c>
       <c r="B188" s="6"/>
       <c r="C188" s="6" t="s">
-        <v>1469</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
-        <v>1470</v>
+        <v>1457</v>
       </c>
       <c r="B189" s="6"/>
       <c r="C189" s="6" t="s">
-        <v>1471</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
-        <v>1472</v>
+        <v>1459</v>
       </c>
       <c r="B190" s="6"/>
       <c r="C190" s="6" t="s">
-        <v>1473</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
-        <v>1474</v>
+        <v>1461</v>
       </c>
       <c r="B191" s="6"/>
       <c r="C191" s="6" t="s">
-        <v>1475</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="B192" s="6"/>
       <c r="C192" s="6" t="s">
-        <v>1437</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
-        <v>1477</v>
+        <v>1464</v>
       </c>
       <c r="B193" s="6"/>
       <c r="C193" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="6" t="s">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="B194" s="6"/>
       <c r="C194" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="6" t="s">
-        <v>1479</v>
+        <v>1466</v>
       </c>
       <c r="B195" s="6"/>
       <c r="C195" s="6" t="s">
-        <v>1480</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="6" t="s">
-        <v>1481</v>
+        <v>1468</v>
       </c>
       <c r="B196" s="6"/>
       <c r="C196" s="6" t="s">
-        <v>1319</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="6" t="s">
-        <v>1482</v>
+        <v>1469</v>
       </c>
       <c r="B197" s="6"/>
       <c r="C197" s="6" t="s">
-        <v>1483</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
-        <v>1484</v>
+        <v>1471</v>
       </c>
       <c r="B198" s="6"/>
       <c r="C198" s="6" t="s">
-        <v>1485</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
-        <v>1486</v>
+        <v>1473</v>
       </c>
       <c r="B199" s="6"/>
       <c r="C199" s="6" t="s">
-        <v>1487</v>
+        <v>1474</v>
       </c>
     </row>
   </sheetData>
@@ -8377,10 +8391,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -8388,10 +8402,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -8418,156 +8432,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -8599,508 +8613,508 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="C8" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="C9" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B11" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C11" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="B16" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B17" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C17" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="B18" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B19" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B20" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C20" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B21" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C21" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B22" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C22" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B23" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C23" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B24" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B25" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C25" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B26" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C26" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="B27" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="C27" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="B28" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C28" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="B29" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C29" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="B30" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C30" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="B31" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="C31" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C32" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="C33" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C34" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="C35" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C36" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="C37" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C38" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B39" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="C39" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C40" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="B41" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="C41" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="C42" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="C43" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C44" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C45" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C46" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C47" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -9132,1732 +9146,1732 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="C2" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C3" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="B4" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="B5" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C5" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B6" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C7" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="B8" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C8" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C9" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="B10" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="C10" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B11" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C11" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="B12" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C12" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="B13" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="C13" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="C24" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="C25" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="C26" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="C27" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C28" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C29" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C30" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C31" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="C32" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="C33" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C34" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="C35" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="C36" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="C37" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="C38" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C39" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C40" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="C41" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C42" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C43" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C44" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C45" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C46" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="C47" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="C48" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C49" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C50" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C51" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="C52" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="C53" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="C54" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="C55" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="C56" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="C57" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="C58" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="C59" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C60" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="C61" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C62" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="C63" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="C64" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="C65" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C66" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C67" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C68" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C69" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C70" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C71" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="C72" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="C73" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C74" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C75" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="C76" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="C77" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C78" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="C79" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="C80" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C81" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="C82" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C83" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="C84" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C85" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="C86" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C87" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="C88" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="C89" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C90" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C91" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C92" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C93" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="C94" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="C95" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C96" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="C97" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C98" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C99" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C100" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="C101" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="C102" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C103" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C104" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="C105" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C106" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C107" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="C108" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="C109" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C110" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="C111" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C112" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="C113" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C114" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C115" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="C116" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="C117" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="C118" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C119" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C120" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C121" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="C122" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C123" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C124" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C125" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C126" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C127" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="C128" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="C129" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="C130" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="C131" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C132" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="C133" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="C134" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="C135" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="C136" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="C137" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="C138" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C139" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="C140" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="C141" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="C142" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="C143" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="C144" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C145" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="C146" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C147" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C148" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="C149" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="C150" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="C151" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C152" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C153" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="C154" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="C155" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="C156" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C157" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C158" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C159" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C160" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C161" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C162" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C163" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C164" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C165" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="C166" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="C167" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="C168" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="C169" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C170" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="C171" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="C172" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C173" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="C174" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="C175" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="C176" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="C177" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="C178" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="C179" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
       <c r="C180" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C181" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="C182" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="C183" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="C184" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="C185" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C186" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="C187" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="C188" t="s">
-        <v>801</v>
+        <v>788</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="C189" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="C190" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>806</v>
+        <v>793</v>
       </c>
       <c r="C191" t="s">
-        <v>807</v>
+        <v>794</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>808</v>
+        <v>795</v>
       </c>
       <c r="C192" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="C193" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="C194" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="C195" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>816</v>
+        <v>803</v>
       </c>
       <c r="C196" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="C197" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="C198" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="C199" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="C200" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="C201" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="C202" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="C203" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="C204" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="C205" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="C206" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="C207" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="C208" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="C209" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -10888,46 +10902,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="B2" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="C2" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="B3" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="C3" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="B4" t="s">
-        <v>851</v>
+        <v>838</v>
       </c>
       <c r="C4" t="s">
-        <v>852</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="B5" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="C5" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -10958,46 +10972,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="B2" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="C2" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="B3" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="C3" t="s">
-        <v>861</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>1488</v>
+        <v>1475</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>1490</v>
+        <v>1477</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1489</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>1491</v>
+        <v>1478</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1492</v>
+        <v>1479</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1492</v>
+        <v>1479</v>
       </c>
     </row>
   </sheetData>
@@ -11028,57 +11042,57 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="B2" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="C2" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="B3" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="C3" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="B4" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="C4" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="B5" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="C5" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="B6" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="C6" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
   </sheetData>
@@ -11089,7 +11103,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -11112,311 +11126,319 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="B2" s="8" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1486</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="9" t="s">
-        <v>44</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="9" t="s">
-        <v>46</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="9" t="s">
-        <v>48</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="9" t="s">
-        <v>50</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="9" t="s">
-        <v>52</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="9" t="s">
-        <v>54</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="9" t="s">
-        <v>56</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="9" t="s">
-        <v>58</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="9" t="s">
-        <v>60</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="9" t="s">
-        <v>62</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="9" t="s">
-        <v>64</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>1493</v>
+        <v>1480</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="9" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>1495</v>
+        <v>1481</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="9" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>1497</v>
+        <v>1482</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="9" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>1499</v>
+        <v>1483</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="9" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>1501</v>
+        <v>1484</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="9" t="s">
         <v>1502</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>1504</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -4868,7 +4868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5534,6 +5534,28 @@
       </c>
       <c r="C60" s="7" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="61">
+      <c r="A61" t="str">
+        <v>BATTLE_FATIGUE</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Fatigue</v>
+      </c>
+      <c r="C61" t="str">
+        <v>疲劳</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="62">
+      <c r="A62" t="str">
+        <v>BATTLE_RETREAT</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Retreat (Q)</v>
+      </c>
+      <c r="C62" t="str">
+        <v>～撤退(Q)～</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -5552,10 +5552,10 @@
         <v>BATTLE_RETREAT</v>
       </c>
       <c r="B62" t="str">
-        <v>Retreat (Q)</v>
+        <v>~Retreat~</v>
       </c>
       <c r="C62" t="str">
-        <v>～撤退(Q)～</v>
+        <v>~撤退~</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengmingliu\LudorkProjects\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C7B4C9-A6EE-480E-B2A2-23476016DEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74767B7-079D-41DC-80FB-0F0B7D88EBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6990" yWindow="2430" windowWidth="28470" windowHeight="16050" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="9850" windowWidth="28470" windowHeight="10270" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="1237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="1289">
   <si>
     <t>ID</t>
   </si>
@@ -3491,9 +3491,6 @@
   </si>
   <si>
     <t>DC_NPC01_2</t>
-  </si>
-  <si>
-    <t>如今魔物复辟，其中一定有什么秘密</t>
   </si>
   <si>
     <t>DC_NPC01_3</t>
@@ -3751,6 +3748,218 @@
   </si>
   <si>
     <t>心镜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>咳…\n呃…\n我还活着？</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>你还好吗？\n你在这个水晶里面被封印了很久</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>公主殿下……\n你怎么……</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>如今魔物再次出现，其中一定有什么秘密</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔物复辟了，我花费了不少时间才到达这里\n没想到还能再见到你</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>咳…\n下面情况恐怕也不容乐观</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么动静…</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>公主殿下！\n噢，还有勇者\n太好了，你们没事</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>这座塔又升到空中了</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>二位，外面发生什么事了</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不过倒不全是坏消息\n外面的那些魔物像是被扯断了线的木偶，看起来失能了\n至少暂时不用担心它们侵略军的问题了</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在的问题是咱们应该怎么下去……</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>或许可以看看，目前塔内是否还有足够材料来改造飞羽\n和之前那样让我们一起下去</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>关于这个……</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么了吗，公主殿下</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主塔的顶部连通魔塔\n魔塔的底部会通向魔界</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>您不会是想……</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>这恐怕很危险</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>但是为了以后的安全，这值得尝试</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>和上一次不同\n现在有了两个通道\n二位恐怕只能各自通过其中的一个</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个传送阵后面有什么，目前也无法获知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>二位要保重</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们暂时会在这里留守，观察外部的同时给二位提供支援</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常感谢</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么我们出发吧</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_6</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_7</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_T_25_11</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_T_25_12</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_13</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_14</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_16</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_17</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_18</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是的，或许我们可以到那边去\n如果可以将魔物问题彻底解决，那是最好的</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_T_25_19</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_20</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_21</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_T_25_22</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_23</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_O_25_24</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_B_25_25</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_P_25_26</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5895,481 +6104,585 @@
         <v>1152</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
-        <v>1153</v>
+      <c r="C16" s="8" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="8" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="8" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
+      <c r="A55" s="8" t="s">
+        <v>1262</v>
+      </c>
       <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+      <c r="C55" s="8" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
+      <c r="A56" s="8" t="s">
+        <v>1263</v>
+      </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
+      <c r="C56" s="8" t="s">
+        <v>1237</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
+      <c r="A57" s="8" t="s">
+        <v>1265</v>
+      </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
+      <c r="C57" s="8" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
+      <c r="A58" s="8" t="s">
+        <v>1264</v>
+      </c>
       <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
+      <c r="C58" s="8" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
+      <c r="A59" s="8" t="s">
+        <v>1266</v>
+      </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
+      <c r="C59" s="8" t="s">
+        <v>1241</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
+      <c r="A60" s="8" t="s">
+        <v>1267</v>
+      </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
+      <c r="C60" s="8" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
+      <c r="A61" s="8" t="s">
+        <v>1268</v>
+      </c>
       <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
+      <c r="C61" s="8" t="s">
+        <v>1243</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
+      <c r="A62" s="8" t="s">
+        <v>1269</v>
+      </c>
       <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
+      <c r="C62" s="8" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
+      <c r="A63" s="8" t="s">
+        <v>1270</v>
+      </c>
       <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
+      <c r="C63" s="8" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
+      <c r="A64" s="8" t="s">
+        <v>1273</v>
+      </c>
       <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
+      <c r="C64" s="8" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
+      <c r="A65" s="8" t="s">
+        <v>1271</v>
+      </c>
       <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
+      <c r="C65" s="8" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
+      <c r="A66" s="8" t="s">
+        <v>1272</v>
+      </c>
       <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
+      <c r="C66" s="8" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
+      <c r="A67" s="8" t="s">
+        <v>1274</v>
+      </c>
       <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
+      <c r="C67" s="8" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
+      <c r="A68" s="8" t="s">
+        <v>1275</v>
+      </c>
       <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
+      <c r="C68" s="8" t="s">
+        <v>1250</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
+      <c r="A69" s="8" t="s">
+        <v>1276</v>
+      </c>
       <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
+      <c r="C69" s="8" t="s">
+        <v>1251</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
+      <c r="A70" s="8" t="s">
+        <v>1277</v>
+      </c>
       <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
+      <c r="C70" s="8" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
+      <c r="A71" s="8" t="s">
+        <v>1278</v>
+      </c>
       <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
+      <c r="C71" s="8" t="s">
+        <v>1253</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
+      <c r="A72" s="8" t="s">
+        <v>1279</v>
+      </c>
       <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
+      <c r="C72" s="8" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
+      <c r="A73" s="8" t="s">
+        <v>1281</v>
+      </c>
       <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
+      <c r="C73" s="8" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
+      <c r="A74" s="8" t="s">
+        <v>1282</v>
+      </c>
       <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
+      <c r="C74" s="8" t="s">
+        <v>1255</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
+      <c r="A75" s="8" t="s">
+        <v>1283</v>
+      </c>
       <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
+      <c r="C75" s="8" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
+      <c r="A76" s="8" t="s">
+        <v>1284</v>
+      </c>
       <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
+      <c r="C76" s="8" t="s">
+        <v>1257</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
+      <c r="A77" s="8" t="s">
+        <v>1285</v>
+      </c>
       <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
+      <c r="C77" s="8" t="s">
+        <v>1258</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
+      <c r="A78" s="8" t="s">
+        <v>1286</v>
+      </c>
       <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
+      <c r="C78" s="8" t="s">
+        <v>1259</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
+      <c r="A79" s="8" t="s">
+        <v>1287</v>
+      </c>
       <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
+      <c r="C79" s="8" t="s">
+        <v>1260</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
+      <c r="A80" s="8" t="s">
+        <v>1288</v>
+      </c>
       <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
+      <c r="C80" s="8" t="s">
+        <v>1261</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
@@ -6969,6 +7282,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7284,10 +7598,10 @@
         <v>316</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>1235</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -7306,10 +7620,10 @@
         <v>320</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -7317,10 +7631,10 @@
         <v>321</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -10032,7 +10346,7 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="9" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -4269,7 +4269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -4957,6 +4957,17 @@
       </c>
       <c r="C62" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>price</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Price</v>
+      </c>
+      <c r="C63" t="str">
+        <v>价格</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="17.33203125" customWidth="1" min="1" max="1"/>
@@ -1469,6 +1469,23 @@
       <c r="C63" t="inlineStr">
         <is>
           <t>价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QUICK_SAVE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Saved to file {slot}.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>已存档到文件 {slot}。</t>
         </is>
       </c>
     </row>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -4544,7 +4544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
@@ -4650,153 +4650,170 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>EXP</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Exp</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>经验</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MAGIC</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>魔力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Gd</t>
+          <t>Exp</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>金币</t>
+          <t>经验</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DMG</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Gd</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>伤害</t>
+          <t>金币</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CRIT</t>
+          <t>DMG</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>临界</t>
+          <t>伤害</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>CRIT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>临界</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>HIT</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Hit</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>攻击次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Player's </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>我方</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>m</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enemy's </t>
+          <t xml:space="preserve">Player's </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>敌方</t>
+          <t>我方</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BREATH</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Breath</t>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enemy's </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>气息</t>
+          <t>敌方</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Breath</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>气息</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>BREATH_LIMIT</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Breath Limit</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>气息上限</t>
         </is>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8317,68 +8317,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWORD_A</t>
+          <t>HUIMU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ironic Sword</t>
+          <t>Gleam Veil</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>铁剑</t>
+          <t>辉幕</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWORD_A_DESC</t>
+          <t>HUIMU_DESC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A sword made by iron, it could bring 10 ATK when it's equipped.</t>
+          <t>Equip to gain 10 DEF. Press X in battle to spend 1 breath pip and reduce that hit to incoming x max(0, incoming - Magic) / (incoming + Magic). Fully negates the hit if Magic is at least the incoming damage.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>铁制造的剑，装备后可提升10攻击力。</t>
+          <t>装备后防御+10。战斗中按X消耗1格气息，将本次来伤变为来伤×max(0,来伤-魔力)/(来伤+魔力)；魔力不低于来伤时完全免伤。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SHIELD_A</t>
+          <t>HUIREN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ironic Shield</t>
+          <t>Gleam Blade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>铁盾</t>
+          <t>辉刃</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SHIELD_A_DESC</t>
+          <t>HUIREN_DESC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A shield made by iron, it could bring 10 DEF when it's equipped.</t>
+          <t>Equip to gain 10 ATK. Press Z in battle to spend 1 breath pip and deal (1 + (Magic + base) / max(1, base - Magic)) times base damage.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>铁制造的盾，装备后可提升10防御力。</t>
+          <t>装备后攻击+10。战斗中按Z消耗1格气息，以直伤为基准造成(1+(魔力+直伤)/max(1,直伤-魔力))倍伤害。</t>
         </is>
       </c>
     </row>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1277">
   <si>
     <t>ID</t>
   </si>
@@ -3848,6 +3848,24 @@
   <si>
     <t>还是正事要紧，没时间回头了…</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC_NPC17_1</t>
+  </si>
+  <si>
+    <t>好好注意周边的墙壁哦\n嘻嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t>DC_NPC18_1</t>
+  </si>
+  <si>
+    <t>巧妙运用手中道具，不必与强敌作战就可前进</t>
+  </si>
+  <si>
+    <t>DC_NPC18_2</t>
+  </si>
+  <si>
+    <t>对了，你要金坷垃吗</t>
   </si>
 </sst>
 </file>
@@ -6491,19 +6509,31 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
+      <c r="A82" s="8" t="s">
+        <v>1271</v>
+      </c>
       <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
+      <c r="C82" s="8" t="s">
+        <v>1272</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
+      <c r="A83" s="8" t="s">
+        <v>1273</v>
+      </c>
       <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
+      <c r="C83" s="8" t="s">
+        <v>1274</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
+      <c r="A84" s="8" t="s">
+        <v>1275</v>
+      </c>
       <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
+      <c r="C84" s="8" t="s">
+        <v>1276</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C01836-5309-46B6-A92A-BE5B2E8BBEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D58B4B-F4D5-114D-B8C6-151FB25E935E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31530" yWindow="2910" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="1339">
   <si>
     <t>ID</t>
   </si>
@@ -43,114 +43,6 @@
     <t>zh_CN</t>
   </si>
   <si>
-    <t>TD_1</t>
-  </si>
-  <si>
-    <t>This is an dialogue example with all information.</t>
-  </si>
-  <si>
-    <t>这是一个带有全部信息的对话示例。</t>
-  </si>
-  <si>
-    <t>TD_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This message will only bring its content. There is no name or refActor parts. The position should be in the middle of the screen. </t>
-  </si>
-  <si>
-    <t>本条消息只含内容，不包含名字和参照Actor，位置应该在屏幕中间。</t>
-  </si>
-  <si>
-    <t>TS_1</t>
-  </si>
-  <si>
-    <t>Test blinking</t>
-  </si>
-  <si>
-    <t>闪烁测试</t>
-  </si>
-  <si>
-    <t>TS_2</t>
-  </si>
-  <si>
-    <t>Test shaking</t>
-  </si>
-  <si>
-    <t>震动测试</t>
-  </si>
-  <si>
-    <t>TS_3</t>
-  </si>
-  <si>
-    <t>Test shop</t>
-  </si>
-  <si>
-    <t>商店测试</t>
-  </si>
-  <si>
-    <t>TS_4</t>
-  </si>
-  <si>
-    <t>Test weather</t>
-  </si>
-  <si>
-    <t>天气测试</t>
-  </si>
-  <si>
-    <t>TS_5</t>
-  </si>
-  <si>
-    <t>Test Video</t>
-  </si>
-  <si>
-    <t>视频测试</t>
-  </si>
-  <si>
-    <t>TS_6</t>
-  </si>
-  <si>
-    <t>More…</t>
-  </si>
-  <si>
-    <t>更多…</t>
-  </si>
-  <si>
-    <t>TV_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This message would bring a voice with no sound effect. </t>
-  </si>
-  <si>
-    <t>本条消息会携带不含特效的语音。</t>
-  </si>
-  <si>
-    <t>TV_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This message would bring a voice with echo sound effect. </t>
-  </si>
-  <si>
-    <t>本条消息会携带回声特效的语音。</t>
-  </si>
-  <si>
-    <t>TV_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This message would bring a voice with distort sound effect. </t>
-  </si>
-  <si>
-    <t>本条消息会携带失真特效的语音。</t>
-  </si>
-  <si>
-    <t>TV_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This message would bring a voice with underwater sound effect. </t>
-  </si>
-  <si>
-    <t>本条消息会携带水下特效的语音。</t>
-  </si>
-  <si>
     <t>DC_NPC00_1</t>
   </si>
   <si>
@@ -3694,9 +3586,6 @@
     <t>BRAVOR</t>
   </si>
   <si>
-    <t>Bravor</t>
-  </si>
-  <si>
     <t>勇士</t>
   </si>
   <si>
@@ -3709,33 +3598,6 @@
     <t>这是一个勇士形式角色。</t>
   </si>
   <si>
-    <t>TD_NAME</t>
-  </si>
-  <si>
-    <t>Dialogue Tester</t>
-  </si>
-  <si>
-    <t>对话功能测试</t>
-  </si>
-  <si>
-    <t>TS_NAME</t>
-  </si>
-  <si>
-    <t>Selection Tester</t>
-  </si>
-  <si>
-    <t>选择项功能测试</t>
-  </si>
-  <si>
-    <t>TV_NAME</t>
-  </si>
-  <si>
-    <t>Voice EffectProcessor Tester</t>
-  </si>
-  <si>
-    <t>语音EffectProcessor测试</t>
-  </si>
-  <si>
     <t>DN_KING</t>
   </si>
   <si>
@@ -3793,12 +3655,6 @@
     <t>DN_NETHER_MAGE</t>
   </si>
   <si>
-    <t>DN_MONSTER_CHIEF</t>
-  </si>
-  <si>
-    <t>魔物首领</t>
-  </si>
-  <si>
     <t>DN_GLOOMY_ELDER</t>
   </si>
   <si>
@@ -3821,21 +3677,6 @@
   </si>
   <si>
     <t>魔族商人</t>
-  </si>
-  <si>
-    <t>DN_DEMON_GOD_XIEDUO</t>
-  </si>
-  <si>
-    <t>DN_DEMON_KING_GELEDI</t>
-  </si>
-  <si>
-    <t>魔王·格勒第</t>
-  </si>
-  <si>
-    <t>DN_DEMON_KING_GUDUN</t>
-  </si>
-  <si>
-    <t>魔界之王·古顿</t>
   </si>
   <si>
     <t>DN_HERO</t>
@@ -3866,13 +3707,358 @@
   </si>
   <si>
     <t>对了，你要金坷垃吗</t>
+  </si>
+  <si>
+    <t>TMT_001</t>
+  </si>
+  <si>
+    <t>魔塔25层</t>
+  </si>
+  <si>
+    <t>TMT_002</t>
+  </si>
+  <si>
+    <t>魔塔24层</t>
+  </si>
+  <si>
+    <t>TMT_003</t>
+  </si>
+  <si>
+    <t>TMT_004</t>
+  </si>
+  <si>
+    <t>TMT_005</t>
+  </si>
+  <si>
+    <t>TMT_006</t>
+  </si>
+  <si>
+    <t>TMT_007</t>
+  </si>
+  <si>
+    <t>TMT_008</t>
+  </si>
+  <si>
+    <t>TMT_009</t>
+  </si>
+  <si>
+    <t>TMT_010</t>
+  </si>
+  <si>
+    <t>TMT_011</t>
+  </si>
+  <si>
+    <t>TMT_012</t>
+  </si>
+  <si>
+    <t>TMT_013</t>
+  </si>
+  <si>
+    <t>TMT_014</t>
+  </si>
+  <si>
+    <t>TMT_015</t>
+  </si>
+  <si>
+    <t>TMT_016</t>
+  </si>
+  <si>
+    <t>TMT_017</t>
+  </si>
+  <si>
+    <t>TMT_018</t>
+  </si>
+  <si>
+    <t>TMT_019</t>
+  </si>
+  <si>
+    <t>TMT_020</t>
+  </si>
+  <si>
+    <t>TMT_021</t>
+  </si>
+  <si>
+    <t>TMT_022</t>
+  </si>
+  <si>
+    <t>TMT_023</t>
+  </si>
+  <si>
+    <t>TMT_024</t>
+  </si>
+  <si>
+    <t>TMT_025</t>
+  </si>
+  <si>
+    <t>魔塔23层</t>
+  </si>
+  <si>
+    <t>魔塔 1层</t>
+  </si>
+  <si>
+    <t>魔塔 2层</t>
+  </si>
+  <si>
+    <t>魔塔 9层</t>
+  </si>
+  <si>
+    <t>魔塔 8层</t>
+  </si>
+  <si>
+    <t>魔塔 7层</t>
+  </si>
+  <si>
+    <t>魔塔 5层</t>
+  </si>
+  <si>
+    <t>魔塔 6层</t>
+  </si>
+  <si>
+    <t>魔塔 4层</t>
+  </si>
+  <si>
+    <t>魔塔 3层</t>
+  </si>
+  <si>
+    <t>魔塔22层</t>
+  </si>
+  <si>
+    <t>魔塔21层</t>
+  </si>
+  <si>
+    <t>魔塔20层</t>
+  </si>
+  <si>
+    <t>魔塔19层</t>
+  </si>
+  <si>
+    <t>魔塔18层</t>
+  </si>
+  <si>
+    <t>魔塔17层</t>
+  </si>
+  <si>
+    <t>魔塔16层</t>
+  </si>
+  <si>
+    <t>魔塔15层</t>
+  </si>
+  <si>
+    <t>魔塔14层</t>
+  </si>
+  <si>
+    <t>魔塔13层</t>
+  </si>
+  <si>
+    <t>魔塔12层</t>
+  </si>
+  <si>
+    <t>魔塔11层</t>
+  </si>
+  <si>
+    <t>魔塔10层</t>
+  </si>
+  <si>
+    <t>Tower M  2F</t>
+  </si>
+  <si>
+    <t>Tower M  1F</t>
+  </si>
+  <si>
+    <t>Tower M  3F</t>
+  </si>
+  <si>
+    <t>Tower M  4F</t>
+  </si>
+  <si>
+    <t>Tower M  5F</t>
+  </si>
+  <si>
+    <t>Tower M  6F</t>
+  </si>
+  <si>
+    <t>Tower M  7F</t>
+  </si>
+  <si>
+    <t>Tower M  8F</t>
+  </si>
+  <si>
+    <t>Tower M  9F</t>
+  </si>
+  <si>
+    <t>Tower M 10F</t>
+  </si>
+  <si>
+    <t>Tower M 11F</t>
+  </si>
+  <si>
+    <t>Tower M 12F</t>
+  </si>
+  <si>
+    <t>Tower M 13F</t>
+  </si>
+  <si>
+    <t>Tower M 14F</t>
+  </si>
+  <si>
+    <t>Tower M 15F</t>
+  </si>
+  <si>
+    <t>Tower M 16F</t>
+  </si>
+  <si>
+    <t>Tower M 17F</t>
+  </si>
+  <si>
+    <t>Tower M 18F</t>
+  </si>
+  <si>
+    <t>Tower M 20F</t>
+  </si>
+  <si>
+    <t>Tower M 19F</t>
+  </si>
+  <si>
+    <t>Tower M 21F</t>
+  </si>
+  <si>
+    <t>Tower M 22F</t>
+  </si>
+  <si>
+    <t>Tower M 23F</t>
+  </si>
+  <si>
+    <t>Tower M 24F</t>
+  </si>
+  <si>
+    <t>Tower M 25F</t>
+  </si>
+  <si>
+    <t>Demon Tower</t>
+  </si>
+  <si>
+    <t>Tower D 22F</t>
+  </si>
+  <si>
+    <t>Tower D 21F</t>
+  </si>
+  <si>
+    <t>Tower D 25 F</t>
+  </si>
+  <si>
+    <t>Tower D 24 F</t>
+  </si>
+  <si>
+    <t>Tower D 23 F</t>
+  </si>
+  <si>
+    <t>Tower D 20F</t>
+  </si>
+  <si>
+    <t>Tower D 19F</t>
+  </si>
+  <si>
+    <t>Tower D 17F</t>
+  </si>
+  <si>
+    <t>Tower D 18F</t>
+  </si>
+  <si>
+    <t>Tower D 16F</t>
+  </si>
+  <si>
+    <t>Tower D 15F</t>
+  </si>
+  <si>
+    <t>Tower D 14F</t>
+  </si>
+  <si>
+    <t>Tower D 13F</t>
+  </si>
+  <si>
+    <t>Tower D 12F</t>
+  </si>
+  <si>
+    <t>Tower D 11F</t>
+  </si>
+  <si>
+    <t>Tower D 10F</t>
+  </si>
+  <si>
+    <t>Tower D  9F</t>
+  </si>
+  <si>
+    <t>Tower D  8F</t>
+  </si>
+  <si>
+    <t>Tower D  7F</t>
+  </si>
+  <si>
+    <t>Tower D  6F</t>
+  </si>
+  <si>
+    <t>Tower D  5F</t>
+  </si>
+  <si>
+    <t>Tower D  3F</t>
+  </si>
+  <si>
+    <t>Tower D  4F</t>
+  </si>
+  <si>
+    <t>Tower D  2F</t>
+  </si>
+  <si>
+    <t>Tower D  1F</t>
+  </si>
+  <si>
+    <t>Bravant</t>
+  </si>
+  <si>
+    <t>The King</t>
+  </si>
+  <si>
+    <t>The Sage of Mirror</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>Hermit</t>
+  </si>
+  <si>
+    <t>Veteran</t>
+  </si>
+  <si>
+    <t>Thief</t>
+  </si>
+  <si>
+    <t>The Elder</t>
+  </si>
+  <si>
+    <t>The Exhausted Elder</t>
+  </si>
+  <si>
+    <t>The Sorcerer</t>
+  </si>
+  <si>
+    <t>Mystic</t>
+  </si>
+  <si>
+    <t>The Insane Elder</t>
+  </si>
+  <si>
+    <t>The Fairy</t>
+  </si>
+  <si>
+    <t>The Demon Merchant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3882,30 +4068,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3919,6 +4110,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3944,27 +4142,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4175,14 +4371,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4193,697 +4389,697 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>173</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B15" t="s">
         <v>174</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C15" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>176</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B16" t="s">
         <v>177</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B17" t="s">
         <v>179</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C17" t="s">
         <v>180</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B18" t="s">
         <v>182</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C18" t="s">
         <v>183</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B19" t="s">
         <v>185</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C19" t="s">
         <v>186</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B20" t="s">
         <v>188</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C20" t="s">
         <v>189</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B21" t="s">
         <v>191</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C21" t="s">
         <v>192</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="B22" t="s">
         <v>194</v>
       </c>
-      <c r="B9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="C22" t="s">
         <v>195</v>
       </c>
-      <c r="B10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B23" t="s">
         <v>197</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C23" t="s">
         <v>198</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B24" t="s">
         <v>200</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C24" t="s">
         <v>201</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B25" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C25" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B26" t="s">
         <v>206</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C26" t="s">
         <v>207</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B27" t="s">
         <v>209</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C27" t="s">
         <v>210</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B28" t="s">
         <v>212</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C28" t="s">
         <v>213</v>
       </c>
-      <c r="C16" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>214</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B29" t="s">
         <v>215</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C29" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>217</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B30" t="s">
         <v>218</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C30" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>220</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B31" t="s">
         <v>221</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C31" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>223</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B32" t="s">
         <v>224</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C32" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>226</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B33" t="s">
         <v>227</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C33" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>229</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B34" t="s">
         <v>230</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C34" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>232</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B35" t="s">
         <v>233</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C35" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>235</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B36" t="s">
         <v>236</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C36" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>238</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B37" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C37" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>241</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B38" t="s">
         <v>242</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C38" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>244</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B39" t="s">
         <v>245</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C39" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B40" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C40" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B41" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C41" s="4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>253</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B42" t="s">
         <v>254</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C42" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>256</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B43" t="s">
         <v>257</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C43" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>259</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B44" t="s">
         <v>260</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C44" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>262</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B45" t="s">
         <v>263</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C45" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>265</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B46" t="s">
         <v>266</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C46" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>268</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B47" t="s">
         <v>269</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C47" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>271</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B48" t="s">
         <v>272</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C48" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>274</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B49" t="s">
         <v>275</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C49" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>277</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B50" t="s">
         <v>278</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C50" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>280</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B51" t="s">
         <v>281</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C51" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>283</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B52" t="s">
         <v>284</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C52" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>286</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B53" t="s">
         <v>287</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C53" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>289</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B54" t="s">
         <v>290</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C54" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="55" spans="1:3" ht="32" customHeight="1">
+      <c r="A55" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B55" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C55" s="7" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="56" spans="1:3" ht="32" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B56" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C56" s="7" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="57" spans="1:3" ht="32" customHeight="1">
+      <c r="A57" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B57" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C57" s="7" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="58" spans="1:3" ht="32" customHeight="1">
+      <c r="A58" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B58" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C58" s="7" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="59" spans="1:3" ht="32" customHeight="1">
+      <c r="A59" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B59" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C59" s="7" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="60" spans="1:3" ht="32" customHeight="1">
+      <c r="A60" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B60" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C60" s="7" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>310</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B61" t="s">
         <v>311</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C61" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>313</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B62" t="s">
         <v>314</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C62" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>316</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B63" t="s">
         <v>317</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C63" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>319</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B64" t="s">
         <v>320</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C64" t="s">
         <v>321</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>322</v>
-      </c>
-      <c r="B53" t="s">
-        <v>323</v>
-      </c>
-      <c r="C53" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>325</v>
-      </c>
-      <c r="B54" t="s">
-        <v>326</v>
-      </c>
-      <c r="C54" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>346</v>
-      </c>
-      <c r="B61" t="s">
-        <v>347</v>
-      </c>
-      <c r="C61" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>349</v>
-      </c>
-      <c r="B62" t="s">
-        <v>350</v>
-      </c>
-      <c r="C62" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>352</v>
-      </c>
-      <c r="B63" t="s">
-        <v>353</v>
-      </c>
-      <c r="C63" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>355</v>
-      </c>
-      <c r="B64" t="s">
-        <v>356</v>
-      </c>
-      <c r="C64" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4895,13 +5091,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4912,552 +5108,552 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C6" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B15" t="s">
         <v>1079</v>
       </c>
-      <c r="B2" t="s">
-        <v>991</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C15" s="6" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>1081</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B16" t="s">
         <v>1082</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C16" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>1084</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B17" t="s">
         <v>1085</v>
       </c>
-      <c r="C4" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C17" t="s">
         <v>1086</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>1087</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B18" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="C18" t="s">
         <v>1089</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>1090</v>
       </c>
-      <c r="C6" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B19" t="s">
         <v>1091</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C19" t="s">
         <v>1092</v>
       </c>
-      <c r="C7" s="8" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B20" t="s">
         <v>1094</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C20" t="s">
         <v>1095</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>1096</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B21" t="s">
         <v>1097</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C21" t="s">
         <v>1098</v>
       </c>
-      <c r="C9" s="6" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B22" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="B10" t="s">
-        <v>375</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="C22" s="4" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
         <v>1102</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B23" s="4" t="s">
         <v>1103</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>1105</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B24" t="s">
         <v>1106</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C24" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>1108</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B25" t="s">
         <v>1109</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C25" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="6" t="s">
         <v>1111</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B26" t="s">
         <v>1112</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C26" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
         <v>1114</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B27" t="s">
         <v>1115</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C27" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>1117</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B28" t="s">
         <v>1118</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C28" s="6" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>1120</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B29" s="6" t="s">
         <v>1121</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C29" s="6" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>1123</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C30" t="s">
         <v>1124</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="C31" t="s">
         <v>1126</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>1127</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C32" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>1129</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C33" t="s">
         <v>1130</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="C34" t="s">
         <v>1132</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>1133</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C35" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>1135</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C36" t="s">
         <v>1136</v>
       </c>
-      <c r="C22" s="4" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="C37" t="s">
         <v>1138</v>
       </c>
-      <c r="B23" s="4" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>1139</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C38" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>1141</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C39" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>1143</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="C40" t="s">
         <v>1144</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>1145</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C41" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>1147</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C42" t="s">
         <v>1148</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="C43" s="8" t="s">
         <v>1150</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>1151</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C44" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>1153</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C45" t="s">
         <v>1154</v>
       </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="C46" t="s">
         <v>1156</v>
       </c>
-      <c r="B29" s="6" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>1157</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C47" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>1159</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C48" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>1161</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C49" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>1163</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C50" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>1165</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C51" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>1167</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C52" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>1169</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C53" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>1171</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C54" t="s">
         <v>1172</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>1173</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C55" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>1175</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C56" t="s">
         <v>1176</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>1177</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C57" t="s">
         <v>1178</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>1179</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C58" t="s">
         <v>1180</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>1181</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C59" t="s">
         <v>1182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>1207</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -5469,13 +5665,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5486,26 +5682,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1220</v>
+        <v>1183</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1325</v>
       </c>
       <c r="C2" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1222</v>
+        <v>1185</v>
       </c>
       <c r="B3" t="s">
-        <v>1223</v>
+        <v>1186</v>
       </c>
       <c r="C3" t="s">
-        <v>1224</v>
+        <v>1187</v>
       </c>
     </row>
   </sheetData>
@@ -5516,15 +5712,15 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5535,208 +5731,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B5" s="6"/>
+        <v>1192</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1327</v>
+      </c>
       <c r="C5" s="6" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>1194</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1328</v>
+      </c>
       <c r="C6" s="6" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B7" s="6"/>
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1329</v>
+      </c>
       <c r="C7" s="6" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B8" s="6"/>
+        <v>1198</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1330</v>
+      </c>
       <c r="C8" s="6" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B9" s="6"/>
+        <v>1200</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1331</v>
+      </c>
       <c r="C9" s="6" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B10" s="6"/>
+        <v>1202</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1332</v>
+      </c>
       <c r="C10" s="6" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B11" s="6"/>
+        <v>1204</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1333</v>
+      </c>
       <c r="C11" s="6" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B12" s="6"/>
+        <v>1206</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1334</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B13" s="6"/>
+        <v>1207</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1335</v>
+      </c>
       <c r="C13" s="6" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B14" s="6"/>
+        <v>1209</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1336</v>
+      </c>
       <c r="C14" s="6" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>1211</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1337</v>
+      </c>
       <c r="C15" s="6" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>1213</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1338</v>
+      </c>
       <c r="C16" s="6" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
-        <v>1267</v>
+        <v>1214</v>
       </c>
     </row>
   </sheetData>
@@ -5747,13 +5904,13 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C199"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C187"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5764,1351 +5921,1219 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B16" s="6"/>
-      <c r="C16" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6"/>
-      <c r="C21" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B33" s="6"/>
-      <c r="C33" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B34" s="6"/>
-      <c r="C34" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="8" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+    <row r="49" spans="1:3">
+      <c r="A49" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6" t="s">
+      <c r="B50" s="6"/>
+      <c r="C50" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
+      <c r="B51" s="6"/>
+      <c r="C51" s="8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6" t="s">
+      <c r="B52" s="6"/>
+      <c r="C52" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+    <row r="53" spans="1:3">
+      <c r="A53" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6" t="s">
+      <c r="B53" s="6"/>
+      <c r="C53" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+    <row r="54" spans="1:3">
+      <c r="A54" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+    <row r="55" spans="1:3">
+      <c r="A55" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="8" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="8" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="8" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="8" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="8" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
-        <v>149</v>
+        <v>1216</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
-        <v>151</v>
+        <v>1218</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="8" t="s">
-        <v>153</v>
+        <v>1220</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="8" t="s">
-        <v>155</v>
+        <v>1222</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="8" t="s">
-        <v>157</v>
-      </c>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="6"/>
       <c r="B73" s="6"/>
-      <c r="C73" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
-        <v>159</v>
-      </c>
+      <c r="C73" s="6"/>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="6"/>
       <c r="B74" s="6"/>
-      <c r="C74" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="8" t="s">
-        <v>161</v>
-      </c>
+      <c r="C74" s="6"/>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="6"/>
       <c r="B75" s="6"/>
-      <c r="C75" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
-        <v>163</v>
-      </c>
+      <c r="C75" s="6"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="6"/>
       <c r="B76" s="6"/>
-      <c r="C76" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="8" t="s">
-        <v>165</v>
-      </c>
+      <c r="C76" s="6"/>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="6"/>
       <c r="B77" s="6"/>
-      <c r="C77" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="8" t="s">
-        <v>167</v>
-      </c>
+      <c r="C77" s="6"/>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="6"/>
       <c r="B78" s="6"/>
-      <c r="C78" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
-        <v>169</v>
-      </c>
+      <c r="C78" s="6"/>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="6"/>
       <c r="B79" s="6"/>
-      <c r="C79" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
-        <v>171</v>
-      </c>
+      <c r="C79" s="6"/>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="6"/>
       <c r="B80" s="6"/>
-      <c r="C80" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="8" t="s">
-        <v>1269</v>
-      </c>
+      <c r="C80" s="6"/>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="6"/>
       <c r="B81" s="6"/>
-      <c r="C81" s="8" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="8" t="s">
-        <v>1271</v>
-      </c>
+      <c r="C81" s="6"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="6"/>
       <c r="B82" s="6"/>
-      <c r="C82" s="8" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="8" t="s">
-        <v>1273</v>
-      </c>
+      <c r="C82" s="6"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="6"/>
       <c r="B83" s="6"/>
-      <c r="C83" s="8" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
-        <v>1275</v>
-      </c>
+      <c r="C83" s="6"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="6"/>
       <c r="B84" s="6"/>
-      <c r="C84" s="8" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="6"/>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -7120,9 +7145,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7133,26 +7158,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -7164,9 +7189,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7177,169 +7202,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C13" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>362</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C15" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>365</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C16" t="s">
         <v>367</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>392</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="C13" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>395</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C14" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>398</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="C15" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>401</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="C16" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -7351,14 +7376,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7369,510 +7394,510 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C5" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C12" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>401</v>
+      </c>
+      <c r="B13" t="s">
+        <v>402</v>
+      </c>
+      <c r="C13" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>404</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B14" t="s">
         <v>405</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C14" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>407</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B15" t="s">
         <v>408</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C15" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>410</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B16" t="s">
         <v>411</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C16" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>413</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B17" t="s">
         <v>414</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C17" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>416</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B18" t="s">
         <v>417</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C18" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>419</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B19" t="s">
         <v>420</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C19" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>422</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B20" t="s">
         <v>423</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C20" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>425</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B21" t="s">
         <v>426</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C21" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>428</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B22" t="s">
         <v>429</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C22" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>431</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B23" t="s">
         <v>432</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C23" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>434</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B24" t="s">
         <v>435</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C24" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>437</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B25" t="s">
         <v>438</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C25" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>440</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B26" t="s">
         <v>441</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C26" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>443</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B27" t="s">
         <v>444</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C27" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>446</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B28" t="s">
         <v>447</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C28" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>449</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B29" t="s">
         <v>450</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C29" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>452</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B30" t="s">
         <v>453</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C30" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>455</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B31" t="s">
         <v>456</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C31" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>458</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B32" t="s">
         <v>459</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C32" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>461</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B33" t="s">
         <v>462</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C33" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>464</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B34" t="s">
         <v>465</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C34" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>467</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B35" t="s">
         <v>468</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C35" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>470</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B36" t="s">
         <v>471</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C36" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>473</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B37" t="s">
         <v>474</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C37" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>476</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B38" t="s">
         <v>477</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C38" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>479</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B39" t="s">
         <v>480</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C39" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>482</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B40" t="s">
         <v>483</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C40" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>485</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B41" t="s">
         <v>486</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C41" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>488</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B42" t="s">
         <v>489</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C42" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>491</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B43" t="s">
         <v>492</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C43" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>494</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B44" t="s">
         <v>495</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C44" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>497</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B45" t="s">
         <v>498</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C45" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>500</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B46" t="s">
         <v>501</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C46" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>503</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B47" t="s">
         <v>504</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C47" t="s">
         <v>505</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>506</v>
-      </c>
-      <c r="B36" t="s">
-        <v>507</v>
-      </c>
-      <c r="C36" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>509</v>
-      </c>
-      <c r="B37" t="s">
-        <v>510</v>
-      </c>
-      <c r="C37" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>512</v>
-      </c>
-      <c r="B38" t="s">
-        <v>513</v>
-      </c>
-      <c r="C38" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>515</v>
-      </c>
-      <c r="B39" t="s">
-        <v>516</v>
-      </c>
-      <c r="C39" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>518</v>
-      </c>
-      <c r="B40" t="s">
-        <v>519</v>
-      </c>
-      <c r="C40" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>521</v>
-      </c>
-      <c r="B41" t="s">
-        <v>522</v>
-      </c>
-      <c r="C41" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>524</v>
-      </c>
-      <c r="B42" t="s">
-        <v>525</v>
-      </c>
-      <c r="C42" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>527</v>
-      </c>
-      <c r="B43" t="s">
-        <v>528</v>
-      </c>
-      <c r="C43" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>530</v>
-      </c>
-      <c r="B44" t="s">
-        <v>531</v>
-      </c>
-      <c r="C44" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>533</v>
-      </c>
-      <c r="B45" t="s">
-        <v>534</v>
-      </c>
-      <c r="C45" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>536</v>
-      </c>
-      <c r="B46" t="s">
-        <v>537</v>
-      </c>
-      <c r="C46" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>539</v>
-      </c>
-      <c r="B47" t="s">
-        <v>540</v>
-      </c>
-      <c r="C47" t="s">
-        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -7884,14 +7909,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C209"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7902,1734 +7927,1734 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>521</v>
+      </c>
+      <c r="B7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C7" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C8" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>527</v>
+      </c>
+      <c r="B9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>530</v>
+      </c>
+      <c r="B10" t="s">
+        <v>531</v>
+      </c>
+      <c r="C10" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>533</v>
+      </c>
+      <c r="B11" t="s">
+        <v>534</v>
+      </c>
+      <c r="C11" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>536</v>
+      </c>
+      <c r="B12" t="s">
+        <v>537</v>
+      </c>
+      <c r="C12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>539</v>
+      </c>
+      <c r="B13" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B14" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C14" s="2" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B15" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C15" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B16" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C16" s="2" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B17" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C17" s="2" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>554</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B18" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C18" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B19" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C19" s="2" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>560</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B20" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C20" s="3" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B21" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C21" s="3" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B22" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C22" s="4" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B23" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C23" s="4" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>572</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C24" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>573</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C25" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C26" t="s">
         <v>575</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>576</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C27" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>578</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C28" t="s">
         <v>579</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="C29" t="s">
         <v>581</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>582</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C30" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>584</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C31" t="s">
         <v>585</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="C32" t="s">
         <v>587</v>
       </c>
-      <c r="B17" s="2" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>588</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C33" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>590</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C34" t="s">
         <v>591</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C35" t="s">
         <v>593</v>
       </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>594</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C36" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>596</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C37" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>597</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C38" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>599</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C39" t="s">
         <v>600</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="C40" t="s">
         <v>602</v>
       </c>
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>603</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C41" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>605</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C42" t="s">
         <v>606</v>
       </c>
-      <c r="C23" s="4" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="C43" t="s">
         <v>608</v>
       </c>
-      <c r="C24" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>609</v>
       </c>
-      <c r="C25" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C44" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>610</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C45" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="C46" t="s">
         <v>612</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C47" t="s">
         <v>614</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="C48" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>616</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C49" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>618</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C50" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>620</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C51" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>622</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C52" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="C53" t="s">
         <v>624</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="C54" t="s">
         <v>626</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="C55" t="s">
         <v>628</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="C56" t="s">
         <v>630</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="C57" t="s">
         <v>632</v>
       </c>
-      <c r="C37" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>633</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C58" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>635</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C59" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
         <v>637</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C60" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>639</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C61" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>641</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C62" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>643</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C63" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>645</v>
       </c>
-      <c r="C44" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="C64" t="s">
         <v>646</v>
       </c>
-      <c r="C45" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
         <v>647</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C65" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>649</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C66" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>651</v>
       </c>
-      <c r="C48" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="C67" t="s">
         <v>652</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="C68" t="s">
         <v>654</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="C69" t="s">
         <v>656</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="C70" t="s">
         <v>658</v>
       </c>
-      <c r="C52" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
         <v>659</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C71" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>661</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C72" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>663</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C73" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>665</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C74" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
         <v>667</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C75" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>669</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C76" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>671</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C77" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>673</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C78" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>675</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C79" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>677</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C80" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>679</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C81" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>681</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C82" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>683</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C83" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>685</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C84" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>687</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C85" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
         <v>689</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C86" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
         <v>691</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C87" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>693</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C88" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
         <v>695</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C89" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>697</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C90" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="C91" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>699</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C92" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
         <v>701</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C93" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
         <v>703</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C94" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="C95" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
         <v>705</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C96" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
         <v>707</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C97" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
         <v>709</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C98" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
         <v>711</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C99" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
         <v>713</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C100" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>715</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C101" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>717</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C102" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
         <v>719</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C103" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>721</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C104" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="C105" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
         <v>723</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C106" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
         <v>725</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C107" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
         <v>727</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C108" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
         <v>729</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C109" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>731</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C110" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
         <v>733</v>
       </c>
-      <c r="C90" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="C111" t="s">
         <v>734</v>
       </c>
-      <c r="C91" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>735</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C112" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>737</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C113" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>739</v>
       </c>
-      <c r="C94" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+      <c r="C114" t="s">
         <v>740</v>
       </c>
-      <c r="C95" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>741</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C115" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>743</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C116" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>745</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C117" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
         <v>747</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C118" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
         <v>749</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C119" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
         <v>751</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C120" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
         <v>753</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C121" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
         <v>755</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C122" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
         <v>757</v>
       </c>
-      <c r="C104" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="C123" t="s">
         <v>758</v>
       </c>
-      <c r="C105" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
         <v>759</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C124" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
         <v>761</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C125" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>763</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C126" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>765</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C127" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
         <v>767</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C128" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
         <v>769</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C129" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
         <v>771</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C130" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
         <v>773</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C131" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
         <v>775</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C132" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
         <v>777</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C133" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
         <v>779</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C134" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
         <v>781</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C135" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
         <v>783</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C136" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
         <v>785</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C137" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>787</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C138" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>789</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C139" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>791</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C140" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
         <v>793</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C141" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
         <v>795</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C142" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
         <v>797</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C143" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
         <v>799</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C144" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
         <v>801</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C145" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
         <v>803</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C146" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
         <v>805</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C147" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
         <v>807</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C148" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
         <v>809</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C149" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>811</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C150" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>813</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C151" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
         <v>815</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C152" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
         <v>817</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C153" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
         <v>819</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C154" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
         <v>821</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C155" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
         <v>823</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C156" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
         <v>825</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C157" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
         <v>827</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C158" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
         <v>829</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C159" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
         <v>831</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C160" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
         <v>833</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C161" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
         <v>835</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C162" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
         <v>837</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C163" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
         <v>839</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C164" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
         <v>841</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C165" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>843</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C166" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>845</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C167" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
         <v>847</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C168" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>849</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C169" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
         <v>851</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C170" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>853</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C171" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
         <v>855</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C172" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
         <v>857</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C173" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
         <v>859</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C174" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>861</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C175" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
         <v>863</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C176" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
         <v>865</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C177" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
         <v>867</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C178" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
         <v>869</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C179" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
         <v>871</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C180" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
         <v>873</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C181" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
         <v>875</v>
       </c>
-      <c r="C164" t="s">
+      <c r="C182" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
         <v>877</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C183" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
         <v>879</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C184" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
         <v>881</v>
       </c>
-      <c r="C167" t="s">
+      <c r="C185" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
         <v>883</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C186" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
         <v>885</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C187" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
         <v>887</v>
       </c>
-      <c r="C170" t="s">
+      <c r="C188" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
         <v>889</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C189" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
         <v>891</v>
       </c>
-      <c r="C172" t="s">
+      <c r="C190" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
         <v>893</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C191" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
         <v>895</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C192" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
         <v>897</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C193" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
         <v>899</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C194" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
         <v>901</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C195" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
         <v>903</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C196" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
         <v>905</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C197" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
         <v>907</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C198" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
         <v>909</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C199" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
         <v>911</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C200" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
         <v>913</v>
       </c>
-      <c r="C183" t="s">
+      <c r="C201" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>915</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C202" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
         <v>917</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C203" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
         <v>919</v>
       </c>
-      <c r="C186" t="s">
+      <c r="C204" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
         <v>921</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C205" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
         <v>923</v>
       </c>
-      <c r="C188" t="s">
+      <c r="C206" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
         <v>925</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C207" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
         <v>927</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C208" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
         <v>929</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C209" t="s">
         <v>930</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>931</v>
-      </c>
-      <c r="C192" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>933</v>
-      </c>
-      <c r="C193" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>935</v>
-      </c>
-      <c r="C194" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>937</v>
-      </c>
-      <c r="C195" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>939</v>
-      </c>
-      <c r="C196" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>941</v>
-      </c>
-      <c r="C197" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>943</v>
-      </c>
-      <c r="C198" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>945</v>
-      </c>
-      <c r="C199" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>947</v>
-      </c>
-      <c r="C200" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>949</v>
-      </c>
-      <c r="C201" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>951</v>
-      </c>
-      <c r="C202" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>953</v>
-      </c>
-      <c r="C203" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>955</v>
-      </c>
-      <c r="C204" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>957</v>
-      </c>
-      <c r="C205" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>959</v>
-      </c>
-      <c r="C206" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>961</v>
-      </c>
-      <c r="C207" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>963</v>
-      </c>
-      <c r="C208" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>965</v>
-      </c>
-      <c r="C209" t="s">
-        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -9641,13 +9666,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9658,48 +9683,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>967</v>
+        <v>931</v>
       </c>
       <c r="B2" t="s">
-        <v>968</v>
+        <v>932</v>
       </c>
       <c r="C2" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="B3" t="s">
-        <v>971</v>
+        <v>935</v>
       </c>
       <c r="C3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>973</v>
+        <v>937</v>
       </c>
       <c r="B4" t="s">
-        <v>974</v>
+        <v>938</v>
       </c>
       <c r="C4" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>976</v>
+        <v>940</v>
       </c>
       <c r="B5" t="s">
-        <v>977</v>
+        <v>941</v>
       </c>
       <c r="C5" t="s">
-        <v>978</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -9711,13 +9736,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9728,48 +9753,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>979</v>
+        <v>943</v>
       </c>
       <c r="B2" t="s">
-        <v>980</v>
+        <v>944</v>
       </c>
       <c r="C2" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>982</v>
+        <v>946</v>
       </c>
       <c r="B3" t="s">
-        <v>983</v>
+        <v>947</v>
       </c>
       <c r="C3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>986</v>
+        <v>950</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>988</v>
+        <v>952</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>989</v>
+        <v>953</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>989</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -9781,13 +9806,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9798,59 +9823,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>990</v>
+        <v>954</v>
       </c>
       <c r="B2" t="s">
-        <v>991</v>
+        <v>955</v>
       </c>
       <c r="C2" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>993</v>
+        <v>957</v>
       </c>
       <c r="B3" t="s">
-        <v>994</v>
+        <v>958</v>
       </c>
       <c r="C3" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>996</v>
+        <v>960</v>
       </c>
       <c r="B4" t="s">
-        <v>997</v>
+        <v>961</v>
       </c>
       <c r="C4" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>999</v>
+        <v>963</v>
       </c>
       <c r="B5" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
       <c r="C5" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>1002</v>
+        <v>966</v>
       </c>
       <c r="B6" t="s">
-        <v>1003</v>
+        <v>967</v>
       </c>
       <c r="C6" t="s">
-        <v>1004</v>
+        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -9861,15 +9886,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9880,323 +9905,653 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>972</v>
+      </c>
+      <c r="B3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C3" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>975</v>
+      </c>
+      <c r="B4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C4" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>978</v>
+      </c>
+      <c r="B5" t="s">
+        <v>979</v>
+      </c>
+      <c r="C5" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
         <v>1005</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B17" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B18" s="9" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B19" s="9" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B20" s="9" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
         <v>1013</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B21" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B22" s="9" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B23" s="9" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
         <v>1019</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="B24" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="B25" s="9" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B26" s="9" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="C8" s="9" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
         <v>1025</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="B27" s="9" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>1026</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="9" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
         <v>1027</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="9" t="s">
+      <c r="B28" s="9" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="9" t="s">
+      <c r="B29" s="9" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="9" t="s">
+      <c r="B30" s="9" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="9" t="s">
+      <c r="B31" s="9" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
         <v>1035</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="9" t="s">
+      <c r="B32" s="9" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9" t="s">
+      <c r="B33" s="9" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="9" t="s">
+      <c r="B34" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="9" t="s">
+      <c r="B35" s="9" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="9" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="9" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="9" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="9" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="9" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="9" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="9" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="9" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="9" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="9" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="9" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="9" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="9" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="9" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="9" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="9" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="9" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>1078</v>
+    <row r="36" spans="1:3">
+      <c r="A36" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="9" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="9" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="9" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="9" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="9" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="9" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="9" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="9" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="9" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="9" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="9" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="9" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>1252</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D58B4B-F4D5-114D-B8C6-151FB25E935E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A4760-B6F4-49F0-8B4A-2826A152AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4150" yWindow="1770" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1337">
   <si>
     <t>ID</t>
   </si>
@@ -166,9 +166,6 @@
     <t>DC_NPC05_2</t>
   </si>
   <si>
-    <t>在你的攻击大于怪物防御时，你的魔力可以加持武器，\n在会心一击时可以通过魔力加持伤害，敌人的防御越高，效果越明显</t>
-  </si>
-  <si>
     <t>DC_NPC06_1</t>
   </si>
   <si>
@@ -2839,12 +2836,6 @@
     <t>HUIMU_DESC</t>
   </si>
   <si>
-    <t>Equip to gain 10 DEF. Press X in battle to spend 1 breath pip and reduce that hit to incoming x max(0, incoming - Magic) / (incoming + Magic). Fully negates the hit if Magic is at least the incoming damage.</t>
-  </si>
-  <si>
-    <t>装备后防御+10。战斗中按X消耗1格气息，将本次来伤变为来伤×max(0,来伤-魔力)/(来伤+魔力)；魔力不低于来伤时完全免伤。</t>
-  </si>
-  <si>
     <t>HUIREN</t>
   </si>
   <si>
@@ -2855,12 +2846,6 @@
   </si>
   <si>
     <t>HUIREN_DESC</t>
-  </si>
-  <si>
-    <t>Equip to gain 10 ATK. Press Z in battle to spend 1 breath pip and deal (1 + (Magic + base) / max(1, base - Magic)) times base damage.</t>
-  </si>
-  <si>
-    <t>装备后攻击+10。战斗中按Z消耗1格气息，以直伤为基准造成(1+(魔力+直伤)/max(1,直伤-魔力))倍伤害。</t>
   </si>
   <si>
     <t>WARRIOR</t>
@@ -4018,9 +4003,6 @@
     <t>The King</t>
   </si>
   <si>
-    <t>The Sage of Mirror</t>
-  </si>
-  <si>
     <t>Merchant</t>
   </si>
   <si>
@@ -4052,13 +4034,29 @@
   </si>
   <si>
     <t>The Demon Merchant</t>
+  </si>
+  <si>
+    <t>降低受到的伤害，魔力值越高受到的伤害会越低。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Sage</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你的攻击大于怪物防御时，你的魔力可以加持武器，\n在会心一击时可以通过魔力加持伤害，你的魔力越高、敌人的防御数值越高，加持效果越明显\n不过在伤害已经足够高的情况下加持效果会相对弱一些</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>附带魔力的剑刃，用来增幅伤害，魔力越高，伤害越高，增幅效果越明显。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4160,7 +4158,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4371,14 +4369,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4389,697 +4387,697 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
         <v>137</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>138</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>141</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>144</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>146</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>147</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>150</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>152</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>153</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>155</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>156</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>158</v>
       </c>
-      <c r="B9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
         <v>159</v>
       </c>
-      <c r="B10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>161</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>162</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>164</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>165</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>167</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>168</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>170</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>171</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>173</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>174</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>176</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>177</v>
       </c>
-      <c r="C16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>178</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>179</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>181</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>182</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>184</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>185</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>187</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>188</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>190</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>191</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>193</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>194</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>196</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>197</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>199</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>200</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="B26" t="s">
         <v>205</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>206</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>208</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>209</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>211</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>212</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>214</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>215</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>217</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>218</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>220</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>221</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>223</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>224</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>226</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>227</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>229</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>230</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>232</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>233</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>235</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>236</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>238</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>239</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>244</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>245</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C40" s="3" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="C41" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C41" s="4" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>253</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>254</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>256</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>257</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>259</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>260</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>262</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>263</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>265</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>266</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>268</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>269</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>274</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>275</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>277</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>278</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>280</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>281</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>283</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>284</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>286</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>287</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>289</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>290</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" customHeight="1">
-      <c r="A55" s="7" t="s">
+      <c r="B55" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C55" s="7" t="s">
+    </row>
+    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" customHeight="1">
-      <c r="A56" s="7" t="s">
+      <c r="B56" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C56" s="7" t="s">
+    </row>
+    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="32" customHeight="1">
-      <c r="A57" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="C57" s="7" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="32" customHeight="1">
-      <c r="A58" s="7" t="s">
+      <c r="B58" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="C58" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C58" s="7" t="s">
+    </row>
+    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" customHeight="1">
-      <c r="A59" s="7" t="s">
+      <c r="B59" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C59" s="7" t="s">
+    </row>
+    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" ht="32" customHeight="1">
-      <c r="A60" s="7" t="s">
+      <c r="B60" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C60" s="7" t="s">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>310</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>311</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
         <v>313</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>314</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
         <v>316</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>317</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>319</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>320</v>
-      </c>
-      <c r="C64" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5091,13 +5089,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5108,552 +5106,552 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>1043</v>
       </c>
-      <c r="B2" t="s">
-        <v>955</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
         <v>1044</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>1045</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" s="8" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>1048</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>1049</v>
       </c>
-      <c r="C4" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="C6" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>1050</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>1053</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>1054</v>
       </c>
-      <c r="C6" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="C8" t="s">
         <v>1055</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>1056</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B9" s="4" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="C9" s="6" t="s">
         <v>1058</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>1059</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>1061</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B11" t="s">
         <v>1062</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>1063</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>1064</v>
       </c>
-      <c r="B10" t="s">
-        <v>339</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B12" t="s">
         <v>1065</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="C12" t="s">
         <v>1066</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>1067</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>1068</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="C13" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>1070</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="C14" s="6" t="s">
         <v>1072</v>
       </c>
-      <c r="B13" s="6" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>1073</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="B15" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="C15" s="6" t="s">
         <v>1075</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>1076</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="B16" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="C16" t="s">
         <v>1078</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>1079</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="B17" t="s">
         <v>1080</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="C17" t="s">
         <v>1081</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>1082</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B18" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="C18" t="s">
         <v>1084</v>
       </c>
-      <c r="B17" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>1085</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B19" t="s">
         <v>1086</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="C19" t="s">
         <v>1087</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>1088</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B20" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
+      <c r="C20" t="s">
         <v>1090</v>
       </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>1091</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B21" t="s">
         <v>1092</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="C21" t="s">
         <v>1093</v>
       </c>
-      <c r="B20" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>1094</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B22" s="4" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
+      <c r="C22" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>1097</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B23" s="4" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>1100</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="B24" t="s">
         <v>1101</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="C24" t="s">
         <v>1102</v>
       </c>
-      <c r="B23" s="4" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>1103</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="B25" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
+      <c r="C25" t="s">
         <v>1105</v>
       </c>
-      <c r="B24" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>1106</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B26" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
+      <c r="C26" t="s">
         <v>1108</v>
       </c>
-      <c r="B25" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>1109</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B27" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="6" t="s">
+      <c r="C27" t="s">
         <v>1111</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>1112</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B28" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>1114</v>
       </c>
-      <c r="B27" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>1115</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B29" s="6" t="s">
         <v>1116</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
+      <c r="C29" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>1118</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C30" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>1120</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C31" t="s">
         <v>1121</v>
       </c>
-      <c r="C29" s="6" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="C32" t="s">
         <v>1123</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
+      <c r="C33" t="s">
         <v>1125</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>1126</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
+      <c r="C34" t="s">
         <v>1127</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>1128</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
+      <c r="C35" t="s">
         <v>1129</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+      <c r="C36" t="s">
         <v>1131</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>1132</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+      <c r="C37" t="s">
         <v>1133</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
+      <c r="C38" t="s">
         <v>1135</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>1136</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+      <c r="C39" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>1138</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="C40" t="s">
         <v>1139</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
+      <c r="C41" t="s">
         <v>1141</v>
       </c>
-      <c r="C39" s="8" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
+      <c r="C42" t="s">
         <v>1143</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>1144</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
+      <c r="C43" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>1146</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+      <c r="C44" t="s">
         <v>1147</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>1148</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+      <c r="C45" t="s">
         <v>1149</v>
       </c>
-      <c r="C43" s="8" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>1150</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+      <c r="C46" t="s">
         <v>1151</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+      <c r="C47" t="s">
         <v>1153</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+      <c r="C48" t="s">
         <v>1155</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+      <c r="C49" t="s">
         <v>1157</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>1158</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
+      <c r="C50" t="s">
         <v>1159</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>1160</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
+      <c r="C51" t="s">
         <v>1161</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+      <c r="C52" t="s">
         <v>1163</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>1164</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+      <c r="C53" t="s">
         <v>1165</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
+      <c r="C54" t="s">
         <v>1167</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
+      <c r="C55" t="s">
         <v>1169</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
+      <c r="C56" t="s">
         <v>1171</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>1172</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
+      <c r="C57" t="s">
         <v>1173</v>
       </c>
-      <c r="C55" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>1174</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
+      <c r="C58" t="s">
         <v>1175</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>1176</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
+      <c r="C59" t="s">
         <v>1177</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1182</v>
       </c>
     </row>
   </sheetData>
@@ -5665,13 +5663,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5682,26 +5680,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="B3" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="C3" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
   </sheetData>
@@ -5713,14 +5711,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5731,169 +5729,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>1188</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>1215</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="6" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C12" s="6" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="6" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C13" s="6" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="6" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C14" s="6" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1331</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="6" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C15" s="6" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="6" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="6" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="6" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1335</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>1209</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="6" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="6" t="s">
-        <v>1213</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>1214</v>
       </c>
     </row>
   </sheetData>
@@ -5905,12 +5903,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5921,7 +5919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -5930,7 +5928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -5939,7 +5937,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -5948,7 +5946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
@@ -5957,7 +5955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
@@ -5966,7 +5964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
@@ -5975,7 +5973,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
@@ -5984,7 +5982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
@@ -5993,7 +5991,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
@@ -6002,7 +6000,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -6011,7 +6009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -6020,7 +6018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
@@ -6029,7 +6027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>27</v>
       </c>
@@ -6038,7 +6036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>29</v>
       </c>
@@ -6047,7 +6045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
@@ -6056,7 +6054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>33</v>
       </c>
@@ -6065,7 +6063,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
@@ -6074,7 +6072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
@@ -6083,7 +6081,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
@@ -6092,7 +6090,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
@@ -6101,1036 +6099,1036 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="8" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="8" t="s">
-        <v>97</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="8" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="8" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="8" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="8" t="s">
-        <v>119</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="8" t="s">
-        <v>123</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="8" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="8" t="s">
-        <v>125</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="8" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="8" t="s">
-        <v>127</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="8" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="8" t="s">
-        <v>129</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="8" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="8" t="s">
-        <v>131</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="8" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="8" t="s">
-        <v>135</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -7145,9 +7143,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7158,26 +7156,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -7189,9 +7187,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7202,169 +7200,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="B13" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" t="s">
         <v>357</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="B14" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" t="s">
         <v>360</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B15" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" t="s">
         <v>363</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B16" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" t="s">
         <v>366</v>
-      </c>
-      <c r="C16" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -7376,14 +7374,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7394,510 +7392,510 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" t="s">
         <v>368</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>369</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>371</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>372</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>374</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>375</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>377</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>378</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>380</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>381</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>383</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>384</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="B8" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="C8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>389</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>390</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="B10" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="B11" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="C11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>398</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>399</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>401</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>402</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>404</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>405</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>407</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>408</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>410</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>411</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>413</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>414</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
         <v>416</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>417</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>419</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>420</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>422</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>423</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
         <v>425</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>426</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
         <v>428</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>429</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
         <v>431</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>432</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
         <v>434</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>435</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>437</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>438</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
         <v>440</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>441</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
         <v>443</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>444</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>446</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>447</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>449</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>450</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>452</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>453</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>455</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>456</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>458</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>459</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>461</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>462</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>464</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>465</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>467</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>468</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
         <v>470</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>471</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>473</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>474</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>476</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>477</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>479</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>480</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>482</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>483</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>485</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>486</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>488</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>489</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>491</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>492</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+      <c r="B44" t="s">
         <v>494</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>495</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>497</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>498</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>500</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>501</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>503</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>504</v>
-      </c>
-      <c r="C47" t="s">
-        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -7909,14 +7907,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C209"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7927,1734 +7925,1734 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" t="s">
         <v>506</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>507</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>509</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>510</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>512</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>513</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>515</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>516</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>518</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>519</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>521</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>522</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>524</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>525</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>527</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>528</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>530</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>531</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>533</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>534</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>536</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>537</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>539</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>540</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="B18" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
+      <c r="B20" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C22" s="4" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C23" s="4" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
+      <c r="C24" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>572</v>
       </c>
-      <c r="C24" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
+      <c r="C25" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>573</v>
       </c>
-      <c r="C25" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
+      <c r="C26" t="s">
         <v>574</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
+      <c r="C27" t="s">
         <v>576</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
+      <c r="C28" t="s">
         <v>578</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
+      <c r="C29" t="s">
         <v>580</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
+      <c r="C30" t="s">
         <v>582</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
+      <c r="C31" t="s">
         <v>584</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
+      <c r="C32" t="s">
         <v>586</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
+      <c r="C33" t="s">
         <v>588</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
+      <c r="C34" t="s">
         <v>590</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
         <v>592</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
+      <c r="C36" t="s">
         <v>594</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
+      <c r="C37" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>596</v>
       </c>
-      <c r="C37" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
         <v>597</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
         <v>599</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
+      <c r="C40" t="s">
         <v>601</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
+      <c r="C41" t="s">
         <v>603</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
+      <c r="C42" t="s">
         <v>605</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
+      <c r="C43" t="s">
         <v>607</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
+      <c r="C44" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>609</v>
       </c>
-      <c r="C44" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
+      <c r="C45" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>610</v>
       </c>
-      <c r="C45" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
+      <c r="C46" t="s">
         <v>611</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
+      <c r="C47" t="s">
         <v>613</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
+      <c r="C48" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>615</v>
       </c>
-      <c r="C48" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
+      <c r="C49" t="s">
         <v>616</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
+      <c r="C50" t="s">
         <v>618</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
+      <c r="C51" t="s">
         <v>620</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
+      <c r="C52" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>622</v>
       </c>
-      <c r="C52" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
+      <c r="C53" t="s">
         <v>623</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
+      <c r="C54" t="s">
         <v>625</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" t="s">
+      <c r="C55" t="s">
         <v>627</v>
       </c>
-      <c r="C55" t="s">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
+      <c r="C56" t="s">
         <v>629</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" t="s">
+      <c r="C57" t="s">
         <v>631</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
+      <c r="C58" t="s">
         <v>633</v>
       </c>
-      <c r="C58" t="s">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
+      <c r="C59" t="s">
         <v>635</v>
       </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
+      <c r="C60" t="s">
         <v>637</v>
       </c>
-      <c r="C60" t="s">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
+      <c r="C61" t="s">
         <v>639</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
+      <c r="C62" t="s">
         <v>641</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
+      <c r="C63" t="s">
         <v>643</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
+      <c r="C64" t="s">
         <v>645</v>
       </c>
-      <c r="C64" t="s">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
+      <c r="C65" t="s">
         <v>647</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
+      <c r="C66" t="s">
         <v>649</v>
       </c>
-      <c r="C66" t="s">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
+      <c r="C67" t="s">
         <v>651</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
+      <c r="C68" t="s">
         <v>653</v>
       </c>
-      <c r="C68" t="s">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
+      <c r="C69" t="s">
         <v>655</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
+      <c r="C70" t="s">
         <v>657</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
+      <c r="C71" t="s">
         <v>659</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
+      <c r="C72" t="s">
         <v>661</v>
       </c>
-      <c r="C72" t="s">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
+      <c r="C73" t="s">
         <v>663</v>
       </c>
-      <c r="C73" t="s">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
+      <c r="C74" t="s">
         <v>665</v>
       </c>
-      <c r="C74" t="s">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
+      <c r="C75" t="s">
         <v>667</v>
       </c>
-      <c r="C75" t="s">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
+      <c r="C76" t="s">
         <v>669</v>
       </c>
-      <c r="C76" t="s">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
+      <c r="C77" t="s">
         <v>671</v>
       </c>
-      <c r="C77" t="s">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
+      <c r="C78" t="s">
         <v>673</v>
       </c>
-      <c r="C78" t="s">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
+      <c r="C79" t="s">
         <v>675</v>
       </c>
-      <c r="C79" t="s">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
+      <c r="C80" t="s">
         <v>677</v>
       </c>
-      <c r="C80" t="s">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
+      <c r="C81" t="s">
         <v>679</v>
       </c>
-      <c r="C81" t="s">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
-      <c r="A82" t="s">
+      <c r="C82" t="s">
         <v>681</v>
       </c>
-      <c r="C82" t="s">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" t="s">
+      <c r="C83" t="s">
         <v>683</v>
       </c>
-      <c r="C83" t="s">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" t="s">
+      <c r="C84" t="s">
         <v>685</v>
       </c>
-      <c r="C84" t="s">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" t="s">
+      <c r="C85" t="s">
         <v>687</v>
       </c>
-      <c r="C85" t="s">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" t="s">
+      <c r="C86" t="s">
         <v>689</v>
       </c>
-      <c r="C86" t="s">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
-      <c r="A87" t="s">
+      <c r="C87" t="s">
         <v>691</v>
       </c>
-      <c r="C87" t="s">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="A88" t="s">
+      <c r="C88" t="s">
         <v>693</v>
       </c>
-      <c r="C88" t="s">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" t="s">
+      <c r="C89" t="s">
         <v>695</v>
       </c>
-      <c r="C89" t="s">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" t="s">
+      <c r="C90" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>697</v>
       </c>
-      <c r="C90" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
-      <c r="A91" t="s">
+      <c r="C91" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>698</v>
       </c>
-      <c r="C91" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
-      <c r="A92" t="s">
+      <c r="C92" t="s">
         <v>699</v>
       </c>
-      <c r="C92" t="s">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" t="s">
+      <c r="C93" t="s">
         <v>701</v>
       </c>
-      <c r="C93" t="s">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" t="s">
+      <c r="C94" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>703</v>
       </c>
-      <c r="C94" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" t="s">
+      <c r="C95" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
         <v>704</v>
       </c>
-      <c r="C95" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
-      <c r="A96" t="s">
+      <c r="C96" t="s">
         <v>705</v>
       </c>
-      <c r="C96" t="s">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
-      <c r="A97" t="s">
+      <c r="C97" t="s">
         <v>707</v>
       </c>
-      <c r="C97" t="s">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" t="s">
+      <c r="C98" t="s">
         <v>709</v>
       </c>
-      <c r="C98" t="s">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" t="s">
+      <c r="C99" t="s">
         <v>711</v>
       </c>
-      <c r="C99" t="s">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" t="s">
+      <c r="C100" t="s">
         <v>713</v>
       </c>
-      <c r="C100" t="s">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" t="s">
+      <c r="C101" t="s">
         <v>715</v>
       </c>
-      <c r="C101" t="s">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" t="s">
+      <c r="C102" t="s">
         <v>717</v>
       </c>
-      <c r="C102" t="s">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" t="s">
+      <c r="C103" t="s">
         <v>719</v>
       </c>
-      <c r="C103" t="s">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" t="s">
+      <c r="C104" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>721</v>
       </c>
-      <c r="C104" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" t="s">
+      <c r="C105" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>722</v>
       </c>
-      <c r="C105" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" t="s">
+      <c r="C106" t="s">
         <v>723</v>
       </c>
-      <c r="C106" t="s">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" t="s">
+      <c r="C107" t="s">
         <v>725</v>
       </c>
-      <c r="C107" t="s">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" t="s">
+      <c r="C108" t="s">
         <v>727</v>
       </c>
-      <c r="C108" t="s">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" t="s">
+      <c r="C109" t="s">
         <v>729</v>
       </c>
-      <c r="C109" t="s">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" t="s">
+      <c r="C110" t="s">
         <v>731</v>
       </c>
-      <c r="C110" t="s">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" t="s">
+      <c r="C111" t="s">
         <v>733</v>
       </c>
-      <c r="C111" t="s">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" t="s">
+      <c r="C112" t="s">
         <v>735</v>
       </c>
-      <c r="C112" t="s">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
+      <c r="C113" t="s">
         <v>737</v>
       </c>
-      <c r="C113" t="s">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
-      <c r="A114" t="s">
+      <c r="C114" t="s">
         <v>739</v>
       </c>
-      <c r="C114" t="s">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" t="s">
+      <c r="C115" t="s">
         <v>741</v>
       </c>
-      <c r="C115" t="s">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
-      <c r="A116" t="s">
+      <c r="C116" t="s">
         <v>743</v>
       </c>
-      <c r="C116" t="s">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
-      <c r="A117" t="s">
+      <c r="C117" t="s">
         <v>745</v>
       </c>
-      <c r="C117" t="s">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
-      <c r="A118" t="s">
+      <c r="C118" t="s">
         <v>747</v>
       </c>
-      <c r="C118" t="s">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" t="s">
+      <c r="C119" t="s">
         <v>749</v>
       </c>
-      <c r="C119" t="s">
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
-      <c r="A120" t="s">
+      <c r="C120" t="s">
         <v>751</v>
       </c>
-      <c r="C120" t="s">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
-      <c r="A121" t="s">
+      <c r="C121" t="s">
         <v>753</v>
       </c>
-      <c r="C121" t="s">
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" t="s">
+      <c r="C122" t="s">
         <v>755</v>
       </c>
-      <c r="C122" t="s">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
-      <c r="A123" t="s">
+      <c r="C123" t="s">
         <v>757</v>
       </c>
-      <c r="C123" t="s">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
-      <c r="A124" t="s">
+      <c r="C124" t="s">
         <v>759</v>
       </c>
-      <c r="C124" t="s">
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
-      <c r="A125" t="s">
+      <c r="C125" t="s">
         <v>761</v>
       </c>
-      <c r="C125" t="s">
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
-      <c r="A126" t="s">
+      <c r="C126" t="s">
         <v>763</v>
       </c>
-      <c r="C126" t="s">
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
-      <c r="A127" t="s">
+      <c r="C127" t="s">
         <v>765</v>
       </c>
-      <c r="C127" t="s">
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
-      <c r="A128" t="s">
+      <c r="C128" t="s">
         <v>767</v>
       </c>
-      <c r="C128" t="s">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
-      <c r="A129" t="s">
+      <c r="C129" t="s">
         <v>769</v>
       </c>
-      <c r="C129" t="s">
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
-      <c r="A130" t="s">
+      <c r="C130" t="s">
         <v>771</v>
       </c>
-      <c r="C130" t="s">
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131" t="s">
+      <c r="C131" t="s">
         <v>773</v>
       </c>
-      <c r="C131" t="s">
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" t="s">
+      <c r="C132" t="s">
         <v>775</v>
       </c>
-      <c r="C132" t="s">
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
-      <c r="A133" t="s">
+      <c r="C133" t="s">
         <v>777</v>
       </c>
-      <c r="C133" t="s">
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" t="s">
+      <c r="C134" t="s">
         <v>779</v>
       </c>
-      <c r="C134" t="s">
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
-      <c r="A135" t="s">
+      <c r="C135" t="s">
         <v>781</v>
       </c>
-      <c r="C135" t="s">
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136" t="s">
+      <c r="C136" t="s">
         <v>783</v>
       </c>
-      <c r="C136" t="s">
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137" t="s">
+      <c r="C137" t="s">
         <v>785</v>
       </c>
-      <c r="C137" t="s">
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138" t="s">
+      <c r="C138" t="s">
         <v>787</v>
       </c>
-      <c r="C138" t="s">
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139" t="s">
+      <c r="C139" t="s">
         <v>789</v>
       </c>
-      <c r="C139" t="s">
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140" t="s">
+      <c r="C140" t="s">
         <v>791</v>
       </c>
-      <c r="C140" t="s">
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
-      <c r="A141" t="s">
+      <c r="C141" t="s">
         <v>793</v>
       </c>
-      <c r="C141" t="s">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
-      <c r="A142" t="s">
+      <c r="C142" t="s">
         <v>795</v>
       </c>
-      <c r="C142" t="s">
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
-      <c r="A143" t="s">
+      <c r="C143" t="s">
         <v>797</v>
       </c>
-      <c r="C143" t="s">
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" t="s">
+      <c r="C144" t="s">
         <v>799</v>
       </c>
-      <c r="C144" t="s">
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" t="s">
+      <c r="C145" t="s">
         <v>801</v>
       </c>
-      <c r="C145" t="s">
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
-      <c r="A146" t="s">
+      <c r="C146" t="s">
         <v>803</v>
       </c>
-      <c r="C146" t="s">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
-      <c r="A147" t="s">
+      <c r="C147" t="s">
         <v>805</v>
       </c>
-      <c r="C147" t="s">
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
-      <c r="A148" t="s">
+      <c r="C148" t="s">
         <v>807</v>
       </c>
-      <c r="C148" t="s">
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
-      <c r="A149" t="s">
+      <c r="C149" t="s">
         <v>809</v>
       </c>
-      <c r="C149" t="s">
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150" t="s">
+      <c r="C150" t="s">
         <v>811</v>
       </c>
-      <c r="C150" t="s">
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151" t="s">
+      <c r="C151" t="s">
         <v>813</v>
       </c>
-      <c r="C151" t="s">
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152" t="s">
+      <c r="C152" t="s">
         <v>815</v>
       </c>
-      <c r="C152" t="s">
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153" t="s">
+      <c r="C153" t="s">
         <v>817</v>
       </c>
-      <c r="C153" t="s">
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" t="s">
+      <c r="C154" t="s">
         <v>819</v>
       </c>
-      <c r="C154" t="s">
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
-      <c r="A155" t="s">
+      <c r="C155" t="s">
         <v>821</v>
       </c>
-      <c r="C155" t="s">
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
+      <c r="C156" t="s">
         <v>823</v>
       </c>
-      <c r="C156" t="s">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" t="s">
+      <c r="C157" t="s">
         <v>825</v>
       </c>
-      <c r="C157" t="s">
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" t="s">
+      <c r="C158" t="s">
         <v>827</v>
       </c>
-      <c r="C158" t="s">
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" t="s">
+      <c r="C159" t="s">
         <v>829</v>
       </c>
-      <c r="C159" t="s">
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" t="s">
+      <c r="C160" t="s">
         <v>831</v>
       </c>
-      <c r="C160" t="s">
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161" t="s">
+      <c r="C161" t="s">
         <v>833</v>
       </c>
-      <c r="C161" t="s">
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" t="s">
+      <c r="C162" t="s">
         <v>835</v>
       </c>
-      <c r="C162" t="s">
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163" t="s">
+      <c r="C163" t="s">
         <v>837</v>
       </c>
-      <c r="C163" t="s">
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" t="s">
+      <c r="C164" t="s">
         <v>839</v>
       </c>
-      <c r="C164" t="s">
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" t="s">
+      <c r="C165" t="s">
         <v>841</v>
       </c>
-      <c r="C165" t="s">
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
+      <c r="C166" t="s">
         <v>843</v>
       </c>
-      <c r="C166" t="s">
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" t="s">
+      <c r="C167" t="s">
         <v>845</v>
       </c>
-      <c r="C167" t="s">
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" t="s">
+      <c r="C168" t="s">
         <v>847</v>
       </c>
-      <c r="C168" t="s">
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" t="s">
+      <c r="C169" t="s">
         <v>849</v>
       </c>
-      <c r="C169" t="s">
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" t="s">
+      <c r="C170" t="s">
         <v>851</v>
       </c>
-      <c r="C170" t="s">
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" t="s">
+      <c r="C171" t="s">
         <v>853</v>
       </c>
-      <c r="C171" t="s">
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" t="s">
+      <c r="C172" t="s">
         <v>855</v>
       </c>
-      <c r="C172" t="s">
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="173" spans="1:3">
-      <c r="A173" t="s">
+      <c r="C173" t="s">
         <v>857</v>
       </c>
-      <c r="C173" t="s">
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" t="s">
+      <c r="C174" t="s">
         <v>859</v>
       </c>
-      <c r="C174" t="s">
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" t="s">
+      <c r="C175" t="s">
         <v>861</v>
       </c>
-      <c r="C175" t="s">
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" t="s">
+      <c r="C176" t="s">
         <v>863</v>
       </c>
-      <c r="C176" t="s">
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" t="s">
+      <c r="C177" t="s">
         <v>865</v>
       </c>
-      <c r="C177" t="s">
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="178" spans="1:3">
-      <c r="A178" t="s">
+      <c r="C178" t="s">
         <v>867</v>
       </c>
-      <c r="C178" t="s">
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" t="s">
+      <c r="C179" t="s">
         <v>869</v>
       </c>
-      <c r="C179" t="s">
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" t="s">
+      <c r="C180" t="s">
         <v>871</v>
       </c>
-      <c r="C180" t="s">
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" t="s">
+      <c r="C181" t="s">
         <v>873</v>
       </c>
-      <c r="C181" t="s">
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" t="s">
+      <c r="C182" t="s">
         <v>875</v>
       </c>
-      <c r="C182" t="s">
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" t="s">
+      <c r="C183" t="s">
         <v>877</v>
       </c>
-      <c r="C183" t="s">
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" t="s">
+      <c r="C184" t="s">
         <v>879</v>
       </c>
-      <c r="C184" t="s">
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="185" spans="1:3">
-      <c r="A185" t="s">
+      <c r="C185" t="s">
         <v>881</v>
       </c>
-      <c r="C185" t="s">
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" t="s">
+      <c r="C186" t="s">
         <v>883</v>
       </c>
-      <c r="C186" t="s">
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" t="s">
+      <c r="C187" t="s">
         <v>885</v>
       </c>
-      <c r="C187" t="s">
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" t="s">
+      <c r="C188" t="s">
         <v>887</v>
       </c>
-      <c r="C188" t="s">
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" t="s">
+      <c r="C189" t="s">
         <v>889</v>
       </c>
-      <c r="C189" t="s">
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" t="s">
+      <c r="C190" t="s">
         <v>891</v>
       </c>
-      <c r="C190" t="s">
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
+      <c r="C191" t="s">
         <v>893</v>
       </c>
-      <c r="C191" t="s">
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
+      <c r="C192" t="s">
         <v>895</v>
       </c>
-      <c r="C192" t="s">
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
+      <c r="C193" t="s">
         <v>897</v>
       </c>
-      <c r="C193" t="s">
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" t="s">
+      <c r="C194" t="s">
         <v>899</v>
       </c>
-      <c r="C194" t="s">
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" t="s">
+      <c r="C195" t="s">
         <v>901</v>
       </c>
-      <c r="C195" t="s">
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" t="s">
+      <c r="C196" t="s">
         <v>903</v>
       </c>
-      <c r="C196" t="s">
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" t="s">
+      <c r="C197" t="s">
         <v>905</v>
       </c>
-      <c r="C197" t="s">
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" t="s">
+      <c r="C198" t="s">
         <v>907</v>
       </c>
-      <c r="C198" t="s">
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
+      <c r="C199" t="s">
         <v>909</v>
       </c>
-      <c r="C199" t="s">
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" t="s">
+      <c r="C200" t="s">
         <v>911</v>
       </c>
-      <c r="C200" t="s">
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" t="s">
+      <c r="C201" t="s">
         <v>913</v>
       </c>
-      <c r="C201" t="s">
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" t="s">
+      <c r="C202" t="s">
         <v>915</v>
       </c>
-      <c r="C202" t="s">
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
         <v>916</v>
       </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
+      <c r="C203" t="s">
         <v>917</v>
       </c>
-      <c r="C203" t="s">
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" t="s">
+      <c r="C204" t="s">
         <v>919</v>
       </c>
-      <c r="C204" t="s">
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
+      <c r="C205" t="s">
         <v>921</v>
       </c>
-      <c r="C205" t="s">
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" t="s">
+      <c r="C206" t="s">
         <v>923</v>
       </c>
-      <c r="C206" t="s">
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" t="s">
+      <c r="C207" t="s">
         <v>925</v>
       </c>
-      <c r="C207" t="s">
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" t="s">
+      <c r="C208" t="s">
         <v>927</v>
       </c>
-      <c r="C208" t="s">
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" t="s">
+      <c r="C209" t="s">
         <v>929</v>
-      </c>
-      <c r="C209" t="s">
-        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -9666,13 +9664,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9683,48 +9681,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2" t="s">
         <v>931</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>932</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>933</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="C3" s="8" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>934</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>935</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>937</v>
       </c>
-      <c r="B4" t="s">
-        <v>938</v>
-      </c>
-      <c r="C4" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>940</v>
-      </c>
-      <c r="B5" t="s">
-        <v>941</v>
-      </c>
-      <c r="C5" t="s">
-        <v>942</v>
+      <c r="C5" s="8" t="s">
+        <v>1336</v>
       </c>
     </row>
   </sheetData>
@@ -9736,13 +9728,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9753,48 +9745,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C2" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>941</v>
+      </c>
+      <c r="B3" t="s">
+        <v>942</v>
+      </c>
+      <c r="C3" t="s">
         <v>943</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" s="8" t="s">
         <v>945</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="C4" s="8" t="s">
         <v>946</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>947</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" s="8" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>949</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>950</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>952</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>953</v>
-      </c>
       <c r="C5" s="8" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -9806,13 +9798,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9823,59 +9815,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>952</v>
+      </c>
+      <c r="B3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C3" t="s">
         <v>954</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>955</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
         <v>957</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>958</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
         <v>959</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="C5" t="s">
         <v>960</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>961</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
         <v>962</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="C6" t="s">
         <v>963</v>
-      </c>
-      <c r="B5" t="s">
-        <v>964</v>
-      </c>
-      <c r="C5" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>966</v>
-      </c>
-      <c r="B6" t="s">
-        <v>967</v>
-      </c>
-      <c r="C6" t="s">
-        <v>968</v>
       </c>
     </row>
   </sheetData>
@@ -9887,14 +9879,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9905,653 +9897,653 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>967</v>
+      </c>
+      <c r="B3" t="s">
+        <v>968</v>
+      </c>
+      <c r="C3" t="s">
         <v>969</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>970</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B4" t="s">
         <v>971</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
         <v>972</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>973</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
         <v>974</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="C5" t="s">
         <v>975</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" s="5" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="C6" s="5" t="s">
         <v>978</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B7" s="8" t="s">
         <v>980</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B9" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>986</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
+      <c r="B10" s="9" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>987</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B11" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="8" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>985</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
+      <c r="B12" s="9" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="B10" s="9" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>1275</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>993</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="8" t="s">
-        <v>995</v>
-      </c>
-      <c r="B12" s="9" t="s">
+      <c r="C16" s="8" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>997</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="C17" s="8" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>1277</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="8" t="s">
-        <v>999</v>
-      </c>
-      <c r="B14" s="9" t="s">
+      <c r="C18" s="8" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>1278</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="8" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="C19" s="8" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>1279</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B16" s="9" t="s">
+      <c r="C20" s="8" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>1280</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B17" s="9" t="s">
+      <c r="C21" s="8" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>1281</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B18" s="9" t="s">
+      <c r="C22" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>1282</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="8" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="C23" s="8" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>1283</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B20" s="9" t="s">
+      <c r="C24" s="8" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>1284</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="8" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="C25" s="8" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>1285</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B22" s="9" t="s">
+      <c r="C26" s="8" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>1286</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="8" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="C27" s="8" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>1287</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="8" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="8" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B25" s="9" t="s">
+      <c r="C29" s="8" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>1289</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="8" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="C30" s="8" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>1290</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="8" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="C31" s="8" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>1291</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="8" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C32" s="8" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>1293</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="8" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="8" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="C34" s="8" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>1294</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="8" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="C35" s="8" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>1295</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="8" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="C39" s="9" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>1296</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="8" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="8" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="8" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="9" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="C40" s="9" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="9" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="9" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>1302</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="9" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="9" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="C44" s="9" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>1304</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C45" s="9" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="9" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="9" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="9" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="9" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="9" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="9" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="9" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="9" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="9" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="9" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="9" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="9" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="9" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="9" t="s">
         <v>1240</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>1314</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="9" t="s">
+      <c r="C55" s="9" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B56" s="9" t="s">
         <v>1315</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="9" t="s">
+      <c r="C56" s="9" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="9" t="s">
         <v>1242</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B57" s="9" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>1316</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="9" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C53" s="9" t="s">
+      <c r="C58" s="9" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="9" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
         <v>1244</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B59" s="9" t="s">
         <v>1318</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="9" t="s">
+      <c r="C59" s="9" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
         <v>1245</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B60" s="9" t="s">
         <v>1319</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="9" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="9" t="s">
+      <c r="C60" s="9" t="s">
         <v>1247</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="9" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="9" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="9" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>1252</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078A4760-B6F4-49F0-8B4A-2826A152AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5A1255-3CD8-F140-88E7-19E6E33F02B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="1770" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,14 @@
     <sheet name="Player" sheetId="11" r:id="rId11"/>
     <sheet name="DialogueNames" sheetId="12" r:id="rId12"/>
     <sheet name="DialogueContents" sheetId="13" r:id="rId13"/>
+    <sheet name="TutorialMessages" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1364">
   <si>
     <t>ID</t>
   </si>
@@ -46,27 +47,15 @@
     <t>DC_NPC00_1</t>
   </si>
   <si>
-    <t>是父王无能，一直以来让你受苦了。\n你一定要逃出去！</t>
-  </si>
-  <si>
     <t>DC_NPC01_1</t>
   </si>
   <si>
-    <t>自从勇者先生拼上性命阻止了魔界之王古顿之后，魔物应当是已经被彻底清除了才对</t>
-  </si>
-  <si>
     <t>DC_NPC01_2</t>
   </si>
   <si>
-    <t>如今魔物再次出现，其中一定有什么秘密</t>
-  </si>
-  <si>
     <t>DC_NPC01_3</t>
   </si>
   <si>
-    <t>勇者先生和古顿明明就在我面前死去，但是至今却并没有找到尸体</t>
-  </si>
-  <si>
     <t>DC_NPC01_4</t>
   </si>
   <si>
@@ -88,51 +77,27 @@
     <t>DC_NPC02_3</t>
   </si>
   <si>
-    <t>你最初被关在塔里时，我有缘将「心镜」赠与了那位勇者</t>
-  </si>
-  <si>
     <t>DC_NPC02_4</t>
   </si>
   <si>
-    <t>原来是这样\n多谢老伯当时相助</t>
-  </si>
-  <si>
     <t>DC_NPC02_5</t>
   </si>
   <si>
-    <t>孩子，如今皇宫尚未沦陷，你又何苦重回这伤心地</t>
-  </si>
-  <si>
     <t>DC_NPC02_6</t>
   </si>
   <si>
-    <t>我不忍弃我的国家和子民于水火\n我希望去做好我能做到的事</t>
-  </si>
-  <si>
     <t>DC_NPC02_7</t>
   </si>
   <si>
-    <t>明白了，我们这帮老骨头会尽力帮助你，这是另一面「心镜」，要妥善保管</t>
-  </si>
-  <si>
     <t>DC_NPC02_8</t>
   </si>
   <si>
-    <t>谢谢你</t>
-  </si>
-  <si>
     <t>DC_NPC03_1</t>
   </si>
   <si>
-    <t>你知道吗\n按下L键可以得知按键指令</t>
-  </si>
-  <si>
     <t>DC_NPC03_2</t>
   </si>
   <si>
-    <t>不用你说……</t>
-  </si>
-  <si>
     <t>DC_NPC04_1</t>
   </si>
   <si>
@@ -1190,9 +1155,6 @@
   </si>
   <si>
     <t>ENEMY_BOOK</t>
-  </si>
-  <si>
-    <t>Heart Mirror</t>
   </si>
   <si>
     <t>心镜</t>
@@ -4050,13 +4012,133 @@
   <si>
     <t>附带魔力的剑刃，用来增幅伤害，魔力越高，伤害越高，增幅效果越明显。</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TM_01</t>
+  </si>
+  <si>
+    <t>点击这里可以打开菜单界面。</t>
+  </si>
+  <si>
+    <t>You can open the menu by clicking here.</t>
+  </si>
+  <si>
+    <t>TM_02</t>
+  </si>
+  <si>
+    <t>宝石可以增加能力值。</t>
+  </si>
+  <si>
+    <t>The gem could enhance your power.</t>
+  </si>
+  <si>
+    <t>TM_03</t>
+  </si>
+  <si>
+    <t>The bottle could increase your HP.</t>
+  </si>
+  <si>
+    <t>血瓶可以增加HP值。</t>
+  </si>
+  <si>
+    <t>…...Your Royal Highness?</t>
+  </si>
+  <si>
+    <t>You seem to know me, sir.</t>
+  </si>
+  <si>
+    <t>The Mirror</t>
+  </si>
+  <si>
+    <t>原来是这样\n多谢老伯当时相助。</t>
+  </si>
+  <si>
+    <t>我不忍弃我的国家和子民于水火。\n我希望去做好我能做到的事。</t>
+  </si>
+  <si>
+    <t>谢谢你。</t>
+  </si>
+  <si>
+    <t>Thank you.</t>
+  </si>
+  <si>
+    <t>你知道吗，\n快捷键可以帮你快速执行很多操作。\n时间就是生命，你说是吧。</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>Do you know that?\nThe hot key could help you save much time.\nAs we always said, time is money.</t>
+  </si>
+  <si>
+    <t>TM_04</t>
+  </si>
+  <si>
+    <t>点击这里或者按L可以查询快捷键。</t>
+  </si>
+  <si>
+    <t>Clicking here or hot key L could help you know the hot keys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have not done right by you. \nYou have suffered for my failings. \nRun, my daughter. \nAs far as possible. </t>
+  </si>
+  <si>
+    <t>是父王无能，\n一直以来让你受苦了。\n你一定要逃出去！</t>
+  </si>
+  <si>
+    <t>Ever since the Bravant thwarted the Ruler of Devilheim's designs, \nthe monsters have vanished from our lands.</t>
+  </si>
+  <si>
+    <t>自从勇者先生拼上性命阻止了魔界之王古顿之后，\n魔物在当时也一并消失了。</t>
+  </si>
+  <si>
+    <t>Now that the monsters have begun to plague these lands once more, \nI fear some greater design may lie behind it all.</t>
+  </si>
+  <si>
+    <t>如今魔物再次为祸，\n恐怕背后有更大的阴谋。</t>
+  </si>
+  <si>
+    <t>当时的那一场大战，\n无论是勇士先生和古顿的尸体都没有找到痕迹。</t>
+  </si>
+  <si>
+    <t>After the great battle all those years ago, \nno trace was ever found of either the Bravant or the Lord.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forgive me, Father. \nThe truth must be found. \nFor our collective good. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you were held captive in the tower,\nI had the good fortune to give The Mirror to the Bravant. </t>
+  </si>
+  <si>
+    <t>你最初被关在塔里时，\n我有缘将「心镜」赠与了那位勇者。</t>
+  </si>
+  <si>
+    <t>Then I am in your debt, sir. \nYou have my heartfelt thanks.</t>
+  </si>
+  <si>
+    <t>The palace has not yet fallen. \nYou could still flee to safety. \nWhy, then, would you return to this place?</t>
+  </si>
+  <si>
+    <t>孩子，如今皇宫尚未沦陷，\n你更是有机会逃跑，\n你又何苦重回这个地方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I cannot abandon my people and our lands to those beings. \nI must fulfill my duty. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I see…\nUs old bones will keep giving you a hand.\nHere is another Mirror. \nKeep it safe. </t>
+  </si>
+  <si>
+    <t>明白了，\n我们这帮老骨头会尽力帮助你，\n这是另一面「心镜」，\n要妥善保管。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4117,6 +4199,12 @@
       <family val="4"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4158,7 +4246,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4369,14 +4457,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C64"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4387,697 +4475,697 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>136</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>137</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>139</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>140</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>142</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>143</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>146</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>148</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B11" t="s">
         <v>149</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>151</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B12" t="s">
         <v>152</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>154</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B13" t="s">
         <v>155</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C13" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>157</v>
       </c>
-      <c r="B9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B17" t="s">
         <v>166</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C17" t="s">
         <v>167</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B18" t="s">
         <v>169</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C18" t="s">
         <v>170</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B19" t="s">
         <v>172</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C19" t="s">
         <v>173</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B20" t="s">
         <v>175</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C20" t="s">
         <v>176</v>
       </c>
-      <c r="C16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>177</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B21" t="s">
         <v>178</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>180</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B22" t="s">
         <v>181</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>183</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B23" t="s">
         <v>184</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C23" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>186</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B24" t="s">
         <v>187</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C24" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C25" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B26" t="s">
         <v>193</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C26" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>195</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>196</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C27" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>198</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B28" t="s">
         <v>199</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C28" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B29" t="s">
         <v>202</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C29" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>204</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B30" t="s">
         <v>205</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C30" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>207</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B31" t="s">
         <v>208</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C31" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>210</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B32" t="s">
         <v>211</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C32" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>213</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B33" t="s">
         <v>214</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C33" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>216</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B34" t="s">
         <v>217</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C34" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>219</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B35" t="s">
         <v>220</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C35" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>222</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>223</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C36" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>225</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B37" t="s">
         <v>226</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C37" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>228</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B38" t="s">
         <v>229</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C38" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>231</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B39" t="s">
         <v>232</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C39" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C40" s="3" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B41" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C41" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>240</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>243</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" t="s">
         <v>244</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C43" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>246</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B44" t="s">
         <v>247</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C44" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>249</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B45" t="s">
         <v>250</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C45" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>252</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B46" t="s">
         <v>253</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C46" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>255</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B47" t="s">
         <v>256</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C47" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>258</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B48" t="s">
         <v>259</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C48" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>261</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B49" t="s">
         <v>262</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C49" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>264</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B50" t="s">
         <v>265</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C50" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>267</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B51" t="s">
         <v>268</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C51" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>270</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>273</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B53" t="s">
         <v>274</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C53" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>276</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B54" t="s">
         <v>277</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C54" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="55" spans="1:3" ht="32" customHeight="1">
+      <c r="A55" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B55" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C55" s="7" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="56" spans="1:3" ht="32" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B56" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C56" s="7" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="57" spans="1:3" ht="32" customHeight="1">
+      <c r="A57" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B57" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C57" s="7" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="58" spans="1:3" ht="32" customHeight="1">
+      <c r="A58" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B58" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C58" s="7" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+    <row r="59" spans="1:3" ht="32" customHeight="1">
+      <c r="A59" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B59" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C59" s="7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+    <row r="60" spans="1:3" ht="32" customHeight="1">
+      <c r="A60" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B60" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>297</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B61" t="s">
         <v>298</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C61" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>300</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B62" t="s">
         <v>301</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C62" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>303</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B63" t="s">
         <v>304</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C63" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>306</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B64" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C64" t="s">
         <v>308</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>309</v>
-      </c>
-      <c r="B61" t="s">
-        <v>310</v>
-      </c>
-      <c r="C61" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>312</v>
-      </c>
-      <c r="B62" t="s">
-        <v>313</v>
-      </c>
-      <c r="C62" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>315</v>
-      </c>
-      <c r="B63" t="s">
-        <v>316</v>
-      </c>
-      <c r="C63" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>318</v>
-      </c>
-      <c r="B64" t="s">
-        <v>319</v>
-      </c>
-      <c r="C64" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5089,13 +5177,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5106,552 +5194,552 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C4" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C6" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="B2" t="s">
-        <v>950</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C7" s="8" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>1040</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B8" t="s">
         <v>1041</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C8" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>1043</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B9" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="C4" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C9" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>1046</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>1048</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B11" t="s">
         <v>1049</v>
       </c>
-      <c r="C6" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="C11" s="4" t="s">
         <v>1050</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>1051</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B12" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C12" t="s">
         <v>1053</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>1054</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B13" s="6" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="C13" s="6" t="s">
         <v>1056</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>1057</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="B14" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="C14" s="6" t="s">
         <v>1059</v>
       </c>
-      <c r="B10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B15" t="s">
         <v>1061</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C15" s="6" t="s">
         <v>1062</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B16" t="s">
         <v>1064</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C16" t="s">
         <v>1065</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B17" t="s">
         <v>1067</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C17" t="s">
         <v>1068</v>
       </c>
-      <c r="C13" s="6" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B18" t="s">
         <v>1070</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C18" t="s">
         <v>1071</v>
       </c>
-      <c r="C14" s="6" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B19" t="s">
         <v>1073</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C19" t="s">
         <v>1074</v>
       </c>
-      <c r="C15" s="6" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B20" t="s">
         <v>1076</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C20" t="s">
         <v>1077</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B21" t="s">
         <v>1079</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C21" t="s">
         <v>1080</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B22" s="4" t="s">
         <v>1082</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C22" s="4" t="s">
         <v>1083</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B23" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C23" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B24" t="s">
         <v>1088</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C24" t="s">
         <v>1089</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>1090</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B25" t="s">
         <v>1091</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C25" t="s">
         <v>1092</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="6" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="B26" t="s">
         <v>1094</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C26" t="s">
         <v>1095</v>
       </c>
-      <c r="C22" s="4" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
         <v>1096</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="B27" t="s">
         <v>1097</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C27" t="s">
         <v>1098</v>
       </c>
-      <c r="C23" s="4" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B28" t="s">
         <v>1100</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C28" s="6" t="s">
         <v>1101</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B29" s="6" t="s">
         <v>1103</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C29" s="6" t="s">
         <v>1104</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="C30" t="s">
         <v>1106</v>
       </c>
-      <c r="B26" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>1107</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C31" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>1109</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C32" t="s">
         <v>1110</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C33" t="s">
         <v>1112</v>
       </c>
-      <c r="B28" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>1113</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C34" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>1115</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C35" t="s">
         <v>1116</v>
       </c>
-      <c r="C29" s="6" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>1117</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="C36" t="s">
         <v>1118</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="C37" t="s">
         <v>1120</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="C38" t="s">
         <v>1122</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>1123</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="C39" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="C40" t="s">
         <v>1126</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="C41" t="s">
         <v>1128</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="C42" t="s">
         <v>1130</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="C43" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="C44" t="s">
         <v>1134</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="C45" t="s">
         <v>1136</v>
       </c>
-      <c r="C39" s="8" t="s">
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="C46" t="s">
         <v>1138</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="C47" t="s">
         <v>1140</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>1141</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="C48" t="s">
         <v>1142</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>1143</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="C49" t="s">
         <v>1144</v>
       </c>
-      <c r="C43" s="8" t="s">
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="C50" t="s">
         <v>1146</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>1147</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="C51" t="s">
         <v>1148</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="C52" t="s">
         <v>1150</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="C53" t="s">
         <v>1152</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>1153</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="C54" t="s">
         <v>1154</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="C55" t="s">
         <v>1156</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>1157</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="C56" t="s">
         <v>1158</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>1159</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="C57" t="s">
         <v>1160</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="C58" t="s">
         <v>1162</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>1163</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="C59" t="s">
         <v>1164</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -5663,13 +5751,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5680,26 +5768,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="C2" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="B3" t="s">
-        <v>1181</v>
+        <v>1168</v>
       </c>
       <c r="C3" t="s">
-        <v>1182</v>
+        <v>1169</v>
       </c>
     </row>
   </sheetData>
@@ -5711,14 +5799,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5729,169 +5817,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
         <v>1184</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="B10" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="6" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="B11" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>1187</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="B12" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6" t="s">
         <v>1189</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B13" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>1190</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
         <v>1191</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B14" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="6" t="s">
         <v>1193</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B15" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="6" t="s">
         <v>1195</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B16" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>1196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>1209</v>
       </c>
     </row>
   </sheetData>
@@ -5903,12 +5991,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="34.5" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="2" max="2" width="101.83203125" customWidth="1"/>
+    <col min="3" max="3" width="87.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5919,1216 +6009,1246 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="B5" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="8" t="s">
+      <c r="B6" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="B7" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
+      <c r="B8" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
+      <c r="B9" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="B10" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
+      <c r="B11" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="B12" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="B13" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="B14" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
+      <c r="B15" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="8" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="8" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="8" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="8" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="8" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="8" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="8" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" s="8" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" s="8" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" s="8" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" s="8" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" s="8" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="8" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="8" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="8" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
-        <v>1211</v>
+        <v>1198</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="8" t="s">
-        <v>1215</v>
+        <v>1202</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="8" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -7140,12 +7260,82 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="32.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7156,26 +7346,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -7187,9 +7377,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7200,169 +7390,169 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>343</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C13" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>346</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C14" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>349</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C15" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>352</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C16" t="s">
         <v>354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>355</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="C13" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>358</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C14" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>361</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C15" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>364</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C16" t="s">
-        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -7374,14 +7564,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7392,510 +7582,510 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>367</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>368</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>370</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
         <v>371</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C7" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>373</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B9" t="s">
         <v>376</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C9" t="s">
         <v>377</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B10" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C10" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B11" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C11" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B12" t="s">
         <v>385</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C12" t="s">
         <v>386</v>
       </c>
-      <c r="C8" s="8" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B13" t="s">
         <v>388</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C13" t="s">
         <v>389</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B14" t="s">
         <v>391</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C14" t="s">
         <v>392</v>
       </c>
-      <c r="C10" s="8" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B15" t="s">
         <v>394</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C15" t="s">
         <v>395</v>
       </c>
-      <c r="C11" s="8" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B16" t="s">
         <v>397</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C16" t="s">
         <v>398</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B17" t="s">
         <v>400</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C17" t="s">
         <v>401</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B18" t="s">
         <v>403</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C18" t="s">
         <v>404</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B19" t="s">
         <v>406</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C19" t="s">
         <v>407</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B20" t="s">
         <v>409</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C20" t="s">
         <v>410</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B21" t="s">
         <v>412</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C21" t="s">
         <v>413</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B22" t="s">
         <v>415</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C22" t="s">
         <v>416</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B23" t="s">
         <v>418</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C23" t="s">
         <v>419</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B24" t="s">
         <v>421</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C24" t="s">
         <v>422</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B25" t="s">
         <v>424</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C25" t="s">
         <v>425</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B26" t="s">
         <v>427</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C26" t="s">
         <v>428</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B27" t="s">
         <v>430</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C27" t="s">
         <v>431</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B28" t="s">
         <v>433</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C28" t="s">
         <v>434</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B29" t="s">
         <v>436</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C29" t="s">
         <v>437</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B30" t="s">
         <v>439</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C30" t="s">
         <v>440</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B31" t="s">
         <v>442</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C31" t="s">
         <v>443</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B32" t="s">
         <v>445</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C32" t="s">
         <v>446</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B33" t="s">
         <v>448</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C33" t="s">
         <v>449</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B34" t="s">
         <v>451</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C34" t="s">
         <v>452</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B35" t="s">
         <v>454</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C35" t="s">
         <v>455</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B36" t="s">
         <v>457</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C36" t="s">
         <v>458</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B37" t="s">
         <v>460</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C37" t="s">
         <v>461</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B38" t="s">
         <v>463</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C38" t="s">
         <v>464</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B39" t="s">
         <v>466</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C39" t="s">
         <v>467</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="B40" t="s">
         <v>469</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C40" t="s">
         <v>470</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B41" t="s">
         <v>472</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C41" t="s">
         <v>473</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B42" t="s">
         <v>475</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C42" t="s">
         <v>476</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B43" t="s">
         <v>478</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C43" t="s">
         <v>479</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B44" t="s">
         <v>481</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C44" t="s">
         <v>482</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="B45" t="s">
         <v>484</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C45" t="s">
         <v>485</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="B46" t="s">
         <v>487</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C46" t="s">
         <v>488</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="B47" t="s">
         <v>490</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C47" t="s">
         <v>491</v>
-      </c>
-      <c r="C43" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>493</v>
-      </c>
-      <c r="B44" t="s">
-        <v>494</v>
-      </c>
-      <c r="C44" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>496</v>
-      </c>
-      <c r="B45" t="s">
-        <v>497</v>
-      </c>
-      <c r="C45" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>499</v>
-      </c>
-      <c r="B46" t="s">
-        <v>500</v>
-      </c>
-      <c r="C46" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>502</v>
-      </c>
-      <c r="B47" t="s">
-        <v>503</v>
-      </c>
-      <c r="C47" t="s">
-        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -7907,14 +8097,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C209"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7925,1734 +8115,1734 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" t="s">
         <v>505</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C6" t="s">
         <v>506</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B7" t="s">
         <v>508</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C7" t="s">
         <v>509</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B8" t="s">
         <v>511</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C8" t="s">
         <v>512</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B9" t="s">
         <v>514</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C9" t="s">
         <v>515</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B10" t="s">
         <v>517</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C10" t="s">
         <v>518</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B11" t="s">
         <v>520</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C11" t="s">
         <v>521</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B12" t="s">
         <v>523</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C12" t="s">
         <v>524</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B13" t="s">
         <v>526</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C13" t="s">
         <v>527</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B14" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C14" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B15" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C15" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B16" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C16" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B17" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C17" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="4" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B22" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="4" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="C19" s="2" t="s">
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="C24" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>559</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C25" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>560</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C26" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>562</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C27" t="s">
         <v>563</v>
       </c>
-      <c r="C21" s="3" t="s">
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="C28" t="s">
         <v>565</v>
       </c>
-      <c r="B22" s="4" t="s">
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>566</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C29" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>568</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C30" t="s">
         <v>569</v>
       </c>
-      <c r="C23" s="4" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="C31" t="s">
         <v>571</v>
       </c>
-      <c r="C24" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>572</v>
       </c>
-      <c r="C25" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C32" t="s">
         <v>573</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="C33" t="s">
         <v>575</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="C34" t="s">
         <v>577</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="C35" t="s">
         <v>579</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="C36" t="s">
         <v>581</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="C37" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>583</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C38" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>585</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C39" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>587</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C40" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>589</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C41" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
         <v>591</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C42" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>593</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C43" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
         <v>595</v>
       </c>
-      <c r="C37" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="C44" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
         <v>596</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C45" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="C46" t="s">
         <v>598</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="C47" t="s">
         <v>600</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="C48" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
         <v>602</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C49" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
         <v>604</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C50" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
         <v>606</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C51" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
         <v>608</v>
       </c>
-      <c r="C44" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="C52" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
         <v>609</v>
       </c>
-      <c r="C45" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="C53" t="s">
         <v>610</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="C54" t="s">
         <v>612</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="C55" t="s">
         <v>614</v>
       </c>
-      <c r="C48" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
         <v>615</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C56" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
         <v>617</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C57" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
         <v>619</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C58" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
         <v>621</v>
       </c>
-      <c r="C52" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="C59" t="s">
         <v>622</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="C60" t="s">
         <v>624</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="C61" t="s">
         <v>626</v>
       </c>
-      <c r="C55" t="s">
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="C62" t="s">
         <v>628</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="C63" t="s">
         <v>630</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="C64" t="s">
         <v>632</v>
       </c>
-      <c r="C58" t="s">
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="C65" t="s">
         <v>634</v>
       </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="C66" t="s">
         <v>636</v>
       </c>
-      <c r="C60" t="s">
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="C67" t="s">
         <v>638</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+      <c r="C68" t="s">
         <v>640</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="C69" t="s">
         <v>642</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="C70" t="s">
         <v>644</v>
       </c>
-      <c r="C64" t="s">
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="C71" t="s">
         <v>646</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="C72" t="s">
         <v>648</v>
       </c>
-      <c r="C66" t="s">
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="C73" t="s">
         <v>650</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="C74" t="s">
         <v>652</v>
       </c>
-      <c r="C68" t="s">
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="C75" t="s">
         <v>654</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+      <c r="C76" t="s">
         <v>656</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="C77" t="s">
         <v>658</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="C78" t="s">
         <v>660</v>
       </c>
-      <c r="C72" t="s">
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="C79" t="s">
         <v>662</v>
       </c>
-      <c r="C73" t="s">
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="C80" t="s">
         <v>664</v>
       </c>
-      <c r="C74" t="s">
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="C81" t="s">
         <v>666</v>
       </c>
-      <c r="C75" t="s">
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="C82" t="s">
         <v>668</v>
       </c>
-      <c r="C76" t="s">
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="C83" t="s">
         <v>670</v>
       </c>
-      <c r="C77" t="s">
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="C84" t="s">
         <v>672</v>
       </c>
-      <c r="C78" t="s">
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+      <c r="C85" t="s">
         <v>674</v>
       </c>
-      <c r="C79" t="s">
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="C86" t="s">
         <v>676</v>
       </c>
-      <c r="C80" t="s">
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+      <c r="C87" t="s">
         <v>678</v>
       </c>
-      <c r="C81" t="s">
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+      <c r="C88" t="s">
         <v>680</v>
       </c>
-      <c r="C82" t="s">
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+      <c r="C89" t="s">
         <v>682</v>
       </c>
-      <c r="C83" t="s">
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+      <c r="C90" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
         <v>684</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C91" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+      <c r="C92" t="s">
         <v>686</v>
       </c>
-      <c r="C85" t="s">
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="C93" t="s">
         <v>688</v>
       </c>
-      <c r="C86" t="s">
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="C94" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
         <v>690</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C95" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="C96" t="s">
         <v>692</v>
       </c>
-      <c r="C88" t="s">
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="C97" t="s">
         <v>694</v>
       </c>
-      <c r="C89" t="s">
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="C98" t="s">
         <v>696</v>
       </c>
-      <c r="C90" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
         <v>697</v>
       </c>
-      <c r="C91" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="C99" t="s">
         <v>698</v>
       </c>
-      <c r="C92" t="s">
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="C100" t="s">
         <v>700</v>
       </c>
-      <c r="C93" t="s">
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+      <c r="C101" t="s">
         <v>702</v>
       </c>
-      <c r="C94" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
         <v>703</v>
       </c>
-      <c r="C95" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+      <c r="C102" t="s">
         <v>704</v>
       </c>
-      <c r="C96" t="s">
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="C103" t="s">
         <v>706</v>
       </c>
-      <c r="C97" t="s">
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+      <c r="C104" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
         <v>708</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C105" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+      <c r="C106" t="s">
         <v>710</v>
       </c>
-      <c r="C99" t="s">
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+      <c r="C107" t="s">
         <v>712</v>
       </c>
-      <c r="C100" t="s">
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="C108" t="s">
         <v>714</v>
       </c>
-      <c r="C101" t="s">
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="C109" t="s">
         <v>716</v>
       </c>
-      <c r="C102" t="s">
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="C110" t="s">
         <v>718</v>
       </c>
-      <c r="C103" t="s">
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="C111" t="s">
         <v>720</v>
       </c>
-      <c r="C104" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
         <v>721</v>
       </c>
-      <c r="C105" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="C112" t="s">
         <v>722</v>
       </c>
-      <c r="C106" t="s">
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="C113" t="s">
         <v>724</v>
       </c>
-      <c r="C107" t="s">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="C114" t="s">
         <v>726</v>
       </c>
-      <c r="C108" t="s">
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="C115" t="s">
         <v>728</v>
       </c>
-      <c r="C109" t="s">
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="C116" t="s">
         <v>730</v>
       </c>
-      <c r="C110" t="s">
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="C117" t="s">
         <v>732</v>
       </c>
-      <c r="C111" t="s">
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="C118" t="s">
         <v>734</v>
       </c>
-      <c r="C112" t="s">
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+      <c r="C119" t="s">
         <v>736</v>
       </c>
-      <c r="C113" t="s">
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+      <c r="C120" t="s">
         <v>738</v>
       </c>
-      <c r="C114" t="s">
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+      <c r="C121" t="s">
         <v>740</v>
       </c>
-      <c r="C115" t="s">
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+      <c r="C122" t="s">
         <v>742</v>
       </c>
-      <c r="C116" t="s">
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+      <c r="C123" t="s">
         <v>744</v>
       </c>
-      <c r="C117" t="s">
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+      <c r="C124" t="s">
         <v>746</v>
       </c>
-      <c r="C118" t="s">
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+      <c r="C125" t="s">
         <v>748</v>
       </c>
-      <c r="C119" t="s">
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+      <c r="C126" t="s">
         <v>750</v>
       </c>
-      <c r="C120" t="s">
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="C127" t="s">
         <v>752</v>
       </c>
-      <c r="C121" t="s">
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="C128" t="s">
         <v>754</v>
       </c>
-      <c r="C122" t="s">
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="C129" t="s">
         <v>756</v>
       </c>
-      <c r="C123" t="s">
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="C130" t="s">
         <v>758</v>
       </c>
-      <c r="C124" t="s">
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="C131" t="s">
         <v>760</v>
       </c>
-      <c r="C125" t="s">
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="C132" t="s">
         <v>762</v>
       </c>
-      <c r="C126" t="s">
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="C133" t="s">
         <v>764</v>
       </c>
-      <c r="C127" t="s">
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="C134" t="s">
         <v>766</v>
       </c>
-      <c r="C128" t="s">
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="C135" t="s">
         <v>768</v>
       </c>
-      <c r="C129" t="s">
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
+      <c r="C136" t="s">
         <v>770</v>
       </c>
-      <c r="C130" t="s">
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
+      <c r="C137" t="s">
         <v>772</v>
       </c>
-      <c r="C131" t="s">
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="C138" t="s">
         <v>774</v>
       </c>
-      <c r="C132" t="s">
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="C139" t="s">
         <v>776</v>
       </c>
-      <c r="C133" t="s">
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="C140" t="s">
         <v>778</v>
       </c>
-      <c r="C134" t="s">
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="C141" t="s">
         <v>780</v>
       </c>
-      <c r="C135" t="s">
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="C142" t="s">
         <v>782</v>
       </c>
-      <c r="C136" t="s">
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="C143" t="s">
         <v>784</v>
       </c>
-      <c r="C137" t="s">
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="C144" t="s">
         <v>786</v>
       </c>
-      <c r="C138" t="s">
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="C145" t="s">
         <v>788</v>
       </c>
-      <c r="C139" t="s">
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="C146" t="s">
         <v>790</v>
       </c>
-      <c r="C140" t="s">
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="C147" t="s">
         <v>792</v>
       </c>
-      <c r="C141" t="s">
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
+      <c r="C148" t="s">
         <v>794</v>
       </c>
-      <c r="C142" t="s">
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
+      <c r="C149" t="s">
         <v>796</v>
       </c>
-      <c r="C143" t="s">
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
+      <c r="C150" t="s">
         <v>798</v>
       </c>
-      <c r="C144" t="s">
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
+      <c r="C151" t="s">
         <v>800</v>
       </c>
-      <c r="C145" t="s">
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
+      <c r="C152" t="s">
         <v>802</v>
       </c>
-      <c r="C146" t="s">
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
+      <c r="C153" t="s">
         <v>804</v>
       </c>
-      <c r="C147" t="s">
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
+      <c r="C154" t="s">
         <v>806</v>
       </c>
-      <c r="C148" t="s">
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
+      <c r="C155" t="s">
         <v>808</v>
       </c>
-      <c r="C149" t="s">
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
+      <c r="C156" t="s">
         <v>810</v>
       </c>
-      <c r="C150" t="s">
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
+      <c r="C157" t="s">
         <v>812</v>
       </c>
-      <c r="C151" t="s">
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
+      <c r="C158" t="s">
         <v>814</v>
       </c>
-      <c r="C152" t="s">
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
+      <c r="C159" t="s">
         <v>816</v>
       </c>
-      <c r="C153" t="s">
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
+      <c r="C160" t="s">
         <v>818</v>
       </c>
-      <c r="C154" t="s">
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
+      <c r="C161" t="s">
         <v>820</v>
       </c>
-      <c r="C155" t="s">
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="C162" t="s">
         <v>822</v>
       </c>
-      <c r="C156" t="s">
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
+      <c r="C163" t="s">
         <v>824</v>
       </c>
-      <c r="C157" t="s">
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
+      <c r="C164" t="s">
         <v>826</v>
       </c>
-      <c r="C158" t="s">
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
+      <c r="C165" t="s">
         <v>828</v>
       </c>
-      <c r="C159" t="s">
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
+      <c r="C166" t="s">
         <v>830</v>
       </c>
-      <c r="C160" t="s">
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
+      <c r="C167" t="s">
         <v>832</v>
       </c>
-      <c r="C161" t="s">
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
+      <c r="C168" t="s">
         <v>834</v>
       </c>
-      <c r="C162" t="s">
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
+      <c r="C169" t="s">
         <v>836</v>
       </c>
-      <c r="C163" t="s">
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
+      <c r="C170" t="s">
         <v>838</v>
       </c>
-      <c r="C164" t="s">
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
+      <c r="C171" t="s">
         <v>840</v>
       </c>
-      <c r="C165" t="s">
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="C172" t="s">
         <v>842</v>
       </c>
-      <c r="C166" t="s">
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+      <c r="C173" t="s">
         <v>844</v>
       </c>
-      <c r="C167" t="s">
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+      <c r="C174" t="s">
         <v>846</v>
       </c>
-      <c r="C168" t="s">
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="C175" t="s">
         <v>848</v>
       </c>
-      <c r="C169" t="s">
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
+      <c r="C176" t="s">
         <v>850</v>
       </c>
-      <c r="C170" t="s">
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
+      <c r="C177" t="s">
         <v>852</v>
       </c>
-      <c r="C171" t="s">
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
+      <c r="C178" t="s">
         <v>854</v>
       </c>
-      <c r="C172" t="s">
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
+      <c r="C179" t="s">
         <v>856</v>
       </c>
-      <c r="C173" t="s">
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
+      <c r="C180" t="s">
         <v>858</v>
       </c>
-      <c r="C174" t="s">
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
+      <c r="C181" t="s">
         <v>860</v>
       </c>
-      <c r="C175" t="s">
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" t="s">
         <v>861</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
+      <c r="C182" t="s">
         <v>862</v>
       </c>
-      <c r="C176" t="s">
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
+      <c r="C183" t="s">
         <v>864</v>
       </c>
-      <c r="C177" t="s">
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
+      <c r="C184" t="s">
         <v>866</v>
       </c>
-      <c r="C178" t="s">
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
+      <c r="C185" t="s">
         <v>868</v>
       </c>
-      <c r="C179" t="s">
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
+      <c r="C186" t="s">
         <v>870</v>
       </c>
-      <c r="C180" t="s">
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
+      <c r="C187" t="s">
         <v>872</v>
       </c>
-      <c r="C181" t="s">
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
+      <c r="C188" t="s">
         <v>874</v>
       </c>
-      <c r="C182" t="s">
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
+      <c r="C189" t="s">
         <v>876</v>
       </c>
-      <c r="C183" t="s">
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+      <c r="C190" t="s">
         <v>878</v>
       </c>
-      <c r="C184" t="s">
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
+      <c r="C191" t="s">
         <v>880</v>
       </c>
-      <c r="C185" t="s">
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+      <c r="C192" t="s">
         <v>882</v>
       </c>
-      <c r="C186" t="s">
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
+      <c r="C193" t="s">
         <v>884</v>
       </c>
-      <c r="C187" t="s">
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
+      <c r="C194" t="s">
         <v>886</v>
       </c>
-      <c r="C188" t="s">
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
+      <c r="C195" t="s">
         <v>888</v>
       </c>
-      <c r="C189" t="s">
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
+      <c r="C196" t="s">
         <v>890</v>
       </c>
-      <c r="C190" t="s">
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
+      <c r="C197" t="s">
         <v>892</v>
       </c>
-      <c r="C191" t="s">
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
+      <c r="C198" t="s">
         <v>894</v>
       </c>
-      <c r="C192" t="s">
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
+      <c r="C199" t="s">
         <v>896</v>
       </c>
-      <c r="C193" t="s">
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
+      <c r="C200" t="s">
         <v>898</v>
       </c>
-      <c r="C194" t="s">
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
+      <c r="C201" t="s">
         <v>900</v>
       </c>
-      <c r="C195" t="s">
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
+      <c r="C202" t="s">
         <v>902</v>
       </c>
-      <c r="C196" t="s">
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
+      <c r="C203" t="s">
         <v>904</v>
       </c>
-      <c r="C197" t="s">
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
+      <c r="C204" t="s">
         <v>906</v>
       </c>
-      <c r="C198" t="s">
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
+      <c r="C205" t="s">
         <v>908</v>
       </c>
-      <c r="C199" t="s">
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
+      <c r="C206" t="s">
         <v>910</v>
       </c>
-      <c r="C200" t="s">
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
+      <c r="C207" t="s">
         <v>912</v>
       </c>
-      <c r="C201" t="s">
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
+      <c r="C208" t="s">
         <v>914</v>
       </c>
-      <c r="C202" t="s">
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
+      <c r="C209" t="s">
         <v>916</v>
-      </c>
-      <c r="C203" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>918</v>
-      </c>
-      <c r="C204" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>920</v>
-      </c>
-      <c r="C205" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>922</v>
-      </c>
-      <c r="C206" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>924</v>
-      </c>
-      <c r="C207" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>926</v>
-      </c>
-      <c r="C208" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>928</v>
-      </c>
-      <c r="C209" t="s">
-        <v>929</v>
       </c>
     </row>
   </sheetData>
@@ -9664,13 +9854,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9681,42 +9871,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="B2" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="C2" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>933</v>
+        <v>920</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="B4" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="C4" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1336</v>
+        <v>1323</v>
       </c>
     </row>
   </sheetData>
@@ -9728,13 +9918,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9745,48 +9935,48 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="B2" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="C2" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="B3" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="C3" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -9798,13 +9988,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9815,59 +10005,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C2" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>939</v>
+      </c>
+      <c r="B3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C3" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>942</v>
+      </c>
+      <c r="B4" t="s">
+        <v>943</v>
+      </c>
+      <c r="C4" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>945</v>
+      </c>
+      <c r="B5" t="s">
+        <v>946</v>
+      </c>
+      <c r="C5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B6" t="s">
         <v>949</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C6" t="s">
         <v>950</v>
-      </c>
-      <c r="C2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>952</v>
-      </c>
-      <c r="B3" t="s">
-        <v>953</v>
-      </c>
-      <c r="C3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>955</v>
-      </c>
-      <c r="B4" t="s">
-        <v>956</v>
-      </c>
-      <c r="C4" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>958</v>
-      </c>
-      <c r="B5" t="s">
-        <v>959</v>
-      </c>
-      <c r="C5" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>961</v>
-      </c>
-      <c r="B6" t="s">
-        <v>962</v>
-      </c>
-      <c r="C6" t="s">
-        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -9879,14 +10069,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C60"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9897,653 +10087,653 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>954</v>
+      </c>
+      <c r="B3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C3" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>957</v>
+      </c>
+      <c r="B4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>960</v>
+      </c>
+      <c r="B5" t="s">
+        <v>961</v>
+      </c>
+      <c r="C5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>964</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="C2" s="8" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B7" s="8" t="s">
         <v>967</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C7" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B8" s="8" t="s">
         <v>970</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C8" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="8" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B9" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B10" s="9" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="8" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="B11" s="9" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="B6" s="5" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B12" s="9" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B13" s="9" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="C7" s="8" t="s">
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="B14" s="9" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
         <v>983</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B15" s="9" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="B16" s="9" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="B10" s="9" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>1270</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>988</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>990</v>
-      </c>
-      <c r="B12" s="9" t="s">
+      <c r="C24" s="8" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>1271</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>992</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="C25" s="8" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>1272</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="B14" s="9" t="s">
+      <c r="C26" s="8" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>1273</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>996</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="C27" s="8" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>1274</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>998</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B17" s="9" t="s">
+      <c r="C29" s="8" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B18" s="9" t="s">
+      <c r="C30" s="8" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>1277</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="C31" s="8" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>1278</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B20" s="9" t="s">
+      <c r="C32" s="8" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>1279</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="C33" s="8" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>1280</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B22" s="9" t="s">
+      <c r="C34" s="8" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>1281</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="C35" s="8" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="9" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="9" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>1282</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B24" s="9" t="s">
+      <c r="C39" s="9" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>1283</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C40" s="9" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>1288</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="C42" s="9" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="9" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="9" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>1289</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="C44" s="9" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>1291</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B33" s="9" t="s">
+      <c r="C45" s="9" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="9" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>1292</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B34" s="9" t="s">
+      <c r="C46" s="9" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>1293</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="C47" s="9" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>1294</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="C48" s="9" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="9" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="9" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B51" s="9" t="s">
         <v>1297</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="C51" s="9" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>1298</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="C52" s="9" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>1299</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
+      <c r="C53" s="9" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B54" s="9" t="s">
         <v>1300</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="C54" s="9" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="9" t="s">
         <v>1227</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>1301</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="C55" s="9" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="9" t="s">
         <v>1228</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B56" s="9" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>1303</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="9" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="C58" s="9" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="9" t="s">
         <v>1231</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B59" s="9" t="s">
         <v>1305</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="9" t="s">
+      <c r="C59" s="9" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="9" t="s">
         <v>1232</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B60" s="9" t="s">
         <v>1306</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
+      <c r="C60" s="9" t="s">
         <v>1234</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="9" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
-        <v>1241</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
-        <v>1245</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>1319</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>1247</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5A1255-3CD8-F140-88E7-19E6E33F02B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5577F4A3-C6EA-604F-B035-1081A46BBD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="1367">
   <si>
     <t>ID</t>
   </si>
@@ -3656,85 +3656,10 @@
     <t>对了，你要金坷垃吗</t>
   </si>
   <si>
-    <t>TMT_001</t>
-  </si>
-  <si>
     <t>魔塔25层</t>
   </si>
   <si>
-    <t>TMT_002</t>
-  </si>
-  <si>
     <t>魔塔24层</t>
-  </si>
-  <si>
-    <t>TMT_003</t>
-  </si>
-  <si>
-    <t>TMT_004</t>
-  </si>
-  <si>
-    <t>TMT_005</t>
-  </si>
-  <si>
-    <t>TMT_006</t>
-  </si>
-  <si>
-    <t>TMT_007</t>
-  </si>
-  <si>
-    <t>TMT_008</t>
-  </si>
-  <si>
-    <t>TMT_009</t>
-  </si>
-  <si>
-    <t>TMT_010</t>
-  </si>
-  <si>
-    <t>TMT_011</t>
-  </si>
-  <si>
-    <t>TMT_012</t>
-  </si>
-  <si>
-    <t>TMT_013</t>
-  </si>
-  <si>
-    <t>TMT_014</t>
-  </si>
-  <si>
-    <t>TMT_015</t>
-  </si>
-  <si>
-    <t>TMT_016</t>
-  </si>
-  <si>
-    <t>TMT_017</t>
-  </si>
-  <si>
-    <t>TMT_018</t>
-  </si>
-  <si>
-    <t>TMT_019</t>
-  </si>
-  <si>
-    <t>TMT_020</t>
-  </si>
-  <si>
-    <t>TMT_021</t>
-  </si>
-  <si>
-    <t>TMT_022</t>
-  </si>
-  <si>
-    <t>TMT_023</t>
-  </si>
-  <si>
-    <t>TMT_024</t>
-  </si>
-  <si>
-    <t>TMT_025</t>
   </si>
   <si>
     <t>魔塔23层</t>
@@ -4132,6 +4057,90 @@
   </si>
   <si>
     <t>明白了，\n我们这帮老骨头会尽力帮助你，\n这是另一面「心镜」，\n要妥善保管。</t>
+  </si>
+  <si>
+    <t>TM_05</t>
+  </si>
+  <si>
+    <t>敌人的能力信息，确认键或点击可以查看详细内容。</t>
+  </si>
+  <si>
+    <t>There is the information of enemies. You can press confirm button or click to view the detail.</t>
+  </si>
+  <si>
+    <t>TMT3_001</t>
+  </si>
+  <si>
+    <t>TMT3_002</t>
+  </si>
+  <si>
+    <t>TMT3_003</t>
+  </si>
+  <si>
+    <t>TMT3_004</t>
+  </si>
+  <si>
+    <t>TMT3_005</t>
+  </si>
+  <si>
+    <t>TMT3_006</t>
+  </si>
+  <si>
+    <t>TMT3_007</t>
+  </si>
+  <si>
+    <t>TMT3_008</t>
+  </si>
+  <si>
+    <t>TMT3_009</t>
+  </si>
+  <si>
+    <t>TMT3_010</t>
+  </si>
+  <si>
+    <t>TMT3_011</t>
+  </si>
+  <si>
+    <t>TMT3_012</t>
+  </si>
+  <si>
+    <t>TMT3_013</t>
+  </si>
+  <si>
+    <t>TMT3_014</t>
+  </si>
+  <si>
+    <t>TMT3_015</t>
+  </si>
+  <si>
+    <t>TMT3_016</t>
+  </si>
+  <si>
+    <t>TMT3_017</t>
+  </si>
+  <si>
+    <t>TMT3_018</t>
+  </si>
+  <si>
+    <t>TMT3_019</t>
+  </si>
+  <si>
+    <t>TMT3_020</t>
+  </si>
+  <si>
+    <t>TMT3_021</t>
+  </si>
+  <si>
+    <t>TMT3_022</t>
+  </si>
+  <si>
+    <t>TMT3_023</t>
+  </si>
+  <si>
+    <t>TMT3_024</t>
+  </si>
+  <si>
+    <t>TMT3_025</t>
   </si>
 </sst>
 </file>
@@ -5773,7 +5782,7 @@
         <v>1165</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1307</v>
+        <v>1282</v>
       </c>
       <c r="C2" t="s">
         <v>1166</v>
@@ -5822,7 +5831,7 @@
         <v>1170</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1308</v>
+        <v>1283</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1171</v>
@@ -5844,7 +5853,7 @@
         <v>1197</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1307</v>
+        <v>1282</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1173</v>
@@ -5855,7 +5864,7 @@
         <v>1174</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1321</v>
+        <v>1296</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>1175</v>
@@ -5866,7 +5875,7 @@
         <v>1176</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1309</v>
+        <v>1284</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1177</v>
@@ -5877,7 +5886,7 @@
         <v>1178</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1310</v>
+        <v>1285</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>1179</v>
@@ -5888,7 +5897,7 @@
         <v>1180</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1311</v>
+        <v>1286</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1181</v>
@@ -5899,7 +5908,7 @@
         <v>1182</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1312</v>
+        <v>1287</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1183</v>
@@ -5910,7 +5919,7 @@
         <v>1184</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1313</v>
+        <v>1288</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1185</v>
@@ -5921,7 +5930,7 @@
         <v>1186</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1314</v>
+        <v>1289</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1187</v>
@@ -5932,7 +5941,7 @@
         <v>1188</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1315</v>
+        <v>1290</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>680</v>
@@ -5943,7 +5952,7 @@
         <v>1189</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1316</v>
+        <v>1291</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1190</v>
@@ -5954,7 +5963,7 @@
         <v>1191</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1317</v>
+        <v>1292</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1192</v>
@@ -5965,7 +5974,7 @@
         <v>1193</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1318</v>
+        <v>1293</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1194</v>
@@ -5976,7 +5985,7 @@
         <v>1195</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1319</v>
+        <v>1294</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1196</v>
@@ -6014,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1347</v>
+        <v>1322</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1348</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6025,10 +6034,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1349</v>
+        <v>1324</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1350</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6036,10 +6045,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1351</v>
+        <v>1326</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1352</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6047,10 +6056,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1354</v>
+        <v>1329</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1353</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6058,7 +6067,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1355</v>
+        <v>1330</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -6069,7 +6078,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1333</v>
+        <v>1308</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -6080,7 +6089,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1334</v>
+        <v>1309</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
@@ -6091,10 +6100,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1356</v>
+        <v>1331</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1357</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6102,10 +6111,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1358</v>
+        <v>1333</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1336</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6113,10 +6122,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1359</v>
+        <v>1334</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1360</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6124,10 +6133,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1361</v>
+        <v>1336</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1337</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6135,10 +6144,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1362</v>
+        <v>1337</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1363</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6146,10 +6155,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1339</v>
+        <v>1314</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1338</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6157,10 +6166,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1343</v>
+        <v>1318</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1340</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6168,10 +6177,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1342</v>
+        <v>1317</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1341</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6225,7 +6234,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="s">
-        <v>1322</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7262,7 +7271,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
@@ -7282,46 +7291,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>1324</v>
+        <v>1299</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1326</v>
+        <v>1301</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1325</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1327</v>
+        <v>1302</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1329</v>
+        <v>1304</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1328</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1330</v>
+        <v>1305</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1331</v>
+        <v>1306</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1332</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1344</v>
+        <v>1319</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1346</v>
+        <v>1321</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1345</v>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1340</v>
       </c>
     </row>
   </sheetData>
@@ -7653,7 +7673,7 @@
         <v>373</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1335</v>
+        <v>1310</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>374</v>
@@ -9887,7 +9907,7 @@
         <v>920</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1320</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9906,7 +9926,7 @@
         <v>924</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1323</v>
+        <v>1298</v>
       </c>
     </row>
   </sheetData>
@@ -10180,7 +10200,7 @@
         <v>973</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1257</v>
+        <v>1232</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>974</v>
@@ -10191,7 +10211,7 @@
         <v>975</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1256</v>
+        <v>1231</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>976</v>
@@ -10202,7 +10222,7 @@
         <v>977</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1258</v>
+        <v>1233</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>978</v>
@@ -10213,7 +10233,7 @@
         <v>979</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1259</v>
+        <v>1234</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>980</v>
@@ -10224,7 +10244,7 @@
         <v>981</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1260</v>
+        <v>1235</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>982</v>
@@ -10235,7 +10255,7 @@
         <v>983</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1261</v>
+        <v>1236</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>984</v>
@@ -10246,7 +10266,7 @@
         <v>985</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1262</v>
+        <v>1237</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>986</v>
@@ -10257,7 +10277,7 @@
         <v>987</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1263</v>
+        <v>1238</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>988</v>
@@ -10268,7 +10288,7 @@
         <v>989</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1264</v>
+        <v>1239</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>990</v>
@@ -10279,7 +10299,7 @@
         <v>991</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>992</v>
@@ -10290,7 +10310,7 @@
         <v>993</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1266</v>
+        <v>1241</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>994</v>
@@ -10301,7 +10321,7 @@
         <v>995</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1267</v>
+        <v>1242</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>996</v>
@@ -10312,7 +10332,7 @@
         <v>997</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1268</v>
+        <v>1243</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>998</v>
@@ -10323,7 +10343,7 @@
         <v>999</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1269</v>
+        <v>1244</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>1000</v>
@@ -10334,7 +10354,7 @@
         <v>1001</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1270</v>
+        <v>1245</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>1002</v>
@@ -10345,7 +10365,7 @@
         <v>1003</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1271</v>
+        <v>1246</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>1004</v>
@@ -10356,7 +10376,7 @@
         <v>1005</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1272</v>
+        <v>1247</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>1006</v>
@@ -10367,7 +10387,7 @@
         <v>1007</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1273</v>
+        <v>1248</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>1008</v>
@@ -10378,7 +10398,7 @@
         <v>1009</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>1010</v>
@@ -10389,7 +10409,7 @@
         <v>1011</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1274</v>
+        <v>1249</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>1012</v>
@@ -10400,7 +10420,7 @@
         <v>1013</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1276</v>
+        <v>1251</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>1014</v>
@@ -10411,7 +10431,7 @@
         <v>1015</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1277</v>
+        <v>1252</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>1016</v>
@@ -10422,7 +10442,7 @@
         <v>1017</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1278</v>
+        <v>1253</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>1018</v>
@@ -10433,7 +10453,7 @@
         <v>1019</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1279</v>
+        <v>1254</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>1020</v>
@@ -10444,7 +10464,7 @@
         <v>1021</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1280</v>
+        <v>1255</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>1022</v>
@@ -10455,7 +10475,7 @@
         <v>1023</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1281</v>
+        <v>1256</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>1024</v>
@@ -10463,277 +10483,277 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>1206</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1208</v>
+        <v>1343</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1285</v>
+        <v>1260</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1210</v>
+        <v>1344</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1286</v>
+        <v>1261</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>1233</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1211</v>
+        <v>1345</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1282</v>
+        <v>1257</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1243</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1212</v>
+        <v>1346</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1244</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1213</v>
+        <v>1347</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1287</v>
+        <v>1262</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1245</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1214</v>
+        <v>1348</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1288</v>
+        <v>1263</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1246</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1215</v>
+        <v>1349</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1290</v>
+        <v>1265</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1247</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1216</v>
+        <v>1350</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1289</v>
+        <v>1264</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1248</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1217</v>
+        <v>1351</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1291</v>
+        <v>1266</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1249</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1218</v>
+        <v>1352</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1292</v>
+        <v>1267</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1250</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1219</v>
+        <v>1353</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1293</v>
+        <v>1268</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1251</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1220</v>
+        <v>1354</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>1294</v>
+        <v>1269</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1252</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1221</v>
+        <v>1355</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>1295</v>
+        <v>1270</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1253</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1222</v>
+        <v>1356</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>1296</v>
+        <v>1271</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1254</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1223</v>
+        <v>1357</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1297</v>
+        <v>1272</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1255</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1224</v>
+        <v>1358</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>1298</v>
+        <v>1273</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1236</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1225</v>
+        <v>1359</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>1299</v>
+        <v>1274</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1237</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1226</v>
+        <v>1360</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1238</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1227</v>
+        <v>1361</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1301</v>
+        <v>1276</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1240</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1228</v>
+        <v>1362</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1302</v>
+        <v>1277</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1239</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1229</v>
+        <v>1363</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1304</v>
+        <v>1279</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1241</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1230</v>
+        <v>1364</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1303</v>
+        <v>1278</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1242</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1231</v>
+        <v>1365</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1305</v>
+        <v>1280</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1235</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1232</v>
+        <v>1366</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1306</v>
+        <v>1281</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1234</v>
+        <v>1209</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -4464,8 +4464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C64"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5175,6 +5175,193 @@
       </c>
       <c r="C64" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HOTKEY_MENU</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Esc: Open menu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Esc：打开菜单</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HOTKEY_ENEMY_BOOK</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D: Enemy book (requires the item)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>D：怪物手册（需要持有道具）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HOTKEY_TELEPORT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>F: Floor teleporter (requires the item)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>F：楼层传送（需要持有道具）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HOTKEY_SAVE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S: Save game</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>S：存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HOTKEY_LOAD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>L: Load game</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L：读档</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HOTKEY_ITEM</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>I: Items</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>I：道具</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HOTKEY_EQUIP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>E: Equipment</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>E：装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HOTKEY_QUICK_SAVE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>[: Quick save</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[：快速存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HOTKEY_QUICK_LOAD</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>]: Quick load</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>]：快速读档</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HOTKEY_MAGIC_DOOR</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>N: Magic Door (requires at least one); confirm to use it ahead, cancel to close.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>N：随意门（至少持有一个）；确认对前方使用，取消关闭。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>HOTKEY_HELP</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>H: Hotkey help; cancel to close.</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>H：快捷键说明；取消关闭。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5998,7 +6185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -6341,8 +6528,10 @@
         <v>54</v>
       </c>
       <c r="B34" s="6"/>
-      <c r="C34" s="6" t="s">
-        <v>55</v>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>长话短说，这一次我也将为你提供随意门，先赠予你3个好了，按N键使用，没有忘记吧？</t>
+        </is>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7270,7 +7459,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -7326,11 +7515,15 @@
       <c r="A5" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1320</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Press H to view the hotkeys.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>按 H 键可以查询快捷键。</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:3">

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5577F4A3-C6EA-604F-B035-1081A46BBD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B24AEF-FC0F-8545-8E3C-44AED7D29FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="1367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="1346">
   <si>
     <t>ID</t>
   </si>
@@ -101,21 +101,12 @@
     <t>DC_NPC04_1</t>
   </si>
   <si>
-    <t>这不是公主殿下吗？\n您怎么在这里？塔内太危险了</t>
-  </si>
-  <si>
     <t>DC_NPC04_2</t>
   </si>
   <si>
-    <t>勇士先生已经不在了…\n我必须要用自己的力量来拯救我的国家</t>
-  </si>
-  <si>
     <t>DC_NPC04_3</t>
   </si>
   <si>
-    <t>唉，他的死确实太可惜了\n这是我打造的飞羽，和勇士曾经拥有的黄金飞羽相似，希望对你有帮助</t>
-  </si>
-  <si>
     <t>DC_NPC04_4</t>
   </si>
   <si>
@@ -125,9 +116,6 @@
     <t>DC_NPC05_1</t>
   </si>
   <si>
-    <t>公主殿下\n你佩戴的头饰具有魔力加持效果</t>
-  </si>
-  <si>
     <t>DC_NPC05_2</t>
   </si>
   <si>
@@ -200,9 +188,6 @@
     <t>DC_NPC09_3</t>
   </si>
   <si>
-    <t>长话短说，这一次我也将为你提供随意门，先赠予你3个好了，按T键使用，没有忘记吧？</t>
-  </si>
-  <si>
     <t>DC_NPC09_4</t>
   </si>
   <si>
@@ -1511,202 +1496,25 @@
     <t>可以将特定的墙变成黄门。</t>
   </si>
   <si>
-    <t>SKELETON_SODIER</t>
-  </si>
-  <si>
-    <t>Skeleton Soldier</t>
-  </si>
-  <si>
     <t>骷髅士兵</t>
   </si>
   <si>
-    <t>SKELETON_SODIER_DESC</t>
-  </si>
-  <si>
-    <t>The skeleton enemy.</t>
-  </si>
-  <si>
     <t>这是一个骷髅。</t>
   </si>
   <si>
-    <t>SLIME</t>
-  </si>
-  <si>
-    <t>Slime</t>
-  </si>
-  <si>
     <t>史莱姆</t>
   </si>
   <si>
-    <t>SLIME_DESC</t>
-  </si>
-  <si>
-    <t>This is a slime.</t>
-  </si>
-  <si>
     <t>这是一个史莱姆。</t>
   </si>
   <si>
-    <t>ROCK</t>
-  </si>
-  <si>
-    <t>Rock</t>
-  </si>
-  <si>
-    <t>石头人</t>
-  </si>
-  <si>
-    <t>ROCK_DESC</t>
-  </si>
-  <si>
-    <t>This is a rock.</t>
-  </si>
-  <si>
-    <t>这是一个石头人。</t>
-  </si>
-  <si>
-    <t>MAGE</t>
-  </si>
-  <si>
-    <t>Mage</t>
-  </si>
-  <si>
-    <t>魔法师</t>
-  </si>
-  <si>
-    <t>MAGE_DESC</t>
-  </si>
-  <si>
-    <t>This is a mage.</t>
-  </si>
-  <si>
-    <t>这是一个魔法师。</t>
-  </si>
-  <si>
-    <t>BAT</t>
-  </si>
-  <si>
-    <t>Bat</t>
-  </si>
-  <si>
     <t>大蝙蝠</t>
   </si>
   <si>
-    <t>BAT_DESC</t>
-  </si>
-  <si>
-    <t>This is a bat.</t>
-  </si>
-  <si>
     <t>这是一个大蝙蝠。</t>
   </si>
   <si>
-    <t>KNIGHT</t>
-  </si>
-  <si>
-    <t>Knight</t>
-  </si>
-  <si>
     <t>骑士</t>
-  </si>
-  <si>
-    <t>KNIGHT_DESC</t>
-  </si>
-  <si>
-    <t>This is a knight.</t>
-  </si>
-  <si>
-    <t>这是一位骑士。</t>
-  </si>
-  <si>
-    <t>WIZARD</t>
-  </si>
-  <si>
-    <t>Wizard</t>
-  </si>
-  <si>
-    <t>巫师</t>
-  </si>
-  <si>
-    <t>WIZARD_DESC</t>
-  </si>
-  <si>
-    <t>This is a wizard.</t>
-  </si>
-  <si>
-    <t>这是一个巫师。</t>
-  </si>
-  <si>
-    <t>WHITE_KING</t>
-  </si>
-  <si>
-    <t>White King</t>
-  </si>
-  <si>
-    <t>魔法警卫</t>
-  </si>
-  <si>
-    <t>WHITE_KING_DESC</t>
-  </si>
-  <si>
-    <t>This is a white king.</t>
-  </si>
-  <si>
-    <t>这是一个魔法警卫。</t>
-  </si>
-  <si>
-    <t>BIG_WIZARD</t>
-  </si>
-  <si>
-    <t>Big Wizard</t>
-  </si>
-  <si>
-    <t>大法师</t>
-  </si>
-  <si>
-    <t>BIG_WIZARD_DESC</t>
-  </si>
-  <si>
-    <t>This is a big wizard.</t>
-  </si>
-  <si>
-    <t>这是一个大法师。</t>
-  </si>
-  <si>
-    <t>GREATIRON</t>
-  </si>
-  <si>
-    <t>Great Iron</t>
-  </si>
-  <si>
-    <t>大铁块</t>
-  </si>
-  <si>
-    <t>GREATIRON_DESC</t>
-  </si>
-  <si>
-    <t>This is a great iron.</t>
-  </si>
-  <si>
-    <t>这是一个巨大铁块。</t>
-  </si>
-  <si>
-    <t>GHOST_SOLDIER</t>
-  </si>
-  <si>
-    <t>Ghost Soldier</t>
-  </si>
-  <si>
-    <t>鬼战士</t>
-  </si>
-  <si>
-    <t>GHOST_SOLDIER_DESC</t>
-  </si>
-  <si>
-    <t>This is a ghost soldier.</t>
-  </si>
-  <si>
-    <t>这是一个鬼战士。</t>
   </si>
   <si>
     <t>E00_SHILAIMU</t>
@@ -3931,10 +3739,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>在你的攻击大于怪物防御时，你的魔力可以加持武器，\n在会心一击时可以通过魔力加持伤害，你的魔力越高、敌人的防御数值越高，加持效果越明显\n不过在伤害已经足够高的情况下加持效果会相对弱一些</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>附带魔力的剑刃，用来增幅伤害，魔力越高，伤害越高，增幅效果越明显。</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4002,12 +3806,6 @@
     <t>TM_04</t>
   </si>
   <si>
-    <t>点击这里或者按L可以查询快捷键。</t>
-  </si>
-  <si>
-    <t>Clicking here or hot key L could help you know the hot keys.</t>
-  </si>
-  <si>
     <t xml:space="preserve">I have not done right by you. \nYou have suffered for my failings. \nRun, my daughter. \nAs far as possible. </t>
   </si>
   <si>
@@ -4141,6 +3939,144 @@
   </si>
   <si>
     <t>TMT3_025</t>
+  </si>
+  <si>
+    <t>HOTKEY_MENU</t>
+  </si>
+  <si>
+    <t>Esc: Open menu</t>
+  </si>
+  <si>
+    <t>Esc：打开菜单</t>
+  </si>
+  <si>
+    <t>HOTKEY_ENEMY_BOOK</t>
+  </si>
+  <si>
+    <t>D: Enemy book (requires the item)</t>
+  </si>
+  <si>
+    <t>D：怪物手册（需要持有道具）</t>
+  </si>
+  <si>
+    <t>HOTKEY_TELEPORT</t>
+  </si>
+  <si>
+    <t>F: Floor teleporter (requires the item)</t>
+  </si>
+  <si>
+    <t>F：楼层传送（需要持有道具）</t>
+  </si>
+  <si>
+    <t>HOTKEY_SAVE</t>
+  </si>
+  <si>
+    <t>S: Save game</t>
+  </si>
+  <si>
+    <t>S：存档</t>
+  </si>
+  <si>
+    <t>HOTKEY_LOAD</t>
+  </si>
+  <si>
+    <t>L: Load game</t>
+  </si>
+  <si>
+    <t>L：读档</t>
+  </si>
+  <si>
+    <t>HOTKEY_ITEM</t>
+  </si>
+  <si>
+    <t>I: Items</t>
+  </si>
+  <si>
+    <t>I：道具</t>
+  </si>
+  <si>
+    <t>HOTKEY_EQUIP</t>
+  </si>
+  <si>
+    <t>E: Equipment</t>
+  </si>
+  <si>
+    <t>E：装备</t>
+  </si>
+  <si>
+    <t>HOTKEY_QUICK_SAVE</t>
+  </si>
+  <si>
+    <t>[: Quick save</t>
+  </si>
+  <si>
+    <t>[：快速存档</t>
+  </si>
+  <si>
+    <t>HOTKEY_QUICK_LOAD</t>
+  </si>
+  <si>
+    <t>]: Quick load</t>
+  </si>
+  <si>
+    <t>]：快速读档</t>
+  </si>
+  <si>
+    <t>HOTKEY_MAGIC_DOOR</t>
+  </si>
+  <si>
+    <t>长话短说，这一次我也将为你提供随意门，先赠予你3个好了，按N键使用，没有忘记吧？</t>
+  </si>
+  <si>
+    <t>Press H to view the hotkeys.</t>
+  </si>
+  <si>
+    <t>按 H 键可以查询快捷键。</t>
+  </si>
+  <si>
+    <t>N：随意门</t>
+  </si>
+  <si>
+    <t>N: Magic Door</t>
+  </si>
+  <si>
+    <t>Mucus</t>
+  </si>
+  <si>
+    <t>In the battle, each attack from the enemy would bring {value} points of fatigue.</t>
+  </si>
+  <si>
+    <t>这不是公主殿下吗？\n您怎么在这里？\n塔内太危险了。</t>
+  </si>
+  <si>
+    <t>Ah, Your Royal Highness!\nCan it truly be you?\nIt is far too dangerous for you to be here.</t>
+  </si>
+  <si>
+    <t>唉，他的死确实太可惜了。\n这是我打造的飞羽，\n和勇士曾经拥有的黄金飞羽相似，\n希望对你有帮助。</t>
+  </si>
+  <si>
+    <t>勇者先生已经不在了…\n危难当头，我需要接过这重任。</t>
+  </si>
+  <si>
+    <t>The Bravant is gone.\nIn this hour of peril, I must shoulder this burden.</t>
+  </si>
+  <si>
+    <t>It is truly a great pity for his death.\nI crafted this feather with my own hands,\nmuch like the one he once wielded.\nI hope it will be of use to you.</t>
+  </si>
+  <si>
+    <t>Your Royal Highness!\nThe accessory you wear could enhance your power with your MAG.</t>
+  </si>
+  <si>
+    <t>公主殿下\n你佩戴的头饰具有魔力加持效果。</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>在你的攻击大于怪物防御时，\n你的魔力可以加持武器，\n在会心一击时可以通过魔力加持伤害，\n你的魔力越高、敌人的防御数值越高，\n加持效果越明显。</t>
+  </si>
+  <si>
+    <t>When you are able to wound your foe,\your MAG may empower your weapon.\nA critical strike shall then carry far greater force.\nThe greater your MAG,\nor the stronger your foe's DEF,\nthe more pronounced the resulting increase shall be.</t>
   </si>
 </sst>
 </file>
@@ -4464,8 +4400,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -4486,882 +4422,805 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B33" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B42" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C42" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C43" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B44" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C44" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B45" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B46" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B48" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C48" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B49" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C49" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B50" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B51" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B52" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C52" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C53" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C54" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="32" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="32" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="32" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="32" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="32" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="32" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B62" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C62" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C63" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B64" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C64" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>HOTKEY_MENU</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Esc: Open menu</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Esc：打开菜单</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>HOTKEY_ENEMY_BOOK</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>D: Enemy book (requires the item)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>D：怪物手册（需要持有道具）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>HOTKEY_TELEPORT</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>F: Floor teleporter (requires the item)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>F：楼层传送（需要持有道具）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>HOTKEY_SAVE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>S: Save game</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>S：存档</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>HOTKEY_LOAD</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>L: Load game</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>L：读档</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>HOTKEY_ITEM</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>I: Items</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>I：道具</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>HOTKEY_EQUIP</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>E: Equipment</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>E：装备</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>HOTKEY_QUICK_SAVE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>[: Quick save</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>[：快速存档</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>HOTKEY_QUICK_LOAD</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>]: Quick load</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>]：快速读档</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>HOTKEY_MAGIC_DOOR</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>N: Magic Door (requires at least one); confirm to use it ahead, cancel to close.</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>N：随意门（至少持有一个）；确认对前方使用，取消关闭。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>HOTKEY_HELP</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>H: Hotkey help; cancel to close.</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>H：快捷键说明；取消关闭。</t>
-        </is>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1331</v>
       </c>
     </row>
   </sheetData>
@@ -5392,550 +5251,556 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1025</v>
+        <v>961</v>
       </c>
       <c r="B2" t="s">
-        <v>937</v>
+        <v>873</v>
       </c>
       <c r="C2" t="s">
-        <v>1026</v>
+        <v>962</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1027</v>
+        <v>963</v>
       </c>
       <c r="B3" t="s">
-        <v>1028</v>
+        <v>964</v>
       </c>
       <c r="C3" t="s">
-        <v>1029</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>1030</v>
+        <v>966</v>
       </c>
       <c r="B4" t="s">
-        <v>1031</v>
+        <v>967</v>
       </c>
       <c r="C4" t="s">
-        <v>941</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1032</v>
+        <v>968</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>1033</v>
+        <v>969</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1034</v>
+        <v>970</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>1035</v>
+        <v>971</v>
       </c>
       <c r="B6" t="s">
-        <v>1036</v>
+        <v>972</v>
       </c>
       <c r="C6" t="s">
-        <v>947</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>1037</v>
+        <v>973</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1038</v>
+        <v>974</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1039</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>1040</v>
+        <v>976</v>
       </c>
       <c r="B8" t="s">
-        <v>1041</v>
+        <v>977</v>
       </c>
       <c r="C8" t="s">
-        <v>1042</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>1043</v>
+        <v>979</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1044</v>
+        <v>980</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1045</v>
+        <v>981</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>1046</v>
+        <v>982</v>
       </c>
       <c r="B10" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C10" t="s">
-        <v>1047</v>
+        <v>983</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>1048</v>
+        <v>984</v>
       </c>
       <c r="B11" t="s">
-        <v>1049</v>
+        <v>985</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1050</v>
+        <v>986</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>1051</v>
+        <v>987</v>
       </c>
       <c r="B12" t="s">
-        <v>1052</v>
+        <v>988</v>
       </c>
       <c r="C12" t="s">
-        <v>1053</v>
+        <v>989</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>1054</v>
+        <v>990</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1055</v>
+        <v>991</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1056</v>
+        <v>992</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>1057</v>
+        <v>993</v>
       </c>
       <c r="B14" t="s">
-        <v>1058</v>
+        <v>994</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1059</v>
+        <v>995</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>1060</v>
+        <v>996</v>
       </c>
       <c r="B15" t="s">
-        <v>1061</v>
+        <v>997</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1062</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>1063</v>
+        <v>999</v>
       </c>
       <c r="B16" t="s">
-        <v>1064</v>
+        <v>1000</v>
       </c>
       <c r="C16" t="s">
-        <v>1065</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>1066</v>
+        <v>1002</v>
       </c>
       <c r="B17" t="s">
-        <v>1067</v>
+        <v>1003</v>
       </c>
       <c r="C17" t="s">
-        <v>1068</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>1069</v>
+        <v>1005</v>
       </c>
       <c r="B18" t="s">
-        <v>1070</v>
+        <v>1006</v>
       </c>
       <c r="C18" t="s">
-        <v>1071</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>1072</v>
+        <v>1008</v>
       </c>
       <c r="B19" t="s">
-        <v>1073</v>
+        <v>1009</v>
       </c>
       <c r="C19" t="s">
-        <v>1074</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>1075</v>
+        <v>1011</v>
       </c>
       <c r="B20" t="s">
-        <v>1076</v>
+        <v>1012</v>
       </c>
       <c r="C20" t="s">
-        <v>1077</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>1078</v>
+        <v>1014</v>
       </c>
       <c r="B21" t="s">
-        <v>1079</v>
+        <v>1015</v>
       </c>
       <c r="C21" t="s">
-        <v>1080</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>1081</v>
+        <v>1017</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1082</v>
+        <v>1018</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1083</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>1084</v>
+        <v>1020</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1085</v>
+        <v>1021</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1086</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>1087</v>
+        <v>1023</v>
       </c>
       <c r="B24" t="s">
-        <v>1088</v>
+        <v>1024</v>
       </c>
       <c r="C24" t="s">
-        <v>1089</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>1090</v>
+        <v>1026</v>
       </c>
       <c r="B25" t="s">
-        <v>1091</v>
+        <v>1027</v>
       </c>
       <c r="C25" t="s">
-        <v>1092</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>1093</v>
+        <v>1029</v>
       </c>
       <c r="B26" t="s">
-        <v>1094</v>
+        <v>1030</v>
       </c>
       <c r="C26" t="s">
-        <v>1095</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>1096</v>
+        <v>1032</v>
       </c>
       <c r="B27" t="s">
-        <v>1097</v>
+        <v>1033</v>
       </c>
       <c r="C27" t="s">
-        <v>1098</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1099</v>
+        <v>1035</v>
       </c>
       <c r="B28" t="s">
-        <v>1100</v>
+        <v>1036</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1101</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1102</v>
+        <v>1038</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1103</v>
+        <v>1039</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1104</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>1105</v>
+        <v>1041</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1333</v>
       </c>
       <c r="C30" t="s">
-        <v>1106</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>1107</v>
+        <v>1043</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1334</v>
       </c>
       <c r="C31" t="s">
-        <v>1108</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1109</v>
+        <v>1045</v>
       </c>
       <c r="C32" t="s">
-        <v>1110</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1111</v>
+        <v>1047</v>
       </c>
       <c r="C33" t="s">
-        <v>1112</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1113</v>
+        <v>1049</v>
       </c>
       <c r="C34" t="s">
-        <v>1114</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1115</v>
+        <v>1051</v>
       </c>
       <c r="C35" t="s">
-        <v>1116</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1117</v>
+        <v>1053</v>
       </c>
       <c r="C36" t="s">
-        <v>1118</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1119</v>
+        <v>1055</v>
       </c>
       <c r="C37" t="s">
-        <v>1120</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1121</v>
+        <v>1057</v>
       </c>
       <c r="C38" t="s">
-        <v>1122</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1123</v>
+        <v>1059</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1124</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1125</v>
+        <v>1061</v>
       </c>
       <c r="C40" t="s">
-        <v>1126</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1127</v>
+        <v>1063</v>
       </c>
       <c r="C41" t="s">
-        <v>1128</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1129</v>
+        <v>1065</v>
       </c>
       <c r="C42" t="s">
-        <v>1130</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1131</v>
+        <v>1067</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>1132</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1133</v>
+        <v>1069</v>
       </c>
       <c r="C44" t="s">
-        <v>1134</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1135</v>
+        <v>1071</v>
       </c>
       <c r="C45" t="s">
-        <v>1136</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1137</v>
+        <v>1073</v>
       </c>
       <c r="C46" t="s">
-        <v>1138</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1139</v>
+        <v>1075</v>
       </c>
       <c r="C47" t="s">
-        <v>1140</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1141</v>
+        <v>1077</v>
       </c>
       <c r="C48" t="s">
-        <v>1142</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1143</v>
+        <v>1079</v>
       </c>
       <c r="C49" t="s">
-        <v>1144</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1145</v>
+        <v>1081</v>
       </c>
       <c r="C50" t="s">
-        <v>1146</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1147</v>
+        <v>1083</v>
       </c>
       <c r="C51" t="s">
-        <v>1148</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>1149</v>
+        <v>1085</v>
       </c>
       <c r="C52" t="s">
-        <v>1150</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1151</v>
+        <v>1087</v>
       </c>
       <c r="C53" t="s">
-        <v>1152</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1153</v>
+        <v>1089</v>
       </c>
       <c r="C54" t="s">
-        <v>1154</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1155</v>
+        <v>1091</v>
       </c>
       <c r="C55" t="s">
-        <v>1156</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1157</v>
+        <v>1093</v>
       </c>
       <c r="C56" t="s">
-        <v>1158</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>1159</v>
+        <v>1095</v>
       </c>
       <c r="C57" t="s">
-        <v>1160</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1161</v>
+        <v>1097</v>
       </c>
       <c r="C58" t="s">
-        <v>1162</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>1163</v>
+        <v>1099</v>
       </c>
       <c r="C59" t="s">
-        <v>1164</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -5966,24 +5831,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1165</v>
+        <v>1101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1282</v>
+        <v>1218</v>
       </c>
       <c r="C2" t="s">
-        <v>1166</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1167</v>
+        <v>1103</v>
       </c>
       <c r="B3" t="s">
-        <v>1168</v>
+        <v>1104</v>
       </c>
       <c r="C3" t="s">
-        <v>1169</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -6015,167 +5880,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>1170</v>
+        <v>1106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1283</v>
+        <v>1219</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1171</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>1172</v>
+        <v>1108</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>932</v>
+        <v>868</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>933</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>1197</v>
+        <v>1133</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1282</v>
+        <v>1218</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1173</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>1174</v>
+        <v>1110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1296</v>
+        <v>1232</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1175</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>1176</v>
+        <v>1112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1284</v>
+        <v>1220</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1177</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>1178</v>
+        <v>1114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1285</v>
+        <v>1221</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1179</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>1180</v>
+        <v>1116</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1286</v>
+        <v>1222</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1181</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>1182</v>
+        <v>1118</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1287</v>
+        <v>1223</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1183</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>1184</v>
+        <v>1120</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1288</v>
+        <v>1224</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1185</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>1186</v>
+        <v>1122</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1289</v>
+        <v>1225</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1187</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>1188</v>
+        <v>1124</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1290</v>
+        <v>1226</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>680</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>1189</v>
+        <v>1125</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1291</v>
+        <v>1227</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1190</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>1191</v>
+        <v>1127</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1292</v>
+        <v>1228</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1192</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>1193</v>
+        <v>1129</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1293</v>
+        <v>1229</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1194</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>1195</v>
+        <v>1131</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1294</v>
+        <v>1230</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1196</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -6185,7 +6050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
@@ -6210,10 +6075,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1322</v>
+        <v>1255</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1323</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6221,10 +6086,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1324</v>
+        <v>1257</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1325</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6232,10 +6097,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1326</v>
+        <v>1259</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1327</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6243,10 +6108,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1329</v>
+        <v>1262</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1328</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6254,7 +6119,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1330</v>
+        <v>1263</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -6265,7 +6130,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1308</v>
+        <v>1243</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -6276,7 +6141,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1309</v>
+        <v>1244</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
@@ -6287,10 +6152,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1331</v>
+        <v>1264</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1332</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6298,10 +6163,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1333</v>
+        <v>1266</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1311</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6309,10 +6174,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1334</v>
+        <v>1267</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1335</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6320,10 +6185,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1336</v>
+        <v>1269</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1312</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6331,10 +6196,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1337</v>
+        <v>1270</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1338</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6342,10 +6207,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1314</v>
+        <v>1249</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1313</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6353,10 +6218,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1318</v>
+        <v>1253</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1315</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6364,516 +6229,526 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1317</v>
+        <v>1252</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1316</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
-        <v>22</v>
+      <c r="B17" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1335</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1249</v>
+      </c>
       <c r="C20" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1341</v>
+      </c>
       <c r="C21" s="8" t="s">
-        <v>30</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1345</v>
+      </c>
       <c r="C22" s="8" t="s">
-        <v>1297</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B34" s="6"/>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>长话短说，这一次我也将为你提供随意门，先赠予你3个好了，按N键使用，没有忘记吧？</t>
-        </is>
+      <c r="C34" s="6" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="8" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="8" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
-        <v>1198</v>
+        <v>1134</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="s">
-        <v>1199</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
-        <v>1200</v>
+        <v>1136</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="s">
-        <v>1201</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="8" t="s">
-        <v>1202</v>
+        <v>1138</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="s">
-        <v>1203</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="8" t="s">
-        <v>1204</v>
+        <v>1140</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="s">
-        <v>1205</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7459,7 +7334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -7480,61 +7355,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>1299</v>
+        <v>1234</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1301</v>
+        <v>1236</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1300</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1302</v>
+        <v>1237</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1304</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1303</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1305</v>
+        <v>1240</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1306</v>
+        <v>1241</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1307</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Press H to view the hotkeys.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>按 H 键可以查询快捷键。</t>
-        </is>
+        <v>1254</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1330</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>1339</v>
+        <v>1272</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1341</v>
+        <v>1274</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1340</v>
+        <v>1273</v>
       </c>
     </row>
   </sheetData>
@@ -7564,10 +7435,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7575,10 +7446,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -7605,167 +7476,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>326</v>
+      <c r="A7" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1343</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C13" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C14" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C15" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -7797,508 +7668,508 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B7" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C7" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1310</v>
+        <v>1245</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C12" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C14" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B15" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C15" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B16" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C16" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B17" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C17" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B18" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C18" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B19" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C19" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B20" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C20" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B21" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C21" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B22" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C22" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B23" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C23" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B24" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C24" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B25" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C25" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C26" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B27" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C27" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B28" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C28" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B29" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C29" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B30" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C30" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B31" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C31" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B32" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C32" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B33" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C33" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B34" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C34" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B35" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C35" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B36" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C36" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B37" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C37" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B38" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C38" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B39" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C39" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B40" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C40" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B41" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C41" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B42" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C42" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B43" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C43" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B44" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B45" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C45" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B46" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C46" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B47" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C47" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -8309,7 +8180,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
@@ -8330,1732 +8201,1490 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>495</v>
       </c>
-      <c r="B3" t="s">
-        <v>496</v>
-      </c>
       <c r="C3" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>498</v>
-      </c>
-      <c r="B4" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>501</v>
-      </c>
-      <c r="B5" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C5" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>504</v>
-      </c>
-      <c r="B6" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B7" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C7" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>510</v>
-      </c>
-      <c r="B8" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C8" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>513</v>
-      </c>
-      <c r="B9" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C9" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>516</v>
-      </c>
-      <c r="B10" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C10" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>519</v>
-      </c>
-      <c r="B11" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C11" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>522</v>
-      </c>
-      <c r="B12" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="C12" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>525</v>
-      </c>
-      <c r="B13" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C13" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>530</v>
+      <c r="A14" t="s">
+        <v>516</v>
+      </c>
+      <c r="C14" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>533</v>
+      <c r="A15" t="s">
+        <v>518</v>
+      </c>
+      <c r="C15" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>536</v>
+      <c r="A16" t="s">
+        <v>519</v>
+      </c>
+      <c r="C16" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>539</v>
+      <c r="A17" t="s">
+        <v>521</v>
+      </c>
+      <c r="C17" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>540</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>542</v>
+        <v>523</v>
+      </c>
+      <c r="C18" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>545</v>
+      <c r="A19" t="s">
+        <v>525</v>
+      </c>
+      <c r="C19" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>546</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>548</v>
+        <v>527</v>
+      </c>
+      <c r="C20" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>551</v>
+      <c r="A21" t="s">
+        <v>529</v>
+      </c>
+      <c r="C21" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>554</v>
+      <c r="A22" t="s">
+        <v>531</v>
+      </c>
+      <c r="C22" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>557</v>
+      <c r="A23" t="s">
+        <v>532</v>
+      </c>
+      <c r="C23" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="C24" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="C25" t="s">
-        <v>503</v>
+        <v>536</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>560</v>
+        <v>537</v>
       </c>
       <c r="C26" t="s">
-        <v>561</v>
+        <v>493</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="C27" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="C28" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="C29" t="s">
-        <v>567</v>
+        <v>543</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="C30" t="s">
-        <v>569</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>570</v>
+        <v>545</v>
       </c>
       <c r="C31" t="s">
-        <v>571</v>
+        <v>546</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="C32" t="s">
-        <v>573</v>
+        <v>548</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="C33" t="s">
-        <v>575</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="C34" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
       <c r="C35" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="C36" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="C37" t="s">
-        <v>497</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C38" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="C39" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C40" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="C41" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="C42" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="C43" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="C44" t="s">
-        <v>518</v>
+        <v>572</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="C45" t="s">
-        <v>521</v>
+        <v>574</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="C46" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="C47" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="C48" t="s">
-        <v>524</v>
+        <v>580</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="C49" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="C50" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="C51" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="C52" t="s">
-        <v>494</v>
+        <v>588</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C53" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="C54" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="C55" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="C56" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="C57" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="C58" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="C59" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="C60" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="C61" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="C62" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="C63" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="C64" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="C65" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="C66" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
       <c r="C67" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>639</v>
+        <v>619</v>
       </c>
       <c r="C68" t="s">
-        <v>640</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="C69" t="s">
-        <v>642</v>
+        <v>490</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>643</v>
+        <v>621</v>
       </c>
       <c r="C70" t="s">
-        <v>644</v>
+        <v>622</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="C71" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>647</v>
+        <v>625</v>
       </c>
       <c r="C72" t="s">
-        <v>648</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="C73" t="s">
-        <v>650</v>
+        <v>503</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C74" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="C75" t="s">
-        <v>654</v>
+        <v>630</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>655</v>
+        <v>631</v>
       </c>
       <c r="C76" t="s">
-        <v>656</v>
+        <v>632</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>657</v>
+        <v>633</v>
       </c>
       <c r="C77" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="C78" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="C79" t="s">
-        <v>662</v>
+        <v>638</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="C80" t="s">
-        <v>664</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>665</v>
+        <v>641</v>
       </c>
       <c r="C81" t="s">
-        <v>666</v>
+        <v>642</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="C82" t="s">
-        <v>668</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="C83" t="s">
-        <v>670</v>
+        <v>488</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="C84" t="s">
-        <v>672</v>
+        <v>646</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>673</v>
+        <v>647</v>
       </c>
       <c r="C85" t="s">
-        <v>674</v>
+        <v>648</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="C86" t="s">
-        <v>676</v>
+        <v>650</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>677</v>
+        <v>651</v>
       </c>
       <c r="C87" t="s">
-        <v>678</v>
+        <v>652</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>679</v>
+        <v>653</v>
       </c>
       <c r="C88" t="s">
-        <v>680</v>
+        <v>654</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="C89" t="s">
-        <v>682</v>
+        <v>656</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="C90" t="s">
-        <v>500</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="C91" t="s">
-        <v>503</v>
+        <v>660</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="C92" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="C93" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="C94" t="s">
-        <v>565</v>
+        <v>666</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="C95" t="s">
-        <v>567</v>
+        <v>668</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>691</v>
+        <v>669</v>
       </c>
       <c r="C96" t="s">
-        <v>692</v>
+        <v>670</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="C97" t="s">
-        <v>694</v>
+        <v>672</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>695</v>
+        <v>673</v>
       </c>
       <c r="C98" t="s">
-        <v>696</v>
+        <v>674</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="C99" t="s">
-        <v>698</v>
+        <v>676</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="C100" t="s">
-        <v>700</v>
+        <v>678</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="C101" t="s">
-        <v>702</v>
+        <v>680</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>703</v>
+        <v>681</v>
       </c>
       <c r="C102" t="s">
-        <v>704</v>
+        <v>682</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="C103" t="s">
-        <v>706</v>
+        <v>684</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>707</v>
+        <v>685</v>
       </c>
       <c r="C104" t="s">
-        <v>581</v>
+        <v>686</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C105" t="s">
-        <v>497</v>
+        <v>688</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="C106" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="C107" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="C108" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>715</v>
+        <v>695</v>
       </c>
       <c r="C109" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="C110" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="C111" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="C112" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="C113" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="C114" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="C115" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="C116" t="s">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="C117" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="C118" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="C119" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="C120" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="C121" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="C122" t="s">
-        <v>742</v>
+        <v>722</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="C123" t="s">
-        <v>744</v>
+        <v>724</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>745</v>
+        <v>725</v>
       </c>
       <c r="C124" t="s">
-        <v>746</v>
+        <v>726</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="C125" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="C126" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="C127" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="C128" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="C129" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="C130" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
       <c r="C131" t="s">
-        <v>760</v>
+        <v>740</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
       <c r="C132" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="C133" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="C134" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="C135" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="C136" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="C137" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="C138" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="C139" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="C140" t="s">
-        <v>778</v>
+        <v>758</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>779</v>
+        <v>759</v>
       </c>
       <c r="C141" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="C142" t="s">
-        <v>782</v>
+        <v>762</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="C143" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="C144" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="C145" t="s">
-        <v>788</v>
+        <v>768</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="C146" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="C147" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="C148" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="C149" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="C150" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="C151" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="C152" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="C153" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
       <c r="C154" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
       <c r="C155" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="C156" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="C157" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
       <c r="C158" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="C159" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="C160" t="s">
-        <v>818</v>
+        <v>798</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>819</v>
+        <v>799</v>
       </c>
       <c r="C161" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="C162" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="C163" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="C164" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="C165" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="C166" t="s">
-        <v>830</v>
+        <v>810</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>831</v>
+        <v>811</v>
       </c>
       <c r="C167" t="s">
-        <v>832</v>
+        <v>812</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="C168" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
       <c r="C169" t="s">
-        <v>836</v>
+        <v>816</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>837</v>
+        <v>817</v>
       </c>
       <c r="C170" t="s">
-        <v>838</v>
+        <v>818</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>839</v>
+        <v>819</v>
       </c>
       <c r="C171" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="C172" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>843</v>
+        <v>823</v>
       </c>
       <c r="C173" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="C174" t="s">
-        <v>846</v>
+        <v>826</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="C175" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="C176" t="s">
-        <v>850</v>
+        <v>830</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>851</v>
+        <v>831</v>
       </c>
       <c r="C177" t="s">
-        <v>852</v>
+        <v>832</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
       <c r="C178" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
       <c r="C179" t="s">
-        <v>856</v>
+        <v>836</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>857</v>
+        <v>837</v>
       </c>
       <c r="C180" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
       <c r="C181" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="C182" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="C183" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="C184" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>867</v>
+        <v>847</v>
       </c>
       <c r="C185" t="s">
-        <v>868</v>
+        <v>848</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="C186" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="C187" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3">
-      <c r="A188" t="s">
-        <v>873</v>
-      </c>
-      <c r="C188" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
-      <c r="A189" t="s">
-        <v>875</v>
-      </c>
-      <c r="C189" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" t="s">
-        <v>877</v>
-      </c>
-      <c r="C190" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" t="s">
-        <v>879</v>
-      </c>
-      <c r="C191" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" t="s">
-        <v>881</v>
-      </c>
-      <c r="C192" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
-        <v>883</v>
-      </c>
-      <c r="C193" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" t="s">
-        <v>885</v>
-      </c>
-      <c r="C194" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" t="s">
-        <v>887</v>
-      </c>
-      <c r="C195" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" t="s">
-        <v>889</v>
-      </c>
-      <c r="C196" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" t="s">
-        <v>891</v>
-      </c>
-      <c r="C197" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" t="s">
-        <v>893</v>
-      </c>
-      <c r="C198" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" t="s">
-        <v>895</v>
-      </c>
-      <c r="C199" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" t="s">
-        <v>897</v>
-      </c>
-      <c r="C200" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" t="s">
-        <v>899</v>
-      </c>
-      <c r="C201" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" t="s">
-        <v>901</v>
-      </c>
-      <c r="C202" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" t="s">
-        <v>903</v>
-      </c>
-      <c r="C203" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" t="s">
-        <v>905</v>
-      </c>
-      <c r="C204" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" t="s">
-        <v>907</v>
-      </c>
-      <c r="C205" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" t="s">
-        <v>909</v>
-      </c>
-      <c r="C206" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" t="s">
-        <v>911</v>
-      </c>
-      <c r="C207" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" t="s">
-        <v>913</v>
-      </c>
-      <c r="C208" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
-      <c r="A209" t="s">
-        <v>915</v>
-      </c>
-      <c r="C209" t="s">
-        <v>916</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -10086,40 +9715,40 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>917</v>
+        <v>853</v>
       </c>
       <c r="B2" t="s">
-        <v>918</v>
+        <v>854</v>
       </c>
       <c r="C2" t="s">
-        <v>919</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>920</v>
+        <v>856</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1295</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>921</v>
+        <v>857</v>
       </c>
       <c r="B4" t="s">
-        <v>922</v>
+        <v>858</v>
       </c>
       <c r="C4" t="s">
-        <v>923</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>924</v>
+        <v>860</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1298</v>
+        <v>1233</v>
       </c>
     </row>
   </sheetData>
@@ -10150,46 +9779,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>925</v>
+        <v>861</v>
       </c>
       <c r="B2" t="s">
-        <v>926</v>
+        <v>862</v>
       </c>
       <c r="C2" t="s">
-        <v>927</v>
+        <v>863</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>928</v>
+        <v>864</v>
       </c>
       <c r="B3" t="s">
-        <v>929</v>
+        <v>865</v>
       </c>
       <c r="C3" t="s">
-        <v>930</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>931</v>
+        <v>867</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>932</v>
+        <v>868</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>933</v>
+        <v>869</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>934</v>
+        <v>870</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>935</v>
+        <v>871</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>935</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -10220,57 +9849,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>936</v>
+        <v>872</v>
       </c>
       <c r="B2" t="s">
-        <v>937</v>
+        <v>873</v>
       </c>
       <c r="C2" t="s">
-        <v>938</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>939</v>
+        <v>875</v>
       </c>
       <c r="B3" t="s">
-        <v>940</v>
+        <v>876</v>
       </c>
       <c r="C3" t="s">
-        <v>941</v>
+        <v>877</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>942</v>
+        <v>878</v>
       </c>
       <c r="B4" t="s">
-        <v>943</v>
+        <v>879</v>
       </c>
       <c r="C4" t="s">
-        <v>944</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>945</v>
+        <v>881</v>
       </c>
       <c r="B5" t="s">
-        <v>946</v>
+        <v>882</v>
       </c>
       <c r="C5" t="s">
-        <v>947</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>948</v>
+        <v>884</v>
       </c>
       <c r="B6" t="s">
-        <v>949</v>
+        <v>885</v>
       </c>
       <c r="C6" t="s">
-        <v>950</v>
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -10302,651 +9931,651 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>951</v>
+        <v>887</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>952</v>
+        <v>888</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>953</v>
+        <v>889</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>954</v>
+        <v>890</v>
       </c>
       <c r="B3" t="s">
-        <v>955</v>
+        <v>891</v>
       </c>
       <c r="C3" t="s">
-        <v>956</v>
+        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>957</v>
+        <v>893</v>
       </c>
       <c r="B4" t="s">
-        <v>958</v>
+        <v>894</v>
       </c>
       <c r="C4" t="s">
-        <v>959</v>
+        <v>895</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>960</v>
+        <v>896</v>
       </c>
       <c r="B5" t="s">
-        <v>961</v>
+        <v>897</v>
       </c>
       <c r="C5" t="s">
-        <v>962</v>
+        <v>898</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>963</v>
+        <v>899</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>964</v>
+        <v>900</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>965</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>966</v>
+        <v>902</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>968</v>
+        <v>904</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>969</v>
+        <v>905</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>970</v>
+        <v>906</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>971</v>
+        <v>907</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>972</v>
+        <v>908</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>968</v>
+        <v>904</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>973</v>
+        <v>909</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1232</v>
+        <v>1168</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>974</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="8" t="s">
-        <v>975</v>
+        <v>911</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1231</v>
+        <v>1167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>976</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="8" t="s">
-        <v>977</v>
+        <v>913</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1233</v>
+        <v>1169</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>978</v>
+        <v>914</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
-        <v>979</v>
+        <v>915</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1234</v>
+        <v>1170</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>980</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>981</v>
+        <v>917</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1235</v>
+        <v>1171</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>982</v>
+        <v>918</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
-        <v>983</v>
+        <v>919</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1236</v>
+        <v>1172</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>984</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
-        <v>985</v>
+        <v>921</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1237</v>
+        <v>1173</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>986</v>
+        <v>922</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>987</v>
+        <v>923</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1238</v>
+        <v>1174</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>988</v>
+        <v>924</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="8" t="s">
-        <v>989</v>
+        <v>925</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1239</v>
+        <v>1175</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>990</v>
+        <v>926</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>991</v>
+        <v>927</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1240</v>
+        <v>1176</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>992</v>
+        <v>928</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>993</v>
+        <v>929</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1241</v>
+        <v>1177</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>994</v>
+        <v>930</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>995</v>
+        <v>931</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1242</v>
+        <v>1178</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>996</v>
+        <v>932</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>997</v>
+        <v>933</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1243</v>
+        <v>1179</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>998</v>
+        <v>934</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>999</v>
+        <v>935</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1244</v>
+        <v>1180</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1000</v>
+        <v>936</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="8" t="s">
-        <v>1001</v>
+        <v>937</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1245</v>
+        <v>1181</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1002</v>
+        <v>938</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="8" t="s">
-        <v>1003</v>
+        <v>939</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1246</v>
+        <v>1182</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1004</v>
+        <v>940</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="8" t="s">
-        <v>1005</v>
+        <v>941</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1247</v>
+        <v>1183</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1006</v>
+        <v>942</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="8" t="s">
-        <v>1007</v>
+        <v>943</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1248</v>
+        <v>1184</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1008</v>
+        <v>944</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="8" t="s">
-        <v>1009</v>
+        <v>945</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1250</v>
+        <v>1186</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1010</v>
+        <v>946</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
-        <v>1011</v>
+        <v>947</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1249</v>
+        <v>1185</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1012</v>
+        <v>948</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="8" t="s">
-        <v>1013</v>
+        <v>949</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1251</v>
+        <v>1187</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1014</v>
+        <v>950</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>1015</v>
+        <v>951</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1252</v>
+        <v>1188</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1016</v>
+        <v>952</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
-        <v>1017</v>
+        <v>953</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1253</v>
+        <v>1189</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1018</v>
+        <v>954</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>1019</v>
+        <v>955</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1254</v>
+        <v>1190</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1020</v>
+        <v>956</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="8" t="s">
-        <v>1021</v>
+        <v>957</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1255</v>
+        <v>1191</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1022</v>
+        <v>958</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="8" t="s">
-        <v>1023</v>
+        <v>959</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1256</v>
+        <v>1192</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1024</v>
+        <v>960</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>1342</v>
+        <v>1275</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>1259</v>
+        <v>1195</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>1206</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1343</v>
+        <v>1276</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1260</v>
+        <v>1196</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1207</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1344</v>
+        <v>1277</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1261</v>
+        <v>1197</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>1208</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1345</v>
+        <v>1278</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1257</v>
+        <v>1193</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1218</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1346</v>
+        <v>1279</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1258</v>
+        <v>1194</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1219</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1347</v>
+        <v>1280</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1262</v>
+        <v>1198</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1220</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1348</v>
+        <v>1281</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1263</v>
+        <v>1199</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1221</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1349</v>
+        <v>1282</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1265</v>
+        <v>1201</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1222</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1350</v>
+        <v>1283</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1264</v>
+        <v>1200</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1223</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1351</v>
+        <v>1284</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1266</v>
+        <v>1202</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1224</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1352</v>
+        <v>1285</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1267</v>
+        <v>1203</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1225</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1353</v>
+        <v>1286</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1268</v>
+        <v>1204</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1226</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1354</v>
+        <v>1287</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>1269</v>
+        <v>1205</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1227</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1355</v>
+        <v>1288</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>1270</v>
+        <v>1206</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1228</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1356</v>
+        <v>1289</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>1271</v>
+        <v>1207</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1229</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1357</v>
+        <v>1290</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1272</v>
+        <v>1208</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1230</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1358</v>
+        <v>1291</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>1273</v>
+        <v>1209</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1211</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1359</v>
+        <v>1292</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>1274</v>
+        <v>1210</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1212</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1360</v>
+        <v>1293</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1275</v>
+        <v>1211</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1213</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1361</v>
+        <v>1294</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1276</v>
+        <v>1212</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1215</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1362</v>
+        <v>1295</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1277</v>
+        <v>1213</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1214</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1363</v>
+        <v>1296</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1279</v>
+        <v>1215</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1216</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1364</v>
+        <v>1297</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1278</v>
+        <v>1214</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1217</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1365</v>
+        <v>1298</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1280</v>
+        <v>1216</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1366</v>
+        <v>1299</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1281</v>
+        <v>1217</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1209</v>
+        <v>1145</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengmingliu\LudorkProjects\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B24AEF-FC0F-8545-8E3C-44AED7D29FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3699206-B968-4AD5-BBE7-7DE1AC2E5C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1780" windowWidth="28800" windowHeight="15380" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="6250" windowWidth="28470" windowHeight="13870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="1349">
   <si>
     <t>ID</t>
   </si>
@@ -3953,21 +3953,9 @@
     <t>HOTKEY_ENEMY_BOOK</t>
   </si>
   <si>
-    <t>D: Enemy book (requires the item)</t>
-  </si>
-  <si>
-    <t>D：怪物手册（需要持有道具）</t>
-  </si>
-  <si>
     <t>HOTKEY_TELEPORT</t>
   </si>
   <si>
-    <t>F: Floor teleporter (requires the item)</t>
-  </si>
-  <si>
-    <t>F：楼层传送（需要持有道具）</t>
-  </si>
-  <si>
     <t>HOTKEY_SAVE</t>
   </si>
   <si>
@@ -4077,13 +4065,40 @@
   </si>
   <si>
     <t>When you are able to wound your foe,\your MAG may empower your weapon.\nA critical strike shall then carry far greater force.\nThe greater your MAG,\nor the stronger your foe's DEF,\nthe more pronounced the resulting increase shall be.</t>
+  </si>
+  <si>
+    <t>HOTKEY_SWITCH_PLAYER</t>
+  </si>
+  <si>
+    <t>D：怪物手册</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>F：楼层传送</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>D: Enemy book</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>F: Floor teleporter</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>U：切换角色</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>U: Switch party member</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4191,7 +4206,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4401,15 +4416,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4420,7 +4435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>119</v>
       </c>
@@ -4431,7 +4446,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -4442,7 +4457,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4453,7 +4468,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -4464,7 +4479,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
@@ -4475,7 +4490,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>134</v>
       </c>
@@ -4486,7 +4501,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -4497,7 +4512,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>140</v>
       </c>
@@ -4508,7 +4523,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -4519,7 +4534,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -4530,7 +4545,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -4541,7 +4556,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -4552,7 +4567,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>152</v>
       </c>
@@ -4563,7 +4578,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -4574,7 +4589,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -4585,7 +4600,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -4596,7 +4611,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -4607,7 +4622,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -4618,7 +4633,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -4629,7 +4644,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>172</v>
       </c>
@@ -4640,7 +4655,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>175</v>
       </c>
@@ -4651,7 +4666,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>178</v>
       </c>
@@ -4662,7 +4677,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>181</v>
       </c>
@@ -4673,7 +4688,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>184</v>
       </c>
@@ -4684,7 +4699,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>187</v>
       </c>
@@ -4695,7 +4710,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -4706,7 +4721,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>193</v>
       </c>
@@ -4717,7 +4732,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>196</v>
       </c>
@@ -4728,7 +4743,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>199</v>
       </c>
@@ -4739,7 +4754,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>202</v>
       </c>
@@ -4750,7 +4765,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -4761,7 +4776,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>208</v>
       </c>
@@ -4772,7 +4787,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>211</v>
       </c>
@@ -4783,7 +4798,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -4794,7 +4809,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>217</v>
       </c>
@@ -4805,7 +4820,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>220</v>
       </c>
@@ -4816,7 +4831,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>223</v>
       </c>
@@ -4827,7 +4842,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>226</v>
       </c>
@@ -4838,7 +4853,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>229</v>
       </c>
@@ -4849,7 +4864,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>232</v>
       </c>
@@ -4860,7 +4875,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>235</v>
       </c>
@@ -4871,7 +4886,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>238</v>
       </c>
@@ -4882,7 +4897,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>241</v>
       </c>
@@ -4893,7 +4908,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>244</v>
       </c>
@@ -4904,7 +4919,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>247</v>
       </c>
@@ -4915,7 +4930,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>250</v>
       </c>
@@ -4926,7 +4941,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>253</v>
       </c>
@@ -4937,7 +4952,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>256</v>
       </c>
@@ -4948,7 +4963,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>259</v>
       </c>
@@ -4959,7 +4974,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>262</v>
       </c>
@@ -4970,7 +4985,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>265</v>
       </c>
@@ -4981,7 +4996,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>268</v>
       </c>
@@ -4992,7 +5007,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>271</v>
       </c>
@@ -5003,7 +5018,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" customHeight="1">
+    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>274</v>
       </c>
@@ -5014,7 +5029,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="32" customHeight="1">
+    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>277</v>
       </c>
@@ -5025,7 +5040,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="32" customHeight="1">
+    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>280</v>
       </c>
@@ -5036,7 +5051,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="32" customHeight="1">
+    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>283</v>
       </c>
@@ -5047,7 +5062,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" customHeight="1">
+    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>286</v>
       </c>
@@ -5058,7 +5073,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="32" customHeight="1">
+    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>289</v>
       </c>
@@ -5069,7 +5084,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>292</v>
       </c>
@@ -5080,7 +5095,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>295</v>
       </c>
@@ -5091,7 +5106,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>298</v>
       </c>
@@ -5102,7 +5117,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>301</v>
       </c>
@@ -5113,7 +5128,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1300</v>
       </c>
@@ -5124,103 +5139,114 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1303</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="8" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>1304</v>
       </c>
-      <c r="C66" t="s">
+      <c r="B67" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>1305</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
+      <c r="B68" t="s">
         <v>1306</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C68" t="s">
         <v>1307</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>1308</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
+      <c r="B69" t="s">
         <v>1309</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C69" t="s">
         <v>1310</v>
       </c>
-      <c r="C68" t="s">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>1311</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
+      <c r="B70" t="s">
         <v>1312</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C70" t="s">
         <v>1313</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>1314</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
+      <c r="B71" t="s">
         <v>1315</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C71" t="s">
         <v>1316</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" t="s">
+      <c r="B72" t="s">
         <v>1318</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C72" t="s">
         <v>1319</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>1320</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
+      <c r="B73" t="s">
         <v>1321</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
         <v>1322</v>
       </c>
-      <c r="C72" t="s">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>1323</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
+      <c r="B74" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1331</v>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>1347</v>
       </c>
     </row>
   </sheetData>
@@ -5232,13 +5258,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5249,7 +5275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>961</v>
       </c>
@@ -5260,7 +5286,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>963</v>
       </c>
@@ -5271,7 +5297,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>966</v>
       </c>
@@ -5282,7 +5308,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>968</v>
       </c>
@@ -5293,7 +5319,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>971</v>
       </c>
@@ -5304,7 +5330,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>973</v>
       </c>
@@ -5315,7 +5341,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>976</v>
       </c>
@@ -5326,7 +5352,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>979</v>
       </c>
@@ -5337,7 +5363,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>982</v>
       </c>
@@ -5348,7 +5374,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>984</v>
       </c>
@@ -5359,7 +5385,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>987</v>
       </c>
@@ -5370,7 +5396,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>990</v>
       </c>
@@ -5381,7 +5407,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>993</v>
       </c>
@@ -5392,7 +5418,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>996</v>
       </c>
@@ -5403,7 +5429,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>999</v>
       </c>
@@ -5414,7 +5440,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1002</v>
       </c>
@@ -5425,7 +5451,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1005</v>
       </c>
@@ -5436,7 +5462,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1008</v>
       </c>
@@ -5447,7 +5473,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1011</v>
       </c>
@@ -5458,7 +5484,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1014</v>
       </c>
@@ -5469,7 +5495,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>1017</v>
       </c>
@@ -5480,7 +5506,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>1020</v>
       </c>
@@ -5491,7 +5517,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1023</v>
       </c>
@@ -5502,7 +5528,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1026</v>
       </c>
@@ -5513,7 +5539,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>1029</v>
       </c>
@@ -5524,7 +5550,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>1032</v>
       </c>
@@ -5535,7 +5561,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1035</v>
       </c>
@@ -5546,7 +5572,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1038</v>
       </c>
@@ -5557,29 +5583,29 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1041</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C30" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1043</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C31" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1045</v>
       </c>
@@ -5587,7 +5613,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1047</v>
       </c>
@@ -5595,7 +5621,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1049</v>
       </c>
@@ -5603,7 +5629,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1051</v>
       </c>
@@ -5611,7 +5637,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1053</v>
       </c>
@@ -5619,7 +5645,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1055</v>
       </c>
@@ -5627,7 +5653,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1057</v>
       </c>
@@ -5635,7 +5661,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1059</v>
       </c>
@@ -5643,7 +5669,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1061</v>
       </c>
@@ -5651,7 +5677,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1063</v>
       </c>
@@ -5659,7 +5685,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1065</v>
       </c>
@@ -5667,7 +5693,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1067</v>
       </c>
@@ -5675,7 +5701,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1069</v>
       </c>
@@ -5683,7 +5709,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1071</v>
       </c>
@@ -5691,7 +5717,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1073</v>
       </c>
@@ -5699,7 +5725,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1075</v>
       </c>
@@ -5707,7 +5733,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1077</v>
       </c>
@@ -5715,7 +5741,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1079</v>
       </c>
@@ -5723,7 +5749,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1081</v>
       </c>
@@ -5731,7 +5757,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1083</v>
       </c>
@@ -5739,7 +5765,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1085</v>
       </c>
@@ -5747,7 +5773,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1087</v>
       </c>
@@ -5755,7 +5781,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1089</v>
       </c>
@@ -5763,7 +5789,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1091</v>
       </c>
@@ -5771,7 +5797,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1093</v>
       </c>
@@ -5779,7 +5805,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1095</v>
       </c>
@@ -5787,7 +5813,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1097</v>
       </c>
@@ -5795,7 +5821,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1099</v>
       </c>
@@ -5812,13 +5838,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5829,7 +5855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1101</v>
       </c>
@@ -5840,7 +5866,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1103</v>
       </c>
@@ -5860,14 +5886,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5878,7 +5904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1106</v>
       </c>
@@ -5889,7 +5915,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>1108</v>
       </c>
@@ -5900,7 +5926,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>1133</v>
       </c>
@@ -5911,7 +5937,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>1110</v>
       </c>
@@ -5922,7 +5948,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>1112</v>
       </c>
@@ -5933,7 +5959,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>1114</v>
       </c>
@@ -5944,7 +5970,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>1116</v>
       </c>
@@ -5955,7 +5981,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>1118</v>
       </c>
@@ -5966,7 +5992,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>1120</v>
       </c>
@@ -5977,7 +6003,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>1122</v>
       </c>
@@ -5988,7 +6014,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>1124</v>
       </c>
@@ -5999,7 +6025,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>1125</v>
       </c>
@@ -6010,7 +6036,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>1127</v>
       </c>
@@ -6021,7 +6047,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>1129</v>
       </c>
@@ -6032,7 +6058,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>1131</v>
       </c>
@@ -6052,14 +6078,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="101.83203125" customWidth="1"/>
     <col min="3" max="3" width="87.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6070,7 +6096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -6081,7 +6107,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -6092,7 +6118,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
@@ -6103,7 +6129,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
@@ -6114,7 +6140,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -6125,7 +6151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
@@ -6136,7 +6162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
@@ -6147,7 +6173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
@@ -6158,7 +6184,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
@@ -6169,7 +6195,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
@@ -6180,7 +6206,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
@@ -6191,7 +6217,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
@@ -6202,7 +6228,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
@@ -6213,7 +6239,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
@@ -6224,7 +6250,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -6235,40 +6261,40 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>24</v>
       </c>
@@ -6279,29 +6305,29 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
@@ -6310,7 +6336,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
@@ -6319,7 +6345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -6328,7 +6354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
@@ -6337,7 +6363,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>36</v>
       </c>
@@ -6346,7 +6372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
@@ -6355,7 +6381,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
@@ -6364,7 +6390,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>42</v>
       </c>
@@ -6373,7 +6399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>44</v>
       </c>
@@ -6382,7 +6408,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>46</v>
       </c>
@@ -6391,7 +6417,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>48</v>
       </c>
@@ -6400,16 +6426,16 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>51</v>
       </c>
@@ -6418,7 +6444,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>53</v>
       </c>
@@ -6427,7 +6453,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>55</v>
       </c>
@@ -6436,7 +6462,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>57</v>
       </c>
@@ -6445,7 +6471,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
@@ -6454,7 +6480,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>61</v>
       </c>
@@ -6463,7 +6489,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>63</v>
       </c>
@@ -6472,7 +6498,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>65</v>
       </c>
@@ -6481,7 +6507,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>67</v>
       </c>
@@ -6490,7 +6516,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>69</v>
       </c>
@@ -6499,7 +6525,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>71</v>
       </c>
@@ -6508,7 +6534,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>73</v>
       </c>
@@ -6517,7 +6543,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>75</v>
       </c>
@@ -6526,7 +6552,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>77</v>
       </c>
@@ -6535,7 +6561,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>79</v>
       </c>
@@ -6544,7 +6570,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>81</v>
       </c>
@@ -6553,7 +6579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>83</v>
       </c>
@@ -6562,7 +6588,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>85</v>
       </c>
@@ -6571,7 +6597,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>87</v>
       </c>
@@ -6580,7 +6606,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>89</v>
       </c>
@@ -6589,7 +6615,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>91</v>
       </c>
@@ -6598,7 +6624,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>93</v>
       </c>
@@ -6607,7 +6633,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>95</v>
       </c>
@@ -6616,7 +6642,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>97</v>
       </c>
@@ -6625,7 +6651,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
@@ -6634,7 +6660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
@@ -6643,7 +6669,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>103</v>
       </c>
@@ -6652,7 +6678,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>105</v>
       </c>
@@ -6661,7 +6687,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>107</v>
       </c>
@@ -6670,7 +6696,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>109</v>
       </c>
@@ -6679,7 +6705,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>111</v>
       </c>
@@ -6688,7 +6714,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>113</v>
       </c>
@@ -6697,7 +6723,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>115</v>
       </c>
@@ -6706,7 +6732,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>117</v>
       </c>
@@ -6715,7 +6741,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>1134</v>
       </c>
@@ -6724,7 +6750,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>1136</v>
       </c>
@@ -6733,7 +6759,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>1138</v>
       </c>
@@ -6742,7 +6768,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>1140</v>
       </c>
@@ -6751,577 +6777,577 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -7336,13 +7362,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7353,7 +7379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1234</v>
       </c>
@@ -7364,7 +7390,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1237</v>
       </c>
@@ -7375,7 +7401,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1240</v>
       </c>
@@ -7386,18 +7412,18 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1254</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1272</v>
       </c>
@@ -7417,9 +7443,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7430,7 +7456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7441,7 +7467,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7461,9 +7487,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7474,7 +7500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>308</v>
       </c>
@@ -7485,7 +7511,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>311</v>
       </c>
@@ -7496,7 +7522,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>314</v>
       </c>
@@ -7507,7 +7533,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>316</v>
       </c>
@@ -7518,7 +7544,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>318</v>
       </c>
@@ -7529,18 +7555,18 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>320</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>323</v>
       </c>
@@ -7551,7 +7577,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>326</v>
       </c>
@@ -7562,7 +7588,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>329</v>
       </c>
@@ -7573,7 +7599,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>332</v>
       </c>
@@ -7584,7 +7610,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>335</v>
       </c>
@@ -7595,7 +7621,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>338</v>
       </c>
@@ -7606,7 +7632,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>341</v>
       </c>
@@ -7617,7 +7643,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>344</v>
       </c>
@@ -7628,7 +7654,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>347</v>
       </c>
@@ -7648,14 +7674,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7666,7 +7692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>350</v>
       </c>
@@ -7677,7 +7703,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>353</v>
       </c>
@@ -7688,7 +7714,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>356</v>
       </c>
@@ -7699,7 +7725,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>359</v>
       </c>
@@ -7710,7 +7736,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>362</v>
       </c>
@@ -7721,7 +7747,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>365</v>
       </c>
@@ -7732,7 +7758,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>368</v>
       </c>
@@ -7743,7 +7769,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>370</v>
       </c>
@@ -7754,7 +7780,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>373</v>
       </c>
@@ -7765,7 +7791,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>376</v>
       </c>
@@ -7776,7 +7802,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>379</v>
       </c>
@@ -7787,7 +7813,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>382</v>
       </c>
@@ -7798,7 +7824,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>385</v>
       </c>
@@ -7809,7 +7835,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>388</v>
       </c>
@@ -7820,7 +7846,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>391</v>
       </c>
@@ -7831,7 +7857,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>394</v>
       </c>
@@ -7842,7 +7868,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>397</v>
       </c>
@@ -7853,7 +7879,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>400</v>
       </c>
@@ -7864,7 +7890,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>403</v>
       </c>
@@ -7875,7 +7901,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>406</v>
       </c>
@@ -7886,7 +7912,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>409</v>
       </c>
@@ -7897,7 +7923,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>412</v>
       </c>
@@ -7908,7 +7934,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>415</v>
       </c>
@@ -7919,7 +7945,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>418</v>
       </c>
@@ -7930,7 +7956,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>421</v>
       </c>
@@ -7941,7 +7967,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>424</v>
       </c>
@@ -7952,7 +7978,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>427</v>
       </c>
@@ -7963,7 +7989,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>430</v>
       </c>
@@ -7974,7 +8000,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>433</v>
       </c>
@@ -7985,7 +8011,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>436</v>
       </c>
@@ -7996,7 +8022,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>439</v>
       </c>
@@ -8007,7 +8033,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>442</v>
       </c>
@@ -8018,7 +8044,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>445</v>
       </c>
@@ -8029,7 +8055,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>448</v>
       </c>
@@ -8040,7 +8066,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>451</v>
       </c>
@@ -8051,7 +8077,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>454</v>
       </c>
@@ -8062,7 +8088,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>457</v>
       </c>
@@ -8073,7 +8099,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>460</v>
       </c>
@@ -8084,7 +8110,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>463</v>
       </c>
@@ -8095,7 +8121,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>466</v>
       </c>
@@ -8106,7 +8132,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>469</v>
       </c>
@@ -8117,7 +8143,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>472</v>
       </c>
@@ -8128,7 +8154,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>475</v>
       </c>
@@ -8139,7 +8165,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>478</v>
       </c>
@@ -8150,7 +8176,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>481</v>
       </c>
@@ -8161,7 +8187,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>484</v>
       </c>
@@ -8181,14 +8207,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8199,7 +8225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>494</v>
       </c>
@@ -8207,7 +8233,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>495</v>
       </c>
@@ -8215,7 +8241,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>496</v>
       </c>
@@ -8223,7 +8249,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>498</v>
       </c>
@@ -8231,7 +8257,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>500</v>
       </c>
@@ -8239,7 +8265,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>502</v>
       </c>
@@ -8247,7 +8273,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>504</v>
       </c>
@@ -8255,7 +8281,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>506</v>
       </c>
@@ -8263,7 +8289,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>508</v>
       </c>
@@ -8271,7 +8297,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>510</v>
       </c>
@@ -8279,7 +8305,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>512</v>
       </c>
@@ -8287,7 +8313,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>514</v>
       </c>
@@ -8295,7 +8321,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>516</v>
       </c>
@@ -8303,7 +8329,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>518</v>
       </c>
@@ -8311,7 +8337,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>519</v>
       </c>
@@ -8319,7 +8345,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>521</v>
       </c>
@@ -8327,7 +8353,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>523</v>
       </c>
@@ -8335,7 +8361,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>525</v>
       </c>
@@ -8343,7 +8369,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>527</v>
       </c>
@@ -8351,7 +8377,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>529</v>
       </c>
@@ -8359,7 +8385,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>531</v>
       </c>
@@ -8367,7 +8393,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>532</v>
       </c>
@@ -8375,7 +8401,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>533</v>
       </c>
@@ -8383,7 +8409,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>535</v>
       </c>
@@ -8391,7 +8417,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>537</v>
       </c>
@@ -8399,7 +8425,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>538</v>
       </c>
@@ -8407,7 +8433,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>540</v>
       </c>
@@ -8415,7 +8441,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>542</v>
       </c>
@@ -8423,7 +8449,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>544</v>
       </c>
@@ -8431,7 +8457,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>545</v>
       </c>
@@ -8439,7 +8465,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>547</v>
       </c>
@@ -8447,7 +8473,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>549</v>
       </c>
@@ -8455,7 +8481,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>551</v>
       </c>
@@ -8463,7 +8489,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>553</v>
       </c>
@@ -8471,7 +8497,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>555</v>
       </c>
@@ -8479,7 +8505,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>557</v>
       </c>
@@ -8487,7 +8513,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>559</v>
       </c>
@@ -8495,7 +8521,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>561</v>
       </c>
@@ -8503,7 +8529,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>563</v>
       </c>
@@ -8511,7 +8537,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>565</v>
       </c>
@@ -8519,7 +8545,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>567</v>
       </c>
@@ -8527,7 +8553,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>569</v>
       </c>
@@ -8535,7 +8561,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>571</v>
       </c>
@@ -8543,7 +8569,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>573</v>
       </c>
@@ -8551,7 +8577,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>575</v>
       </c>
@@ -8559,7 +8585,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>577</v>
       </c>
@@ -8567,7 +8593,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>579</v>
       </c>
@@ -8575,7 +8601,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>581</v>
       </c>
@@ -8583,7 +8609,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>583</v>
       </c>
@@ -8591,7 +8617,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>585</v>
       </c>
@@ -8599,7 +8625,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>587</v>
       </c>
@@ -8607,7 +8633,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>589</v>
       </c>
@@ -8615,7 +8641,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>591</v>
       </c>
@@ -8623,7 +8649,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>593</v>
       </c>
@@ -8631,7 +8657,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>595</v>
       </c>
@@ -8639,7 +8665,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>597</v>
       </c>
@@ -8647,7 +8673,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>599</v>
       </c>
@@ -8655,7 +8681,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>601</v>
       </c>
@@ -8663,7 +8689,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>603</v>
       </c>
@@ -8671,7 +8697,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>605</v>
       </c>
@@ -8679,7 +8705,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>607</v>
       </c>
@@ -8687,7 +8713,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>609</v>
       </c>
@@ -8695,7 +8721,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>611</v>
       </c>
@@ -8703,7 +8729,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>613</v>
       </c>
@@ -8711,7 +8737,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>615</v>
       </c>
@@ -8719,7 +8745,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>617</v>
       </c>
@@ -8727,7 +8753,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>619</v>
       </c>
@@ -8735,7 +8761,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>620</v>
       </c>
@@ -8743,7 +8769,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>621</v>
       </c>
@@ -8751,7 +8777,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>623</v>
       </c>
@@ -8759,7 +8785,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>625</v>
       </c>
@@ -8767,7 +8793,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>626</v>
       </c>
@@ -8775,7 +8801,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>627</v>
       </c>
@@ -8783,7 +8809,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>629</v>
       </c>
@@ -8791,7 +8817,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>631</v>
       </c>
@@ -8799,7 +8825,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>633</v>
       </c>
@@ -8807,7 +8833,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>635</v>
       </c>
@@ -8815,7 +8841,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>637</v>
       </c>
@@ -8823,7 +8849,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>639</v>
       </c>
@@ -8831,7 +8857,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>641</v>
       </c>
@@ -8839,7 +8865,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>643</v>
       </c>
@@ -8847,7 +8873,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>644</v>
       </c>
@@ -8855,7 +8881,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>645</v>
       </c>
@@ -8863,7 +8889,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>647</v>
       </c>
@@ -8871,7 +8897,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>649</v>
       </c>
@@ -8879,7 +8905,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>651</v>
       </c>
@@ -8887,7 +8913,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>653</v>
       </c>
@@ -8895,7 +8921,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>655</v>
       </c>
@@ -8903,7 +8929,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>657</v>
       </c>
@@ -8911,7 +8937,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>659</v>
       </c>
@@ -8919,7 +8945,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>661</v>
       </c>
@@ -8927,7 +8953,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>663</v>
       </c>
@@ -8935,7 +8961,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>665</v>
       </c>
@@ -8943,7 +8969,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>667</v>
       </c>
@@ -8951,7 +8977,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>669</v>
       </c>
@@ -8959,7 +8985,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>671</v>
       </c>
@@ -8967,7 +8993,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>673</v>
       </c>
@@ -8975,7 +9001,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>675</v>
       </c>
@@ -8983,7 +9009,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>677</v>
       </c>
@@ -8991,7 +9017,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>679</v>
       </c>
@@ -8999,7 +9025,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>681</v>
       </c>
@@ -9007,7 +9033,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>683</v>
       </c>
@@ -9015,7 +9041,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>685</v>
       </c>
@@ -9023,7 +9049,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>687</v>
       </c>
@@ -9031,7 +9057,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>689</v>
       </c>
@@ -9039,7 +9065,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>691</v>
       </c>
@@ -9047,7 +9073,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>693</v>
       </c>
@@ -9055,7 +9081,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>695</v>
       </c>
@@ -9063,7 +9089,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>697</v>
       </c>
@@ -9071,7 +9097,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>699</v>
       </c>
@@ -9079,7 +9105,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>701</v>
       </c>
@@ -9087,7 +9113,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>703</v>
       </c>
@@ -9095,7 +9121,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>705</v>
       </c>
@@ -9103,7 +9129,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>707</v>
       </c>
@@ -9111,7 +9137,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>709</v>
       </c>
@@ -9119,7 +9145,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>711</v>
       </c>
@@ -9127,7 +9153,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>713</v>
       </c>
@@ -9135,7 +9161,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>715</v>
       </c>
@@ -9143,7 +9169,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>717</v>
       </c>
@@ -9151,7 +9177,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>719</v>
       </c>
@@ -9159,7 +9185,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>721</v>
       </c>
@@ -9167,7 +9193,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>723</v>
       </c>
@@ -9175,7 +9201,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>725</v>
       </c>
@@ -9183,7 +9209,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>727</v>
       </c>
@@ -9191,7 +9217,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>729</v>
       </c>
@@ -9199,7 +9225,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>731</v>
       </c>
@@ -9207,7 +9233,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>733</v>
       </c>
@@ -9215,7 +9241,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>735</v>
       </c>
@@ -9223,7 +9249,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>737</v>
       </c>
@@ -9231,7 +9257,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>739</v>
       </c>
@@ -9239,7 +9265,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>741</v>
       </c>
@@ -9247,7 +9273,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>743</v>
       </c>
@@ -9255,7 +9281,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>745</v>
       </c>
@@ -9263,7 +9289,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>747</v>
       </c>
@@ -9271,7 +9297,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>749</v>
       </c>
@@ -9279,7 +9305,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>751</v>
       </c>
@@ -9287,7 +9313,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>753</v>
       </c>
@@ -9295,7 +9321,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>755</v>
       </c>
@@ -9303,7 +9329,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>757</v>
       </c>
@@ -9311,7 +9337,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>759</v>
       </c>
@@ -9319,7 +9345,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>761</v>
       </c>
@@ -9327,7 +9353,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>763</v>
       </c>
@@ -9335,7 +9361,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>765</v>
       </c>
@@ -9343,7 +9369,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>767</v>
       </c>
@@ -9351,7 +9377,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>769</v>
       </c>
@@ -9359,7 +9385,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>771</v>
       </c>
@@ -9367,7 +9393,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>773</v>
       </c>
@@ -9375,7 +9401,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>775</v>
       </c>
@@ -9383,7 +9409,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>777</v>
       </c>
@@ -9391,7 +9417,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>779</v>
       </c>
@@ -9399,7 +9425,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>781</v>
       </c>
@@ -9407,7 +9433,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>783</v>
       </c>
@@ -9415,7 +9441,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>785</v>
       </c>
@@ -9423,7 +9449,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>787</v>
       </c>
@@ -9431,7 +9457,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>789</v>
       </c>
@@ -9439,7 +9465,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>791</v>
       </c>
@@ -9447,7 +9473,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>793</v>
       </c>
@@ -9455,7 +9481,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>795</v>
       </c>
@@ -9463,7 +9489,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>797</v>
       </c>
@@ -9471,7 +9497,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>799</v>
       </c>
@@ -9479,7 +9505,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>801</v>
       </c>
@@ -9487,7 +9513,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>803</v>
       </c>
@@ -9495,7 +9521,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>805</v>
       </c>
@@ -9503,7 +9529,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>807</v>
       </c>
@@ -9511,7 +9537,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>809</v>
       </c>
@@ -9519,7 +9545,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>811</v>
       </c>
@@ -9527,7 +9553,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>813</v>
       </c>
@@ -9535,7 +9561,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>815</v>
       </c>
@@ -9543,7 +9569,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>817</v>
       </c>
@@ -9551,7 +9577,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>819</v>
       </c>
@@ -9559,7 +9585,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>821</v>
       </c>
@@ -9567,7 +9593,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>823</v>
       </c>
@@ -9575,7 +9601,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>825</v>
       </c>
@@ -9583,7 +9609,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>827</v>
       </c>
@@ -9591,7 +9617,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>829</v>
       </c>
@@ -9599,7 +9625,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>831</v>
       </c>
@@ -9607,7 +9633,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>833</v>
       </c>
@@ -9615,7 +9641,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>835</v>
       </c>
@@ -9623,7 +9649,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>837</v>
       </c>
@@ -9631,7 +9657,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>839</v>
       </c>
@@ -9639,7 +9665,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>841</v>
       </c>
@@ -9647,7 +9673,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>843</v>
       </c>
@@ -9655,7 +9681,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>845</v>
       </c>
@@ -9663,7 +9689,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>847</v>
       </c>
@@ -9671,7 +9697,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>849</v>
       </c>
@@ -9679,7 +9705,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>851</v>
       </c>
@@ -9696,13 +9722,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9713,7 +9739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>853</v>
       </c>
@@ -9724,7 +9750,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>856</v>
       </c>
@@ -9732,7 +9758,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>857</v>
       </c>
@@ -9743,7 +9769,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>860</v>
       </c>
@@ -9760,13 +9786,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9777,7 +9803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>861</v>
       </c>
@@ -9788,7 +9814,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>864</v>
       </c>
@@ -9799,7 +9825,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>867</v>
       </c>
@@ -9810,7 +9836,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>870</v>
       </c>
@@ -9830,13 +9856,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9847,7 +9873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>872</v>
       </c>
@@ -9858,7 +9884,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>875</v>
       </c>
@@ -9869,7 +9895,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>878</v>
       </c>
@@ -9880,7 +9906,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>881</v>
       </c>
@@ -9891,7 +9917,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>884</v>
       </c>
@@ -9911,14 +9937,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9929,7 +9955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>887</v>
       </c>
@@ -9940,7 +9966,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>890</v>
       </c>
@@ -9951,7 +9977,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>893</v>
       </c>
@@ -9962,7 +9988,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>896</v>
       </c>
@@ -9973,7 +9999,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>899</v>
       </c>
@@ -9984,7 +10010,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>902</v>
       </c>
@@ -9995,7 +10021,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>905</v>
       </c>
@@ -10006,7 +10032,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>908</v>
       </c>
@@ -10017,7 +10043,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>909</v>
       </c>
@@ -10028,7 +10054,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>911</v>
       </c>
@@ -10039,7 +10065,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>913</v>
       </c>
@@ -10050,7 +10076,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>915</v>
       </c>
@@ -10061,7 +10087,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>917</v>
       </c>
@@ -10072,7 +10098,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>919</v>
       </c>
@@ -10083,7 +10109,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>921</v>
       </c>
@@ -10094,7 +10120,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>923</v>
       </c>
@@ -10105,7 +10131,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>925</v>
       </c>
@@ -10116,7 +10142,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>927</v>
       </c>
@@ -10127,7 +10153,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>929</v>
       </c>
@@ -10138,7 +10164,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>931</v>
       </c>
@@ -10149,7 +10175,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>933</v>
       </c>
@@ -10160,7 +10186,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>935</v>
       </c>
@@ -10171,7 +10197,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>937</v>
       </c>
@@ -10182,7 +10208,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>939</v>
       </c>
@@ -10193,7 +10219,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>941</v>
       </c>
@@ -10204,7 +10230,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>943</v>
       </c>
@@ -10215,7 +10241,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>945</v>
       </c>
@@ -10226,7 +10252,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>947</v>
       </c>
@@ -10237,7 +10263,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>949</v>
       </c>
@@ -10248,7 +10274,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>951</v>
       </c>
@@ -10259,7 +10285,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>953</v>
       </c>
@@ -10270,7 +10296,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>955</v>
       </c>
@@ -10281,7 +10307,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>957</v>
       </c>
@@ -10292,7 +10318,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>959</v>
       </c>
@@ -10303,7 +10329,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>1275</v>
       </c>
@@ -10314,7 +10340,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>1276</v>
       </c>
@@ -10325,7 +10351,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>1277</v>
       </c>
@@ -10336,7 +10362,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>1278</v>
       </c>
@@ -10347,7 +10373,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>1279</v>
       </c>
@@ -10358,7 +10384,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>1280</v>
       </c>
@@ -10369,7 +10395,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>1281</v>
       </c>
@@ -10380,7 +10406,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>1282</v>
       </c>
@@ -10391,7 +10417,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>1283</v>
       </c>
@@ -10402,7 +10428,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>1284</v>
       </c>
@@ -10413,7 +10439,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>1285</v>
       </c>
@@ -10424,7 +10450,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>1286</v>
       </c>
@@ -10435,7 +10461,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>1287</v>
       </c>
@@ -10446,7 +10472,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>1288</v>
       </c>
@@ -10457,7 +10483,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>1289</v>
       </c>
@@ -10468,7 +10494,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>1290</v>
       </c>
@@ -10479,7 +10505,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>1291</v>
       </c>
@@ -10490,7 +10516,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>1292</v>
       </c>
@@ -10501,7 +10527,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>1293</v>
       </c>
@@ -10512,7 +10538,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>1294</v>
       </c>
@@ -10523,7 +10549,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>1295</v>
       </c>
@@ -10534,7 +10560,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>1296</v>
       </c>
@@ -10545,7 +10571,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>1297</v>
       </c>
@@ -10556,7 +10582,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>1298</v>
       </c>
@@ -10567,7 +10593,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>1299</v>
       </c>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengmingliu\LudorkProjects\ProjectMT3\Data\Locale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3699206-B968-4AD5-BBE7-7DE1AC2E5C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E09E6D-084F-BB4D-88E2-5577DE5EC379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="6250" windowWidth="28470" windowHeight="13870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1760" yWindow="4080" windowWidth="28480" windowHeight="13880" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="1373">
   <si>
     <t>ID</t>
   </si>
@@ -3764,9 +3764,6 @@
     <t>TM_03</t>
   </si>
   <si>
-    <t>The bottle could increase your HP.</t>
-  </si>
-  <si>
     <t>血瓶可以增加HP值。</t>
   </si>
   <si>
@@ -4092,13 +4089,88 @@
   <si>
     <t>U: Switch party member</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOTTLE_150</t>
+  </si>
+  <si>
+    <t>BOTTLE_150_DESC</t>
+  </si>
+  <si>
+    <t>BOTTLE_400</t>
+  </si>
+  <si>
+    <t>BOTTLE_400_DESC</t>
+  </si>
+  <si>
+    <t>Potion</t>
+  </si>
+  <si>
+    <t>伤药</t>
+  </si>
+  <si>
+    <t>Potion Elite</t>
+  </si>
+  <si>
+    <t>高级伤药</t>
+  </si>
+  <si>
+    <t>TM_06</t>
+  </si>
+  <si>
+    <t>拾取血瓶时，溢出的HP会储存在你的背包中。</t>
+  </si>
+  <si>
+    <t>When picking up a potion, any excess HP is stored in your inventory.</t>
+  </si>
+  <si>
+    <t>The potion could increase your HP.</t>
+  </si>
+  <si>
+    <t>HOTKEY_BOTTLE</t>
+  </si>
+  <si>
+    <t>B: Potions</t>
+  </si>
+  <si>
+    <t>B：药瓶</t>
+  </si>
+  <si>
+    <t>Restores 400 HP.</t>
+  </si>
+  <si>
+    <t>Restores 150 HP.</t>
+  </si>
+  <si>
+    <t>恢复150点HP，可在背包中使用。</t>
+  </si>
+  <si>
+    <t>恢复400点HP，可在背包中使用。</t>
+  </si>
+  <si>
+    <t>TM_07</t>
+  </si>
+  <si>
+    <t>按 B 键可以快速使用，在这里可以查看更多快捷键。</t>
+  </si>
+  <si>
+    <t>You can use them quickly by pressing B. Here you can view more of hotkeys.</t>
+  </si>
+  <si>
+    <t>TM_08</t>
+  </si>
+  <si>
+    <t>You can use them quickly by pressing N. Here you can view more of hotkeys.</t>
+  </si>
+  <si>
+    <t>按 N 键可以快速使用，在这里可以查看更多快捷键。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4206,7 +4278,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4416,15 +4488,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C75"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4435,7 +4507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>119</v>
       </c>
@@ -4446,7 +4518,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -4457,7 +4529,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -4468,7 +4540,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
@@ -4479,7 +4551,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
@@ -4490,7 +4562,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>134</v>
       </c>
@@ -4501,7 +4573,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -4512,7 +4584,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
         <v>140</v>
       </c>
@@ -4523,7 +4595,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
@@ -4534,7 +4606,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -4545,7 +4617,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -4556,7 +4628,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>149</v>
       </c>
@@ -4567,7 +4639,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>152</v>
       </c>
@@ -4578,7 +4650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -4589,7 +4661,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>158</v>
       </c>
@@ -4600,7 +4672,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -4611,7 +4683,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -4622,7 +4694,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -4633,7 +4705,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -4644,7 +4716,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>172</v>
       </c>
@@ -4655,7 +4727,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>175</v>
       </c>
@@ -4666,7 +4738,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>178</v>
       </c>
@@ -4677,7 +4749,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>181</v>
       </c>
@@ -4688,7 +4760,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>184</v>
       </c>
@@ -4699,7 +4771,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>187</v>
       </c>
@@ -4710,7 +4782,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -4721,7 +4793,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>193</v>
       </c>
@@ -4732,7 +4804,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>196</v>
       </c>
@@ -4743,7 +4815,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>199</v>
       </c>
@@ -4754,7 +4826,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>202</v>
       </c>
@@ -4765,7 +4837,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>205</v>
       </c>
@@ -4776,7 +4848,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>208</v>
       </c>
@@ -4787,7 +4859,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>211</v>
       </c>
@@ -4798,7 +4870,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -4809,7 +4881,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>217</v>
       </c>
@@ -4820,7 +4892,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>220</v>
       </c>
@@ -4831,7 +4903,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>223</v>
       </c>
@@ -4842,7 +4914,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>226</v>
       </c>
@@ -4853,7 +4925,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
         <v>229</v>
       </c>
@@ -4864,7 +4936,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
         <v>232</v>
       </c>
@@ -4875,7 +4947,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>235</v>
       </c>
@@ -4886,7 +4958,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>238</v>
       </c>
@@ -4897,7 +4969,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>241</v>
       </c>
@@ -4908,7 +4980,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>244</v>
       </c>
@@ -4919,7 +4991,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>247</v>
       </c>
@@ -4930,7 +5002,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>250</v>
       </c>
@@ -4941,7 +5013,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>253</v>
       </c>
@@ -4952,7 +5024,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>256</v>
       </c>
@@ -4963,7 +5035,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>259</v>
       </c>
@@ -4974,7 +5046,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>262</v>
       </c>
@@ -4985,7 +5057,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>265</v>
       </c>
@@ -4996,7 +5068,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>268</v>
       </c>
@@ -5007,7 +5079,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>271</v>
       </c>
@@ -5018,7 +5090,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="32" customHeight="1">
       <c r="A55" s="7" t="s">
         <v>274</v>
       </c>
@@ -5029,7 +5101,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="32" customHeight="1">
       <c r="A56" s="7" t="s">
         <v>277</v>
       </c>
@@ -5040,7 +5112,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="32" customHeight="1">
       <c r="A57" s="7" t="s">
         <v>280</v>
       </c>
@@ -5051,7 +5123,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="32" customHeight="1">
       <c r="A58" s="7" t="s">
         <v>283</v>
       </c>
@@ -5062,7 +5134,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="32" customHeight="1">
       <c r="A59" s="7" t="s">
         <v>286</v>
       </c>
@@ -5073,7 +5145,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="32" customHeight="1">
       <c r="A60" s="7" t="s">
         <v>289</v>
       </c>
@@ -5084,7 +5156,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>292</v>
       </c>
@@ -5095,7 +5167,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>295</v>
       </c>
@@ -5106,7 +5178,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>298</v>
       </c>
@@ -5117,7 +5189,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>301</v>
       </c>
@@ -5128,125 +5200,136 @@
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B65" t="s">
         <v>1300</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>1301</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
         <v>1302</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="B66" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
         <v>1303</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B67" s="8" t="s">
         <v>1345</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C67" s="8" t="s">
         <v>1343</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
         <v>1304</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B68" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>1342</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>1347</v>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1362</v>
       </c>
     </row>
   </sheetData>
@@ -5258,13 +5341,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="43.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5275,7 +5358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>961</v>
       </c>
@@ -5286,7 +5369,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>963</v>
       </c>
@@ -5297,7 +5380,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>966</v>
       </c>
@@ -5308,7 +5391,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>968</v>
       </c>
@@ -5319,7 +5402,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>971</v>
       </c>
@@ -5330,7 +5413,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>973</v>
       </c>
@@ -5341,7 +5424,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>976</v>
       </c>
@@ -5352,7 +5435,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>979</v>
       </c>
@@ -5363,7 +5446,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>982</v>
       </c>
@@ -5374,7 +5457,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>984</v>
       </c>
@@ -5385,7 +5468,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>987</v>
       </c>
@@ -5396,7 +5479,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>990</v>
       </c>
@@ -5407,7 +5490,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>993</v>
       </c>
@@ -5418,7 +5501,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>996</v>
       </c>
@@ -5429,7 +5512,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>999</v>
       </c>
@@ -5440,7 +5523,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>1002</v>
       </c>
@@ -5451,7 +5534,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>1005</v>
       </c>
@@ -5462,7 +5545,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>1008</v>
       </c>
@@ -5473,7 +5556,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>1011</v>
       </c>
@@ -5484,7 +5567,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>1014</v>
       </c>
@@ -5495,7 +5578,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
         <v>1017</v>
       </c>
@@ -5506,7 +5589,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
         <v>1020</v>
       </c>
@@ -5517,7 +5600,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>1023</v>
       </c>
@@ -5528,7 +5611,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>1026</v>
       </c>
@@ -5539,7 +5622,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
         <v>1029</v>
       </c>
@@ -5550,7 +5633,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
         <v>1032</v>
       </c>
@@ -5561,7 +5644,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>1035</v>
       </c>
@@ -5572,7 +5655,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>1038</v>
       </c>
@@ -5583,29 +5666,29 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>1041</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C30" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>1043</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C31" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>1045</v>
       </c>
@@ -5613,7 +5696,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>1047</v>
       </c>
@@ -5621,7 +5704,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>1049</v>
       </c>
@@ -5629,7 +5712,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>1051</v>
       </c>
@@ -5637,7 +5720,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>1053</v>
       </c>
@@ -5645,7 +5728,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>1055</v>
       </c>
@@ -5653,7 +5736,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>1057</v>
       </c>
@@ -5661,7 +5744,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>1059</v>
       </c>
@@ -5669,7 +5752,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>1061</v>
       </c>
@@ -5677,7 +5760,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>1063</v>
       </c>
@@ -5685,7 +5768,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>1065</v>
       </c>
@@ -5693,7 +5776,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>1067</v>
       </c>
@@ -5701,7 +5784,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>1069</v>
       </c>
@@ -5709,7 +5792,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>1071</v>
       </c>
@@ -5717,7 +5800,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>1073</v>
       </c>
@@ -5725,7 +5808,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>1075</v>
       </c>
@@ -5733,7 +5816,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>1077</v>
       </c>
@@ -5741,7 +5824,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>1079</v>
       </c>
@@ -5749,7 +5832,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>1081</v>
       </c>
@@ -5757,7 +5840,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>1083</v>
       </c>
@@ -5765,7 +5848,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>1085</v>
       </c>
@@ -5773,7 +5856,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>1087</v>
       </c>
@@ -5781,7 +5864,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>1089</v>
       </c>
@@ -5789,7 +5872,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>1091</v>
       </c>
@@ -5797,7 +5880,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>1093</v>
       </c>
@@ -5805,7 +5888,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>1095</v>
       </c>
@@ -5813,7 +5896,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>1097</v>
       </c>
@@ -5821,7 +5904,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>1099</v>
       </c>
@@ -5838,13 +5921,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5855,7 +5938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1101</v>
       </c>
@@ -5866,7 +5949,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>1103</v>
       </c>
@@ -5886,14 +5969,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5904,7 +5987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
         <v>1106</v>
       </c>
@@ -5915,7 +5998,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
         <v>1108</v>
       </c>
@@ -5926,7 +6009,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
         <v>1133</v>
       </c>
@@ -5937,7 +6020,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
         <v>1110</v>
       </c>
@@ -5948,7 +6031,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
         <v>1112</v>
       </c>
@@ -5959,7 +6042,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
         <v>1114</v>
       </c>
@@ -5970,7 +6053,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
         <v>1116</v>
       </c>
@@ -5981,7 +6064,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
         <v>1118</v>
       </c>
@@ -5992,7 +6075,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
         <v>1120</v>
       </c>
@@ -6003,7 +6086,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
         <v>1122</v>
       </c>
@@ -6014,7 +6097,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
         <v>1124</v>
       </c>
@@ -6025,7 +6108,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
         <v>1125</v>
       </c>
@@ -6036,7 +6119,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
         <v>1127</v>
       </c>
@@ -6047,7 +6130,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
         <v>1129</v>
       </c>
@@ -6058,7 +6141,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
         <v>1131</v>
       </c>
@@ -6078,14 +6161,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
     <col min="2" max="2" width="101.83203125" customWidth="1"/>
     <col min="3" max="3" width="87.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6096,238 +6179,238 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>1259</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>1267</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
@@ -6336,7 +6419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
@@ -6345,7 +6428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
@@ -6354,7 +6437,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
@@ -6363,7 +6446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
         <v>36</v>
       </c>
@@ -6372,7 +6455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
@@ -6381,7 +6464,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
@@ -6390,7 +6473,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
         <v>42</v>
       </c>
@@ -6399,7 +6482,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
         <v>44</v>
       </c>
@@ -6408,7 +6491,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
         <v>46</v>
       </c>
@@ -6417,7 +6500,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
         <v>48</v>
       </c>
@@ -6426,16 +6509,16 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
         <v>51</v>
       </c>
@@ -6444,7 +6527,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
         <v>53</v>
       </c>
@@ -6453,7 +6536,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
         <v>55</v>
       </c>
@@ -6462,7 +6545,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
         <v>57</v>
       </c>
@@ -6471,7 +6554,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
@@ -6480,7 +6563,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
         <v>61</v>
       </c>
@@ -6489,7 +6572,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="6" t="s">
         <v>63</v>
       </c>
@@ -6498,7 +6581,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="6" t="s">
         <v>65</v>
       </c>
@@ -6507,7 +6590,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
         <v>67</v>
       </c>
@@ -6516,7 +6599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
         <v>69</v>
       </c>
@@ -6525,7 +6608,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
         <v>71</v>
       </c>
@@ -6534,7 +6617,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
         <v>73</v>
       </c>
@@ -6543,7 +6626,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="8" t="s">
         <v>75</v>
       </c>
@@ -6552,7 +6635,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" s="8" t="s">
         <v>77</v>
       </c>
@@ -6561,7 +6644,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
         <v>79</v>
       </c>
@@ -6570,7 +6653,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" s="8" t="s">
         <v>81</v>
       </c>
@@ -6579,7 +6662,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" s="8" t="s">
         <v>83</v>
       </c>
@@ -6588,7 +6671,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" s="8" t="s">
         <v>85</v>
       </c>
@@ -6597,7 +6680,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" s="8" t="s">
         <v>87</v>
       </c>
@@ -6606,7 +6689,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" s="8" t="s">
         <v>89</v>
       </c>
@@ -6615,7 +6698,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" s="8" t="s">
         <v>91</v>
       </c>
@@ -6624,7 +6707,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
         <v>93</v>
       </c>
@@ -6633,7 +6716,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
         <v>95</v>
       </c>
@@ -6642,7 +6725,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
         <v>97</v>
       </c>
@@ -6651,7 +6734,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
         <v>99</v>
       </c>
@@ -6660,7 +6743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
         <v>101</v>
       </c>
@@ -6669,7 +6752,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" s="8" t="s">
         <v>103</v>
       </c>
@@ -6678,7 +6761,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" s="8" t="s">
         <v>105</v>
       </c>
@@ -6687,7 +6770,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" s="8" t="s">
         <v>107</v>
       </c>
@@ -6696,7 +6779,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" s="8" t="s">
         <v>109</v>
       </c>
@@ -6705,7 +6788,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="8" t="s">
         <v>111</v>
       </c>
@@ -6714,7 +6797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="8" t="s">
         <v>113</v>
       </c>
@@ -6723,7 +6806,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="8" t="s">
         <v>115</v>
       </c>
@@ -6732,7 +6815,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="8" t="s">
         <v>117</v>
       </c>
@@ -6741,7 +6824,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
         <v>1134</v>
       </c>
@@ -6750,7 +6833,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
         <v>1136</v>
       </c>
@@ -6759,7 +6842,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="8" t="s">
         <v>1138</v>
       </c>
@@ -6768,7 +6851,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="A72" s="8" t="s">
         <v>1140</v>
       </c>
@@ -6777,577 +6860,577 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
@@ -7361,14 +7444,14 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7379,7 +7462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>1234</v>
       </c>
@@ -7390,7 +7473,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>1237</v>
       </c>
@@ -7401,37 +7484,70 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>1240</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1273</v>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -7443,9 +7559,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7456,7 +7572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7467,7 +7583,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7487,9 +7603,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7500,7 +7616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>308</v>
       </c>
@@ -7511,7 +7627,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>311</v>
       </c>
@@ -7522,7 +7638,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>314</v>
       </c>
@@ -7533,7 +7649,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>316</v>
       </c>
@@ -7544,7 +7660,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>318</v>
       </c>
@@ -7555,18 +7671,18 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>320</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>323</v>
       </c>
@@ -7577,7 +7693,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>326</v>
       </c>
@@ -7588,7 +7704,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>329</v>
       </c>
@@ -7599,7 +7715,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>332</v>
       </c>
@@ -7610,7 +7726,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>335</v>
       </c>
@@ -7621,7 +7737,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>338</v>
       </c>
@@ -7632,7 +7748,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>341</v>
       </c>
@@ -7643,7 +7759,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>344</v>
       </c>
@@ -7654,7 +7770,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>347</v>
       </c>
@@ -7673,15 +7789,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7692,7 +7808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>350</v>
       </c>
@@ -7703,7 +7819,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>353</v>
       </c>
@@ -7714,7 +7830,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>356</v>
       </c>
@@ -7725,7 +7841,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>359</v>
       </c>
@@ -7736,7 +7852,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>362</v>
       </c>
@@ -7747,7 +7863,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>365</v>
       </c>
@@ -7758,18 +7874,18 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>368</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>370</v>
       </c>
@@ -7780,7 +7896,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>373</v>
       </c>
@@ -7791,7 +7907,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>376</v>
       </c>
@@ -7802,7 +7918,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>379</v>
       </c>
@@ -7813,7 +7929,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>382</v>
       </c>
@@ -7824,7 +7940,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>385</v>
       </c>
@@ -7835,7 +7951,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>388</v>
       </c>
@@ -7846,7 +7962,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>391</v>
       </c>
@@ -7857,7 +7973,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>394</v>
       </c>
@@ -7868,7 +7984,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>397</v>
       </c>
@@ -7879,7 +7995,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>400</v>
       </c>
@@ -7890,7 +8006,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>403</v>
       </c>
@@ -7901,7 +8017,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>406</v>
       </c>
@@ -7912,7 +8028,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>409</v>
       </c>
@@ -7923,7 +8039,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>412</v>
       </c>
@@ -7934,7 +8050,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>415</v>
       </c>
@@ -7945,7 +8061,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>418</v>
       </c>
@@ -7956,7 +8072,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>421</v>
       </c>
@@ -7967,7 +8083,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>424</v>
       </c>
@@ -7978,7 +8094,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>427</v>
       </c>
@@ -7989,7 +8105,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>430</v>
       </c>
@@ -8000,7 +8116,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>433</v>
       </c>
@@ -8011,7 +8127,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>436</v>
       </c>
@@ -8022,7 +8138,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>439</v>
       </c>
@@ -8033,7 +8149,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>442</v>
       </c>
@@ -8044,7 +8160,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>445</v>
       </c>
@@ -8055,7 +8171,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>448</v>
       </c>
@@ -8066,7 +8182,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>451</v>
       </c>
@@ -8077,7 +8193,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>454</v>
       </c>
@@ -8088,7 +8204,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>457</v>
       </c>
@@ -8099,7 +8215,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>460</v>
       </c>
@@ -8110,7 +8226,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>463</v>
       </c>
@@ -8121,7 +8237,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>466</v>
       </c>
@@ -8132,7 +8248,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>469</v>
       </c>
@@ -8143,7 +8259,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>472</v>
       </c>
@@ -8154,7 +8270,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>475</v>
       </c>
@@ -8165,7 +8281,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>478</v>
       </c>
@@ -8176,7 +8292,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>481</v>
       </c>
@@ -8187,7 +8303,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>484</v>
       </c>
@@ -8196,6 +8312,50 @@
       </c>
       <c r="C47" t="s">
         <v>486</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>1366</v>
       </c>
     </row>
   </sheetData>
@@ -8207,14 +8367,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C187"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8225,7 +8385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>494</v>
       </c>
@@ -8233,7 +8393,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>495</v>
       </c>
@@ -8241,7 +8401,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>496</v>
       </c>
@@ -8249,7 +8409,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>498</v>
       </c>
@@ -8257,7 +8417,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>500</v>
       </c>
@@ -8265,7 +8425,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>502</v>
       </c>
@@ -8273,7 +8433,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>504</v>
       </c>
@@ -8281,7 +8441,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>506</v>
       </c>
@@ -8289,7 +8449,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>508</v>
       </c>
@@ -8297,7 +8457,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>510</v>
       </c>
@@ -8305,7 +8465,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>512</v>
       </c>
@@ -8313,7 +8473,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>514</v>
       </c>
@@ -8321,7 +8481,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>516</v>
       </c>
@@ -8329,7 +8489,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>518</v>
       </c>
@@ -8337,7 +8497,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>519</v>
       </c>
@@ -8345,7 +8505,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>521</v>
       </c>
@@ -8353,7 +8513,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>523</v>
       </c>
@@ -8361,7 +8521,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>525</v>
       </c>
@@ -8369,7 +8529,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>527</v>
       </c>
@@ -8377,7 +8537,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>529</v>
       </c>
@@ -8385,7 +8545,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>531</v>
       </c>
@@ -8393,7 +8553,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>532</v>
       </c>
@@ -8401,7 +8561,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>533</v>
       </c>
@@ -8409,7 +8569,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>535</v>
       </c>
@@ -8417,7 +8577,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>537</v>
       </c>
@@ -8425,7 +8585,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>538</v>
       </c>
@@ -8433,7 +8593,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>540</v>
       </c>
@@ -8441,7 +8601,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>542</v>
       </c>
@@ -8449,7 +8609,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>544</v>
       </c>
@@ -8457,7 +8617,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>545</v>
       </c>
@@ -8465,7 +8625,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>547</v>
       </c>
@@ -8473,7 +8633,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>549</v>
       </c>
@@ -8481,7 +8641,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>551</v>
       </c>
@@ -8489,7 +8649,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>553</v>
       </c>
@@ -8497,7 +8657,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>555</v>
       </c>
@@ -8505,7 +8665,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>557</v>
       </c>
@@ -8513,7 +8673,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>559</v>
       </c>
@@ -8521,7 +8681,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>561</v>
       </c>
@@ -8529,7 +8689,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>563</v>
       </c>
@@ -8537,7 +8697,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>565</v>
       </c>
@@ -8545,7 +8705,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>567</v>
       </c>
@@ -8553,7 +8713,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>569</v>
       </c>
@@ -8561,7 +8721,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>571</v>
       </c>
@@ -8569,7 +8729,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>573</v>
       </c>
@@ -8577,7 +8737,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>575</v>
       </c>
@@ -8585,7 +8745,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>577</v>
       </c>
@@ -8593,7 +8753,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>579</v>
       </c>
@@ -8601,7 +8761,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>581</v>
       </c>
@@ -8609,7 +8769,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>583</v>
       </c>
@@ -8617,7 +8777,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>585</v>
       </c>
@@ -8625,7 +8785,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>587</v>
       </c>
@@ -8633,7 +8793,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>589</v>
       </c>
@@ -8641,7 +8801,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>591</v>
       </c>
@@ -8649,7 +8809,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>593</v>
       </c>
@@ -8657,7 +8817,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>595</v>
       </c>
@@ -8665,7 +8825,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>597</v>
       </c>
@@ -8673,7 +8833,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>599</v>
       </c>
@@ -8681,7 +8841,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>601</v>
       </c>
@@ -8689,7 +8849,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>603</v>
       </c>
@@ -8697,7 +8857,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>605</v>
       </c>
@@ -8705,7 +8865,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>607</v>
       </c>
@@ -8713,7 +8873,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>609</v>
       </c>
@@ -8721,7 +8881,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>611</v>
       </c>
@@ -8729,7 +8889,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>613</v>
       </c>
@@ -8737,7 +8897,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>615</v>
       </c>
@@ -8745,7 +8905,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>617</v>
       </c>
@@ -8753,7 +8913,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>619</v>
       </c>
@@ -8761,7 +8921,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>620</v>
       </c>
@@ -8769,7 +8929,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>621</v>
       </c>
@@ -8777,7 +8937,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>623</v>
       </c>
@@ -8785,7 +8945,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>625</v>
       </c>
@@ -8793,7 +8953,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>626</v>
       </c>
@@ -8801,7 +8961,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>627</v>
       </c>
@@ -8809,7 +8969,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>629</v>
       </c>
@@ -8817,7 +8977,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>631</v>
       </c>
@@ -8825,7 +8985,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>633</v>
       </c>
@@ -8833,7 +8993,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>635</v>
       </c>
@@ -8841,7 +9001,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>637</v>
       </c>
@@ -8849,7 +9009,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>639</v>
       </c>
@@ -8857,7 +9017,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>641</v>
       </c>
@@ -8865,7 +9025,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>643</v>
       </c>
@@ -8873,7 +9033,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>644</v>
       </c>
@@ -8881,7 +9041,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>645</v>
       </c>
@@ -8889,7 +9049,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>647</v>
       </c>
@@ -8897,7 +9057,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>649</v>
       </c>
@@ -8905,7 +9065,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>651</v>
       </c>
@@ -8913,7 +9073,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>653</v>
       </c>
@@ -8921,7 +9081,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>655</v>
       </c>
@@ -8929,7 +9089,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>657</v>
       </c>
@@ -8937,7 +9097,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>659</v>
       </c>
@@ -8945,7 +9105,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>661</v>
       </c>
@@ -8953,7 +9113,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>663</v>
       </c>
@@ -8961,7 +9121,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>665</v>
       </c>
@@ -8969,7 +9129,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>667</v>
       </c>
@@ -8977,7 +9137,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>669</v>
       </c>
@@ -8985,7 +9145,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>671</v>
       </c>
@@ -8993,7 +9153,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>673</v>
       </c>
@@ -9001,7 +9161,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>675</v>
       </c>
@@ -9009,7 +9169,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>677</v>
       </c>
@@ -9017,7 +9177,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>679</v>
       </c>
@@ -9025,7 +9185,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>681</v>
       </c>
@@ -9033,7 +9193,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>683</v>
       </c>
@@ -9041,7 +9201,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>685</v>
       </c>
@@ -9049,7 +9209,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>687</v>
       </c>
@@ -9057,7 +9217,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>689</v>
       </c>
@@ -9065,7 +9225,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>691</v>
       </c>
@@ -9073,7 +9233,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>693</v>
       </c>
@@ -9081,7 +9241,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>695</v>
       </c>
@@ -9089,7 +9249,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>697</v>
       </c>
@@ -9097,7 +9257,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>699</v>
       </c>
@@ -9105,7 +9265,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>701</v>
       </c>
@@ -9113,7 +9273,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>703</v>
       </c>
@@ -9121,7 +9281,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>705</v>
       </c>
@@ -9129,7 +9289,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>707</v>
       </c>
@@ -9137,7 +9297,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>709</v>
       </c>
@@ -9145,7 +9305,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3">
       <c r="A117" t="s">
         <v>711</v>
       </c>
@@ -9153,7 +9313,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>713</v>
       </c>
@@ -9161,7 +9321,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>715</v>
       </c>
@@ -9169,7 +9329,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>717</v>
       </c>
@@ -9177,7 +9337,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>719</v>
       </c>
@@ -9185,7 +9345,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>721</v>
       </c>
@@ -9193,7 +9353,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>723</v>
       </c>
@@ -9201,7 +9361,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>725</v>
       </c>
@@ -9209,7 +9369,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>727</v>
       </c>
@@ -9217,7 +9377,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>729</v>
       </c>
@@ -9225,7 +9385,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>731</v>
       </c>
@@ -9233,7 +9393,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>733</v>
       </c>
@@ -9241,7 +9401,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>735</v>
       </c>
@@ -9249,7 +9409,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>737</v>
       </c>
@@ -9257,7 +9417,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>739</v>
       </c>
@@ -9265,7 +9425,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>741</v>
       </c>
@@ -9273,7 +9433,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>743</v>
       </c>
@@ -9281,7 +9441,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>745</v>
       </c>
@@ -9289,7 +9449,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>747</v>
       </c>
@@ -9297,7 +9457,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>749</v>
       </c>
@@ -9305,7 +9465,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>751</v>
       </c>
@@ -9313,7 +9473,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>753</v>
       </c>
@@ -9321,7 +9481,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>755</v>
       </c>
@@ -9329,7 +9489,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>757</v>
       </c>
@@ -9337,7 +9497,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>759</v>
       </c>
@@ -9345,7 +9505,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>761</v>
       </c>
@@ -9353,7 +9513,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>763</v>
       </c>
@@ -9361,7 +9521,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>765</v>
       </c>
@@ -9369,7 +9529,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>767</v>
       </c>
@@ -9377,7 +9537,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>769</v>
       </c>
@@ -9385,7 +9545,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>771</v>
       </c>
@@ -9393,7 +9553,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>773</v>
       </c>
@@ -9401,7 +9561,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>775</v>
       </c>
@@ -9409,7 +9569,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
         <v>777</v>
       </c>
@@ -9417,7 +9577,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>779</v>
       </c>
@@ -9425,7 +9585,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
         <v>781</v>
       </c>
@@ -9433,7 +9593,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>783</v>
       </c>
@@ -9441,7 +9601,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
         <v>785</v>
       </c>
@@ -9449,7 +9609,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3">
       <c r="A155" t="s">
         <v>787</v>
       </c>
@@ -9457,7 +9617,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3">
       <c r="A156" t="s">
         <v>789</v>
       </c>
@@ -9465,7 +9625,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
         <v>791</v>
       </c>
@@ -9473,7 +9633,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
         <v>793</v>
       </c>
@@ -9481,7 +9641,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
         <v>795</v>
       </c>
@@ -9489,7 +9649,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
         <v>797</v>
       </c>
@@ -9497,7 +9657,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3">
       <c r="A161" t="s">
         <v>799</v>
       </c>
@@ -9505,7 +9665,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3">
       <c r="A162" t="s">
         <v>801</v>
       </c>
@@ -9513,7 +9673,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3">
       <c r="A163" t="s">
         <v>803</v>
       </c>
@@ -9521,7 +9681,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3">
       <c r="A164" t="s">
         <v>805</v>
       </c>
@@ -9529,7 +9689,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3">
       <c r="A165" t="s">
         <v>807</v>
       </c>
@@ -9537,7 +9697,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3">
       <c r="A166" t="s">
         <v>809</v>
       </c>
@@ -9545,7 +9705,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3">
       <c r="A167" t="s">
         <v>811</v>
       </c>
@@ -9553,7 +9713,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3">
       <c r="A168" t="s">
         <v>813</v>
       </c>
@@ -9561,7 +9721,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3">
       <c r="A169" t="s">
         <v>815</v>
       </c>
@@ -9569,7 +9729,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3">
       <c r="A170" t="s">
         <v>817</v>
       </c>
@@ -9577,7 +9737,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3">
       <c r="A171" t="s">
         <v>819</v>
       </c>
@@ -9585,7 +9745,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3">
       <c r="A172" t="s">
         <v>821</v>
       </c>
@@ -9593,7 +9753,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>823</v>
       </c>
@@ -9601,7 +9761,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>825</v>
       </c>
@@ -9609,7 +9769,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3">
       <c r="A175" t="s">
         <v>827</v>
       </c>
@@ -9617,7 +9777,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
         <v>829</v>
       </c>
@@ -9625,7 +9785,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3">
       <c r="A177" t="s">
         <v>831</v>
       </c>
@@ -9633,7 +9793,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3">
       <c r="A178" t="s">
         <v>833</v>
       </c>
@@ -9641,7 +9801,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3">
       <c r="A179" t="s">
         <v>835</v>
       </c>
@@ -9649,7 +9809,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3">
       <c r="A180" t="s">
         <v>837</v>
       </c>
@@ -9657,7 +9817,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3">
       <c r="A181" t="s">
         <v>839</v>
       </c>
@@ -9665,7 +9825,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3">
       <c r="A182" t="s">
         <v>841</v>
       </c>
@@ -9673,7 +9833,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3">
       <c r="A183" t="s">
         <v>843</v>
       </c>
@@ -9681,7 +9841,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3">
       <c r="A184" t="s">
         <v>845</v>
       </c>
@@ -9689,7 +9849,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3">
       <c r="A185" t="s">
         <v>847</v>
       </c>
@@ -9697,7 +9857,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3">
       <c r="A186" t="s">
         <v>849</v>
       </c>
@@ -9705,7 +9865,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3">
       <c r="A187" t="s">
         <v>851</v>
       </c>
@@ -9722,13 +9882,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9739,7 +9899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>853</v>
       </c>
@@ -9750,7 +9910,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>856</v>
       </c>
@@ -9758,7 +9918,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>857</v>
       </c>
@@ -9769,7 +9929,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>860</v>
       </c>
@@ -9786,13 +9946,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9803,7 +9963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>861</v>
       </c>
@@ -9814,7 +9974,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>864</v>
       </c>
@@ -9825,7 +9985,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
         <v>867</v>
       </c>
@@ -9836,7 +9996,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
         <v>870</v>
       </c>
@@ -9856,13 +10016,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.1640625" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9873,7 +10033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>872</v>
       </c>
@@ -9884,7 +10044,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>875</v>
       </c>
@@ -9895,7 +10055,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>878</v>
       </c>
@@ -9906,7 +10066,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>881</v>
       </c>
@@ -9917,7 +10077,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>884</v>
       </c>
@@ -9937,14 +10097,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C60"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9955,7 +10115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>887</v>
       </c>
@@ -9966,7 +10126,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>890</v>
       </c>
@@ -9977,7 +10137,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>893</v>
       </c>
@@ -9988,7 +10148,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>896</v>
       </c>
@@ -9999,7 +10159,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
         <v>899</v>
       </c>
@@ -10010,7 +10170,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="8" t="s">
         <v>902</v>
       </c>
@@ -10021,7 +10181,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="8" t="s">
         <v>905</v>
       </c>
@@ -10032,7 +10192,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
         <v>908</v>
       </c>
@@ -10043,7 +10203,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
         <v>909</v>
       </c>
@@ -10054,7 +10214,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="8" t="s">
         <v>911</v>
       </c>
@@ -10065,7 +10225,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="8" t="s">
         <v>913</v>
       </c>
@@ -10076,7 +10236,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
         <v>915</v>
       </c>
@@ -10087,7 +10247,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
         <v>917</v>
       </c>
@@ -10098,7 +10258,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
         <v>919</v>
       </c>
@@ -10109,7 +10269,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
         <v>921</v>
       </c>
@@ -10120,7 +10280,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
         <v>923</v>
       </c>
@@ -10131,7 +10291,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" s="8" t="s">
         <v>925</v>
       </c>
@@ -10142,7 +10302,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
         <v>927</v>
       </c>
@@ -10153,7 +10313,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
         <v>929</v>
       </c>
@@ -10164,7 +10324,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
         <v>931</v>
       </c>
@@ -10175,7 +10335,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
         <v>933</v>
       </c>
@@ -10186,7 +10346,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
         <v>935</v>
       </c>
@@ -10197,7 +10357,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24" s="8" t="s">
         <v>937</v>
       </c>
@@ -10208,7 +10368,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25" s="8" t="s">
         <v>939</v>
       </c>
@@ -10219,7 +10379,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26" s="8" t="s">
         <v>941</v>
       </c>
@@ -10230,7 +10390,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27" s="8" t="s">
         <v>943</v>
       </c>
@@ -10241,7 +10401,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28" s="8" t="s">
         <v>945</v>
       </c>
@@ -10252,7 +10412,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
         <v>947</v>
       </c>
@@ -10263,7 +10423,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30" s="8" t="s">
         <v>949</v>
       </c>
@@ -10274,7 +10434,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
         <v>951</v>
       </c>
@@ -10285,7 +10445,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
         <v>953</v>
       </c>
@@ -10296,7 +10456,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
         <v>955</v>
       </c>
@@ -10307,7 +10467,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3">
       <c r="A34" s="8" t="s">
         <v>957</v>
       </c>
@@ -10318,7 +10478,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3">
       <c r="A35" s="8" t="s">
         <v>959</v>
       </c>
@@ -10329,9 +10489,9 @@
         <v>960</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>1195</v>
@@ -10340,9 +10500,9 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>1196</v>
@@ -10351,9 +10511,9 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>1197</v>
@@ -10362,9 +10522,9 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>1193</v>
@@ -10373,9 +10533,9 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>1194</v>
@@ -10384,9 +10544,9 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>1198</v>
@@ -10395,9 +10555,9 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>1199</v>
@@ -10406,9 +10566,9 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>1201</v>
@@ -10417,9 +10577,9 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>1200</v>
@@ -10428,9 +10588,9 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>1202</v>
@@ -10439,9 +10599,9 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>1203</v>
@@ -10450,9 +10610,9 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>1204</v>
@@ -10461,9 +10621,9 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>1205</v>
@@ -10472,9 +10632,9 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>1206</v>
@@ -10483,9 +10643,9 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>1207</v>
@@ -10494,9 +10654,9 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>1208</v>
@@ -10505,9 +10665,9 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>1209</v>
@@ -10516,9 +10676,9 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>1210</v>
@@ -10527,9 +10687,9 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>1211</v>
@@ -10538,9 +10698,9 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>1212</v>
@@ -10549,9 +10709,9 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>1213</v>
@@ -10560,9 +10720,9 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>1215</v>
@@ -10571,9 +10731,9 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>1214</v>
@@ -10582,9 +10742,9 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>1216</v>
@@ -10593,9 +10753,9 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>1217</v>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E09E6D-084F-BB4D-88E2-5577DE5EC379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5781CFF9-01F1-1948-906D-928932170FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="4080" windowWidth="28480" windowHeight="13880" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -3044,12 +3044,6 @@
     <t>S_DOMAIN_DESC</t>
   </si>
   <si>
-    <t>After each player move, the enemy deals one-round damage while the player is within its {value}-cell Manhattan range.</t>
-  </si>
-  <si>
-    <t>玩家每次移动后，若处于敌人的{value}格曼哈顿领域范围内，敌人造成一次单回合伤害。</t>
-  </si>
-  <si>
     <t>S_FLANK</t>
   </si>
   <si>
@@ -4164,6 +4158,12 @@
   </si>
   <si>
     <t>按 N 键可以快速使用，在这里可以查看更多快捷键。</t>
+  </si>
+  <si>
+    <t>玩家每次移动后，若处于敌人的{value}格范围内，敌人造成一次单回合伤害。</t>
+  </si>
+  <si>
+    <t>After each player move, the enemy deals one-round damage while the player is within its {value}-cell range.</t>
   </si>
 </sst>
 </file>
@@ -5202,134 +5202,134 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C65" t="s">
         <v>1299</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C68" t="s">
         <v>1304</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C69" t="s">
         <v>1307</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C70" t="s">
         <v>1310</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C71" t="s">
         <v>1313</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C72" t="s">
         <v>1316</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C73" t="s">
         <v>1319</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C76" t="s">
         <v>1360</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1362</v>
       </c>
     </row>
   </sheetData>
@@ -5527,389 +5527,389 @@
       <c r="A17" t="s">
         <v>1002</v>
       </c>
-      <c r="B17" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1004</v>
+      <c r="B17" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1371</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C18" t="s">
         <v>1005</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C19" t="s">
         <v>1008</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C20" t="s">
         <v>1011</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C21" t="s">
         <v>1014</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>1017</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C24" t="s">
         <v>1023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C25" t="s">
         <v>1026</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C26" t="s">
         <v>1029</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C27" t="s">
         <v>1032</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>1035</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>1038</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C30" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C31" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C32" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C33" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C34" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C35" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C36" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C37" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C38" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C40" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C41" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C42" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C44" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C45" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C46" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C47" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C48" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C49" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C50" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C51" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C52" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C53" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C54" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C55" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C56" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C57" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C58" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C59" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
   </sheetData>
@@ -5940,24 +5940,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C2" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C3" t="s">
         <v>1103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -5989,18 +5989,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>868</v>
@@ -6011,98 +6011,98 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>616</v>
@@ -6110,46 +6110,46 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
@@ -6184,10 +6184,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6195,10 +6195,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6206,10 +6206,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6217,10 +6217,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6228,7 +6228,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -6239,7 +6239,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -6250,7 +6250,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
@@ -6261,10 +6261,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6272,10 +6272,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6283,10 +6283,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6294,10 +6294,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6316,10 +6316,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6327,10 +6327,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6338,10 +6338,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6349,10 +6349,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6360,10 +6360,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6371,10 +6371,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6382,7 +6382,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>25</v>
@@ -6393,10 +6393,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6404,10 +6404,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6826,38 +6826,38 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="8" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="8" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7464,90 +7464,90 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1236</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>1239</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1273</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1356</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1358</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1369</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>1370</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -7676,7 +7676,7 @@
         <v>320</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>322</v>
@@ -7879,7 +7879,7 @@
         <v>368</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>369</v>
@@ -8316,46 +8316,46 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
   </sheetData>
@@ -9915,7 +9915,7 @@
         <v>856</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -9934,7 +9934,7 @@
         <v>860</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
   </sheetData>
@@ -10208,7 +10208,7 @@
         <v>909</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>910</v>
@@ -10219,7 +10219,7 @@
         <v>911</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>912</v>
@@ -10230,7 +10230,7 @@
         <v>913</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>914</v>
@@ -10241,7 +10241,7 @@
         <v>915</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>916</v>
@@ -10252,7 +10252,7 @@
         <v>917</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>918</v>
@@ -10263,7 +10263,7 @@
         <v>919</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>920</v>
@@ -10274,7 +10274,7 @@
         <v>921</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>922</v>
@@ -10285,7 +10285,7 @@
         <v>923</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>924</v>
@@ -10296,7 +10296,7 @@
         <v>925</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>926</v>
@@ -10307,7 +10307,7 @@
         <v>927</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>928</v>
@@ -10318,7 +10318,7 @@
         <v>929</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>930</v>
@@ -10329,7 +10329,7 @@
         <v>931</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>932</v>
@@ -10340,7 +10340,7 @@
         <v>933</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>934</v>
@@ -10351,7 +10351,7 @@
         <v>935</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>936</v>
@@ -10362,7 +10362,7 @@
         <v>937</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>938</v>
@@ -10373,7 +10373,7 @@
         <v>939</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>940</v>
@@ -10384,7 +10384,7 @@
         <v>941</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>942</v>
@@ -10395,7 +10395,7 @@
         <v>943</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>944</v>
@@ -10406,7 +10406,7 @@
         <v>945</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>946</v>
@@ -10417,7 +10417,7 @@
         <v>947</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>948</v>
@@ -10428,7 +10428,7 @@
         <v>949</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>950</v>
@@ -10439,7 +10439,7 @@
         <v>951</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>952</v>
@@ -10450,7 +10450,7 @@
         <v>953</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>954</v>
@@ -10461,7 +10461,7 @@
         <v>955</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>956</v>
@@ -10472,7 +10472,7 @@
         <v>957</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>958</v>
@@ -10483,7 +10483,7 @@
         <v>959</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>960</v>
@@ -10491,277 +10491,277 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5781CFF9-01F1-1948-906D-928932170FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0263CEDC-C360-5349-8E90-8F4B555C1DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="1373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1417">
   <si>
     <t>ID</t>
   </si>
@@ -122,51 +122,27 @@
     <t>DC_NPC06_1</t>
   </si>
   <si>
-    <t>咦\n这不是上次的公主吗</t>
-  </si>
-  <si>
     <t>DC_NPC06_2</t>
   </si>
   <si>
-    <t>你好，盗贼先生</t>
-  </si>
-  <si>
     <t>DC_NPC06_3</t>
   </si>
   <si>
-    <t>我就不多嘴问你此行目的了\n这一回冒险我仍然准备了大量的钥匙</t>
-  </si>
-  <si>
     <t>DC_NPC06_4</t>
   </si>
   <si>
-    <t>不足的话随时来找我吧</t>
-  </si>
-  <si>
     <t>DC_NPC07_1</t>
   </si>
   <si>
-    <t>你知道什么是攻击魔术和防御魔术吗</t>
-  </si>
-  <si>
     <t>DC_NPC07_2</t>
   </si>
   <si>
-    <t>它们都是一种特殊的秘术，在战斗中按Z和X可以使用。它能够消耗气息并搭配你的魔力，打出特殊效果</t>
-  </si>
-  <si>
     <t>DC_NPC07_3</t>
   </si>
   <si>
-    <t>但是这种魔术难以学习，只有达到一定等级才能成功使用</t>
-  </si>
-  <si>
     <t>DC_NPC08_1</t>
   </si>
   <si>
-    <t>想必你已经受够了这些恶心的弓兵以及疯狗一般的怪物</t>
-  </si>
-  <si>
     <t>DC_NPC08_2</t>
   </si>
   <si>
@@ -176,48 +152,21 @@
     <t>DC_NPC09_1</t>
   </si>
   <si>
-    <t>孩子，你终于到达这里了，一路上没少吃苦吧</t>
-  </si>
-  <si>
     <t>DC_NPC09_2</t>
   </si>
   <si>
-    <t>确实艰难…\n勇者先生当初一定很辛苦吧</t>
-  </si>
-  <si>
     <t>DC_NPC09_3</t>
   </si>
   <si>
     <t>DC_NPC09_4</t>
   </si>
   <si>
-    <t>这是自然</t>
-  </si>
-  <si>
     <t>DC_NPC09_5</t>
   </si>
   <si>
-    <t>看在是旧相识的份上，之后我会以$30的单价卖给你，不够的话尽管来找我吧</t>
-  </si>
-  <si>
-    <t>DC_NPC10_1</t>
-  </si>
-  <si>
-    <t>持有此物，你可以抵挡一半来自怪物的地图伤害…</t>
-  </si>
-  <si>
     <t>DC_NPC11_1</t>
   </si>
   <si>
-    <t>就要抵达塔顶了，一定要当心，做好万全准备再上去</t>
-  </si>
-  <si>
-    <t>DC_NPC11_2</t>
-  </si>
-  <si>
-    <t>对了\n据说前面的楼层隐藏着一种宝物，可以阻挡怪物从地图上对你造成的伤害</t>
-  </si>
-  <si>
     <t>DC_NPC12_1</t>
   </si>
   <si>
@@ -251,9 +200,6 @@
     <t>DC_P_25_3</t>
   </si>
   <si>
-    <t>你还好吗？\n你在这个水晶里面被封印了很久</t>
-  </si>
-  <si>
     <t>DC_B_25_4</t>
   </si>
   <si>
@@ -263,15 +209,9 @@
     <t>DC_P_25_5</t>
   </si>
   <si>
-    <t>魔物复辟了，我花费了不少时间才到达这里\n没想到还能再见到你</t>
-  </si>
-  <si>
     <t>DC_B_25_6</t>
   </si>
   <si>
-    <t>咳…\n下面情况恐怕也不容乐观</t>
-  </si>
-  <si>
     <t>DC_P_25_7</t>
   </si>
   <si>
@@ -281,27 +221,15 @@
     <t>DC_O_25_8</t>
   </si>
   <si>
-    <t>公主殿下！\n噢，还有勇者\n太好了，你们没事</t>
-  </si>
-  <si>
     <t>DC_B_25_9</t>
   </si>
   <si>
-    <t>二位，外面发生什么事了</t>
-  </si>
-  <si>
     <t>DC_O_25_10</t>
   </si>
   <si>
-    <t>这座塔又升到空中了</t>
-  </si>
-  <si>
     <t>DC_T_25_11</t>
   </si>
   <si>
-    <t>不过倒不全是坏消息\n外面的那些魔物像是被扯断了线的木偶，看起来失能了\n至少暂时不用担心它们侵略军的问题了</t>
-  </si>
-  <si>
     <t>DC_T_25_12</t>
   </si>
   <si>
@@ -311,9 +239,6 @@
     <t>DC_O_25_13</t>
   </si>
   <si>
-    <t>或许可以看看，目前塔内是否还有足够材料来改造飞羽\n和之前那样让我们一起下去</t>
-  </si>
-  <si>
     <t>DC_P_25_14</t>
   </si>
   <si>
@@ -323,15 +248,9 @@
     <t>DC_B_25_15</t>
   </si>
   <si>
-    <t>怎么了吗，公主殿下</t>
-  </si>
-  <si>
     <t>DC_P_25_16</t>
   </si>
   <si>
-    <t>主塔的顶部连通魔塔\n魔塔的底部会通向魔界</t>
-  </si>
-  <si>
     <t>DC_O_25_17</t>
   </si>
   <si>
@@ -341,55 +260,28 @@
     <t>DC_P_25_18</t>
   </si>
   <si>
-    <t>是的，或许我们可以到那边去\n如果可以将魔物问题彻底解决，那是最好的</t>
-  </si>
-  <si>
     <t>DC_T_25_19</t>
   </si>
   <si>
-    <t>这恐怕很危险</t>
-  </si>
-  <si>
     <t>DC_B_25_20</t>
   </si>
   <si>
-    <t>但是为了以后的安全，这值得尝试</t>
-  </si>
-  <si>
     <t>DC_O_25_21</t>
   </si>
   <si>
-    <t>和上一次不同\n现在有了两个通道\n二位恐怕只能各自通过其中的一个</t>
-  </si>
-  <si>
     <t>DC_T_25_22</t>
   </si>
   <si>
-    <t>这个传送阵后面有什么，目前也无法获知</t>
-  </si>
-  <si>
     <t>DC_O_25_23</t>
   </si>
   <si>
-    <t>二位要保重</t>
-  </si>
-  <si>
     <t>DC_O_25_24</t>
   </si>
   <si>
-    <t>我们暂时会在这里留守，观察外部的同时给二位提供支援</t>
-  </si>
-  <si>
     <t>DC_B_25_25</t>
   </si>
   <si>
-    <t>非常感谢</t>
-  </si>
-  <si>
     <t>DC_P_25_26</t>
-  </si>
-  <si>
-    <t>那么我们出发吧</t>
   </si>
   <si>
     <t>TITLE_START</t>
@@ -3443,13 +3335,7 @@
     <t>DC_NPC17_1</t>
   </si>
   <si>
-    <t>好好注意周边的墙壁哦\n嘻嘻嘻嘻…</t>
-  </si>
-  <si>
     <t>DC_NPC18_1</t>
-  </si>
-  <si>
-    <t>巧妙运用手中道具，不必与强敌作战就可前进</t>
   </si>
   <si>
     <t>DC_NPC18_2</t>
@@ -3791,9 +3677,6 @@
     <t>???</t>
   </si>
   <si>
-    <t>Do you know that?\nThe hot key could help you save much time.\nAs we always said, time is money.</t>
-  </si>
-  <si>
     <t>TM_04</t>
   </si>
   <si>
@@ -3839,12 +3722,6 @@
     <t>孩子，如今皇宫尚未沦陷，\n你更是有机会逃跑，\n你又何苦重回这个地方。</t>
   </si>
   <si>
-    <t xml:space="preserve">I cannot abandon my people and our lands to those beings. \nI must fulfill my duty. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">I see…\nUs old bones will keep giving you a hand.\nHere is another Mirror. \nKeep it safe. </t>
-  </si>
-  <si>
     <t>明白了，\n我们这帮老骨头会尽力帮助你，\n这是另一面「心镜」，\n要妥善保管。</t>
   </si>
   <si>
@@ -4004,9 +3881,6 @@
     <t>HOTKEY_MAGIC_DOOR</t>
   </si>
   <si>
-    <t>长话短说，这一次我也将为你提供随意门，先赠予你3个好了，按N键使用，没有忘记吧？</t>
-  </si>
-  <si>
     <t>Press H to view the hotkeys.</t>
   </si>
   <si>
@@ -4040,12 +3914,6 @@
     <t>The Bravant is gone.\nIn this hour of peril, I must shoulder this burden.</t>
   </si>
   <si>
-    <t>It is truly a great pity for his death.\nI crafted this feather with my own hands,\nmuch like the one he once wielded.\nI hope it will be of use to you.</t>
-  </si>
-  <si>
-    <t>Your Royal Highness!\nThe accessory you wear could enhance your power with your MAG.</t>
-  </si>
-  <si>
     <t>公主殿下\n你佩戴的头饰具有魔力加持效果。</t>
   </si>
   <si>
@@ -4053,9 +3921,6 @@
   </si>
   <si>
     <t>在你的攻击大于怪物防御时，\n你的魔力可以加持武器，\n在会心一击时可以通过魔力加持伤害，\n你的魔力越高、敌人的防御数值越高，\n加持效果越明显。</t>
-  </si>
-  <si>
-    <t>When you are able to wound your foe,\your MAG may empower your weapon.\nA critical strike shall then carry far greater force.\nThe greater your MAG,\nor the stronger your foe's DEF,\nthe more pronounced the resulting increase shall be.</t>
   </si>
   <si>
     <t>HOTKEY_SWITCH_PLAYER</t>
@@ -4164,6 +4029,273 @@
   </si>
   <si>
     <t>After each player move, the enemy deals one-round damage while the player is within its {value}-cell range.</t>
+  </si>
+  <si>
+    <t>I cannot abandon my people and our lands to those beings. \nI must fulfil my duty.</t>
+  </si>
+  <si>
+    <t>I understand…\nWe elders shall do all we can to aid you.\nHere is another Mirror.\nKeep it safe.</t>
+  </si>
+  <si>
+    <t>Did you know?\nKeyboard shortcuts allow you to act more swiftly.\nTime is life itself, would you not agree?</t>
+  </si>
+  <si>
+    <t>Alas, his death is a grievous loss.\nI crafted this feather with my own hands,\nmuch like the golden feather he once carried.\nI hope it will be of use to you.</t>
+  </si>
+  <si>
+    <t>Your Royal Highness,\nthe headdress you wear can channel your magic\nto lend strength to your blows.</t>
+  </si>
+  <si>
+    <t>When your ATK exceeds your foe's DEF,\nyour MAG can lend power to your weapon,\ncausing a critical strike to deal greater damage.\nThe higher your MAG and your foe's DEF,\nthe greater this increase shall be.</t>
+  </si>
+  <si>
+    <t>Well, well!\nIf it isn't the princess from last time.</t>
+  </si>
+  <si>
+    <t>I won't pry into what brings you here.\nI've brought plenty of keys for this little adventure, too.</t>
+  </si>
+  <si>
+    <t>If you're running short, you know where to find me.</t>
+  </si>
+  <si>
+    <t>Are you familiar with offensive and defensive magic?</t>
+  </si>
+  <si>
+    <t>Both are arcane arts.\nIn battle, press Z for offensive magic and X for defensive magic.\nThey consume Breath and draw upon your MAG\nto produce their special effects.</t>
+  </si>
+  <si>
+    <t>You must surely have grown weary of those wretched archers\nand the creatures that pursue you like rabid hounds.</t>
+  </si>
+  <si>
+    <t>The elder who once supplied your party with Magic Doors is upstairs.\nI urge you to seek him out.</t>
+  </si>
+  <si>
+    <t>My child, you have reached me at last.\nThe journey must have been a bitter trial.</t>
+  </si>
+  <si>
+    <t>It has indeed…\nHow much the Bravant must have endured before me.</t>
+  </si>
+  <si>
+    <t>To be brief, I shall supply you with Magic Doors once more.\nLet these first three be my gift to you.\nYou remember to press N to use them, I trust?</t>
+  </si>
+  <si>
+    <t>Indeed, I do.</t>
+  </si>
+  <si>
+    <t>For an old acquaintance, my price shall be $30 apiece.\nShould you need more, you need only ask.</t>
+  </si>
+  <si>
+    <t>The summit is near. You must take great care.\nSee that you are fully prepared before you ascend.</t>
+  </si>
+  <si>
+    <t>It is the Bravant!</t>
+  </si>
+  <si>
+    <t>Stand aside, fiend!</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Are you well?\nYou have been sealed within this crystal for so long.</t>
+  </si>
+  <si>
+    <t>Your Royal Highness…\nHow did you…?</t>
+  </si>
+  <si>
+    <t>The monsters have returned. It has taken me so long to reach you.\nI had not thought we would meet again.</t>
+  </si>
+  <si>
+    <t>What was that sound…?</t>
+  </si>
+  <si>
+    <t>Your Royal Highness!\nAh, and the Bravant as well.\nWhat a relief to find you both unharmed.</t>
+  </si>
+  <si>
+    <t>My friends, what has happened outside?</t>
+  </si>
+  <si>
+    <t>The tower has risen into the sky once more.</t>
+  </si>
+  <si>
+    <t>Still, it's not all bad news.\nThe monsters outside have gone limp, like puppets with cut strings.\nAt least we won't have their army to worry about for a while.</t>
+  </si>
+  <si>
+    <t>Trouble is, how are we going to get down…?</t>
+  </si>
+  <si>
+    <t>Perhaps enough materials remain within the tower to modify the feather.\nThen it could carry us all down, as it did before.</t>
+  </si>
+  <si>
+    <t>About that…</t>
+  </si>
+  <si>
+    <t>What is it, Your Royal Highness?</t>
+  </si>
+  <si>
+    <t>The summit of the Main Tower connects to the Demon Tower.\nAt the foot of the Demon Tower lies a passage to Devilheim.</t>
+  </si>
+  <si>
+    <t>Surely you do not mean to…?</t>
+  </si>
+  <si>
+    <t>I do. Perhaps we could venture there.\nIf we could end this scourge once and for all,\nthere could be no better outcome.</t>
+  </si>
+  <si>
+    <t>That sounds like a dangerous business.</t>
+  </si>
+  <si>
+    <t>Even so, for the sake of lasting peace, we must try.</t>
+  </si>
+  <si>
+    <t>Unlike before, there are now two passages.\nI fear you must each take a separate path.</t>
+  </si>
+  <si>
+    <t>And there's no telling what lies beyond this magic circle.</t>
+  </si>
+  <si>
+    <t>Take care, both of you.</t>
+  </si>
+  <si>
+    <t>For now, we shall remain here and keep watch outside.\nWe shall offer you what aid we can.</t>
+  </si>
+  <si>
+    <t>You have my deepest thanks.</t>
+  </si>
+  <si>
+    <t>Then let us be on our way.</t>
+  </si>
+  <si>
+    <t>Our task must come first. There is no time to turn back…</t>
+  </si>
+  <si>
+    <t>Do pay close attention to the walls about you.\nHee hee hee…</t>
+  </si>
+  <si>
+    <t>Use the items in your possession wisely,\nand you may advance without crossing blades with mighty foes.</t>
+  </si>
+  <si>
+    <t>By the way, might I interest you in some Jin Kela fertiliser?</t>
+  </si>
+  <si>
+    <t>Ah…\nAm I still alive?</t>
+  </si>
+  <si>
+    <t>Into...luda…koros…</t>
+  </si>
+  <si>
+    <t>I fear matters below are scarcely better.</t>
+  </si>
+  <si>
+    <t>Good day to you, mister.</t>
+  </si>
+  <si>
+    <t>你好，盗贼先生。</t>
+  </si>
+  <si>
+    <t>咦。\n这不是上次的公主吗。</t>
+  </si>
+  <si>
+    <t>我就不多嘴问你此行目的了。\n这一回冒险我仍然准备了大量的钥匙。</t>
+  </si>
+  <si>
+    <t>不足的话随时来找我吧。</t>
+  </si>
+  <si>
+    <t>你知道什么是攻击魔术和防御魔术吗。</t>
+  </si>
+  <si>
+    <t>它们都是一种特殊的秘术，在战斗中按Z和X可以使用。\n它能够消耗气息并搭配你的魔力，打出特殊效果。</t>
+  </si>
+  <si>
+    <t>但是这种魔术难以学习，越是高级的技能守护它的敌人就越强。</t>
+  </si>
+  <si>
+    <t>Yet such arts are difficult to master.\nThe more powerful the art is, the more fierce the guard could be.</t>
+  </si>
+  <si>
+    <t>想必你已经受够了这些恶心的弓兵以及疯狗一般的怪物。</t>
+  </si>
+  <si>
+    <t>孩子，你终于到达这里了，一路上没少吃苦吧。</t>
+  </si>
+  <si>
+    <t>确实艰难…\n勇者先生当初一定很辛苦吧。</t>
+  </si>
+  <si>
+    <t>长话短说，这一次我也将为你提供随意门，\n先赠予你3个好了，按N键使用，没有忘记吧？</t>
+  </si>
+  <si>
+    <t>这是自然。</t>
+  </si>
+  <si>
+    <t>看在是旧相识的份上，之后我会以$30的单价卖给你，不够的话尽管来找我吧。</t>
+  </si>
+  <si>
+    <t>就要抵达塔顶了，一定要当心，做好万全准备再上去。</t>
+  </si>
+  <si>
+    <t>咳…\n下面情况恐怕也不容乐观。</t>
+  </si>
+  <si>
+    <t>你还好吗？\n你在这个水晶里面被封印了很久。</t>
+  </si>
+  <si>
+    <t>魔物复辟了，我花费了不少时间才到达这里\n没想到还能再见到你。</t>
+  </si>
+  <si>
+    <t>公主殿下！\n噢，还有勇者。\n太好了，你们没事。</t>
+  </si>
+  <si>
+    <t>二位，外面发生什么事了？</t>
+  </si>
+  <si>
+    <t>这座塔又升到空中了。</t>
+  </si>
+  <si>
+    <t>不过倒不全是坏消息，\n外面的那些魔物像是被扯断了线的木偶，看起来失能了，\n至少暂时不用担心它们侵略军的问题了。</t>
+  </si>
+  <si>
+    <t>或许可以看看，目前塔内是否还有足够材料来改造飞羽，\n和之前那样让我们一起下去。</t>
+  </si>
+  <si>
+    <t>怎么了吗，公主殿下？</t>
+  </si>
+  <si>
+    <t>主塔的顶部连通魔塔，\n魔塔的底部会通向魔界。</t>
+  </si>
+  <si>
+    <t>是的，或许我们可以到那边去，\n如果可以将魔物问题彻底解决，那是最好的。</t>
+  </si>
+  <si>
+    <t>这恐怕很危险。</t>
+  </si>
+  <si>
+    <t>但是为了以后的安全，这值得尝试。</t>
+  </si>
+  <si>
+    <t>和上一次不同\n现在有了两个通道，\n二位恐怕只能各自通过其中的一个。</t>
+  </si>
+  <si>
+    <t>这个传送阵后面有什么，目前也无法获知。</t>
+  </si>
+  <si>
+    <t>二位要保重。</t>
+  </si>
+  <si>
+    <t>我们暂时会在这里留守，观察外部的同时给二位提供支援。</t>
+  </si>
+  <si>
+    <t>非常感谢。</t>
+  </si>
+  <si>
+    <t>那么我们出发吧。</t>
+  </si>
+  <si>
+    <t>好好注意周边的墙壁哦，\n嘻嘻嘻嘻…</t>
+  </si>
+  <si>
+    <t>巧妙运用手中道具，不必与强敌作战就可前进。</t>
   </si>
 </sst>
 </file>
@@ -4509,827 +4641,827 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="C34" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="B35" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="C35" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="4" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="C47" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="C53" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="C54" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="32" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="32" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="32" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="32" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="32" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="32" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="C61" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="B62" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="B63" t="s">
-        <v>299</v>
+        <v>263</v>
       </c>
       <c r="C63" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="B64" t="s">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="C64" t="s">
-        <v>303</v>
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>1297</v>
+        <v>1256</v>
       </c>
       <c r="B65" t="s">
-        <v>1298</v>
+        <v>1257</v>
       </c>
       <c r="C65" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>1300</v>
+        <v>1259</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1342</v>
+        <v>1297</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1340</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>1301</v>
+        <v>1260</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1343</v>
+        <v>1298</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>1341</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>1302</v>
+        <v>1261</v>
       </c>
       <c r="B68" t="s">
-        <v>1303</v>
+        <v>1262</v>
       </c>
       <c r="C68" t="s">
-        <v>1304</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>1305</v>
+        <v>1264</v>
       </c>
       <c r="B69" t="s">
-        <v>1306</v>
+        <v>1265</v>
       </c>
       <c r="C69" t="s">
-        <v>1307</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>1308</v>
+        <v>1267</v>
       </c>
       <c r="B70" t="s">
-        <v>1309</v>
+        <v>1268</v>
       </c>
       <c r="C70" t="s">
-        <v>1310</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>1311</v>
+        <v>1270</v>
       </c>
       <c r="B71" t="s">
-        <v>1312</v>
+        <v>1271</v>
       </c>
       <c r="C71" t="s">
-        <v>1313</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>1314</v>
+        <v>1273</v>
       </c>
       <c r="B72" t="s">
-        <v>1315</v>
+        <v>1274</v>
       </c>
       <c r="C72" t="s">
-        <v>1316</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>1317</v>
+        <v>1276</v>
       </c>
       <c r="B73" t="s">
-        <v>1318</v>
+        <v>1277</v>
       </c>
       <c r="C73" t="s">
-        <v>1319</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>1320</v>
+        <v>1279</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1325</v>
+        <v>1283</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1324</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>1339</v>
+        <v>1294</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1345</v>
+        <v>1300</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1344</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>1358</v>
+        <v>1313</v>
       </c>
       <c r="B76" t="s">
-        <v>1359</v>
+        <v>1314</v>
       </c>
       <c r="C76" t="s">
-        <v>1360</v>
+        <v>1315</v>
       </c>
     </row>
   </sheetData>
@@ -5360,556 +5492,556 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>961</v>
+        <v>925</v>
       </c>
       <c r="B2" t="s">
-        <v>873</v>
+        <v>837</v>
       </c>
       <c r="C2" t="s">
-        <v>962</v>
+        <v>926</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>963</v>
+        <v>927</v>
       </c>
       <c r="B3" t="s">
-        <v>964</v>
+        <v>928</v>
       </c>
       <c r="C3" t="s">
-        <v>965</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>966</v>
+        <v>930</v>
       </c>
       <c r="B4" t="s">
-        <v>967</v>
+        <v>931</v>
       </c>
       <c r="C4" t="s">
-        <v>877</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>968</v>
+        <v>932</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>969</v>
+        <v>933</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>970</v>
+        <v>934</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>971</v>
+        <v>935</v>
       </c>
       <c r="B6" t="s">
-        <v>972</v>
+        <v>936</v>
       </c>
       <c r="C6" t="s">
-        <v>883</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>973</v>
+        <v>937</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>974</v>
+        <v>938</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>975</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>976</v>
+        <v>940</v>
       </c>
       <c r="B8" t="s">
-        <v>977</v>
+        <v>941</v>
       </c>
       <c r="C8" t="s">
-        <v>978</v>
+        <v>942</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>979</v>
+        <v>943</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>980</v>
+        <v>944</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>981</v>
+        <v>945</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>982</v>
+        <v>946</v>
       </c>
       <c r="B10" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
-        <v>983</v>
+        <v>947</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>984</v>
+        <v>948</v>
       </c>
       <c r="B11" t="s">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>986</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>987</v>
+        <v>951</v>
       </c>
       <c r="B12" t="s">
-        <v>988</v>
+        <v>952</v>
       </c>
       <c r="C12" t="s">
-        <v>989</v>
+        <v>953</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>990</v>
+        <v>954</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>991</v>
+        <v>955</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>992</v>
+        <v>956</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>993</v>
+        <v>957</v>
       </c>
       <c r="B14" t="s">
-        <v>994</v>
+        <v>958</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>995</v>
+        <v>959</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>996</v>
+        <v>960</v>
       </c>
       <c r="B15" t="s">
-        <v>997</v>
+        <v>961</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>998</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>999</v>
+        <v>963</v>
       </c>
       <c r="B16" t="s">
-        <v>1000</v>
+        <v>964</v>
       </c>
       <c r="C16" t="s">
-        <v>1001</v>
+        <v>965</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>1002</v>
+        <v>966</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1372</v>
+        <v>1327</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1371</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>1003</v>
+        <v>967</v>
       </c>
       <c r="B18" t="s">
-        <v>1004</v>
+        <v>968</v>
       </c>
       <c r="C18" t="s">
-        <v>1005</v>
+        <v>969</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>1006</v>
+        <v>970</v>
       </c>
       <c r="B19" t="s">
-        <v>1007</v>
+        <v>971</v>
       </c>
       <c r="C19" t="s">
-        <v>1008</v>
+        <v>972</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>1009</v>
+        <v>973</v>
       </c>
       <c r="B20" t="s">
-        <v>1010</v>
+        <v>974</v>
       </c>
       <c r="C20" t="s">
-        <v>1011</v>
+        <v>975</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>1012</v>
+        <v>976</v>
       </c>
       <c r="B21" t="s">
-        <v>1013</v>
+        <v>977</v>
       </c>
       <c r="C21" t="s">
-        <v>1014</v>
+        <v>978</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>1015</v>
+        <v>979</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1016</v>
+        <v>980</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1017</v>
+        <v>981</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>1018</v>
+        <v>982</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1019</v>
+        <v>983</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1020</v>
+        <v>984</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>1021</v>
+        <v>985</v>
       </c>
       <c r="B24" t="s">
-        <v>1022</v>
+        <v>986</v>
       </c>
       <c r="C24" t="s">
-        <v>1023</v>
+        <v>987</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>1024</v>
+        <v>988</v>
       </c>
       <c r="B25" t="s">
-        <v>1025</v>
+        <v>989</v>
       </c>
       <c r="C25" t="s">
-        <v>1026</v>
+        <v>990</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>1027</v>
+        <v>991</v>
       </c>
       <c r="B26" t="s">
-        <v>1028</v>
+        <v>992</v>
       </c>
       <c r="C26" t="s">
-        <v>1029</v>
+        <v>993</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>1030</v>
+        <v>994</v>
       </c>
       <c r="B27" t="s">
-        <v>1031</v>
+        <v>995</v>
       </c>
       <c r="C27" t="s">
-        <v>1032</v>
+        <v>996</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>1033</v>
+        <v>997</v>
       </c>
       <c r="B28" t="s">
-        <v>1034</v>
+        <v>998</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1035</v>
+        <v>999</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>1036</v>
+        <v>1000</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1037</v>
+        <v>1001</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1038</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>1039</v>
+        <v>1003</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1326</v>
+        <v>1284</v>
       </c>
       <c r="C30" t="s">
-        <v>1040</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>1041</v>
+        <v>1005</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1327</v>
+        <v>1285</v>
       </c>
       <c r="C31" t="s">
-        <v>1042</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>1043</v>
+        <v>1007</v>
       </c>
       <c r="C32" t="s">
-        <v>1044</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>1045</v>
+        <v>1009</v>
       </c>
       <c r="C33" t="s">
-        <v>1046</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>1047</v>
+        <v>1011</v>
       </c>
       <c r="C34" t="s">
-        <v>1048</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>1049</v>
+        <v>1013</v>
       </c>
       <c r="C35" t="s">
-        <v>1050</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>1051</v>
+        <v>1015</v>
       </c>
       <c r="C36" t="s">
-        <v>1052</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>1053</v>
+        <v>1017</v>
       </c>
       <c r="C37" t="s">
-        <v>1054</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>1055</v>
+        <v>1019</v>
       </c>
       <c r="C38" t="s">
-        <v>1056</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>1057</v>
+        <v>1021</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1058</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>1059</v>
+        <v>1023</v>
       </c>
       <c r="C40" t="s">
-        <v>1060</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>1061</v>
+        <v>1025</v>
       </c>
       <c r="C41" t="s">
-        <v>1062</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>1063</v>
+        <v>1027</v>
       </c>
       <c r="C42" t="s">
-        <v>1064</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1065</v>
+        <v>1029</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>1066</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1067</v>
+        <v>1031</v>
       </c>
       <c r="C44" t="s">
-        <v>1068</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1069</v>
+        <v>1033</v>
       </c>
       <c r="C45" t="s">
-        <v>1070</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1071</v>
+        <v>1035</v>
       </c>
       <c r="C46" t="s">
-        <v>1072</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1073</v>
+        <v>1037</v>
       </c>
       <c r="C47" t="s">
-        <v>1074</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1075</v>
+        <v>1039</v>
       </c>
       <c r="C48" t="s">
-        <v>1076</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1077</v>
+        <v>1041</v>
       </c>
       <c r="C49" t="s">
-        <v>1078</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1079</v>
+        <v>1043</v>
       </c>
       <c r="C50" t="s">
-        <v>1080</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1081</v>
+        <v>1045</v>
       </c>
       <c r="C51" t="s">
-        <v>1082</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>1083</v>
+        <v>1047</v>
       </c>
       <c r="C52" t="s">
-        <v>1084</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>1085</v>
+        <v>1049</v>
       </c>
       <c r="C53" t="s">
-        <v>1086</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1087</v>
+        <v>1051</v>
       </c>
       <c r="C54" t="s">
-        <v>1088</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1089</v>
+        <v>1053</v>
       </c>
       <c r="C55" t="s">
-        <v>1090</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1091</v>
+        <v>1055</v>
       </c>
       <c r="C56" t="s">
-        <v>1092</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>1093</v>
+        <v>1057</v>
       </c>
       <c r="C57" t="s">
-        <v>1094</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1095</v>
+        <v>1059</v>
       </c>
       <c r="C58" t="s">
-        <v>1096</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>1097</v>
+        <v>1061</v>
       </c>
       <c r="C59" t="s">
-        <v>1098</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -5940,24 +6072,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>1099</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1216</v>
+        <v>1178</v>
       </c>
       <c r="C2" t="s">
-        <v>1100</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>1101</v>
+        <v>1065</v>
       </c>
       <c r="B3" t="s">
-        <v>1102</v>
+        <v>1066</v>
       </c>
       <c r="C3" t="s">
-        <v>1103</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -5989,167 +6121,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>1104</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1217</v>
+        <v>1179</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1105</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>1106</v>
+        <v>1070</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>869</v>
+        <v>833</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>1131</v>
+        <v>1095</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1216</v>
+        <v>1178</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1107</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>1108</v>
+        <v>1072</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1230</v>
+        <v>1192</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1109</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>1110</v>
+        <v>1074</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1218</v>
+        <v>1180</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1111</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>1112</v>
+        <v>1076</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1219</v>
+        <v>1181</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1113</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>1114</v>
+        <v>1078</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1220</v>
+        <v>1182</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1115</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>1116</v>
+        <v>1080</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1221</v>
+        <v>1183</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1117</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6" t="s">
-        <v>1118</v>
+        <v>1082</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1222</v>
+        <v>1184</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1119</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>1120</v>
+        <v>1084</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1223</v>
+        <v>1185</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1121</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="6" t="s">
-        <v>1122</v>
+        <v>1086</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1224</v>
+        <v>1186</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>616</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6" t="s">
-        <v>1123</v>
+        <v>1087</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1225</v>
+        <v>1187</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1124</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6" t="s">
-        <v>1125</v>
+        <v>1089</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1226</v>
+        <v>1188</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1126</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6" t="s">
-        <v>1127</v>
+        <v>1091</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1227</v>
+        <v>1189</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1128</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6" t="s">
-        <v>1129</v>
+        <v>1093</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1228</v>
+        <v>1190</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1130</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
@@ -6160,7 +6292,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -6184,10 +6316,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1252</v>
+        <v>1213</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1253</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6195,10 +6327,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1254</v>
+        <v>1215</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1255</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6206,10 +6338,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1256</v>
+        <v>1217</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1257</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6217,10 +6349,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1259</v>
+        <v>1220</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1258</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6228,7 +6360,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1260</v>
+        <v>1221</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -6239,7 +6371,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1240</v>
+        <v>1202</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -6250,7 +6382,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1241</v>
+        <v>1203</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
@@ -6261,10 +6393,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1261</v>
+        <v>1222</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1262</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6272,10 +6404,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1263</v>
+        <v>1224</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1243</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6283,10 +6415,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1264</v>
+        <v>1225</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1265</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6294,10 +6426,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1266</v>
+        <v>1328</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1244</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6305,10 +6437,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1267</v>
+        <v>1329</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1268</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6316,10 +6448,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1246</v>
+        <v>1208</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1245</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6327,10 +6459,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1250</v>
+        <v>1330</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1247</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6338,10 +6470,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1249</v>
+        <v>1211</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1248</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6349,10 +6481,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1329</v>
+        <v>1287</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1328</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6360,10 +6492,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1332</v>
+        <v>1290</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1331</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6371,10 +6503,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1330</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6382,7 +6514,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1246</v>
+        <v>1208</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>25</v>
@@ -6393,10 +6525,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1335</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6404,461 +6536,549 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1337</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
-        <v>29</v>
+      <c r="B23" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1382</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1381</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1383</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1384</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1385</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1386</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1387</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1389</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>1340</v>
+      </c>
       <c r="C31" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1390</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6" t="s">
-        <v>1321</v>
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1393</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1394</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1395</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>1347</v>
+      </c>
       <c r="C38" s="6" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1378</v>
+      </c>
       <c r="C39" s="6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>1348</v>
+      </c>
       <c r="C40" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6" t="s">
-        <v>64</v>
+      <c r="A41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6" t="s">
-        <v>66</v>
+      <c r="A42" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>1350</v>
+      </c>
       <c r="C43" s="8" t="s">
-        <v>68</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>1351</v>
+      </c>
       <c r="C44" s="8" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>1352</v>
+      </c>
       <c r="C45" s="8" t="s">
-        <v>72</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>1379</v>
+      </c>
       <c r="C46" s="8" t="s">
-        <v>74</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>1353</v>
+      </c>
       <c r="C47" s="8" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>1354</v>
+      </c>
       <c r="C48" s="8" t="s">
-        <v>78</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="6"/>
+        <v>62</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>1355</v>
+      </c>
       <c r="C49" s="8" t="s">
-        <v>80</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>1356</v>
+      </c>
       <c r="C50" s="8" t="s">
-        <v>82</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" s="6"/>
+        <v>64</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>1357</v>
+      </c>
       <c r="C51" s="8" t="s">
-        <v>84</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B52" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>1358</v>
+      </c>
       <c r="C52" s="8" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>1359</v>
+      </c>
       <c r="C53" s="8" t="s">
-        <v>88</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>1360</v>
+      </c>
       <c r="C54" s="8" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>1361</v>
+      </c>
       <c r="C55" s="8" t="s">
-        <v>92</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>1362</v>
+      </c>
       <c r="C56" s="8" t="s">
-        <v>94</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B57" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>1363</v>
+      </c>
       <c r="C57" s="8" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B58" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>1364</v>
+      </c>
       <c r="C58" s="8" t="s">
-        <v>98</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>1365</v>
+      </c>
       <c r="C59" s="8" t="s">
-        <v>100</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>1366</v>
+      </c>
       <c r="C60" s="8" t="s">
-        <v>102</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>1367</v>
+      </c>
       <c r="C61" s="8" t="s">
-        <v>104</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="6"/>
+        <v>78</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>1368</v>
+      </c>
       <c r="C62" s="8" t="s">
-        <v>106</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>1369</v>
+      </c>
       <c r="C63" s="8" t="s">
-        <v>108</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B64" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>1370</v>
+      </c>
       <c r="C64" s="8" t="s">
-        <v>110</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B65" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>1371</v>
+      </c>
       <c r="C65" s="8" t="s">
-        <v>112</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B66" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>1372</v>
+      </c>
       <c r="C66" s="8" t="s">
-        <v>114</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B67" s="6"/>
+        <v>1096</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>1373</v>
+      </c>
       <c r="C67" s="8" t="s">
-        <v>116</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" s="6"/>
+        <v>1098</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>1374</v>
+      </c>
       <c r="C68" s="8" t="s">
-        <v>118</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B69" s="6"/>
+        <v>1099</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>1375</v>
+      </c>
       <c r="C69" s="8" t="s">
-        <v>1133</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="8" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B70" s="6"/>
+        <v>1100</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>1376</v>
+      </c>
       <c r="C70" s="8" t="s">
-        <v>1135</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="8" t="s">
-        <v>1136</v>
-      </c>
+      <c r="A71" s="6"/>
       <c r="B71" s="6"/>
-      <c r="C71" s="8" t="s">
-        <v>1137</v>
-      </c>
+      <c r="C71" s="6"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="8" t="s">
-        <v>1138</v>
-      </c>
+      <c r="A72" s="6"/>
       <c r="B72" s="6"/>
-      <c r="C72" s="8" t="s">
-        <v>1139</v>
-      </c>
+      <c r="C72" s="6"/>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="6"/>
@@ -7424,16 +7644,6 @@
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
-    </row>
-    <row r="186" spans="1:3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-    </row>
-    <row r="187" spans="1:3">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -7464,90 +7674,90 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>1232</v>
+        <v>1194</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1234</v>
+        <v>1196</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1233</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>1235</v>
+        <v>1197</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1237</v>
+        <v>1199</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1236</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>1238</v>
+        <v>1200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1357</v>
+        <v>1312</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1239</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>1251</v>
+        <v>1212</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1322</v>
+        <v>1280</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1323</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>1269</v>
+        <v>1228</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1271</v>
+        <v>1230</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1270</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>1354</v>
+        <v>1309</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1356</v>
+        <v>1311</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1355</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>1365</v>
+        <v>1320</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1367</v>
+        <v>1322</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1366</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>1368</v>
+        <v>1323</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1369</v>
+        <v>1324</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1370</v>
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -7577,10 +7787,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>268</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7588,10 +7798,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -7618,167 +7828,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1336</v>
+        <v>1292</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>343</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="C15" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="C16" t="s">
-        <v>349</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -7810,552 +8020,552 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="B3" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C5" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1242</v>
+        <v>1204</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="B12" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="C12" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="B13" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="C13" t="s">
-        <v>384</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="B14" t="s">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="C14" t="s">
-        <v>387</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C15" t="s">
-        <v>390</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>391</v>
+        <v>355</v>
       </c>
       <c r="B16" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="C16" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="B17" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="C17" t="s">
-        <v>396</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="C18" t="s">
-        <v>399</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="B19" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="C19" t="s">
-        <v>402</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="B20" t="s">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="C20" t="s">
-        <v>405</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="B21" t="s">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="C21" t="s">
-        <v>408</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="B22" t="s">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="C22" t="s">
-        <v>411</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="B23" t="s">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="C23" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="B24" t="s">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="C24" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="B25" t="s">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="B26" t="s">
-        <v>422</v>
+        <v>386</v>
       </c>
       <c r="C26" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="B27" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="C27" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="B28" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="C28" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="B30" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="C30" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="B31" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="C31" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="B32" t="s">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="C32" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="B34" t="s">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="C34" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="B35" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="C35" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="B36" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="C36" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="B37" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="C37" t="s">
-        <v>456</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="B38" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="C38" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="B39" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="C39" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="B40" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="C40" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="B41" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="C41" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="B42" t="s">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="C42" t="s">
-        <v>471</v>
+        <v>435</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="B43" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="C43" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="B44" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="C44" t="s">
-        <v>477</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="C45" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>481</v>
+        <v>445</v>
       </c>
       <c r="B46" t="s">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="C46" t="s">
-        <v>483</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>484</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="C47" t="s">
-        <v>486</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1346</v>
+        <v>1301</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1350</v>
+        <v>1305</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1351</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1347</v>
+        <v>1302</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1362</v>
+        <v>1317</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1363</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1348</v>
+        <v>1303</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1352</v>
+        <v>1307</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1353</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1349</v>
+        <v>1304</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1364</v>
+        <v>1319</v>
       </c>
     </row>
   </sheetData>
@@ -8387,1490 +8597,1490 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="C2" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="C3" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>460</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="C5" t="s">
-        <v>499</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>500</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="C7" t="s">
-        <v>503</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="C8" t="s">
-        <v>505</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="C9" t="s">
-        <v>507</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="C10" t="s">
-        <v>509</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>510</v>
+        <v>474</v>
       </c>
       <c r="C11" t="s">
-        <v>511</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>512</v>
+        <v>476</v>
       </c>
       <c r="C12" t="s">
-        <v>513</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="C13" t="s">
-        <v>515</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>516</v>
+        <v>480</v>
       </c>
       <c r="C14" t="s">
-        <v>517</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>518</v>
+        <v>482</v>
       </c>
       <c r="C15" t="s">
-        <v>488</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>519</v>
+        <v>483</v>
       </c>
       <c r="C16" t="s">
-        <v>520</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="C17" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="C18" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>525</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
-        <v>526</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="C20" t="s">
-        <v>528</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="C21" t="s">
-        <v>530</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="C22" t="s">
-        <v>491</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>532</v>
+        <v>496</v>
       </c>
       <c r="C23" t="s">
-        <v>492</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>533</v>
+        <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>534</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>535</v>
+        <v>499</v>
       </c>
       <c r="C25" t="s">
-        <v>536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>537</v>
+        <v>501</v>
       </c>
       <c r="C26" t="s">
-        <v>493</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>538</v>
+        <v>502</v>
       </c>
       <c r="C27" t="s">
-        <v>539</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>540</v>
+        <v>504</v>
       </c>
       <c r="C28" t="s">
-        <v>541</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>542</v>
+        <v>506</v>
       </c>
       <c r="C29" t="s">
-        <v>543</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="C30" t="s">
-        <v>487</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="C31" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>547</v>
+        <v>511</v>
       </c>
       <c r="C32" t="s">
-        <v>548</v>
+        <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="C33" t="s">
-        <v>550</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>551</v>
+        <v>515</v>
       </c>
       <c r="C34" t="s">
-        <v>552</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>553</v>
+        <v>517</v>
       </c>
       <c r="C35" t="s">
-        <v>554</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="C36" t="s">
-        <v>556</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="C37" t="s">
-        <v>558</v>
+        <v>522</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>559</v>
+        <v>523</v>
       </c>
       <c r="C38" t="s">
-        <v>560</v>
+        <v>524</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="C39" t="s">
-        <v>562</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="C40" t="s">
-        <v>564</v>
+        <v>528</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>565</v>
+        <v>529</v>
       </c>
       <c r="C41" t="s">
-        <v>566</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="C42" t="s">
-        <v>568</v>
+        <v>532</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="C43" t="s">
-        <v>570</v>
+        <v>534</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
-        <v>572</v>
+        <v>536</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>573</v>
+        <v>537</v>
       </c>
       <c r="C45" t="s">
-        <v>574</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="C46" t="s">
-        <v>576</v>
+        <v>540</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>577</v>
+        <v>541</v>
       </c>
       <c r="C47" t="s">
-        <v>578</v>
+        <v>542</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="C48" t="s">
-        <v>580</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>581</v>
+        <v>545</v>
       </c>
       <c r="C49" t="s">
-        <v>582</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>583</v>
+        <v>547</v>
       </c>
       <c r="C50" t="s">
-        <v>584</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>585</v>
+        <v>549</v>
       </c>
       <c r="C51" t="s">
-        <v>586</v>
+        <v>550</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>587</v>
+        <v>551</v>
       </c>
       <c r="C52" t="s">
-        <v>588</v>
+        <v>552</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>589</v>
+        <v>553</v>
       </c>
       <c r="C53" t="s">
-        <v>590</v>
+        <v>554</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>591</v>
+        <v>555</v>
       </c>
       <c r="C54" t="s">
-        <v>592</v>
+        <v>556</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>593</v>
+        <v>557</v>
       </c>
       <c r="C55" t="s">
-        <v>594</v>
+        <v>558</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>595</v>
+        <v>559</v>
       </c>
       <c r="C56" t="s">
-        <v>596</v>
+        <v>560</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>597</v>
+        <v>561</v>
       </c>
       <c r="C57" t="s">
-        <v>598</v>
+        <v>562</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>599</v>
+        <v>563</v>
       </c>
       <c r="C58" t="s">
-        <v>600</v>
+        <v>564</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="C59" t="s">
-        <v>602</v>
+        <v>566</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>603</v>
+        <v>567</v>
       </c>
       <c r="C60" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="C61" t="s">
-        <v>606</v>
+        <v>570</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>607</v>
+        <v>571</v>
       </c>
       <c r="C62" t="s">
-        <v>608</v>
+        <v>572</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>609</v>
+        <v>573</v>
       </c>
       <c r="C63" t="s">
-        <v>610</v>
+        <v>574</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="C64" t="s">
-        <v>612</v>
+        <v>576</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>613</v>
+        <v>577</v>
       </c>
       <c r="C65" t="s">
-        <v>614</v>
+        <v>578</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>615</v>
+        <v>579</v>
       </c>
       <c r="C66" t="s">
-        <v>616</v>
+        <v>580</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>617</v>
+        <v>581</v>
       </c>
       <c r="C67" t="s">
-        <v>618</v>
+        <v>582</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>619</v>
+        <v>583</v>
       </c>
       <c r="C68" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>620</v>
+        <v>584</v>
       </c>
       <c r="C69" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>621</v>
+        <v>585</v>
       </c>
       <c r="C70" t="s">
-        <v>622</v>
+        <v>586</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>623</v>
+        <v>587</v>
       </c>
       <c r="C71" t="s">
-        <v>624</v>
+        <v>588</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>625</v>
+        <v>589</v>
       </c>
       <c r="C72" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>626</v>
+        <v>590</v>
       </c>
       <c r="C73" t="s">
-        <v>503</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>627</v>
+        <v>591</v>
       </c>
       <c r="C74" t="s">
-        <v>628</v>
+        <v>592</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="C75" t="s">
-        <v>630</v>
+        <v>594</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>631</v>
+        <v>595</v>
       </c>
       <c r="C76" t="s">
-        <v>632</v>
+        <v>596</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>633</v>
+        <v>597</v>
       </c>
       <c r="C77" t="s">
-        <v>634</v>
+        <v>598</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="C78" t="s">
-        <v>636</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>637</v>
+        <v>601</v>
       </c>
       <c r="C79" t="s">
-        <v>638</v>
+        <v>602</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>639</v>
+        <v>603</v>
       </c>
       <c r="C80" t="s">
-        <v>640</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>641</v>
+        <v>605</v>
       </c>
       <c r="C81" t="s">
-        <v>642</v>
+        <v>606</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>643</v>
+        <v>607</v>
       </c>
       <c r="C82" t="s">
-        <v>517</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>644</v>
+        <v>608</v>
       </c>
       <c r="C83" t="s">
-        <v>488</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>645</v>
+        <v>609</v>
       </c>
       <c r="C84" t="s">
-        <v>646</v>
+        <v>610</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="C85" t="s">
-        <v>648</v>
+        <v>612</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="C86" t="s">
-        <v>650</v>
+        <v>614</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>651</v>
+        <v>615</v>
       </c>
       <c r="C87" t="s">
-        <v>652</v>
+        <v>616</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>653</v>
+        <v>617</v>
       </c>
       <c r="C88" t="s">
-        <v>654</v>
+        <v>618</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>655</v>
+        <v>619</v>
       </c>
       <c r="C89" t="s">
-        <v>656</v>
+        <v>620</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="C90" t="s">
-        <v>658</v>
+        <v>622</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="C91" t="s">
-        <v>660</v>
+        <v>624</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>661</v>
+        <v>625</v>
       </c>
       <c r="C92" t="s">
-        <v>662</v>
+        <v>626</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>663</v>
+        <v>627</v>
       </c>
       <c r="C93" t="s">
-        <v>664</v>
+        <v>628</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="C94" t="s">
-        <v>666</v>
+        <v>630</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>667</v>
+        <v>631</v>
       </c>
       <c r="C95" t="s">
-        <v>668</v>
+        <v>632</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
-        <v>669</v>
+        <v>633</v>
       </c>
       <c r="C96" t="s">
-        <v>670</v>
+        <v>634</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
-        <v>671</v>
+        <v>635</v>
       </c>
       <c r="C97" t="s">
-        <v>672</v>
+        <v>636</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>673</v>
+        <v>637</v>
       </c>
       <c r="C98" t="s">
-        <v>674</v>
+        <v>638</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>675</v>
+        <v>639</v>
       </c>
       <c r="C99" t="s">
-        <v>676</v>
+        <v>640</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>677</v>
+        <v>641</v>
       </c>
       <c r="C100" t="s">
-        <v>678</v>
+        <v>642</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
-        <v>679</v>
+        <v>643</v>
       </c>
       <c r="C101" t="s">
-        <v>680</v>
+        <v>644</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>681</v>
+        <v>645</v>
       </c>
       <c r="C102" t="s">
-        <v>682</v>
+        <v>646</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>683</v>
+        <v>647</v>
       </c>
       <c r="C103" t="s">
-        <v>684</v>
+        <v>648</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>685</v>
+        <v>649</v>
       </c>
       <c r="C104" t="s">
-        <v>686</v>
+        <v>650</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
-        <v>687</v>
+        <v>651</v>
       </c>
       <c r="C105" t="s">
-        <v>688</v>
+        <v>652</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
-        <v>689</v>
+        <v>653</v>
       </c>
       <c r="C106" t="s">
-        <v>690</v>
+        <v>654</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
-        <v>691</v>
+        <v>655</v>
       </c>
       <c r="C107" t="s">
-        <v>692</v>
+        <v>656</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="C108" t="s">
-        <v>694</v>
+        <v>658</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>695</v>
+        <v>659</v>
       </c>
       <c r="C109" t="s">
-        <v>696</v>
+        <v>660</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
-        <v>697</v>
+        <v>661</v>
       </c>
       <c r="C110" t="s">
-        <v>698</v>
+        <v>662</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" t="s">
-        <v>699</v>
+        <v>663</v>
       </c>
       <c r="C111" t="s">
-        <v>700</v>
+        <v>664</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>701</v>
+        <v>665</v>
       </c>
       <c r="C112" t="s">
-        <v>702</v>
+        <v>666</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" t="s">
-        <v>703</v>
+        <v>667</v>
       </c>
       <c r="C113" t="s">
-        <v>704</v>
+        <v>668</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
-        <v>705</v>
+        <v>669</v>
       </c>
       <c r="C114" t="s">
-        <v>706</v>
+        <v>670</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>707</v>
+        <v>671</v>
       </c>
       <c r="C115" t="s">
-        <v>708</v>
+        <v>672</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>709</v>
+        <v>673</v>
       </c>
       <c r="C116" t="s">
-        <v>710</v>
+        <v>674</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>711</v>
+        <v>675</v>
       </c>
       <c r="C117" t="s">
-        <v>712</v>
+        <v>676</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>713</v>
+        <v>677</v>
       </c>
       <c r="C118" t="s">
-        <v>714</v>
+        <v>678</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>715</v>
+        <v>679</v>
       </c>
       <c r="C119" t="s">
-        <v>716</v>
+        <v>680</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>717</v>
+        <v>681</v>
       </c>
       <c r="C120" t="s">
-        <v>718</v>
+        <v>682</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>719</v>
+        <v>683</v>
       </c>
       <c r="C121" t="s">
-        <v>720</v>
+        <v>684</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>721</v>
+        <v>685</v>
       </c>
       <c r="C122" t="s">
-        <v>722</v>
+        <v>686</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>723</v>
+        <v>687</v>
       </c>
       <c r="C123" t="s">
-        <v>724</v>
+        <v>688</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>725</v>
+        <v>689</v>
       </c>
       <c r="C124" t="s">
-        <v>726</v>
+        <v>690</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>727</v>
+        <v>691</v>
       </c>
       <c r="C125" t="s">
-        <v>728</v>
+        <v>692</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>729</v>
+        <v>693</v>
       </c>
       <c r="C126" t="s">
-        <v>730</v>
+        <v>694</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>731</v>
+        <v>695</v>
       </c>
       <c r="C127" t="s">
-        <v>732</v>
+        <v>696</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
-        <v>733</v>
+        <v>697</v>
       </c>
       <c r="C128" t="s">
-        <v>734</v>
+        <v>698</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" t="s">
-        <v>735</v>
+        <v>699</v>
       </c>
       <c r="C129" t="s">
-        <v>736</v>
+        <v>700</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>737</v>
+        <v>701</v>
       </c>
       <c r="C130" t="s">
-        <v>738</v>
+        <v>702</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C131" t="s">
-        <v>740</v>
+        <v>704</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>741</v>
+        <v>705</v>
       </c>
       <c r="C132" t="s">
-        <v>742</v>
+        <v>706</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>743</v>
+        <v>707</v>
       </c>
       <c r="C133" t="s">
-        <v>744</v>
+        <v>708</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>745</v>
+        <v>709</v>
       </c>
       <c r="C134" t="s">
-        <v>746</v>
+        <v>710</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>747</v>
+        <v>711</v>
       </c>
       <c r="C135" t="s">
-        <v>748</v>
+        <v>712</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>749</v>
+        <v>713</v>
       </c>
       <c r="C136" t="s">
-        <v>750</v>
+        <v>714</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>751</v>
+        <v>715</v>
       </c>
       <c r="C137" t="s">
-        <v>752</v>
+        <v>716</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>753</v>
+        <v>717</v>
       </c>
       <c r="C138" t="s">
-        <v>754</v>
+        <v>718</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>755</v>
+        <v>719</v>
       </c>
       <c r="C139" t="s">
-        <v>756</v>
+        <v>720</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>757</v>
+        <v>721</v>
       </c>
       <c r="C140" t="s">
-        <v>758</v>
+        <v>722</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>759</v>
+        <v>723</v>
       </c>
       <c r="C141" t="s">
-        <v>760</v>
+        <v>724</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>761</v>
+        <v>725</v>
       </c>
       <c r="C142" t="s">
-        <v>762</v>
+        <v>726</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>763</v>
+        <v>727</v>
       </c>
       <c r="C143" t="s">
-        <v>764</v>
+        <v>728</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>765</v>
+        <v>729</v>
       </c>
       <c r="C144" t="s">
-        <v>766</v>
+        <v>730</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>767</v>
+        <v>731</v>
       </c>
       <c r="C145" t="s">
-        <v>768</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>769</v>
+        <v>733</v>
       </c>
       <c r="C146" t="s">
-        <v>770</v>
+        <v>734</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>771</v>
+        <v>735</v>
       </c>
       <c r="C147" t="s">
-        <v>772</v>
+        <v>736</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="C148" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>775</v>
+        <v>739</v>
       </c>
       <c r="C149" t="s">
-        <v>776</v>
+        <v>740</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="C150" t="s">
-        <v>778</v>
+        <v>742</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="C151" t="s">
-        <v>780</v>
+        <v>744</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>781</v>
+        <v>745</v>
       </c>
       <c r="C152" t="s">
-        <v>782</v>
+        <v>746</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>783</v>
+        <v>747</v>
       </c>
       <c r="C153" t="s">
-        <v>784</v>
+        <v>748</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>785</v>
+        <v>749</v>
       </c>
       <c r="C154" t="s">
-        <v>786</v>
+        <v>750</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>787</v>
+        <v>751</v>
       </c>
       <c r="C155" t="s">
-        <v>788</v>
+        <v>752</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" t="s">
-        <v>789</v>
+        <v>753</v>
       </c>
       <c r="C156" t="s">
-        <v>790</v>
+        <v>754</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" t="s">
-        <v>791</v>
+        <v>755</v>
       </c>
       <c r="C157" t="s">
-        <v>792</v>
+        <v>756</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" t="s">
-        <v>793</v>
+        <v>757</v>
       </c>
       <c r="C158" t="s">
-        <v>794</v>
+        <v>758</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
-        <v>795</v>
+        <v>759</v>
       </c>
       <c r="C159" t="s">
-        <v>796</v>
+        <v>760</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
-        <v>797</v>
+        <v>761</v>
       </c>
       <c r="C160" t="s">
-        <v>798</v>
+        <v>762</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
-        <v>799</v>
+        <v>763</v>
       </c>
       <c r="C161" t="s">
-        <v>800</v>
+        <v>764</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>801</v>
+        <v>765</v>
       </c>
       <c r="C162" t="s">
-        <v>802</v>
+        <v>766</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" t="s">
-        <v>803</v>
+        <v>767</v>
       </c>
       <c r="C163" t="s">
-        <v>804</v>
+        <v>768</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" t="s">
-        <v>805</v>
+        <v>769</v>
       </c>
       <c r="C164" t="s">
-        <v>806</v>
+        <v>770</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" t="s">
-        <v>807</v>
+        <v>771</v>
       </c>
       <c r="C165" t="s">
-        <v>808</v>
+        <v>772</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
-        <v>809</v>
+        <v>773</v>
       </c>
       <c r="C166" t="s">
-        <v>810</v>
+        <v>774</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>811</v>
+        <v>775</v>
       </c>
       <c r="C167" t="s">
-        <v>812</v>
+        <v>776</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" t="s">
-        <v>813</v>
+        <v>777</v>
       </c>
       <c r="C168" t="s">
-        <v>814</v>
+        <v>778</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" t="s">
-        <v>815</v>
+        <v>779</v>
       </c>
       <c r="C169" t="s">
-        <v>816</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
-        <v>817</v>
+        <v>781</v>
       </c>
       <c r="C170" t="s">
-        <v>818</v>
+        <v>782</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
-        <v>819</v>
+        <v>783</v>
       </c>
       <c r="C171" t="s">
-        <v>820</v>
+        <v>784</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
-        <v>821</v>
+        <v>785</v>
       </c>
       <c r="C172" t="s">
-        <v>822</v>
+        <v>786</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
-        <v>823</v>
+        <v>787</v>
       </c>
       <c r="C173" t="s">
-        <v>824</v>
+        <v>788</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
-        <v>825</v>
+        <v>789</v>
       </c>
       <c r="C174" t="s">
-        <v>826</v>
+        <v>790</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
-        <v>827</v>
+        <v>791</v>
       </c>
       <c r="C175" t="s">
-        <v>828</v>
+        <v>792</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
-        <v>829</v>
+        <v>793</v>
       </c>
       <c r="C176" t="s">
-        <v>830</v>
+        <v>794</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
-        <v>831</v>
+        <v>795</v>
       </c>
       <c r="C177" t="s">
-        <v>832</v>
+        <v>796</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
-        <v>833</v>
+        <v>797</v>
       </c>
       <c r="C178" t="s">
-        <v>834</v>
+        <v>798</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
-        <v>835</v>
+        <v>799</v>
       </c>
       <c r="C179" t="s">
-        <v>836</v>
+        <v>800</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
-        <v>837</v>
+        <v>801</v>
       </c>
       <c r="C180" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="C181" t="s">
-        <v>840</v>
+        <v>804</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
-        <v>841</v>
+        <v>805</v>
       </c>
       <c r="C182" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="C183" t="s">
-        <v>844</v>
+        <v>808</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="C184" t="s">
-        <v>846</v>
+        <v>810</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>847</v>
+        <v>811</v>
       </c>
       <c r="C185" t="s">
-        <v>848</v>
+        <v>812</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
-        <v>849</v>
+        <v>813</v>
       </c>
       <c r="C186" t="s">
-        <v>850</v>
+        <v>814</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
-        <v>851</v>
+        <v>815</v>
       </c>
       <c r="C187" t="s">
-        <v>852</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -9901,40 +10111,40 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>853</v>
+        <v>817</v>
       </c>
       <c r="B2" t="s">
-        <v>854</v>
+        <v>818</v>
       </c>
       <c r="C2" t="s">
-        <v>855</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>856</v>
+        <v>820</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1229</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>857</v>
+        <v>821</v>
       </c>
       <c r="B4" t="s">
-        <v>858</v>
+        <v>822</v>
       </c>
       <c r="C4" t="s">
-        <v>859</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>824</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1231</v>
+        <v>1193</v>
       </c>
     </row>
   </sheetData>
@@ -9965,46 +10175,46 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>861</v>
+        <v>825</v>
       </c>
       <c r="B2" t="s">
-        <v>862</v>
+        <v>826</v>
       </c>
       <c r="C2" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
       <c r="B3" t="s">
-        <v>865</v>
+        <v>829</v>
       </c>
       <c r="C3" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>869</v>
+        <v>833</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>870</v>
+        <v>834</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>871</v>
+        <v>835</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>871</v>
+        <v>835</v>
       </c>
     </row>
   </sheetData>
@@ -10035,57 +10245,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>872</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
-        <v>873</v>
+        <v>837</v>
       </c>
       <c r="C2" t="s">
-        <v>874</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>875</v>
+        <v>839</v>
       </c>
       <c r="B3" t="s">
-        <v>876</v>
+        <v>840</v>
       </c>
       <c r="C3" t="s">
-        <v>877</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>878</v>
+        <v>842</v>
       </c>
       <c r="B4" t="s">
-        <v>879</v>
+        <v>843</v>
       </c>
       <c r="C4" t="s">
-        <v>880</v>
+        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="B5" t="s">
-        <v>882</v>
+        <v>846</v>
       </c>
       <c r="C5" t="s">
-        <v>883</v>
+        <v>847</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>884</v>
+        <v>848</v>
       </c>
       <c r="B6" t="s">
-        <v>885</v>
+        <v>849</v>
       </c>
       <c r="C6" t="s">
-        <v>886</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -10117,651 +10327,651 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>887</v>
+        <v>851</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>888</v>
+        <v>852</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>889</v>
+        <v>853</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>890</v>
+        <v>854</v>
       </c>
       <c r="B3" t="s">
-        <v>891</v>
+        <v>855</v>
       </c>
       <c r="C3" t="s">
-        <v>892</v>
+        <v>856</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>893</v>
+        <v>857</v>
       </c>
       <c r="B4" t="s">
-        <v>894</v>
+        <v>858</v>
       </c>
       <c r="C4" t="s">
-        <v>895</v>
+        <v>859</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>896</v>
+        <v>860</v>
       </c>
       <c r="B5" t="s">
-        <v>897</v>
+        <v>861</v>
       </c>
       <c r="C5" t="s">
-        <v>898</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>899</v>
+        <v>863</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>900</v>
+        <v>864</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>901</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="8" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>904</v>
+        <v>868</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="8" t="s">
-        <v>905</v>
+        <v>869</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>906</v>
+        <v>870</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>907</v>
+        <v>871</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>908</v>
+        <v>872</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>904</v>
+        <v>868</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>909</v>
+        <v>873</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1166</v>
+        <v>1128</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="8" t="s">
-        <v>911</v>
+        <v>875</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1165</v>
+        <v>1127</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>912</v>
+        <v>876</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="8" t="s">
-        <v>913</v>
+        <v>877</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1167</v>
+        <v>1129</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>914</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="8" t="s">
-        <v>915</v>
+        <v>879</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1168</v>
+        <v>1130</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>916</v>
+        <v>880</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="8" t="s">
-        <v>917</v>
+        <v>881</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1169</v>
+        <v>1131</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>918</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="8" t="s">
-        <v>919</v>
+        <v>883</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1170</v>
+        <v>1132</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>920</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="8" t="s">
-        <v>921</v>
+        <v>885</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1171</v>
+        <v>1133</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>922</v>
+        <v>886</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>923</v>
+        <v>887</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1172</v>
+        <v>1134</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>924</v>
+        <v>888</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="8" t="s">
-        <v>925</v>
+        <v>889</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1173</v>
+        <v>1135</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>926</v>
+        <v>890</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>927</v>
+        <v>891</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1174</v>
+        <v>1136</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>928</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>929</v>
+        <v>893</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1175</v>
+        <v>1137</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>930</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>931</v>
+        <v>895</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1176</v>
+        <v>1138</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>932</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>933</v>
+        <v>897</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1177</v>
+        <v>1139</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>934</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>935</v>
+        <v>899</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1178</v>
+        <v>1140</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>936</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="8" t="s">
-        <v>937</v>
+        <v>901</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1179</v>
+        <v>1141</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>938</v>
+        <v>902</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="8" t="s">
-        <v>939</v>
+        <v>903</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1180</v>
+        <v>1142</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>940</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="8" t="s">
-        <v>941</v>
+        <v>905</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1181</v>
+        <v>1143</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>942</v>
+        <v>906</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="8" t="s">
-        <v>943</v>
+        <v>907</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>944</v>
+        <v>908</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="8" t="s">
-        <v>945</v>
+        <v>909</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1184</v>
+        <v>1146</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>946</v>
+        <v>910</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="8" t="s">
-        <v>947</v>
+        <v>911</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1183</v>
+        <v>1145</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="8" t="s">
-        <v>949</v>
+        <v>913</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1185</v>
+        <v>1147</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>950</v>
+        <v>914</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>951</v>
+        <v>915</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1186</v>
+        <v>1148</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>952</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="8" t="s">
-        <v>953</v>
+        <v>917</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1187</v>
+        <v>1149</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>954</v>
+        <v>918</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>955</v>
+        <v>919</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1188</v>
+        <v>1150</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>956</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="8" t="s">
-        <v>957</v>
+        <v>921</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1189</v>
+        <v>1151</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>958</v>
+        <v>922</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="8" t="s">
-        <v>959</v>
+        <v>923</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1190</v>
+        <v>1152</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>960</v>
+        <v>924</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>1272</v>
+        <v>1231</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>1193</v>
+        <v>1155</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>1140</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1273</v>
+        <v>1232</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1194</v>
+        <v>1156</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1141</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1274</v>
+        <v>1233</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1195</v>
+        <v>1157</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>1142</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1275</v>
+        <v>1234</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1191</v>
+        <v>1153</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1152</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1192</v>
+        <v>1154</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1153</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1277</v>
+        <v>1236</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1196</v>
+        <v>1158</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1154</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1278</v>
+        <v>1237</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1197</v>
+        <v>1159</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1155</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1279</v>
+        <v>1238</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1199</v>
+        <v>1161</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1156</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1280</v>
+        <v>1239</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1198</v>
+        <v>1160</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1157</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1281</v>
+        <v>1240</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1200</v>
+        <v>1162</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1158</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1282</v>
+        <v>1241</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1201</v>
+        <v>1163</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1159</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1283</v>
+        <v>1242</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1202</v>
+        <v>1164</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1160</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1284</v>
+        <v>1243</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>1203</v>
+        <v>1165</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1161</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1285</v>
+        <v>1244</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>1204</v>
+        <v>1166</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1162</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1286</v>
+        <v>1245</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>1205</v>
+        <v>1167</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1163</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1287</v>
+        <v>1246</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1206</v>
+        <v>1168</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1164</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1288</v>
+        <v>1247</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>1207</v>
+        <v>1169</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1145</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1289</v>
+        <v>1248</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>1208</v>
+        <v>1170</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1146</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1290</v>
+        <v>1249</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1209</v>
+        <v>1171</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1147</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1291</v>
+        <v>1250</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1210</v>
+        <v>1172</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1149</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1292</v>
+        <v>1251</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1211</v>
+        <v>1173</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1148</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1293</v>
+        <v>1252</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1213</v>
+        <v>1175</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1150</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1294</v>
+        <v>1253</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1212</v>
+        <v>1174</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1151</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1295</v>
+        <v>1254</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1214</v>
+        <v>1176</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1144</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1296</v>
+        <v>1255</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1215</v>
+        <v>1177</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1143</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengmingliu/Dev/ProjectMT3/Data/Locale/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0263CEDC-C360-5349-8E90-8F4B555C1DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C372DBD2-842F-8A4D-8653-24A5171CC3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="1504">
   <si>
     <t>ID</t>
   </si>
@@ -3728,12 +3728,6 @@
     <t>TM_05</t>
   </si>
   <si>
-    <t>敌人的能力信息，确认键或点击可以查看详细内容。</t>
-  </si>
-  <si>
-    <t>There is the information of enemies. You can press confirm button or click to view the detail.</t>
-  </si>
-  <si>
     <t>TMT3_001</t>
   </si>
   <si>
@@ -4010,21 +4004,6 @@
     <t>TM_07</t>
   </si>
   <si>
-    <t>按 B 键可以快速使用，在这里可以查看更多快捷键。</t>
-  </si>
-  <si>
-    <t>You can use them quickly by pressing B. Here you can view more of hotkeys.</t>
-  </si>
-  <si>
-    <t>TM_08</t>
-  </si>
-  <si>
-    <t>You can use them quickly by pressing N. Here you can view more of hotkeys.</t>
-  </si>
-  <si>
-    <t>按 N 键可以快速使用，在这里可以查看更多快捷键。</t>
-  </si>
-  <si>
     <t>玩家每次移动后，若处于敌人的{value}格范围内，敌人造成一次单回合伤害。</t>
   </si>
   <si>
@@ -4296,6 +4275,288 @@
   </si>
   <si>
     <t>巧妙运用手中道具，不必与强敌作战就可前进。</t>
+  </si>
+  <si>
+    <t>Slime</t>
+  </si>
+  <si>
+    <t>Red Slime</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Water Mage</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>Thunder Mage</t>
+  </si>
+  <si>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>Black Slime</t>
+  </si>
+  <si>
+    <t>Slime Man</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Big Bat</t>
+  </si>
+  <si>
+    <t>Stone Golem</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Greatsword Fighter</t>
+  </si>
+  <si>
+    <t>Skeleton Soldier</t>
+  </si>
+  <si>
+    <t>Skeleton Armiger</t>
+  </si>
+  <si>
+    <t>Veteran Guard</t>
+  </si>
+  <si>
+    <t>Iron Knight</t>
+  </si>
+  <si>
+    <t>Red Bat</t>
+  </si>
+  <si>
+    <t>Baby Octopus</t>
+  </si>
+  <si>
+    <t>Slime Berserker</t>
+  </si>
+  <si>
+    <t>Slime King</t>
+  </si>
+  <si>
+    <t>Flame Mage</t>
+  </si>
+  <si>
+    <t>Zombie Swordsman</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Demon Slime</t>
+  </si>
+  <si>
+    <t>Blood Bat</t>
+  </si>
+  <si>
+    <t>Skeleton Captain</t>
+  </si>
+  <si>
+    <t>Wind Wizard</t>
+  </si>
+  <si>
+    <t>Evil-Eye Slime</t>
+  </si>
+  <si>
+    <t>White Guard</t>
+  </si>
+  <si>
+    <t>Grey Knight</t>
+  </si>
+  <si>
+    <t>Nether Mage</t>
+  </si>
+  <si>
+    <t>Big Slime</t>
+  </si>
+  <si>
+    <t>Mage</t>
+  </si>
+  <si>
+    <t>Poison Zombie</t>
+  </si>
+  <si>
+    <t>Poison Bat</t>
+  </si>
+  <si>
+    <t>Skeleton Chief</t>
+  </si>
+  <si>
+    <t>Conehead</t>
+  </si>
+  <si>
+    <t>Orc</t>
+  </si>
+  <si>
+    <t>Crab Slime</t>
+  </si>
+  <si>
+    <t>Elite Archer</t>
+  </si>
+  <si>
+    <t>Frail Sentinel</t>
+  </si>
+  <si>
+    <t>Berserk Sentinel</t>
+  </si>
+  <si>
+    <t>Speedster</t>
+  </si>
+  <si>
+    <t>Blue Guard</t>
+  </si>
+  <si>
+    <t>Demon Guard</t>
+  </si>
+  <si>
+    <t>Swift Hound</t>
+  </si>
+  <si>
+    <t>Steel Golem</t>
+  </si>
+  <si>
+    <t>Elite Guard</t>
+  </si>
+  <si>
+    <t>Iron Golem</t>
+  </si>
+  <si>
+    <t>Mercury Man</t>
+  </si>
+  <si>
+    <t>Adept Mage</t>
+  </si>
+  <si>
+    <t>Unstable Machine</t>
+  </si>
+  <si>
+    <t>Armoured Skeleton</t>
+  </si>
+  <si>
+    <t>Medium Bat</t>
+  </si>
+  <si>
+    <t>Ice Slime</t>
+  </si>
+  <si>
+    <t>Poison Octopus</t>
+  </si>
+  <si>
+    <t>Blazing Zombie</t>
+  </si>
+  <si>
+    <t>Frozen Bones</t>
+  </si>
+  <si>
+    <t>Sentinel</t>
+  </si>
+  <si>
+    <t>Ironclad Sentinel</t>
+  </si>
+  <si>
+    <t>Royal Knight</t>
+  </si>
+  <si>
+    <t>Ghost Flame</t>
+  </si>
+  <si>
+    <t>Orc Soldier</t>
+  </si>
+  <si>
+    <t>Flame Wizard</t>
+  </si>
+  <si>
+    <t>Crimson Overlord</t>
+  </si>
+  <si>
+    <t>Vampire Count</t>
+  </si>
+  <si>
+    <t>Hammer Skeleton</t>
+  </si>
+  <si>
+    <t>Gale Hound</t>
+  </si>
+  <si>
+    <t>Giant Bat</t>
+  </si>
+  <si>
+    <t>Frail Octopus</t>
+  </si>
+  <si>
+    <t>Frost Wizard</t>
+  </si>
+  <si>
+    <t>Tentacle Plant</t>
+  </si>
+  <si>
+    <t>Archmage</t>
+  </si>
+  <si>
+    <t>Skeleton Swordsman</t>
+  </si>
+  <si>
+    <t>Giant Octopus</t>
+  </si>
+  <si>
+    <t>Demon Dragon</t>
+  </si>
+  <si>
+    <t>Death Knight</t>
+  </si>
+  <si>
+    <t>Blood Mage</t>
+  </si>
+  <si>
+    <t>Slime Asura</t>
+  </si>
+  <si>
+    <t>Mad Tentacle</t>
+  </si>
+  <si>
+    <t>Royal Lancer</t>
+  </si>
+  <si>
+    <t>Dragon Bat</t>
+  </si>
+  <si>
+    <t>敌人的能力信息，确认键查看详细内容。</t>
+  </si>
+  <si>
+    <t>There is the information of enemies. You can press confirm button to view the detail.</t>
+  </si>
+  <si>
+    <t>TM_05_M</t>
+  </si>
+  <si>
+    <t>There is the information of enemies. You can click to view the detail.</t>
+  </si>
+  <si>
+    <t>敌人的能力信息，点击查看详细内容。</t>
+  </si>
+  <si>
+    <t>按 N 键可以快速使用。</t>
+  </si>
+  <si>
+    <t>You can use them quickly by pressing N.</t>
+  </si>
+  <si>
+    <t>拾取血瓶时，溢出的HP会储存在你的背包中。按 B 键可以快速使用。</t>
+  </si>
+  <si>
+    <t>When picking up a potion, any excess HP is stored in your inventory.You can use them quickly by pressing B.</t>
+  </si>
+  <si>
+    <t>TM_06_D</t>
   </si>
 </sst>
 </file>
@@ -5334,134 +5595,134 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C65" t="s">
         <v>1256</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C68" t="s">
         <v>1261</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C69" t="s">
         <v>1264</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C70" t="s">
         <v>1267</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C71" t="s">
         <v>1270</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C72" t="s">
         <v>1273</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C73" t="s">
         <v>1276</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C76" t="s">
         <v>1313</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1315</v>
       </c>
     </row>
   </sheetData>
@@ -5660,10 +5921,10 @@
         <v>966</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5803,7 +6064,7 @@
         <v>1003</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C30" t="s">
         <v>1004</v>
@@ -5814,7 +6075,7 @@
         <v>1005</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C31" t="s">
         <v>1006</v>
@@ -6426,7 +6687,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>1206</v>
@@ -6437,7 +6698,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1329</v>
+        <v>1322</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1227</v>
@@ -6459,7 +6720,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1330</v>
+        <v>1323</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>1209</v>
@@ -6481,10 +6742,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6492,10 +6753,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6503,10 +6764,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6525,10 +6786,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6536,10 +6797,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6547,10 +6808,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6558,10 +6819,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6569,10 +6830,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6580,10 +6841,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6591,10 +6852,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6602,10 +6863,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6613,10 +6874,10 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1387</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6624,10 +6885,10 @@
         <v>35</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6635,7 +6896,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>37</v>
@@ -6646,10 +6907,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6657,10 +6918,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6668,10 +6929,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6679,10 +6940,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6690,10 +6951,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6701,10 +6962,10 @@
         <v>43</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1346</v>
+        <v>1339</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6712,7 +6973,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>45</v>
@@ -6723,7 +6984,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>47</v>
@@ -6734,7 +6995,7 @@
         <v>48</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>49</v>
@@ -6745,7 +7006,7 @@
         <v>50</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>51</v>
@@ -6756,7 +7017,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>53</v>
@@ -6767,10 +7028,10 @@
         <v>54</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6778,7 +7039,7 @@
         <v>55</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>56</v>
@@ -6789,10 +7050,10 @@
         <v>57</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6800,10 +7061,10 @@
         <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6811,7 +7072,7 @@
         <v>59</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>60</v>
@@ -6822,10 +7083,10 @@
         <v>61</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>1354</v>
+        <v>1347</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6833,10 +7094,10 @@
         <v>62</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>1355</v>
+        <v>1348</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6844,10 +7105,10 @@
         <v>63</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6855,10 +7116,10 @@
         <v>64</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6866,7 +7127,7 @@
         <v>65</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>66</v>
@@ -6877,10 +7138,10 @@
         <v>67</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6888,7 +7149,7 @@
         <v>68</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>69</v>
@@ -6899,10 +7160,10 @@
         <v>70</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6910,10 +7171,10 @@
         <v>71</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6921,7 +7182,7 @@
         <v>72</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>73</v>
@@ -6932,10 +7193,10 @@
         <v>74</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6943,10 +7204,10 @@
         <v>75</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6954,10 +7215,10 @@
         <v>76</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6965,10 +7226,10 @@
         <v>77</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6976,10 +7237,10 @@
         <v>78</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6987,10 +7248,10 @@
         <v>79</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6998,10 +7259,10 @@
         <v>80</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7009,10 +7270,10 @@
         <v>81</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1371</v>
+        <v>1364</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7020,10 +7281,10 @@
         <v>82</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7031,7 +7292,7 @@
         <v>1096</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>1097</v>
@@ -7042,10 +7303,10 @@
         <v>1098</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7053,10 +7314,10 @@
         <v>1099</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7064,7 +7325,7 @@
         <v>1100</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>1101</v>
@@ -7654,7 +7915,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
@@ -7699,7 +7960,7 @@
         <v>1200</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1201</v>
@@ -7710,10 +7971,10 @@
         <v>1212</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7721,43 +7982,54 @@
         <v>1228</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1230</v>
+        <v>1495</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1229</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>1309</v>
+        <v>1496</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1311</v>
+        <v>1497</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1310</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>1320</v>
+        <v>1307</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>1323</v>
+        <v>1503</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1324</v>
+        <v>1502</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1325</v>
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1499</v>
       </c>
     </row>
   </sheetData>
@@ -7886,7 +8158,7 @@
         <v>284</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>286</v>
@@ -8526,46 +8798,46 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
   </sheetData>
@@ -8599,6 +8871,9 @@
       <c r="A2" t="s">
         <v>458</v>
       </c>
+      <c r="B2" t="s">
+        <v>1410</v>
+      </c>
       <c r="C2" t="s">
         <v>453</v>
       </c>
@@ -8615,6 +8890,9 @@
       <c r="A4" t="s">
         <v>460</v>
       </c>
+      <c r="B4" t="s">
+        <v>1411</v>
+      </c>
       <c r="C4" t="s">
         <v>461</v>
       </c>
@@ -8631,6 +8909,9 @@
       <c r="A6" t="s">
         <v>464</v>
       </c>
+      <c r="B6" t="s">
+        <v>1412</v>
+      </c>
       <c r="C6" t="s">
         <v>465</v>
       </c>
@@ -8647,6 +8928,9 @@
       <c r="A8" t="s">
         <v>468</v>
       </c>
+      <c r="B8" t="s">
+        <v>1413</v>
+      </c>
       <c r="C8" t="s">
         <v>469</v>
       </c>
@@ -8663,6 +8947,9 @@
       <c r="A10" t="s">
         <v>472</v>
       </c>
+      <c r="B10" t="s">
+        <v>1414</v>
+      </c>
       <c r="C10" t="s">
         <v>473</v>
       </c>
@@ -8679,6 +8966,9 @@
       <c r="A12" t="s">
         <v>476</v>
       </c>
+      <c r="B12" t="s">
+        <v>1415</v>
+      </c>
       <c r="C12" t="s">
         <v>477</v>
       </c>
@@ -8695,6 +8985,9 @@
       <c r="A14" t="s">
         <v>480</v>
       </c>
+      <c r="B14" t="s">
+        <v>1416</v>
+      </c>
       <c r="C14" t="s">
         <v>481</v>
       </c>
@@ -8711,6 +9004,9 @@
       <c r="A16" t="s">
         <v>483</v>
       </c>
+      <c r="B16" t="s">
+        <v>1417</v>
+      </c>
       <c r="C16" t="s">
         <v>484</v>
       </c>
@@ -8727,6 +9023,9 @@
       <c r="A18" t="s">
         <v>487</v>
       </c>
+      <c r="B18" t="s">
+        <v>1418</v>
+      </c>
       <c r="C18" t="s">
         <v>488</v>
       </c>
@@ -8743,6 +9042,9 @@
       <c r="A20" t="s">
         <v>491</v>
       </c>
+      <c r="B20" t="s">
+        <v>1419</v>
+      </c>
       <c r="C20" t="s">
         <v>492</v>
       </c>
@@ -8759,6 +9061,9 @@
       <c r="A22" t="s">
         <v>495</v>
       </c>
+      <c r="B22" t="s">
+        <v>1420</v>
+      </c>
       <c r="C22" t="s">
         <v>455</v>
       </c>
@@ -8775,6 +9080,9 @@
       <c r="A24" t="s">
         <v>497</v>
       </c>
+      <c r="B24" t="s">
+        <v>1421</v>
+      </c>
       <c r="C24" t="s">
         <v>498</v>
       </c>
@@ -8791,6 +9099,9 @@
       <c r="A26" t="s">
         <v>501</v>
       </c>
+      <c r="B26" t="s">
+        <v>1422</v>
+      </c>
       <c r="C26" t="s">
         <v>457</v>
       </c>
@@ -8807,6 +9118,9 @@
       <c r="A28" t="s">
         <v>504</v>
       </c>
+      <c r="B28" t="s">
+        <v>1423</v>
+      </c>
       <c r="C28" t="s">
         <v>505</v>
       </c>
@@ -8823,6 +9137,9 @@
       <c r="A30" t="s">
         <v>508</v>
       </c>
+      <c r="B30" t="s">
+        <v>1424</v>
+      </c>
       <c r="C30" t="s">
         <v>451</v>
       </c>
@@ -8839,6 +9156,9 @@
       <c r="A32" t="s">
         <v>511</v>
       </c>
+      <c r="B32" t="s">
+        <v>1425</v>
+      </c>
       <c r="C32" t="s">
         <v>512</v>
       </c>
@@ -8855,6 +9175,9 @@
       <c r="A34" t="s">
         <v>515</v>
       </c>
+      <c r="B34" t="s">
+        <v>1426</v>
+      </c>
       <c r="C34" t="s">
         <v>516</v>
       </c>
@@ -8871,6 +9194,9 @@
       <c r="A36" t="s">
         <v>519</v>
       </c>
+      <c r="B36" t="s">
+        <v>1427</v>
+      </c>
       <c r="C36" t="s">
         <v>520</v>
       </c>
@@ -8887,6 +9213,9 @@
       <c r="A38" t="s">
         <v>523</v>
       </c>
+      <c r="B38" t="s">
+        <v>1428</v>
+      </c>
       <c r="C38" t="s">
         <v>524</v>
       </c>
@@ -8903,6 +9232,9 @@
       <c r="A40" t="s">
         <v>527</v>
       </c>
+      <c r="B40" t="s">
+        <v>1429</v>
+      </c>
       <c r="C40" t="s">
         <v>528</v>
       </c>
@@ -8919,6 +9251,9 @@
       <c r="A42" t="s">
         <v>531</v>
       </c>
+      <c r="B42" t="s">
+        <v>1430</v>
+      </c>
       <c r="C42" t="s">
         <v>532</v>
       </c>
@@ -8935,6 +9270,9 @@
       <c r="A44" t="s">
         <v>535</v>
       </c>
+      <c r="B44" t="s">
+        <v>1431</v>
+      </c>
       <c r="C44" t="s">
         <v>536</v>
       </c>
@@ -8951,6 +9289,9 @@
       <c r="A46" t="s">
         <v>539</v>
       </c>
+      <c r="B46" t="s">
+        <v>1432</v>
+      </c>
       <c r="C46" t="s">
         <v>540</v>
       </c>
@@ -8967,6 +9308,9 @@
       <c r="A48" t="s">
         <v>543</v>
       </c>
+      <c r="B48" t="s">
+        <v>1433</v>
+      </c>
       <c r="C48" t="s">
         <v>544</v>
       </c>
@@ -8983,6 +9327,9 @@
       <c r="A50" t="s">
         <v>547</v>
       </c>
+      <c r="B50" t="s">
+        <v>1434</v>
+      </c>
       <c r="C50" t="s">
         <v>548</v>
       </c>
@@ -8999,6 +9346,9 @@
       <c r="A52" t="s">
         <v>551</v>
       </c>
+      <c r="B52" t="s">
+        <v>1435</v>
+      </c>
       <c r="C52" t="s">
         <v>552</v>
       </c>
@@ -9015,6 +9365,9 @@
       <c r="A54" t="s">
         <v>555</v>
       </c>
+      <c r="B54" t="s">
+        <v>1436</v>
+      </c>
       <c r="C54" t="s">
         <v>556</v>
       </c>
@@ -9031,6 +9384,9 @@
       <c r="A56" t="s">
         <v>559</v>
       </c>
+      <c r="B56" t="s">
+        <v>1437</v>
+      </c>
       <c r="C56" t="s">
         <v>560</v>
       </c>
@@ -9047,6 +9403,9 @@
       <c r="A58" t="s">
         <v>563</v>
       </c>
+      <c r="B58" t="s">
+        <v>1438</v>
+      </c>
       <c r="C58" t="s">
         <v>564</v>
       </c>
@@ -9063,6 +9422,9 @@
       <c r="A60" t="s">
         <v>567</v>
       </c>
+      <c r="B60" t="s">
+        <v>1439</v>
+      </c>
       <c r="C60" t="s">
         <v>568</v>
       </c>
@@ -9079,6 +9441,9 @@
       <c r="A62" t="s">
         <v>571</v>
       </c>
+      <c r="B62" t="s">
+        <v>1440</v>
+      </c>
       <c r="C62" t="s">
         <v>572</v>
       </c>
@@ -9095,6 +9460,9 @@
       <c r="A64" t="s">
         <v>575</v>
       </c>
+      <c r="B64" t="s">
+        <v>1441</v>
+      </c>
       <c r="C64" t="s">
         <v>576</v>
       </c>
@@ -9111,6 +9479,9 @@
       <c r="A66" t="s">
         <v>579</v>
       </c>
+      <c r="B66" t="s">
+        <v>1442</v>
+      </c>
       <c r="C66" t="s">
         <v>580</v>
       </c>
@@ -9127,6 +9498,9 @@
       <c r="A68" t="s">
         <v>583</v>
       </c>
+      <c r="B68" t="s">
+        <v>1410</v>
+      </c>
       <c r="C68" t="s">
         <v>453</v>
       </c>
@@ -9143,6 +9517,9 @@
       <c r="A70" t="s">
         <v>585</v>
       </c>
+      <c r="B70" t="s">
+        <v>1443</v>
+      </c>
       <c r="C70" t="s">
         <v>586</v>
       </c>
@@ -9159,6 +9536,9 @@
       <c r="A72" t="s">
         <v>589</v>
       </c>
+      <c r="B72" t="s">
+        <v>1412</v>
+      </c>
       <c r="C72" t="s">
         <v>465</v>
       </c>
@@ -9175,6 +9555,9 @@
       <c r="A74" t="s">
         <v>591</v>
       </c>
+      <c r="B74" t="s">
+        <v>1444</v>
+      </c>
       <c r="C74" t="s">
         <v>592</v>
       </c>
@@ -9191,6 +9574,9 @@
       <c r="A76" t="s">
         <v>595</v>
       </c>
+      <c r="B76" t="s">
+        <v>1445</v>
+      </c>
       <c r="C76" t="s">
         <v>596</v>
       </c>
@@ -9207,6 +9593,9 @@
       <c r="A78" t="s">
         <v>599</v>
       </c>
+      <c r="B78" t="s">
+        <v>1446</v>
+      </c>
       <c r="C78" t="s">
         <v>600</v>
       </c>
@@ -9223,6 +9612,9 @@
       <c r="A80" t="s">
         <v>603</v>
       </c>
+      <c r="B80" t="s">
+        <v>1447</v>
+      </c>
       <c r="C80" t="s">
         <v>604</v>
       </c>
@@ -9239,6 +9631,9 @@
       <c r="A82" t="s">
         <v>607</v>
       </c>
+      <c r="B82" t="s">
+        <v>1416</v>
+      </c>
       <c r="C82" t="s">
         <v>481</v>
       </c>
@@ -9255,6 +9650,9 @@
       <c r="A84" t="s">
         <v>609</v>
       </c>
+      <c r="B84" t="s">
+        <v>1448</v>
+      </c>
       <c r="C84" t="s">
         <v>610</v>
       </c>
@@ -9271,6 +9669,9 @@
       <c r="A86" t="s">
         <v>613</v>
       </c>
+      <c r="B86" t="s">
+        <v>1449</v>
+      </c>
       <c r="C86" t="s">
         <v>614</v>
       </c>
@@ -9287,6 +9688,9 @@
       <c r="A88" t="s">
         <v>617</v>
       </c>
+      <c r="B88" t="s">
+        <v>1450</v>
+      </c>
       <c r="C88" t="s">
         <v>618</v>
       </c>
@@ -9303,6 +9707,9 @@
       <c r="A90" t="s">
         <v>621</v>
       </c>
+      <c r="B90" t="s">
+        <v>1451</v>
+      </c>
       <c r="C90" t="s">
         <v>622</v>
       </c>
@@ -9319,6 +9726,9 @@
       <c r="A92" t="s">
         <v>625</v>
       </c>
+      <c r="B92" t="s">
+        <v>1452</v>
+      </c>
       <c r="C92" t="s">
         <v>626</v>
       </c>
@@ -9335,6 +9745,9 @@
       <c r="A94" t="s">
         <v>629</v>
       </c>
+      <c r="B94" t="s">
+        <v>1453</v>
+      </c>
       <c r="C94" t="s">
         <v>630</v>
       </c>
@@ -9351,6 +9764,9 @@
       <c r="A96" t="s">
         <v>633</v>
       </c>
+      <c r="B96" t="s">
+        <v>1454</v>
+      </c>
       <c r="C96" t="s">
         <v>634</v>
       </c>
@@ -9367,6 +9783,9 @@
       <c r="A98" t="s">
         <v>637</v>
       </c>
+      <c r="B98" t="s">
+        <v>1455</v>
+      </c>
       <c r="C98" t="s">
         <v>638</v>
       </c>
@@ -9383,6 +9802,9 @@
       <c r="A100" t="s">
         <v>641</v>
       </c>
+      <c r="B100" t="s">
+        <v>1456</v>
+      </c>
       <c r="C100" t="s">
         <v>642</v>
       </c>
@@ -9399,6 +9821,9 @@
       <c r="A102" t="s">
         <v>645</v>
       </c>
+      <c r="B102" t="s">
+        <v>1457</v>
+      </c>
       <c r="C102" t="s">
         <v>646</v>
       </c>
@@ -9415,6 +9840,9 @@
       <c r="A104" t="s">
         <v>649</v>
       </c>
+      <c r="B104" t="s">
+        <v>1458</v>
+      </c>
       <c r="C104" t="s">
         <v>650</v>
       </c>
@@ -9431,6 +9859,9 @@
       <c r="A106" t="s">
         <v>653</v>
       </c>
+      <c r="B106" t="s">
+        <v>1459</v>
+      </c>
       <c r="C106" t="s">
         <v>654</v>
       </c>
@@ -9447,6 +9878,9 @@
       <c r="A108" t="s">
         <v>657</v>
       </c>
+      <c r="B108" t="s">
+        <v>1460</v>
+      </c>
       <c r="C108" t="s">
         <v>658</v>
       </c>
@@ -9463,6 +9897,9 @@
       <c r="A110" t="s">
         <v>661</v>
       </c>
+      <c r="B110" t="s">
+        <v>1461</v>
+      </c>
       <c r="C110" t="s">
         <v>662</v>
       </c>
@@ -9479,6 +9916,9 @@
       <c r="A112" t="s">
         <v>665</v>
       </c>
+      <c r="B112" t="s">
+        <v>1462</v>
+      </c>
       <c r="C112" t="s">
         <v>666</v>
       </c>
@@ -9495,6 +9935,9 @@
       <c r="A114" t="s">
         <v>669</v>
       </c>
+      <c r="B114" t="s">
+        <v>1463</v>
+      </c>
       <c r="C114" t="s">
         <v>670</v>
       </c>
@@ -9511,6 +9954,9 @@
       <c r="A116" t="s">
         <v>673</v>
       </c>
+      <c r="B116" t="s">
+        <v>1464</v>
+      </c>
       <c r="C116" t="s">
         <v>674</v>
       </c>
@@ -9527,6 +9973,9 @@
       <c r="A118" t="s">
         <v>677</v>
       </c>
+      <c r="B118" t="s">
+        <v>1465</v>
+      </c>
       <c r="C118" t="s">
         <v>678</v>
       </c>
@@ -9543,6 +9992,9 @@
       <c r="A120" t="s">
         <v>681</v>
       </c>
+      <c r="B120" t="s">
+        <v>1466</v>
+      </c>
       <c r="C120" t="s">
         <v>682</v>
       </c>
@@ -9559,6 +10011,9 @@
       <c r="A122" t="s">
         <v>685</v>
       </c>
+      <c r="B122" t="s">
+        <v>1467</v>
+      </c>
       <c r="C122" t="s">
         <v>686</v>
       </c>
@@ -9575,6 +10030,9 @@
       <c r="A124" t="s">
         <v>689</v>
       </c>
+      <c r="B124" t="s">
+        <v>1468</v>
+      </c>
       <c r="C124" t="s">
         <v>690</v>
       </c>
@@ -9591,6 +10049,9 @@
       <c r="A126" t="s">
         <v>693</v>
       </c>
+      <c r="B126" t="s">
+        <v>1469</v>
+      </c>
       <c r="C126" t="s">
         <v>694</v>
       </c>
@@ -9607,6 +10068,9 @@
       <c r="A128" t="s">
         <v>697</v>
       </c>
+      <c r="B128" t="s">
+        <v>1470</v>
+      </c>
       <c r="C128" t="s">
         <v>698</v>
       </c>
@@ -9623,6 +10087,9 @@
       <c r="A130" t="s">
         <v>701</v>
       </c>
+      <c r="B130" t="s">
+        <v>1471</v>
+      </c>
       <c r="C130" t="s">
         <v>702</v>
       </c>
@@ -9639,6 +10106,9 @@
       <c r="A132" t="s">
         <v>705</v>
       </c>
+      <c r="B132" t="s">
+        <v>1472</v>
+      </c>
       <c r="C132" t="s">
         <v>706</v>
       </c>
@@ -9655,6 +10125,9 @@
       <c r="A134" t="s">
         <v>709</v>
       </c>
+      <c r="B134" t="s">
+        <v>1473</v>
+      </c>
       <c r="C134" t="s">
         <v>710</v>
       </c>
@@ -9671,6 +10144,9 @@
       <c r="A136" t="s">
         <v>713</v>
       </c>
+      <c r="B136" t="s">
+        <v>1474</v>
+      </c>
       <c r="C136" t="s">
         <v>714</v>
       </c>
@@ -9687,6 +10163,9 @@
       <c r="A138" t="s">
         <v>717</v>
       </c>
+      <c r="B138" t="s">
+        <v>1475</v>
+      </c>
       <c r="C138" t="s">
         <v>718</v>
       </c>
@@ -9703,6 +10182,9 @@
       <c r="A140" t="s">
         <v>721</v>
       </c>
+      <c r="B140" t="s">
+        <v>1476</v>
+      </c>
       <c r="C140" t="s">
         <v>722</v>
       </c>
@@ -9719,6 +10201,9 @@
       <c r="A142" t="s">
         <v>725</v>
       </c>
+      <c r="B142" t="s">
+        <v>1477</v>
+      </c>
       <c r="C142" t="s">
         <v>726</v>
       </c>
@@ -9735,6 +10220,9 @@
       <c r="A144" t="s">
         <v>729</v>
       </c>
+      <c r="B144" t="s">
+        <v>1478</v>
+      </c>
       <c r="C144" t="s">
         <v>730</v>
       </c>
@@ -9751,6 +10239,9 @@
       <c r="A146" t="s">
         <v>733</v>
       </c>
+      <c r="B146" t="s">
+        <v>1479</v>
+      </c>
       <c r="C146" t="s">
         <v>734</v>
       </c>
@@ -9767,6 +10258,9 @@
       <c r="A148" t="s">
         <v>737</v>
       </c>
+      <c r="B148" t="s">
+        <v>1480</v>
+      </c>
       <c r="C148" t="s">
         <v>738</v>
       </c>
@@ -9783,6 +10277,9 @@
       <c r="A150" t="s">
         <v>741</v>
       </c>
+      <c r="B150" t="s">
+        <v>1481</v>
+      </c>
       <c r="C150" t="s">
         <v>742</v>
       </c>
@@ -9799,6 +10296,9 @@
       <c r="A152" t="s">
         <v>745</v>
       </c>
+      <c r="B152" t="s">
+        <v>1482</v>
+      </c>
       <c r="C152" t="s">
         <v>746</v>
       </c>
@@ -9815,6 +10315,9 @@
       <c r="A154" t="s">
         <v>749</v>
       </c>
+      <c r="B154" t="s">
+        <v>1483</v>
+      </c>
       <c r="C154" t="s">
         <v>750</v>
       </c>
@@ -9831,6 +10334,9 @@
       <c r="A156" t="s">
         <v>753</v>
       </c>
+      <c r="B156" t="s">
+        <v>1484</v>
+      </c>
       <c r="C156" t="s">
         <v>754</v>
       </c>
@@ -9847,6 +10353,9 @@
       <c r="A158" t="s">
         <v>757</v>
       </c>
+      <c r="B158" t="s">
+        <v>1485</v>
+      </c>
       <c r="C158" t="s">
         <v>758</v>
       </c>
@@ -9863,6 +10372,9 @@
       <c r="A160" t="s">
         <v>761</v>
       </c>
+      <c r="B160" t="s">
+        <v>1486</v>
+      </c>
       <c r="C160" t="s">
         <v>762</v>
       </c>
@@ -9879,6 +10391,9 @@
       <c r="A162" t="s">
         <v>765</v>
       </c>
+      <c r="B162" t="s">
+        <v>1487</v>
+      </c>
       <c r="C162" t="s">
         <v>766</v>
       </c>
@@ -9895,6 +10410,9 @@
       <c r="A164" t="s">
         <v>769</v>
       </c>
+      <c r="B164" t="s">
+        <v>1488</v>
+      </c>
       <c r="C164" t="s">
         <v>770</v>
       </c>
@@ -9911,6 +10429,9 @@
       <c r="A166" t="s">
         <v>773</v>
       </c>
+      <c r="B166" t="s">
+        <v>1489</v>
+      </c>
       <c r="C166" t="s">
         <v>774</v>
       </c>
@@ -9927,6 +10448,9 @@
       <c r="A168" t="s">
         <v>777</v>
       </c>
+      <c r="B168" t="s">
+        <v>1490</v>
+      </c>
       <c r="C168" t="s">
         <v>778</v>
       </c>
@@ -9943,6 +10467,9 @@
       <c r="A170" t="s">
         <v>781</v>
       </c>
+      <c r="B170" t="s">
+        <v>1491</v>
+      </c>
       <c r="C170" t="s">
         <v>782</v>
       </c>
@@ -9959,6 +10486,9 @@
       <c r="A172" t="s">
         <v>785</v>
       </c>
+      <c r="B172" t="s">
+        <v>1492</v>
+      </c>
       <c r="C172" t="s">
         <v>786</v>
       </c>
@@ -9974,6 +10504,9 @@
     <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>789</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1493</v>
       </c>
       <c r="C174" t="s">
         <v>790</v>
@@ -10701,7 +11234,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="9" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>1155</v>
@@ -10712,7 +11245,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>1156</v>
@@ -10723,7 +11256,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="9" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>1157</v>
@@ -10734,7 +11267,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>1153</v>
@@ -10745,7 +11278,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="9" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>1154</v>
@@ -10756,7 +11289,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="9" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>1158</v>
@@ -10767,7 +11300,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="9" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>1159</v>
@@ -10778,7 +11311,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="9" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>1161</v>
@@ -10789,7 +11322,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>1160</v>
@@ -10800,7 +11333,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="9" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>1162</v>
@@ -10811,7 +11344,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="9" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>1163</v>
@@ -10822,7 +11355,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="9" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>1164</v>
@@ -10833,7 +11366,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="9" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>1165</v>
@@ -10844,7 +11377,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="9" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>1166</v>
@@ -10855,7 +11388,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="9" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>1167</v>
@@ -10866,7 +11399,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>1168</v>
@@ -10877,7 +11410,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="9" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>1169</v>
@@ -10888,7 +11421,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="9" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>1170</v>
@@ -10899,7 +11432,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="9" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>1171</v>
@@ -10910,7 +11443,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="9" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>1172</v>
@@ -10921,7 +11454,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="9" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>1173</v>
@@ -10932,7 +11465,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="9" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>1175</v>
@@ -10943,7 +11476,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>1174</v>
@@ -10954,7 +11487,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="9" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>1176</v>
@@ -10965,7 +11498,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="9" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>1177</v>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8890,8 +8890,10 @@
       <c r="A4" t="s">
         <v>460</v>
       </c>
-      <c r="B4" t="s">
-        <v>1411</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Slime Ruber</t>
+        </is>
       </c>
       <c r="C4" t="s">
         <v>461</v>
@@ -8928,8 +8930,10 @@
       <c r="A8" t="s">
         <v>468</v>
       </c>
-      <c r="B8" t="s">
-        <v>1413</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mage Hydro</t>
+        </is>
       </c>
       <c r="C8" t="s">
         <v>469</v>
@@ -8966,8 +8970,10 @@
       <c r="A12" t="s">
         <v>476</v>
       </c>
-      <c r="B12" t="s">
-        <v>1415</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mage Bronto</t>
+        </is>
       </c>
       <c r="C12" t="s">
         <v>477</v>
@@ -9004,8 +9010,10 @@
       <c r="A16" t="s">
         <v>483</v>
       </c>
-      <c r="B16" t="s">
-        <v>1417</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Slime Niger</t>
+        </is>
       </c>
       <c r="C16" t="s">
         <v>484</v>
@@ -9080,8 +9088,10 @@
       <c r="A24" t="s">
         <v>497</v>
       </c>
-      <c r="B24" t="s">
-        <v>1421</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Golem Lithos</t>
+        </is>
       </c>
       <c r="C24" t="s">
         <v>498</v>
@@ -9194,8 +9204,10 @@
       <c r="A36" t="s">
         <v>519</v>
       </c>
-      <c r="B36" t="s">
-        <v>1427</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knight Ferrum</t>
+        </is>
       </c>
       <c r="C36" t="s">
         <v>520</v>
@@ -9213,8 +9225,10 @@
       <c r="A38" t="s">
         <v>523</v>
       </c>
-      <c r="B38" t="s">
-        <v>1428</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bat Ruber</t>
+        </is>
       </c>
       <c r="C38" t="s">
         <v>524</v>
@@ -9289,8 +9303,10 @@
       <c r="A46" t="s">
         <v>539</v>
       </c>
-      <c r="B46" t="s">
-        <v>1432</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mage Pyro</t>
+        </is>
       </c>
       <c r="C46" t="s">
         <v>540</v>
@@ -9365,8 +9381,10 @@
       <c r="A54" t="s">
         <v>555</v>
       </c>
-      <c r="B54" t="s">
-        <v>1436</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bat Haemo</t>
+        </is>
       </c>
       <c r="C54" t="s">
         <v>556</v>
@@ -9403,8 +9421,10 @@
       <c r="A58" t="s">
         <v>563</v>
       </c>
-      <c r="B58" t="s">
-        <v>1438</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Wizard Aero</t>
+        </is>
       </c>
       <c r="C58" t="s">
         <v>564</v>
@@ -9441,8 +9461,10 @@
       <c r="A62" t="s">
         <v>571</v>
       </c>
-      <c r="B62" t="s">
-        <v>1440</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Guard Albus</t>
+        </is>
       </c>
       <c r="C62" t="s">
         <v>572</v>
@@ -9460,8 +9482,10 @@
       <c r="A64" t="s">
         <v>575</v>
       </c>
-      <c r="B64" t="s">
-        <v>1441</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Knight Cinereus</t>
+        </is>
       </c>
       <c r="C64" t="s">
         <v>576</v>
@@ -9574,8 +9598,10 @@
       <c r="A76" t="s">
         <v>595</v>
       </c>
-      <c r="B76" t="s">
-        <v>1445</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Zombie Toxicon</t>
+        </is>
       </c>
       <c r="C76" t="s">
         <v>596</v>
@@ -9593,8 +9619,10 @@
       <c r="A78" t="s">
         <v>599</v>
       </c>
-      <c r="B78" t="s">
-        <v>1446</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bat Toxicon</t>
+        </is>
       </c>
       <c r="C78" t="s">
         <v>600</v>
@@ -9783,8 +9811,10 @@
       <c r="A98" t="s">
         <v>637</v>
       </c>
-      <c r="B98" t="s">
-        <v>1455</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Guard Cyaneus</t>
+        </is>
       </c>
       <c r="C98" t="s">
         <v>638</v>
@@ -9840,8 +9870,10 @@
       <c r="A104" t="s">
         <v>649</v>
       </c>
-      <c r="B104" t="s">
-        <v>1458</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Golem Chalybs</t>
+        </is>
       </c>
       <c r="C104" t="s">
         <v>650</v>
@@ -9878,8 +9910,10 @@
       <c r="A108" t="s">
         <v>657</v>
       </c>
-      <c r="B108" t="s">
-        <v>1460</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Golem Ferrum</t>
+        </is>
       </c>
       <c r="C108" t="s">
         <v>658</v>
@@ -9897,8 +9931,10 @@
       <c r="A110" t="s">
         <v>661</v>
       </c>
-      <c r="B110" t="s">
-        <v>1461</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Man Hydrargyrum</t>
+        </is>
       </c>
       <c r="C110" t="s">
         <v>662</v>
@@ -9992,8 +10028,10 @@
       <c r="A120" t="s">
         <v>681</v>
       </c>
-      <c r="B120" t="s">
-        <v>1466</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Slime Cryo</t>
+        </is>
       </c>
       <c r="C120" t="s">
         <v>682</v>
@@ -10011,8 +10049,10 @@
       <c r="A122" t="s">
         <v>685</v>
       </c>
-      <c r="B122" t="s">
-        <v>1467</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Octopus Toxicon</t>
+        </is>
       </c>
       <c r="C122" t="s">
         <v>686</v>
@@ -10030,8 +10070,10 @@
       <c r="A124" t="s">
         <v>689</v>
       </c>
-      <c r="B124" t="s">
-        <v>1468</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Zombie Pyro</t>
+        </is>
       </c>
       <c r="C124" t="s">
         <v>690</v>
@@ -10049,8 +10091,10 @@
       <c r="A126" t="s">
         <v>693</v>
       </c>
-      <c r="B126" t="s">
-        <v>1469</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Bones Cryo</t>
+        </is>
       </c>
       <c r="C126" t="s">
         <v>694</v>
@@ -10087,8 +10131,10 @@
       <c r="A130" t="s">
         <v>701</v>
       </c>
-      <c r="B130" t="s">
-        <v>1471</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sentinel Ferrum</t>
+        </is>
       </c>
       <c r="C130" t="s">
         <v>702</v>
@@ -10163,8 +10209,10 @@
       <c r="A138" t="s">
         <v>717</v>
       </c>
-      <c r="B138" t="s">
-        <v>1475</v>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Wizard Pyro</t>
+        </is>
       </c>
       <c r="C138" t="s">
         <v>718</v>
@@ -10182,8 +10230,10 @@
       <c r="A140" t="s">
         <v>721</v>
       </c>
-      <c r="B140" t="s">
-        <v>1476</v>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Overlord Ruber</t>
+        </is>
       </c>
       <c r="C140" t="s">
         <v>722</v>
@@ -10239,8 +10289,10 @@
       <c r="A146" t="s">
         <v>733</v>
       </c>
-      <c r="B146" t="s">
-        <v>1479</v>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Hound Aero</t>
+        </is>
       </c>
       <c r="C146" t="s">
         <v>734</v>
@@ -10296,8 +10348,10 @@
       <c r="A152" t="s">
         <v>745</v>
       </c>
-      <c r="B152" t="s">
-        <v>1482</v>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Wizard Cryo</t>
+        </is>
       </c>
       <c r="C152" t="s">
         <v>746</v>
@@ -10429,8 +10483,10 @@
       <c r="A166" t="s">
         <v>773</v>
       </c>
-      <c r="B166" t="s">
-        <v>1489</v>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Mage Haemo</t>
+        </is>
       </c>
       <c r="C166" t="s">
         <v>774</v>
@@ -10624,7 +10680,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -10678,6 +10734,74 @@
       </c>
       <c r="C5" s="8" t="s">
         <v>1193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YUREN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Royal Blade</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>御刃</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>YUREN_DESC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Converts some defence into attack with magic for the rest of the battle. Can be used repeatedly. Higher magic improves the conversion.</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>以魔力将部分防御转为攻击，持续至战斗结束，可重复施放。魔力越高，转化效果越好。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JINGMU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mirror Veil</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>镜幕</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JINGMU_DESC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reduces incoming damage and blocks harmful effects from that attack. When blocking a critical hit, reflects those effects back at the attacker.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>降低受到的伤害，并免疫此次攻击附加的负面效果；抵挡会心一击时，将负面效果反弹给对方。</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,35 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3SA\ProjectMT3\Data\Locale\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05565F7-69A6-401A-9814-1867478C7723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-32560" yWindow="2030" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="UI" sheetId="1" r:id="rId1"/>
-    <sheet name="Languages" sheetId="2" r:id="rId2"/>
-    <sheet name="Attrs" sheetId="3" r:id="rId3"/>
-    <sheet name="Items" sheetId="4" r:id="rId4"/>
-    <sheet name="Enemies" sheetId="5" r:id="rId5"/>
-    <sheet name="Equips" sheetId="6" r:id="rId6"/>
-    <sheet name="Classes" sheetId="7" r:id="rId7"/>
-    <sheet name="States" sheetId="8" r:id="rId8"/>
-    <sheet name="MapNames" sheetId="9" r:id="rId9"/>
-    <sheet name="Specials" sheetId="10" r:id="rId10"/>
-    <sheet name="Player" sheetId="11" r:id="rId11"/>
-    <sheet name="DialogueNames" sheetId="12" r:id="rId12"/>
-    <sheet name="DialogueContents" sheetId="13" r:id="rId13"/>
-    <sheet name="TutorialMessages" sheetId="15" r:id="rId14"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+  <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <ns0:workbookPr/>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="D:\Dev\ProjectMT3SA\ProjectMT3\Data\Locale\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
+  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05565F7-69A6-401A-9814-1867478C7723}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <ns0:bookViews>
+    <ns0:workbookView xWindow="-32560" yWindow="2030" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="8" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="UI" sheetId="1" ns7:id="rId1"/>
+    <ns0:sheet name="Languages" sheetId="2" ns7:id="rId2"/>
+    <ns0:sheet name="Attrs" sheetId="3" ns7:id="rId3"/>
+    <ns0:sheet name="Items" sheetId="4" ns7:id="rId4"/>
+    <ns0:sheet name="Enemies" sheetId="5" ns7:id="rId5"/>
+    <ns0:sheet name="Equips" sheetId="6" ns7:id="rId6"/>
+    <ns0:sheet name="Classes" sheetId="7" ns7:id="rId7"/>
+    <ns0:sheet name="States" sheetId="8" ns7:id="rId8"/>
+    <ns0:sheet name="MapNames" sheetId="9" ns7:id="rId9"/>
+    <ns0:sheet name="Specials" sheetId="10" ns7:id="rId10"/>
+    <ns0:sheet name="Player" sheetId="11" ns7:id="rId11"/>
+    <ns0:sheet name="DialogueNames" sheetId="12" ns7:id="rId12"/>
+    <ns0:sheet name="DialogueContents" sheetId="13" ns7:id="rId13"/>
+    <ns0:sheet name="TutorialMessages" sheetId="15" ns7:id="rId14"/>
+    <ns0:sheet name="messages" sheetId="15" ns7:id="rId18"/>
+  </ns0:sheets>
+  <ns0:calcPr calcId="0"/>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8181,6 +8182,394 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetFormatPr defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <ns0:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <ns0:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="str" s="1">
+        <ns0:v>ID</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" t="str" s="1">
+        <ns0:v>en_GB</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" t="str" s="1">
+        <ns0:v>zh_CN</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_LABEL</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" t="str">
+        <ns0:v>Template</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" t="str">
+        <ns0:v>句式</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" t="str">
+        <ns0:v>MESSAGES_WORD_LABEL</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" t="str">
+        <ns0:v>Word</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" t="str">
+        <ns0:v>词语</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" t="str">
+        <ns0:v>MESSAGES_PUBLISH</ns0:v>
+      </ns0:c>
+      <ns0:c r="B4" t="str">
+        <ns0:v>Confirm</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" t="str">
+        <ns0:v>确认</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" t="str">
+        <ns0:v>MESSAGES_HOTKEY</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5" t="str">
+        <ns0:v>T: Leave a message</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" t="str">
+        <ns0:v>T：留下箴言</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" t="str">
+        <ns0:v>MESSAGES_NETWORK_BAD</ns0:v>
+      </ns0:c>
+      <ns0:c r="B6" t="str">
+        <ns0:v>Poor network connection. Please try again later.</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" t="str">
+        <ns0:v>当前网络环境不佳，请稍后再试。</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" t="str">
+        <ns0:v>MESSAGES_CHECKING</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" t="str">
+        <ns0:v>Checking connection…</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" t="str">
+        <ns0:v>正在检测网络连接……</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" t="str">
+        <ns0:v>MESSAGES_OFFLINE</ns0:v>
+      </ns0:c>
+      <ns0:c r="B8" t="str">
+        <ns0:v>Connection unavailable</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" t="str">
+        <ns0:v>当前网络环境不佳</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" t="str">
+        <ns0:v>MESSAGES_READY</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" t="str">
+        <ns0:v>Ready to publish</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" t="str">
+        <ns0:v>可以发布留言</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" t="str">
+        <ns0:v>MESSAGES_SENDING</ns0:v>
+      </ns0:c>
+      <ns0:c r="B10" t="str">
+        <ns0:v>Publishing…</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" t="str">
+        <ns0:v>正在发布……</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" t="str">
+        <ns0:v>MESSAGES_SENT</ns0:v>
+      </ns0:c>
+      <ns0:c r="B11" t="str">
+        <ns0:v>Message published.</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" t="str">
+        <ns0:v>留言已发布。</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" t="str">
+        <ns0:v>MESSAGES_FAILED</ns0:v>
+      </ns0:c>
+      <ns0:c r="B12" t="str">
+        <ns0:v>Could not publish. The local message was removed.</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" t="str">
+        <ns0:v>留言发布失败，已移除本地留言。</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" t="str">
+        <ns0:v>MESSAGES_RATE_LIMITED</ns0:v>
+      </ns0:c>
+      <ns0:c r="B13" t="str">
+        <ns0:v>Please wait {seconds} seconds before publishing again.</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" t="str">
+        <ns0:v>请等待 {seconds} 秒后再发布留言。</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_AHEAD</ns0:v>
+      </ns0:c>
+      <ns0:c r="B14" t="str">
+        <ns0:v>{word} ahead</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" t="str">
+        <ns0:v>前方有{word}</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_BEWARE</ns0:v>
+      </ns0:c>
+      <ns0:c r="B15" t="str">
+        <ns0:v>Beware of {word}</ns0:v>
+      </ns0:c>
+      <ns0:c r="C15" t="str">
+        <ns0:v>小心{word}</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_SEEK</ns0:v>
+      </ns0:c>
+      <ns0:c r="B16" t="str">
+        <ns0:v>Seek {word}</ns0:v>
+      </ns0:c>
+      <ns0:c r="C16" t="str">
+        <ns0:v>寻找{word}</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_REMEMBER</ns0:v>
+      </ns0:c>
+      <ns0:c r="B17" t="str">
+        <ns0:v>Do not forget {word}</ns0:v>
+      </ns0:c>
+      <ns0:c r="C17" t="str">
+        <ns0:v>别忘了{word}</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" t="str">
+        <ns0:v>MESSAGES_TEMPLATE_NEED</ns0:v>
+      </ns0:c>
+      <ns0:c r="B18" t="str">
+        <ns0:v>{word} required</ns0:v>
+      </ns0:c>
+      <ns0:c r="C18" t="str">
+        <ns0:v>需要{word}</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" t="str">
+        <ns0:v>MESSAGES_WORD_ENEMY</ns0:v>
+      </ns0:c>
+      <ns0:c r="B19" t="str">
+        <ns0:v>a strong enemy</ns0:v>
+      </ns0:c>
+      <ns0:c r="C19" t="str">
+        <ns0:v>强敌</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" t="str">
+        <ns0:v>MESSAGES_WORD_AMBUSH</ns0:v>
+      </ns0:c>
+      <ns0:c r="B20" t="str">
+        <ns0:v>an ambush</ns0:v>
+      </ns0:c>
+      <ns0:c r="C20" t="str">
+        <ns0:v>伏击</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" t="str">
+        <ns0:v>MESSAGES_WORD_TRAP</ns0:v>
+      </ns0:c>
+      <ns0:c r="B21" t="str">
+        <ns0:v>a trap</ns0:v>
+      </ns0:c>
+      <ns0:c r="C21" t="str">
+        <ns0:v>陷阱</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" t="str">
+        <ns0:v>MESSAGES_WORD_POISON</ns0:v>
+      </ns0:c>
+      <ns0:c r="B22" t="str">
+        <ns0:v>poison</ns0:v>
+      </ns0:c>
+      <ns0:c r="C22" t="str">
+        <ns0:v>中毒</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" t="str">
+        <ns0:v>MESSAGES_WORD_WEAKNESS</ns0:v>
+      </ns0:c>
+      <ns0:c r="B23" t="str">
+        <ns0:v>weakness</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" t="str">
+        <ns0:v>衰弱</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" t="str">
+        <ns0:v>MESSAGES_WORD_MECHANISM</ns0:v>
+      </ns0:c>
+      <ns0:c r="B24" t="str">
+        <ns0:v>a mechanism</ns0:v>
+      </ns0:c>
+      <ns0:c r="C24" t="str">
+        <ns0:v>机关</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" t="str">
+        <ns0:v>MESSAGES_WORD_PASSAGE</ns0:v>
+      </ns0:c>
+      <ns0:c r="B25" t="str">
+        <ns0:v>a hidden passage</ns0:v>
+      </ns0:c>
+      <ns0:c r="C25" t="str">
+        <ns0:v>暗道</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" t="str">
+        <ns0:v>MESSAGES_WORD_STAIRS</ns0:v>
+      </ns0:c>
+      <ns0:c r="B26" t="str">
+        <ns0:v>stairs</ns0:v>
+      </ns0:c>
+      <ns0:c r="C26" t="str">
+        <ns0:v>楼梯</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" t="str">
+        <ns0:v>MESSAGES_WORD_KEY</ns0:v>
+      </ns0:c>
+      <ns0:c r="B27" t="str">
+        <ns0:v>a key</ns0:v>
+      </ns0:c>
+      <ns0:c r="C27" t="str">
+        <ns0:v>钥匙</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" t="str">
+        <ns0:v>MESSAGES_WORD_POTION</ns0:v>
+      </ns0:c>
+      <ns0:c r="B28" t="str">
+        <ns0:v>a potion</ns0:v>
+      </ns0:c>
+      <ns0:c r="C28" t="str">
+        <ns0:v>药水</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" t="str">
+        <ns0:v>MESSAGES_WORD_GEM</ns0:v>
+      </ns0:c>
+      <ns0:c r="B29" t="str">
+        <ns0:v>a gem</ns0:v>
+      </ns0:c>
+      <ns0:c r="C29" t="str">
+        <ns0:v>宝石</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" t="str">
+        <ns0:v>MESSAGES_WORD_CHEST</ns0:v>
+      </ns0:c>
+      <ns0:c r="B30" t="str">
+        <ns0:v>a chest</ns0:v>
+      </ns0:c>
+      <ns0:c r="C30" t="str">
+        <ns0:v>宝箱</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" t="str">
+        <ns0:v>MESSAGES_WORD_SHOP</ns0:v>
+      </ns0:c>
+      <ns0:c r="B31" t="str">
+        <ns0:v>a shop</ns0:v>
+      </ns0:c>
+      <ns0:c r="C31" t="str">
+        <ns0:v>商店</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" t="str">
+        <ns0:v>MESSAGES_WORD_WEAPON</ns0:v>
+      </ns0:c>
+      <ns0:c r="B32" t="str">
+        <ns0:v>a weapon</ns0:v>
+      </ns0:c>
+      <ns0:c r="C32" t="str">
+        <ns0:v>武器</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" t="str">
+        <ns0:v>MESSAGES_WORD_ARMOUR</ns0:v>
+      </ns0:c>
+      <ns0:c r="B33" t="str">
+        <ns0:v>armour</ns0:v>
+      </ns0:c>
+      <ns0:c r="C33" t="str">
+        <ns0:v>防具</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="34">
+      <ns0:c r="A34" t="str">
+        <ns0:v>MESSAGES_WORD_TELEPORTER</ns0:v>
+      </ns0:c>
+      <ns0:c r="B34" t="str">
+        <ns0:v>a teleporter</ns0:v>
+      </ns0:c>
+      <ns0:c r="C34" t="str">
+        <ns0:v>传送点</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -5025,7 +5025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5705,14 +5705,20 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>259</v>
-      </c>
-      <c r="B62" t="s">
-        <v>260</v>
-      </c>
-      <c r="C62" t="s">
-        <v>261</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BATTLE_RETREAT</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Retreat</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>撤退</t>
+        </is>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -5867,6 +5873,210 @@
       </c>
       <c r="C76" t="s">
         <v>1300</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CONTROLS_TITLE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>操作说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HOTKEY_CONTROLS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>H: Controls</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>H：操作说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>HOTKEY_BATTLE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Battle — Q: Retreat; C: Critical hit; Z/X: Attack/defense skill</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>战斗：Q 撤退，C 会心一击，Z/X 攻击/防御技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GAMEPAD_MOVE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Left stick / D-pad: Move</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>左摇杆／十字键：移动</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>GAMEPAD_MENU</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Menu: Open menu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>菜单键：打开菜单</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>GAMEPAD_CONTROLS</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>X: Controls</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>X：操作说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>GAMEPAD_CONFIRM</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A: Confirm; B: Back</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A：确认；B：返回</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>GAMEPAD_BATTLE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Battle — B: Retreat; A: Critical hit; D-pad left/right: Attack/defense skill</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>战斗：B 撤退，A 会心一击，十字键左/右使用攻击/防御技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TOUCH_MOVE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tap the map: Move to the destination</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>点击地图：移动到目标位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TOUCH_MENU</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tap an avatar: Menu; swipe avatars: Switch party member</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>点击头像：菜单；左右滑动头像：切换角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TOUCH_CONTROLS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tap Controls to view the controls</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>点击操作说明查看操作方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TOUCH_BATTLE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Battle: Tap the skill, critical hit or retreat button</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>战斗：点击技能、会心一击或撤退按钮</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8059,7 +8269,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4933D5-C722-C646-96A3-51CA5B4C6607}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43" customWidth="1"/>
@@ -8111,14 +8321,20 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1266</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TM_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Press H to view the controls.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>按 H 键可以查看操作说明。</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -8174,6 +8390,74 @@
       </c>
       <c r="C10" s="2" t="s">
         <v>1458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TM_04_G</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Press X to view the controls.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>按 X 键可以查看操作说明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TM_04_M</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Tap Controls to view the controls.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>点击操作说明可以查看操作方式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TM_05_G</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Enemy information. Press A to view details.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>敌人的能力信息，按 A 查看详细内容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TM_07_MENU</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Open Items from the menu to use this item.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>打开菜单中的道具来使用。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8565,6 +8849,40 @@
         <ns0:v>传送点</ns0:v>
       </ns0:c>
     </ns0:row>
+    <ns0:row r="35">
+      <ns0:c r="A35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MESSAGES_GAMEPAD_HOTKEY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y: Leave a message</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C35" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y：留言</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>MESSAGES_TOUCH_HOTKEY</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Hold your current tile: Leave a message</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C36" t="inlineStr">
+        <ns0:is>
+          <ns0:t>长按角色当前格子：留言</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
   </ns0:sheetData>
   <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </ns0:worksheet>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -5025,7 +5025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5912,17 +5912,17 @@
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HOTKEY_BATTLE</t>
+          <t>HOTKEY_BATTLE_RETREAT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Battle — Q: Retreat; C: Critical hit; Z/X: Attack/defense skill</t>
+          <t>Q: Retreat</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>战斗：Q 撤退，C 会心一击，Z/X 攻击/防御技能</t>
+          <t>Q：撤退</t>
         </is>
       </c>
     </row>
@@ -5997,17 +5997,17 @@
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GAMEPAD_BATTLE</t>
+          <t>GAMEPAD_BATTLE_RETREAT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Battle — B: Retreat; A: Critical hit; D-pad left/right: Attack/defense skill</t>
+          <t>B: Retreat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>战斗：B 撤退，A 会心一击，十字键左/右使用攻击/防御技能</t>
+          <t>B：撤退</t>
         </is>
       </c>
     </row>
@@ -6065,17 +6065,204 @@
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TOUCH_BATTLE</t>
+          <t>TOUCH_BATTLE_RETREAT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Battle: Tap the skill, critical hit or retreat button</t>
+          <t>Tap Retreat</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>战斗：点击技能、会心一击或撤退按钮</t>
+          <t>点击撤退按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CONTROLS_DAILY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>日常</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CONTROLS_BATTLE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HOTKEY_BATTLE_CRITICAL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>C: Critical hit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>C：会心一击</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HOTKEY_BATTLE_ATTACK_SKILL</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Z: Attack skill</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Z：攻击技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>HOTKEY_BATTLE_DEFENSE_SKILL</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>X: Defense skill</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>X：防御技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GAMEPAD_BATTLE_CRITICAL</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A: Critical hit</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>A：会心一击</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GAMEPAD_BATTLE_ATTACK_SKILL</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D-pad left: Attack skill</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>十字键左：攻击技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>GAMEPAD_BATTLE_DEFENSE_SKILL</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D-pad right: Defense skill</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>十字键右：防御技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TOUCH_BATTLE_CRITICAL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tap Critical hit</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>点击会心一击按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TOUCH_BATTLE_ATTACK_SKILL</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tap Attack skill</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>点击攻击技能按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TOUCH_BATTLE_DEFENSE_SKILL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tap Defense skill</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>点击防御技能按钮</t>
         </is>
       </c>
     </row>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns7="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
-  <ns0:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <ns0:workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="D:\Dev\ProjectMT3SA\ProjectMT3\Data\Locale\"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
-  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05565F7-69A6-401A-9814-1867478C7723}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <ns0:bookViews>
-    <ns0:workbookView xWindow="-32560" yWindow="2030" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="8" ns6:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </ns0:bookViews>
-  <ns0:sheets>
-    <ns0:sheet name="UI" sheetId="1" ns7:id="rId1"/>
-    <ns0:sheet name="Languages" sheetId="2" ns7:id="rId2"/>
-    <ns0:sheet name="Attrs" sheetId="3" ns7:id="rId3"/>
-    <ns0:sheet name="Items" sheetId="4" ns7:id="rId4"/>
-    <ns0:sheet name="Enemies" sheetId="5" ns7:id="rId5"/>
-    <ns0:sheet name="Equips" sheetId="6" ns7:id="rId6"/>
-    <ns0:sheet name="Classes" sheetId="7" ns7:id="rId7"/>
-    <ns0:sheet name="States" sheetId="8" ns7:id="rId8"/>
-    <ns0:sheet name="MapNames" sheetId="9" ns7:id="rId9"/>
-    <ns0:sheet name="Specials" sheetId="10" ns7:id="rId10"/>
-    <ns0:sheet name="Player" sheetId="11" ns7:id="rId11"/>
-    <ns0:sheet name="DialogueNames" sheetId="12" ns7:id="rId12"/>
-    <ns0:sheet name="DialogueContents" sheetId="13" ns7:id="rId13"/>
-    <ns0:sheet name="TutorialMessages" sheetId="15" ns7:id="rId14"/>
-    <ns0:sheet name="messages" sheetId="15" ns7:id="rId18"/>
-  </ns0:sheets>
-  <ns0:calcPr calcId="0"/>
-</ns0:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3SA\ProjectMT3\Data\Locale\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B76F656-EA37-4A09-BBE7-E31CBC4BE910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-30420" yWindow="2600" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="UI" sheetId="1" r:id="rId1"/>
+    <sheet name="Languages" sheetId="2" r:id="rId2"/>
+    <sheet name="Attrs" sheetId="3" r:id="rId3"/>
+    <sheet name="Items" sheetId="4" r:id="rId4"/>
+    <sheet name="Enemies" sheetId="5" r:id="rId5"/>
+    <sheet name="Equips" sheetId="6" r:id="rId6"/>
+    <sheet name="Classes" sheetId="7" r:id="rId7"/>
+    <sheet name="States" sheetId="8" r:id="rId8"/>
+    <sheet name="MapNames" sheetId="9" r:id="rId9"/>
+    <sheet name="Specials" sheetId="10" r:id="rId10"/>
+    <sheet name="Player" sheetId="11" r:id="rId11"/>
+    <sheet name="DialogueNames" sheetId="12" r:id="rId12"/>
+    <sheet name="DialogueContents" sheetId="13" r:id="rId13"/>
+    <sheet name="TutorialMessages" sheetId="15" r:id="rId14"/>
+    <sheet name="messages" sheetId="16" r:id="rId15"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="1736">
   <si>
     <t>ID</t>
   </si>
@@ -814,12 +814,6 @@
   </si>
   <si>
     <t>BATTLE_RETREAT</t>
-  </si>
-  <si>
-    <t>~Retreat~</t>
-  </si>
-  <si>
-    <t>~撤退~</t>
   </si>
   <si>
     <t>price</t>
@@ -3837,12 +3831,6 @@
     <t>HOTKEY_MAGIC_DOOR</t>
   </si>
   <si>
-    <t>Press H to view the hotkeys.</t>
-  </si>
-  <si>
-    <t>按 H 键可以查询快捷键。</t>
-  </si>
-  <si>
     <t>N：随意门</t>
   </si>
   <si>
@@ -4708,6 +4696,581 @@
   </si>
   <si>
     <t>Tower S 10F</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retreat</t>
+  </si>
+  <si>
+    <t>撤退</t>
+  </si>
+  <si>
+    <t>CONTROLS_TITLE</t>
+  </si>
+  <si>
+    <t>Controls</t>
+  </si>
+  <si>
+    <t>操作说明</t>
+  </si>
+  <si>
+    <t>HOTKEY_CONTROLS</t>
+  </si>
+  <si>
+    <t>H: Controls</t>
+  </si>
+  <si>
+    <t>H：操作说明</t>
+  </si>
+  <si>
+    <t>HOTKEY_BATTLE_RETREAT</t>
+  </si>
+  <si>
+    <t>Q: Retreat</t>
+  </si>
+  <si>
+    <t>Q：撤退</t>
+  </si>
+  <si>
+    <t>GAMEPAD_MOVE</t>
+  </si>
+  <si>
+    <t>Left stick / D-pad: Move</t>
+  </si>
+  <si>
+    <t>左摇杆／十字键：移动</t>
+  </si>
+  <si>
+    <t>GAMEPAD_MENU</t>
+  </si>
+  <si>
+    <t>Menu: Open menu</t>
+  </si>
+  <si>
+    <t>菜单键：打开菜单</t>
+  </si>
+  <si>
+    <t>GAMEPAD_CONTROLS</t>
+  </si>
+  <si>
+    <t>X: Controls</t>
+  </si>
+  <si>
+    <t>X：操作说明</t>
+  </si>
+  <si>
+    <t>GAMEPAD_CONFIRM</t>
+  </si>
+  <si>
+    <t>A: Confirm; B: Back</t>
+  </si>
+  <si>
+    <t>A：确认；B：返回</t>
+  </si>
+  <si>
+    <t>GAMEPAD_BATTLE_RETREAT</t>
+  </si>
+  <si>
+    <t>B: Retreat</t>
+  </si>
+  <si>
+    <t>B：撤退</t>
+  </si>
+  <si>
+    <t>TOUCH_MOVE</t>
+  </si>
+  <si>
+    <t>Tap the map: Move to the destination</t>
+  </si>
+  <si>
+    <t>点击地图：移动到目标位置</t>
+  </si>
+  <si>
+    <t>TOUCH_MENU</t>
+  </si>
+  <si>
+    <t>Tap an avatar: Menu; swipe avatars: Switch party member</t>
+  </si>
+  <si>
+    <t>点击头像：菜单；左右滑动头像：切换角色</t>
+  </si>
+  <si>
+    <t>TOUCH_CONTROLS</t>
+  </si>
+  <si>
+    <t>Tap Controls to view the controls</t>
+  </si>
+  <si>
+    <t>点击操作说明查看操作方式</t>
+  </si>
+  <si>
+    <t>TOUCH_BATTLE_RETREAT</t>
+  </si>
+  <si>
+    <t>Tap Retreat</t>
+  </si>
+  <si>
+    <t>点击撤退按钮</t>
+  </si>
+  <si>
+    <t>CONTROLS_DAILY</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>日常</t>
+  </si>
+  <si>
+    <t>CONTROLS_BATTLE</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
+  <si>
+    <t>战斗</t>
+  </si>
+  <si>
+    <t>HOTKEY_BATTLE_CRITICAL</t>
+  </si>
+  <si>
+    <t>C: Critical hit</t>
+  </si>
+  <si>
+    <t>C：会心一击</t>
+  </si>
+  <si>
+    <t>HOTKEY_BATTLE_ATTACK_SKILL</t>
+  </si>
+  <si>
+    <t>Z: Attack skill</t>
+  </si>
+  <si>
+    <t>Z：攻击技能</t>
+  </si>
+  <si>
+    <t>HOTKEY_BATTLE_DEFENSE_SKILL</t>
+  </si>
+  <si>
+    <t>X: Defense skill</t>
+  </si>
+  <si>
+    <t>X：防御技能</t>
+  </si>
+  <si>
+    <t>GAMEPAD_BATTLE_CRITICAL</t>
+  </si>
+  <si>
+    <t>A: Critical hit</t>
+  </si>
+  <si>
+    <t>A：会心一击</t>
+  </si>
+  <si>
+    <t>GAMEPAD_BATTLE_ATTACK_SKILL</t>
+  </si>
+  <si>
+    <t>D-pad left: Attack skill</t>
+  </si>
+  <si>
+    <t>十字键左：攻击技能</t>
+  </si>
+  <si>
+    <t>GAMEPAD_BATTLE_DEFENSE_SKILL</t>
+  </si>
+  <si>
+    <t>D-pad right: Defense skill</t>
+  </si>
+  <si>
+    <t>十字键右：防御技能</t>
+  </si>
+  <si>
+    <t>TOUCH_BATTLE_CRITICAL</t>
+  </si>
+  <si>
+    <t>Tap Critical hit</t>
+  </si>
+  <si>
+    <t>点击会心一击按钮</t>
+  </si>
+  <si>
+    <t>TOUCH_BATTLE_ATTACK_SKILL</t>
+  </si>
+  <si>
+    <t>Tap Attack skill</t>
+  </si>
+  <si>
+    <t>点击攻击技能按钮</t>
+  </si>
+  <si>
+    <t>TOUCH_BATTLE_DEFENSE_SKILL</t>
+  </si>
+  <si>
+    <t>Tap Defense skill</t>
+  </si>
+  <si>
+    <t>点击防御技能按钮</t>
+  </si>
+  <si>
+    <t>Press H to view the controls.</t>
+  </si>
+  <si>
+    <t>按 H 键可以查看操作说明。</t>
+  </si>
+  <si>
+    <t>TM_04_G</t>
+  </si>
+  <si>
+    <t>Press X to view the controls.</t>
+  </si>
+  <si>
+    <t>按 X 键可以查看操作说明。</t>
+  </si>
+  <si>
+    <t>TM_04_M</t>
+  </si>
+  <si>
+    <t>Tap Controls to view the controls.</t>
+  </si>
+  <si>
+    <t>点击操作说明可以查看操作方式。</t>
+  </si>
+  <si>
+    <t>TM_05_G</t>
+  </si>
+  <si>
+    <t>Enemy information. Press A to view details.</t>
+  </si>
+  <si>
+    <t>敌人的能力信息，按 A 查看详细内容。</t>
+  </si>
+  <si>
+    <t>TM_07_MENU</t>
+  </si>
+  <si>
+    <t>Open Items from the menu to use this item.</t>
+  </si>
+  <si>
+    <t>打开菜单中的道具来使用。</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_LABEL</t>
+  </si>
+  <si>
+    <t>Template</t>
+  </si>
+  <si>
+    <t>句式</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_LABEL</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>词语</t>
+  </si>
+  <si>
+    <t>MESSAGES_PUBLISH</t>
+  </si>
+  <si>
+    <t>MESSAGES_HOTKEY</t>
+  </si>
+  <si>
+    <t>T: Leave a message</t>
+  </si>
+  <si>
+    <t>T：留下箴言</t>
+  </si>
+  <si>
+    <t>MESSAGES_NETWORK_BAD</t>
+  </si>
+  <si>
+    <t>Poor network connection. Please try again later.</t>
+  </si>
+  <si>
+    <t>当前网络环境不佳，请稍后再试。</t>
+  </si>
+  <si>
+    <t>MESSAGES_CHECKING</t>
+  </si>
+  <si>
+    <t>Checking connection…</t>
+  </si>
+  <si>
+    <t>正在检测网络连接……</t>
+  </si>
+  <si>
+    <t>MESSAGES_OFFLINE</t>
+  </si>
+  <si>
+    <t>Connection unavailable</t>
+  </si>
+  <si>
+    <t>当前网络环境不佳</t>
+  </si>
+  <si>
+    <t>MESSAGES_READY</t>
+  </si>
+  <si>
+    <t>Ready to publish</t>
+  </si>
+  <si>
+    <t>可以发布留言</t>
+  </si>
+  <si>
+    <t>MESSAGES_SENDING</t>
+  </si>
+  <si>
+    <t>Publishing…</t>
+  </si>
+  <si>
+    <t>正在发布……</t>
+  </si>
+  <si>
+    <t>MESSAGES_SENT</t>
+  </si>
+  <si>
+    <t>Message published.</t>
+  </si>
+  <si>
+    <t>留言已发布。</t>
+  </si>
+  <si>
+    <t>MESSAGES_FAILED</t>
+  </si>
+  <si>
+    <t>Could not publish. The local message was removed.</t>
+  </si>
+  <si>
+    <t>留言发布失败，已移除本地留言。</t>
+  </si>
+  <si>
+    <t>MESSAGES_RATE_LIMITED</t>
+  </si>
+  <si>
+    <t>Please wait {seconds} seconds before publishing again.</t>
+  </si>
+  <si>
+    <t>请等待 {seconds} 秒后再发布留言。</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_AHEAD</t>
+  </si>
+  <si>
+    <t>{word} ahead</t>
+  </si>
+  <si>
+    <t>前方有{word}</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_BEWARE</t>
+  </si>
+  <si>
+    <t>Beware of {word}</t>
+  </si>
+  <si>
+    <t>小心{word}</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_SEEK</t>
+  </si>
+  <si>
+    <t>Seek {word}</t>
+  </si>
+  <si>
+    <t>寻找{word}</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_REMEMBER</t>
+  </si>
+  <si>
+    <t>Do not forget {word}</t>
+  </si>
+  <si>
+    <t>别忘了{word}</t>
+  </si>
+  <si>
+    <t>MESSAGES_TEMPLATE_NEED</t>
+  </si>
+  <si>
+    <t>{word} required</t>
+  </si>
+  <si>
+    <t>需要{word}</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_ENEMY</t>
+  </si>
+  <si>
+    <t>a strong enemy</t>
+  </si>
+  <si>
+    <t>强敌</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_AMBUSH</t>
+  </si>
+  <si>
+    <t>an ambush</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_TRAP</t>
+  </si>
+  <si>
+    <t>a trap</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_POISON</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_WEAKNESS</t>
+  </si>
+  <si>
+    <t>weakness</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_MECHANISM</t>
+  </si>
+  <si>
+    <t>a mechanism</t>
+  </si>
+  <si>
+    <t>机关</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_PASSAGE</t>
+  </si>
+  <si>
+    <t>a hidden passage</t>
+  </si>
+  <si>
+    <t>暗道</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_STAIRS</t>
+  </si>
+  <si>
+    <t>stairs</t>
+  </si>
+  <si>
+    <t>楼梯</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_KEY</t>
+  </si>
+  <si>
+    <t>a key</t>
+  </si>
+  <si>
+    <t>钥匙</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_POTION</t>
+  </si>
+  <si>
+    <t>a potion</t>
+  </si>
+  <si>
+    <t>药水</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_GEM</t>
+  </si>
+  <si>
+    <t>a gem</t>
+  </si>
+  <si>
+    <t>宝石</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_CHEST</t>
+  </si>
+  <si>
+    <t>a chest</t>
+  </si>
+  <si>
+    <t>宝箱</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_SHOP</t>
+  </si>
+  <si>
+    <t>a shop</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_WEAPON</t>
+  </si>
+  <si>
+    <t>a weapon</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_ARMOUR</t>
+  </si>
+  <si>
+    <t>armour</t>
+  </si>
+  <si>
+    <t>防具</t>
+  </si>
+  <si>
+    <t>MESSAGES_WORD_TELEPORTER</t>
+  </si>
+  <si>
+    <t>a teleporter</t>
+  </si>
+  <si>
+    <t>传送点</t>
+  </si>
+  <si>
+    <t>MESSAGES_GAMEPAD_HOTKEY</t>
+  </si>
+  <si>
+    <t>Y: Leave a message</t>
+  </si>
+  <si>
+    <t>Y：留言</t>
+  </si>
+  <si>
+    <t>MESSAGES_TOUCH_HOTKEY</t>
+  </si>
+  <si>
+    <t>Hold your current tile: Leave a message</t>
+  </si>
+  <si>
+    <t>长按角色当前格子：留言</t>
+  </si>
+  <si>
+    <t>E42_SHOUREN_ARCHER</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E42_SHOUREN_ARCHER_DESC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orc Archer</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>兽人弓兵</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一个兽人弓兵。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -5705,565 +6268,421 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BATTLE_RETREAT</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Retreat</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>撤退</t>
-        </is>
+      <c r="A62" t="s">
+        <v>259</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1547</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>260</v>
+      </c>
+      <c r="B63" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" t="s">
         <v>262</v>
-      </c>
-      <c r="B63" t="s">
-        <v>263</v>
-      </c>
-      <c r="C63" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>263</v>
+      </c>
+      <c r="B64" t="s">
+        <v>264</v>
+      </c>
+      <c r="C64" t="s">
         <v>265</v>
-      </c>
-      <c r="B64" t="s">
-        <v>266</v>
-      </c>
-      <c r="C64" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C65" t="s">
         <v>1241</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C68" t="s">
         <v>1246</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C69" t="s">
         <v>1249</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1250</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C70" t="s">
         <v>1252</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C71" t="s">
         <v>1255</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C72" t="s">
         <v>1258</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C73" t="s">
         <v>1261</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>1264</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>1268</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B76" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C76" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CONTROLS_TITLE</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Controls</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>操作说明</t>
-        </is>
+      <c r="A77" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>HOTKEY_CONTROLS</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>H: Controls</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>H：操作说明</t>
-        </is>
+      <c r="A78" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1553</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>HOTKEY_BATTLE_RETREAT</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Q: Retreat</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Q：撤退</t>
-        </is>
+      <c r="A79" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1556</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>GAMEPAD_MOVE</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Left stick / D-pad: Move</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>左摇杆／十字键：移动</t>
-        </is>
+      <c r="A80" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1559</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>GAMEPAD_MENU</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Menu: Open menu</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>菜单键：打开菜单</t>
-        </is>
+      <c r="A81" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1562</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>GAMEPAD_CONTROLS</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>X: Controls</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>X：操作说明</t>
-        </is>
+      <c r="A82" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1565</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>GAMEPAD_CONFIRM</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>A: Confirm; B: Back</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>A：确认；B：返回</t>
-        </is>
+      <c r="A83" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1568</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>GAMEPAD_BATTLE_RETREAT</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>B: Retreat</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>B：撤退</t>
-        </is>
+      <c r="A84" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1571</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TOUCH_MOVE</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tap the map: Move to the destination</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>点击地图：移动到目标位置</t>
-        </is>
+      <c r="A85" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1574</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TOUCH_MENU</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Tap an avatar: Menu; swipe avatars: Switch party member</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>点击头像：菜单；左右滑动头像：切换角色</t>
-        </is>
+      <c r="A86" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1577</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TOUCH_CONTROLS</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Tap Controls to view the controls</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>点击操作说明查看操作方式</t>
-        </is>
+      <c r="A87" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1580</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TOUCH_BATTLE_RETREAT</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Tap Retreat</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>点击撤退按钮</t>
-        </is>
+      <c r="A88" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>CONTROLS_DAILY</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>日常</t>
-        </is>
+      <c r="A89" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1586</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>CONTROLS_BATTLE</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Battle</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>战斗</t>
-        </is>
+      <c r="A90" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1589</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>HOTKEY_BATTLE_CRITICAL</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>C: Critical hit</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>C：会心一击</t>
-        </is>
+      <c r="A91" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1592</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>HOTKEY_BATTLE_ATTACK_SKILL</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Z: Attack skill</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Z：攻击技能</t>
-        </is>
+      <c r="A92" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1595</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>HOTKEY_BATTLE_DEFENSE_SKILL</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>X: Defense skill</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>X：防御技能</t>
-        </is>
+      <c r="A93" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1598</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>GAMEPAD_BATTLE_CRITICAL</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>A: Critical hit</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>A：会心一击</t>
-        </is>
+      <c r="A94" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1601</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>GAMEPAD_BATTLE_ATTACK_SKILL</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>D-pad left: Attack skill</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>十字键左：攻击技能</t>
-        </is>
+      <c r="A95" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1604</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>GAMEPAD_BATTLE_DEFENSE_SKILL</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>D-pad right: Defense skill</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>十字键右：防御技能</t>
-        </is>
+      <c r="A96" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1607</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>TOUCH_BATTLE_CRITICAL</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tap Critical hit</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>点击会心一击按钮</t>
-        </is>
+      <c r="A97" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1610</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>TOUCH_BATTLE_ATTACK_SKILL</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Tap Attack skill</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>点击攻击技能按钮</t>
-        </is>
+      <c r="A98" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1613</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>TOUCH_BATTLE_DEFENSE_SKILL</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Tap Defense skill</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>点击防御技能按钮</t>
-        </is>
+      <c r="A99" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1616</v>
       </c>
     </row>
   </sheetData>
@@ -6294,556 +6713,556 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>912</v>
+      </c>
+      <c r="B3" t="s">
+        <v>913</v>
+      </c>
+      <c r="C3" t="s">
         <v>914</v>
-      </c>
-      <c r="B3" t="s">
-        <v>915</v>
-      </c>
-      <c r="C3" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>919</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B6" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>922</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>924</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>925</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>925</v>
+      </c>
+      <c r="B8" t="s">
+        <v>926</v>
+      </c>
+      <c r="C8" t="s">
         <v>927</v>
-      </c>
-      <c r="B8" t="s">
-        <v>928</v>
-      </c>
-      <c r="C8" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>928</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>930</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>933</v>
+      </c>
+      <c r="B11" t="s">
+        <v>934</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>935</v>
-      </c>
-      <c r="B11" t="s">
-        <v>936</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>936</v>
+      </c>
+      <c r="B12" t="s">
+        <v>937</v>
+      </c>
+      <c r="C12" t="s">
         <v>938</v>
-      </c>
-      <c r="B12" t="s">
-        <v>939</v>
-      </c>
-      <c r="C12" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>939</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>941</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>942</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>942</v>
+      </c>
+      <c r="B14" t="s">
+        <v>943</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>944</v>
-      </c>
-      <c r="B14" t="s">
-        <v>945</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>945</v>
+      </c>
+      <c r="B15" t="s">
+        <v>946</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>947</v>
-      </c>
-      <c r="B15" t="s">
-        <v>948</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>948</v>
+      </c>
+      <c r="B16" t="s">
+        <v>949</v>
+      </c>
+      <c r="C16" t="s">
         <v>950</v>
-      </c>
-      <c r="B16" t="s">
-        <v>951</v>
-      </c>
-      <c r="C16" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>952</v>
+      </c>
+      <c r="B18" t="s">
+        <v>953</v>
+      </c>
+      <c r="C18" t="s">
         <v>954</v>
-      </c>
-      <c r="B18" t="s">
-        <v>955</v>
-      </c>
-      <c r="C18" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>955</v>
+      </c>
+      <c r="B19" t="s">
+        <v>956</v>
+      </c>
+      <c r="C19" t="s">
         <v>957</v>
-      </c>
-      <c r="B19" t="s">
-        <v>958</v>
-      </c>
-      <c r="C19" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>958</v>
+      </c>
+      <c r="B20" t="s">
+        <v>959</v>
+      </c>
+      <c r="C20" t="s">
         <v>960</v>
-      </c>
-      <c r="B20" t="s">
-        <v>961</v>
-      </c>
-      <c r="C20" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>961</v>
+      </c>
+      <c r="B21" t="s">
+        <v>962</v>
+      </c>
+      <c r="C21" t="s">
         <v>963</v>
-      </c>
-      <c r="B21" t="s">
-        <v>964</v>
-      </c>
-      <c r="C21" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>966</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>969</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>970</v>
+      </c>
+      <c r="B24" t="s">
+        <v>971</v>
+      </c>
+      <c r="C24" t="s">
         <v>972</v>
-      </c>
-      <c r="B24" t="s">
-        <v>973</v>
-      </c>
-      <c r="C24" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>973</v>
+      </c>
+      <c r="B25" t="s">
+        <v>974</v>
+      </c>
+      <c r="C25" t="s">
         <v>975</v>
-      </c>
-      <c r="B25" t="s">
-        <v>976</v>
-      </c>
-      <c r="C25" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="B26" t="s">
+        <v>977</v>
+      </c>
+      <c r="C26" t="s">
         <v>978</v>
-      </c>
-      <c r="B26" t="s">
-        <v>979</v>
-      </c>
-      <c r="C26" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="B27" t="s">
+        <v>980</v>
+      </c>
+      <c r="C27" t="s">
         <v>981</v>
-      </c>
-      <c r="B27" t="s">
-        <v>982</v>
-      </c>
-      <c r="C27" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>982</v>
+      </c>
+      <c r="B28" t="s">
+        <v>983</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>984</v>
-      </c>
-      <c r="B28" t="s">
-        <v>985</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>985</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>987</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>988</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C30" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="C31" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C32" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C33" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C34" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C35" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C36" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C37" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C38" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C40" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C41" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C42" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C44" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C45" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C46" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C47" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C48" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C49" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C50" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C51" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C52" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C53" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C54" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C55" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C56" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C57" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C58" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C59" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -6874,24 +7293,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C3" t="s">
         <v>1052</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1054</v>
       </c>
     </row>
   </sheetData>
@@ -6923,167 +7342,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
   </sheetData>
@@ -7118,10 +7537,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -7129,10 +7548,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -7140,10 +7559,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -7151,10 +7570,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -7162,7 +7581,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
@@ -7173,7 +7592,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>10</v>
@@ -7184,7 +7603,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>12</v>
@@ -7195,10 +7614,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -7206,10 +7625,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -7217,10 +7636,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -7228,10 +7647,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -7239,10 +7658,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -7250,10 +7669,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -7261,10 +7680,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -7272,10 +7691,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7283,10 +7702,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -7294,10 +7713,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -7305,10 +7724,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7316,7 +7735,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>25</v>
@@ -7327,10 +7746,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -7338,10 +7757,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -7349,10 +7768,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -7360,10 +7779,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -7371,10 +7790,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -7382,10 +7801,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -7393,10 +7812,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -7404,10 +7823,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -7415,10 +7834,10 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -7426,10 +7845,10 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -7437,7 +7856,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>37</v>
@@ -7448,10 +7867,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -7459,10 +7878,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -7470,10 +7889,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -7481,10 +7900,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -7492,10 +7911,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -7503,10 +7922,10 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -7514,7 +7933,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>45</v>
@@ -7525,7 +7944,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>47</v>
@@ -7536,7 +7955,7 @@
         <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>49</v>
@@ -7547,7 +7966,7 @@
         <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>51</v>
@@ -7558,7 +7977,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>53</v>
@@ -7569,10 +7988,10 @@
         <v>54</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -7580,7 +7999,7 @@
         <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>56</v>
@@ -7591,10 +8010,10 @@
         <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -7602,10 +8021,10 @@
         <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -7613,7 +8032,7 @@
         <v>59</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>60</v>
@@ -7624,10 +8043,10 @@
         <v>61</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -7635,10 +8054,10 @@
         <v>62</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -7646,10 +8065,10 @@
         <v>63</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -7657,10 +8076,10 @@
         <v>64</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -7668,7 +8087,7 @@
         <v>65</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>66</v>
@@ -7679,10 +8098,10 @@
         <v>67</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -7690,7 +8109,7 @@
         <v>68</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>69</v>
@@ -7701,10 +8120,10 @@
         <v>70</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -7712,10 +8131,10 @@
         <v>71</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -7723,7 +8142,7 @@
         <v>72</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>73</v>
@@ -7734,10 +8153,10 @@
         <v>74</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -7745,10 +8164,10 @@
         <v>75</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -7756,10 +8175,10 @@
         <v>76</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -7767,10 +8186,10 @@
         <v>77</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -7778,10 +8197,10 @@
         <v>78</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -7789,10 +8208,10 @@
         <v>79</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -7800,10 +8219,10 @@
         <v>80</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -7811,10 +8230,10 @@
         <v>81</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -7822,54 +8241,54 @@
         <v>82</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -8476,175 +8895,145 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1181</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1183</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1184</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>1186</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TM_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Press H to view the controls.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>按 H 键可以查看操作说明。</t>
-        </is>
+      <c r="A5" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1618</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TM_04_G</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Press X to view the controls.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>按 X 键可以查看操作说明。</t>
-        </is>
+      <c r="A11" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1621</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TM_04_M</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Tap Controls to view the controls.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>点击操作说明可以查看操作方式。</t>
-        </is>
+      <c r="A12" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1624</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TM_05_G</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Enemy information. Press A to view details.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>敌人的能力信息，按 A 查看详细内容。</t>
-        </is>
+      <c r="A13" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1627</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TM_07_MENU</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Open Items from the menu to use this item.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>打开菜单中的道具来使用。</t>
-        </is>
+      <c r="A14" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1630</v>
       </c>
     </row>
   </sheetData>
@@ -8654,425 +9043,415 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetFormatPr defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
-    <ns0:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <ns0:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" t="str" s="1">
-        <ns0:v>ID</ns0:v>
-      </ns0:c>
-      <ns0:c r="B1" t="str" s="1">
-        <ns0:v>en_GB</ns0:v>
-      </ns0:c>
-      <ns0:c r="C1" t="str" s="1">
-        <ns0:v>zh_CN</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_LABEL</ns0:v>
-      </ns0:c>
-      <ns0:c r="B2" t="str">
-        <ns0:v>Template</ns0:v>
-      </ns0:c>
-      <ns0:c r="C2" t="str">
-        <ns0:v>句式</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" t="str">
-        <ns0:v>MESSAGES_WORD_LABEL</ns0:v>
-      </ns0:c>
-      <ns0:c r="B3" t="str">
-        <ns0:v>Word</ns0:v>
-      </ns0:c>
-      <ns0:c r="C3" t="str">
-        <ns0:v>词语</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" t="str">
-        <ns0:v>MESSAGES_PUBLISH</ns0:v>
-      </ns0:c>
-      <ns0:c r="B4" t="str">
-        <ns0:v>Confirm</ns0:v>
-      </ns0:c>
-      <ns0:c r="C4" t="str">
-        <ns0:v>确认</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" t="str">
-        <ns0:v>MESSAGES_HOTKEY</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" t="str">
-        <ns0:v>T: Leave a message</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" t="str">
-        <ns0:v>T：留下箴言</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" t="str">
-        <ns0:v>MESSAGES_NETWORK_BAD</ns0:v>
-      </ns0:c>
-      <ns0:c r="B6" t="str">
-        <ns0:v>Poor network connection. Please try again later.</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" t="str">
-        <ns0:v>当前网络环境不佳，请稍后再试。</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" t="str">
-        <ns0:v>MESSAGES_CHECKING</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" t="str">
-        <ns0:v>Checking connection…</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" t="str">
-        <ns0:v>正在检测网络连接……</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" t="str">
-        <ns0:v>MESSAGES_OFFLINE</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" t="str">
-        <ns0:v>Connection unavailable</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" t="str">
-        <ns0:v>当前网络环境不佳</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" t="str">
-        <ns0:v>MESSAGES_READY</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" t="str">
-        <ns0:v>Ready to publish</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" t="str">
-        <ns0:v>可以发布留言</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" t="str">
-        <ns0:v>MESSAGES_SENDING</ns0:v>
-      </ns0:c>
-      <ns0:c r="B10" t="str">
-        <ns0:v>Publishing…</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" t="str">
-        <ns0:v>正在发布……</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" t="str">
-        <ns0:v>MESSAGES_SENT</ns0:v>
-      </ns0:c>
-      <ns0:c r="B11" t="str">
-        <ns0:v>Message published.</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" t="str">
-        <ns0:v>留言已发布。</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12">
-      <ns0:c r="A12" t="str">
-        <ns0:v>MESSAGES_FAILED</ns0:v>
-      </ns0:c>
-      <ns0:c r="B12" t="str">
-        <ns0:v>Could not publish. The local message was removed.</ns0:v>
-      </ns0:c>
-      <ns0:c r="C12" t="str">
-        <ns0:v>留言发布失败，已移除本地留言。</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="A13" t="str">
-        <ns0:v>MESSAGES_RATE_LIMITED</ns0:v>
-      </ns0:c>
-      <ns0:c r="B13" t="str">
-        <ns0:v>Please wait {seconds} seconds before publishing again.</ns0:v>
-      </ns0:c>
-      <ns0:c r="C13" t="str">
-        <ns0:v>请等待 {seconds} 秒后再发布留言。</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_AHEAD</ns0:v>
-      </ns0:c>
-      <ns0:c r="B14" t="str">
-        <ns0:v>{word} ahead</ns0:v>
-      </ns0:c>
-      <ns0:c r="C14" t="str">
-        <ns0:v>前方有{word}</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15">
-      <ns0:c r="A15" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_BEWARE</ns0:v>
-      </ns0:c>
-      <ns0:c r="B15" t="str">
-        <ns0:v>Beware of {word}</ns0:v>
-      </ns0:c>
-      <ns0:c r="C15" t="str">
-        <ns0:v>小心{word}</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16">
-      <ns0:c r="A16" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_SEEK</ns0:v>
-      </ns0:c>
-      <ns0:c r="B16" t="str">
-        <ns0:v>Seek {word}</ns0:v>
-      </ns0:c>
-      <ns0:c r="C16" t="str">
-        <ns0:v>寻找{word}</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17">
-      <ns0:c r="A17" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_REMEMBER</ns0:v>
-      </ns0:c>
-      <ns0:c r="B17" t="str">
-        <ns0:v>Do not forget {word}</ns0:v>
-      </ns0:c>
-      <ns0:c r="C17" t="str">
-        <ns0:v>别忘了{word}</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18">
-      <ns0:c r="A18" t="str">
-        <ns0:v>MESSAGES_TEMPLATE_NEED</ns0:v>
-      </ns0:c>
-      <ns0:c r="B18" t="str">
-        <ns0:v>{word} required</ns0:v>
-      </ns0:c>
-      <ns0:c r="C18" t="str">
-        <ns0:v>需要{word}</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19">
-      <ns0:c r="A19" t="str">
-        <ns0:v>MESSAGES_WORD_ENEMY</ns0:v>
-      </ns0:c>
-      <ns0:c r="B19" t="str">
-        <ns0:v>a strong enemy</ns0:v>
-      </ns0:c>
-      <ns0:c r="C19" t="str">
-        <ns0:v>强敌</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20">
-      <ns0:c r="A20" t="str">
-        <ns0:v>MESSAGES_WORD_AMBUSH</ns0:v>
-      </ns0:c>
-      <ns0:c r="B20" t="str">
-        <ns0:v>an ambush</ns0:v>
-      </ns0:c>
-      <ns0:c r="C20" t="str">
-        <ns0:v>伏击</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21">
-      <ns0:c r="A21" t="str">
-        <ns0:v>MESSAGES_WORD_TRAP</ns0:v>
-      </ns0:c>
-      <ns0:c r="B21" t="str">
-        <ns0:v>a trap</ns0:v>
-      </ns0:c>
-      <ns0:c r="C21" t="str">
-        <ns0:v>陷阱</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22">
-      <ns0:c r="A22" t="str">
-        <ns0:v>MESSAGES_WORD_POISON</ns0:v>
-      </ns0:c>
-      <ns0:c r="B22" t="str">
-        <ns0:v>poison</ns0:v>
-      </ns0:c>
-      <ns0:c r="C22" t="str">
-        <ns0:v>中毒</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23">
-      <ns0:c r="A23" t="str">
-        <ns0:v>MESSAGES_WORD_WEAKNESS</ns0:v>
-      </ns0:c>
-      <ns0:c r="B23" t="str">
-        <ns0:v>weakness</ns0:v>
-      </ns0:c>
-      <ns0:c r="C23" t="str">
-        <ns0:v>衰弱</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24">
-      <ns0:c r="A24" t="str">
-        <ns0:v>MESSAGES_WORD_MECHANISM</ns0:v>
-      </ns0:c>
-      <ns0:c r="B24" t="str">
-        <ns0:v>a mechanism</ns0:v>
-      </ns0:c>
-      <ns0:c r="C24" t="str">
-        <ns0:v>机关</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25">
-      <ns0:c r="A25" t="str">
-        <ns0:v>MESSAGES_WORD_PASSAGE</ns0:v>
-      </ns0:c>
-      <ns0:c r="B25" t="str">
-        <ns0:v>a hidden passage</ns0:v>
-      </ns0:c>
-      <ns0:c r="C25" t="str">
-        <ns0:v>暗道</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26">
-      <ns0:c r="A26" t="str">
-        <ns0:v>MESSAGES_WORD_STAIRS</ns0:v>
-      </ns0:c>
-      <ns0:c r="B26" t="str">
-        <ns0:v>stairs</ns0:v>
-      </ns0:c>
-      <ns0:c r="C26" t="str">
-        <ns0:v>楼梯</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27">
-      <ns0:c r="A27" t="str">
-        <ns0:v>MESSAGES_WORD_KEY</ns0:v>
-      </ns0:c>
-      <ns0:c r="B27" t="str">
-        <ns0:v>a key</ns0:v>
-      </ns0:c>
-      <ns0:c r="C27" t="str">
-        <ns0:v>钥匙</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28">
-      <ns0:c r="A28" t="str">
-        <ns0:v>MESSAGES_WORD_POTION</ns0:v>
-      </ns0:c>
-      <ns0:c r="B28" t="str">
-        <ns0:v>a potion</ns0:v>
-      </ns0:c>
-      <ns0:c r="C28" t="str">
-        <ns0:v>药水</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29">
-      <ns0:c r="A29" t="str">
-        <ns0:v>MESSAGES_WORD_GEM</ns0:v>
-      </ns0:c>
-      <ns0:c r="B29" t="str">
-        <ns0:v>a gem</ns0:v>
-      </ns0:c>
-      <ns0:c r="C29" t="str">
-        <ns0:v>宝石</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="30">
-      <ns0:c r="A30" t="str">
-        <ns0:v>MESSAGES_WORD_CHEST</ns0:v>
-      </ns0:c>
-      <ns0:c r="B30" t="str">
-        <ns0:v>a chest</ns0:v>
-      </ns0:c>
-      <ns0:c r="C30" t="str">
-        <ns0:v>宝箱</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="31">
-      <ns0:c r="A31" t="str">
-        <ns0:v>MESSAGES_WORD_SHOP</ns0:v>
-      </ns0:c>
-      <ns0:c r="B31" t="str">
-        <ns0:v>a shop</ns0:v>
-      </ns0:c>
-      <ns0:c r="C31" t="str">
-        <ns0:v>商店</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32">
-      <ns0:c r="A32" t="str">
-        <ns0:v>MESSAGES_WORD_WEAPON</ns0:v>
-      </ns0:c>
-      <ns0:c r="B32" t="str">
-        <ns0:v>a weapon</ns0:v>
-      </ns0:c>
-      <ns0:c r="C32" t="str">
-        <ns0:v>武器</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33">
-      <ns0:c r="A33" t="str">
-        <ns0:v>MESSAGES_WORD_ARMOUR</ns0:v>
-      </ns0:c>
-      <ns0:c r="B33" t="str">
-        <ns0:v>armour</ns0:v>
-      </ns0:c>
-      <ns0:c r="C33" t="str">
-        <ns0:v>防具</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34">
-      <ns0:c r="A34" t="str">
-        <ns0:v>MESSAGES_WORD_TELEPORTER</ns0:v>
-      </ns0:c>
-      <ns0:c r="B34" t="str">
-        <ns0:v>a teleporter</ns0:v>
-      </ns0:c>
-      <ns0:c r="C34" t="str">
-        <ns0:v>传送点</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35">
-      <ns0:c r="A35" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MESSAGES_GAMEPAD_HOTKEY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B35" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y: Leave a message</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C35" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y：留言</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36">
-      <ns0:c r="A36" t="inlineStr">
-        <ns0:is>
-          <ns0:t>MESSAGES_TOUCH_HOTKEY</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B36" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Hold your current tile: Leave a message</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C36" t="inlineStr">
-        <ns0:is>
-          <ns0:t>长按角色当前格子：留言</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C22" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C23" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9096,10 +9475,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -9107,10 +9486,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -9137,167 +9516,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" t="s">
         <v>302</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C13" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" t="s">
         <v>305</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C14" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
         <v>308</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C15" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" t="s">
         <v>311</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C16" t="s">
-        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -9329,552 +9708,552 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" t="s">
         <v>314</v>
-      </c>
-      <c r="B2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" t="s">
         <v>317</v>
-      </c>
-      <c r="B3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C3" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" t="s">
         <v>320</v>
-      </c>
-      <c r="B4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
-      </c>
-      <c r="C5" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C6" t="s">
         <v>326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" t="s">
         <v>329</v>
-      </c>
-      <c r="B7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C9" t="s">
         <v>334</v>
-      </c>
-      <c r="B9" t="s">
-        <v>335</v>
-      </c>
-      <c r="C9" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B12" t="s">
+        <v>342</v>
+      </c>
+      <c r="C12" t="s">
         <v>343</v>
-      </c>
-      <c r="B12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C12" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" t="s">
+        <v>345</v>
+      </c>
+      <c r="C13" t="s">
         <v>346</v>
-      </c>
-      <c r="B13" t="s">
-        <v>347</v>
-      </c>
-      <c r="C13" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>347</v>
+      </c>
+      <c r="B14" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" t="s">
         <v>349</v>
-      </c>
-      <c r="B14" t="s">
-        <v>350</v>
-      </c>
-      <c r="C14" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" t="s">
         <v>352</v>
-      </c>
-      <c r="B15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C15" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C16" t="s">
         <v>355</v>
-      </c>
-      <c r="B16" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B17" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" t="s">
         <v>358</v>
-      </c>
-      <c r="B17" t="s">
-        <v>359</v>
-      </c>
-      <c r="C17" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" t="s">
         <v>361</v>
-      </c>
-      <c r="B18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" t="s">
         <v>364</v>
-      </c>
-      <c r="B19" t="s">
-        <v>365</v>
-      </c>
-      <c r="C19" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B20" t="s">
+        <v>366</v>
+      </c>
+      <c r="C20" t="s">
         <v>367</v>
-      </c>
-      <c r="B20" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" t="s">
         <v>370</v>
-      </c>
-      <c r="B21" t="s">
-        <v>371</v>
-      </c>
-      <c r="C21" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>371</v>
+      </c>
+      <c r="B22" t="s">
+        <v>372</v>
+      </c>
+      <c r="C22" t="s">
         <v>373</v>
-      </c>
-      <c r="B22" t="s">
-        <v>374</v>
-      </c>
-      <c r="C22" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>374</v>
+      </c>
+      <c r="B23" t="s">
+        <v>375</v>
+      </c>
+      <c r="C23" t="s">
         <v>376</v>
-      </c>
-      <c r="B23" t="s">
-        <v>377</v>
-      </c>
-      <c r="C23" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>377</v>
+      </c>
+      <c r="B24" t="s">
+        <v>378</v>
+      </c>
+      <c r="C24" t="s">
         <v>379</v>
-      </c>
-      <c r="B24" t="s">
-        <v>380</v>
-      </c>
-      <c r="C24" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" t="s">
+        <v>381</v>
+      </c>
+      <c r="C25" t="s">
         <v>382</v>
-      </c>
-      <c r="B25" t="s">
-        <v>383</v>
-      </c>
-      <c r="C25" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>383</v>
+      </c>
+      <c r="B26" t="s">
+        <v>384</v>
+      </c>
+      <c r="C26" t="s">
         <v>385</v>
-      </c>
-      <c r="B26" t="s">
-        <v>386</v>
-      </c>
-      <c r="C26" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>386</v>
+      </c>
+      <c r="B27" t="s">
+        <v>387</v>
+      </c>
+      <c r="C27" t="s">
         <v>388</v>
-      </c>
-      <c r="B27" t="s">
-        <v>389</v>
-      </c>
-      <c r="C27" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>389</v>
+      </c>
+      <c r="B28" t="s">
+        <v>390</v>
+      </c>
+      <c r="C28" t="s">
         <v>391</v>
-      </c>
-      <c r="B28" t="s">
-        <v>392</v>
-      </c>
-      <c r="C28" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>392</v>
+      </c>
+      <c r="B29" t="s">
+        <v>393</v>
+      </c>
+      <c r="C29" t="s">
         <v>394</v>
-      </c>
-      <c r="B29" t="s">
-        <v>395</v>
-      </c>
-      <c r="C29" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>395</v>
+      </c>
+      <c r="B30" t="s">
+        <v>396</v>
+      </c>
+      <c r="C30" t="s">
         <v>397</v>
-      </c>
-      <c r="B30" t="s">
-        <v>398</v>
-      </c>
-      <c r="C30" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>398</v>
+      </c>
+      <c r="B31" t="s">
+        <v>399</v>
+      </c>
+      <c r="C31" t="s">
         <v>400</v>
-      </c>
-      <c r="B31" t="s">
-        <v>401</v>
-      </c>
-      <c r="C31" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B32" t="s">
+        <v>402</v>
+      </c>
+      <c r="C32" t="s">
         <v>403</v>
-      </c>
-      <c r="B32" t="s">
-        <v>404</v>
-      </c>
-      <c r="C32" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>404</v>
+      </c>
+      <c r="B33" t="s">
+        <v>405</v>
+      </c>
+      <c r="C33" t="s">
         <v>406</v>
-      </c>
-      <c r="B33" t="s">
-        <v>407</v>
-      </c>
-      <c r="C33" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>407</v>
+      </c>
+      <c r="B34" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" t="s">
         <v>409</v>
-      </c>
-      <c r="B34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C34" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>410</v>
+      </c>
+      <c r="B35" t="s">
+        <v>411</v>
+      </c>
+      <c r="C35" t="s">
         <v>412</v>
-      </c>
-      <c r="B35" t="s">
-        <v>413</v>
-      </c>
-      <c r="C35" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>413</v>
+      </c>
+      <c r="B36" t="s">
+        <v>414</v>
+      </c>
+      <c r="C36" t="s">
         <v>415</v>
-      </c>
-      <c r="B36" t="s">
-        <v>416</v>
-      </c>
-      <c r="C36" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>416</v>
+      </c>
+      <c r="B37" t="s">
+        <v>417</v>
+      </c>
+      <c r="C37" t="s">
         <v>418</v>
-      </c>
-      <c r="B37" t="s">
-        <v>419</v>
-      </c>
-      <c r="C37" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>419</v>
+      </c>
+      <c r="B38" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" t="s">
         <v>421</v>
-      </c>
-      <c r="B38" t="s">
-        <v>422</v>
-      </c>
-      <c r="C38" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>422</v>
+      </c>
+      <c r="B39" t="s">
+        <v>423</v>
+      </c>
+      <c r="C39" t="s">
         <v>424</v>
-      </c>
-      <c r="B39" t="s">
-        <v>425</v>
-      </c>
-      <c r="C39" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B40" t="s">
+        <v>426</v>
+      </c>
+      <c r="C40" t="s">
         <v>427</v>
-      </c>
-      <c r="B40" t="s">
-        <v>428</v>
-      </c>
-      <c r="C40" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>428</v>
+      </c>
+      <c r="B41" t="s">
+        <v>429</v>
+      </c>
+      <c r="C41" t="s">
         <v>430</v>
-      </c>
-      <c r="B41" t="s">
-        <v>431</v>
-      </c>
-      <c r="C41" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>431</v>
+      </c>
+      <c r="B42" t="s">
+        <v>432</v>
+      </c>
+      <c r="C42" t="s">
         <v>433</v>
-      </c>
-      <c r="B42" t="s">
-        <v>434</v>
-      </c>
-      <c r="C42" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>434</v>
+      </c>
+      <c r="B43" t="s">
+        <v>435</v>
+      </c>
+      <c r="C43" t="s">
         <v>436</v>
-      </c>
-      <c r="B43" t="s">
-        <v>437</v>
-      </c>
-      <c r="C43" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>437</v>
+      </c>
+      <c r="B44" t="s">
+        <v>438</v>
+      </c>
+      <c r="C44" t="s">
         <v>439</v>
-      </c>
-      <c r="B44" t="s">
-        <v>440</v>
-      </c>
-      <c r="C44" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>440</v>
+      </c>
+      <c r="B45" t="s">
+        <v>441</v>
+      </c>
+      <c r="C45" t="s">
         <v>442</v>
-      </c>
-      <c r="B45" t="s">
-        <v>443</v>
-      </c>
-      <c r="C45" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>443</v>
+      </c>
+      <c r="B46" t="s">
+        <v>444</v>
+      </c>
+      <c r="C46" t="s">
         <v>445</v>
-      </c>
-      <c r="B46" t="s">
-        <v>446</v>
-      </c>
-      <c r="C46" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>446</v>
+      </c>
+      <c r="B47" t="s">
+        <v>447</v>
+      </c>
+      <c r="C47" t="s">
         <v>448</v>
-      </c>
-      <c r="B47" t="s">
-        <v>449</v>
-      </c>
-      <c r="C47" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>1290</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>1288</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1292</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -9885,7 +10264,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5" customWidth="1"/>
@@ -9906,1751 +10285,1770 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B2" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="C2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B4" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="C4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B6" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B8" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="C8" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B10" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C10" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B12" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="C12" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B14" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="C14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B16" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="C16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B18" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="C18" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C19" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B20" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="C20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C21" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B22" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="C22" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C23" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B24" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="C24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C25" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B26" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="C26" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B28" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C28" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C29" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B30" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C30" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C31" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B32" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="C32" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C33" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B34" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="C34" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C35" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B36" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="C36" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C37" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B38" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C38" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C39" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B40" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="C40" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C41" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B42" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="C42" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C43" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B44" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C44" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C45" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B46" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C47" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B48" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="C48" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C49" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B50" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="C50" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C51" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B52" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="C52" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C53" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B54" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="C54" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C55" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B56" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="C56" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C57" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B58" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="C58" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C59" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B60" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="C60" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B62" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="C62" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C63" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B64" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="C64" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C65" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B66" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="C66" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C67" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B68" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="C68" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C69" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B70" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="C70" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C71" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B72" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="C72" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C73" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B74" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="C74" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C75" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B76" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="C76" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C77" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B78" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="C78" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C79" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B80" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C80" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C81" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B82" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="C82" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C83" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B84" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C84" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C85" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="C86" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C87" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>617</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C88" t="s">
-        <v>618</v>
+      <c r="A88" s="7" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>1734</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>619</v>
-      </c>
-      <c r="C89" t="s">
-        <v>620</v>
+      <c r="A89" s="7" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>1735</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B90" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="C90" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C91" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="C92" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="C93" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B94" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="C94" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C95" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B96" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="C96" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C97" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B98" t="s">
-        <v>1477</v>
+        <v>1423</v>
       </c>
       <c r="C98" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C99" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B100" t="s">
-        <v>1428</v>
+        <v>1473</v>
       </c>
       <c r="C100" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C101" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B102" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="C102" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C103" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B104" t="s">
-        <v>1478</v>
+        <v>1425</v>
       </c>
       <c r="C104" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C105" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B106" t="s">
-        <v>1430</v>
+        <v>1474</v>
       </c>
       <c r="C106" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C107" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B108" t="s">
-        <v>1479</v>
+        <v>1426</v>
       </c>
       <c r="C108" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C109" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="C110" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C111" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B112" t="s">
-        <v>1431</v>
+        <v>1476</v>
       </c>
       <c r="C112" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="C113" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B114" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="C114" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="C115" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B116" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="C116" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C117" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B118" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="C118" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C119" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B120" t="s">
-        <v>1481</v>
+        <v>1430</v>
       </c>
       <c r="C120" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C121" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B122" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="C122" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C123" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B124" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="C124" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C125" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B126" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="C126" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C127" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B128" t="s">
-        <v>1435</v>
+        <v>1480</v>
       </c>
       <c r="C128" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C129" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B130" t="s">
-        <v>1485</v>
+        <v>1431</v>
       </c>
       <c r="C130" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C131" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B132" t="s">
-        <v>1436</v>
+        <v>1481</v>
       </c>
       <c r="C132" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C133" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B134" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="C134" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C135" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="B136" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="C136" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C137" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B138" t="s">
-        <v>1486</v>
+        <v>1434</v>
       </c>
       <c r="C138" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C139" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="B140" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="C140" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C141" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B142" t="s">
-        <v>1439</v>
+        <v>1483</v>
       </c>
       <c r="C142" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="C143" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="B144" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="C144" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C145" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="B146" t="s">
-        <v>1488</v>
+        <v>1436</v>
       </c>
       <c r="C146" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C147" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="B148" t="s">
-        <v>1441</v>
+        <v>1484</v>
       </c>
       <c r="C148" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C149" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="B150" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="C150" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C151" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B152" t="s">
-        <v>1489</v>
+        <v>1438</v>
       </c>
       <c r="C152" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C153" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B154" t="s">
-        <v>1443</v>
+        <v>1485</v>
       </c>
       <c r="C154" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C155" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B156" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="C156" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C157" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="B158" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="C158" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C159" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B160" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="C160" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C161" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B162" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C162" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C163" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B164" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="C164" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C165" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B166" t="s">
-        <v>1490</v>
+        <v>1444</v>
       </c>
       <c r="C166" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="C167" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B168" t="s">
-        <v>1449</v>
+        <v>1486</v>
       </c>
       <c r="C168" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C169" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B170" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="C170" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C171" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B172" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="C172" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C173" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B174" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="C174" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C175" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>793</v>
+        <v>787</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1448</v>
       </c>
       <c r="C176" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="C177" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C178" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="C179" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="C180" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="C181" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="C182" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C183" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C184" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C185" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C186" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="C187" t="s">
-        <v>816</v>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>811</v>
+      </c>
+      <c r="C188" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>813</v>
+      </c>
+      <c r="C189" t="s">
+        <v>814</v>
       </c>
     </row>
   </sheetData>
@@ -11681,84 +12079,84 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" t="s">
         <v>817</v>
-      </c>
-      <c r="B2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C2" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>819</v>
+      </c>
+      <c r="B4" t="s">
+        <v>820</v>
+      </c>
+      <c r="C4" t="s">
         <v>821</v>
-      </c>
-      <c r="B4" t="s">
-        <v>822</v>
-      </c>
-      <c r="C4" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="B6" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="C6" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="B7" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="B8" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="C8" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B9" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
     </row>
   </sheetData>
@@ -11789,46 +12187,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C2" t="s">
         <v>825</v>
-      </c>
-      <c r="B2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C2" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>826</v>
+      </c>
+      <c r="B3" t="s">
+        <v>827</v>
+      </c>
+      <c r="C3" t="s">
         <v>828</v>
-      </c>
-      <c r="B3" t="s">
-        <v>829</v>
-      </c>
-      <c r="C3" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>831</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -11859,57 +12257,57 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C2" t="s">
         <v>836</v>
-      </c>
-      <c r="B2" t="s">
-        <v>837</v>
-      </c>
-      <c r="C2" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>837</v>
+      </c>
+      <c r="B3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C3" t="s">
         <v>839</v>
-      </c>
-      <c r="B3" t="s">
-        <v>840</v>
-      </c>
-      <c r="C3" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>840</v>
+      </c>
+      <c r="B4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C4" t="s">
         <v>842</v>
-      </c>
-      <c r="B4" t="s">
-        <v>843</v>
-      </c>
-      <c r="C4" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>843</v>
+      </c>
+      <c r="B5" t="s">
+        <v>844</v>
+      </c>
+      <c r="C5" t="s">
         <v>845</v>
-      </c>
-      <c r="B5" t="s">
-        <v>846</v>
-      </c>
-      <c r="C5" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>846</v>
+      </c>
+      <c r="B6" t="s">
+        <v>847</v>
+      </c>
+      <c r="C6" t="s">
         <v>848</v>
-      </c>
-      <c r="B6" t="s">
-        <v>849</v>
-      </c>
-      <c r="C6" t="s">
-        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -11941,871 +12339,871 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>851</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>854</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>855</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Locale/Locale.xlsx
+++ b/Data/Locale/Locale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\ProjectMT3SA\ProjectMT3\Data\Locale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B76F656-EA37-4A09-BBE7-E31CBC4BE910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660A883B-D4AC-406A-8E25-E325F1A32A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30420" yWindow="2600" windowWidth="28800" windowHeight="15370" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2073,18 +2073,6 @@
     <t>这是一个中型蝙蝠。</t>
   </si>
   <si>
-    <t>E59_HANBINGSHILAIMU</t>
-  </si>
-  <si>
-    <t>寒冰史莱姆</t>
-  </si>
-  <si>
-    <t>E59_HANBINGSHILAIMU_DESC</t>
-  </si>
-  <si>
-    <t>这是一个寒冰史莱姆。</t>
-  </si>
-  <si>
     <t>E60_DUZHANGYU</t>
   </si>
   <si>
@@ -4479,9 +4467,6 @@
     <t>Man Hydrargyrum</t>
   </si>
   <si>
-    <t>Slime Cryo</t>
-  </si>
-  <si>
     <t>Octopus Toxicon</t>
   </si>
   <si>
@@ -5271,6 +5256,26 @@
   </si>
   <si>
     <t>这是一个兽人弓兵。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E59_QISHISHILAIMU</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E59_QISHISHILAIMU_DESC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime Knight</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>史莱姆骑士</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是一个史莱姆骑士。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -6272,10 +6277,10 @@
         <v>259</v>
       </c>
       <c r="B62" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="C62" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -6302,387 +6307,387 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B65" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C65" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B68" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="C68" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B69" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C69" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="B70" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="C70" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="B71" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="C71" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="B72" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="C72" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B73" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C73" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B76" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="C76" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="B77" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="C77" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="B78" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="C78" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="B79" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="C79" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="B80" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="C80" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="B81" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="C81" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="B82" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="C82" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="B83" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="C83" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="B84" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="C84" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="B85" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="C85" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="B86" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="C86" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="B87" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="C87" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="B88" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="C88" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="B89" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="C89" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="B90" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="C90" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="B91" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="C91" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="B92" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="C92" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="B93" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="C93" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="B94" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="C94" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="B95" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="C95" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="B96" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="C96" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="B97" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="C97" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="B98" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="C98" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="B99" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="C99" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
     </row>
   </sheetData>
@@ -6713,556 +6718,556 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C2" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B3" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C4" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B6" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C6" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B8" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C8" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B10" t="s">
         <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B11" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B12" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C12" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B14" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B15" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B16" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C16" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B18" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C18" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B19" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C19" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B20" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C20" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B21" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C21" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B24" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C24" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B25" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C25" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B26" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C26" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B27" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C27" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B28" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="C30" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C31" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C32" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C33" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C34" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C35" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C36" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C37" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C38" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C40" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C41" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C42" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C44" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C45" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C46" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C47" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="C48" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C49" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C50" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C51" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C52" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C53" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C54" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C55" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C56" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="C57" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C58" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C59" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -7293,24 +7298,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B3" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C3" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
@@ -7342,120 +7347,120 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>578</v>
@@ -7463,46 +7468,46 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -7537,10 +7542,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -7548,10 +7553,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -7559,10 +7564,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -7570,10 +7575,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -7581,7 +7586,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>8</v>
@@ -7592,7 +7597,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>10</v>
@@ -7603,7 +7608,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>12</v>
@@ -7614,10 +7619,10 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -7625,10 +7630,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -7636,10 +7641,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -7647,10 +7652,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -7658,10 +7663,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -7669,10 +7674,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -7680,10 +7685,10 @@
         <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -7691,10 +7696,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -7702,10 +7707,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -7713,10 +7718,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -7724,10 +7729,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -7735,7 +7740,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>25</v>
@@ -7746,10 +7751,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -7757,10 +7762,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -7768,10 +7773,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -7779,10 +7784,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -7790,10 +7795,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -7801,10 +7806,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -7812,10 +7817,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -7823,10 +7828,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -7834,10 +7839,10 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -7845,10 +7850,10 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -7856,7 +7861,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>37</v>
@@ -7867,10 +7872,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -7878,10 +7883,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -7889,10 +7894,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -7900,10 +7905,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -7911,10 +7916,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -7922,10 +7927,10 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -7933,7 +7938,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>45</v>
@@ -7944,7 +7949,7 @@
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>47</v>
@@ -7955,7 +7960,7 @@
         <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>49</v>
@@ -7966,7 +7971,7 @@
         <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>51</v>
@@ -7977,7 +7982,7 @@
         <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>53</v>
@@ -7988,10 +7993,10 @@
         <v>54</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -7999,7 +8004,7 @@
         <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>56</v>
@@ -8010,10 +8015,10 @@
         <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -8021,10 +8026,10 @@
         <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -8032,7 +8037,7 @@
         <v>59</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>60</v>
@@ -8043,10 +8048,10 @@
         <v>61</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -8054,10 +8059,10 @@
         <v>62</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -8065,10 +8070,10 @@
         <v>63</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -8076,10 +8081,10 @@
         <v>64</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -8087,7 +8092,7 @@
         <v>65</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>66</v>
@@ -8098,10 +8103,10 @@
         <v>67</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -8109,7 +8114,7 @@
         <v>68</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>69</v>
@@ -8120,10 +8125,10 @@
         <v>70</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -8131,10 +8136,10 @@
         <v>71</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -8142,7 +8147,7 @@
         <v>72</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>73</v>
@@ -8153,10 +8158,10 @@
         <v>74</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -8164,10 +8169,10 @@
         <v>75</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -8175,10 +8180,10 @@
         <v>76</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -8186,10 +8191,10 @@
         <v>77</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -8197,10 +8202,10 @@
         <v>78</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -8208,10 +8213,10 @@
         <v>79</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -8219,10 +8224,10 @@
         <v>80</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -8230,10 +8235,10 @@
         <v>81</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -8241,54 +8246,54 @@
         <v>82</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -8895,145 +8900,145 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
   </sheetData>
@@ -9065,29 +9070,29 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="B2" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="C2" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="B3" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="C3" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="B4" t="s">
         <v>248</v>
@@ -9098,354 +9103,354 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="B5" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="B6" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="C6" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="B7" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="C7" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="B8" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="C8" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="B9" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="C9" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="B10" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="C10" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="B11" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="C11" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="B12" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="C12" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="B13" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="C13" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="B14" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C14" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="B15" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="C15" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="B16" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="C16" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="B17" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="C17" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="B18" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="C18" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="B19" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="C19" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="B20" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="C20" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="B21" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="C21" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
       <c r="B22" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="C22" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="B23" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="C23" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="B24" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="C24" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="B25" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="C25" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
       <c r="B26" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="C26" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="B27" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
       <c r="C27" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="B28" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="C28" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="B29" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="C29" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="B30" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="C30" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1713</v>
+        <v>1708</v>
       <